--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -66,21 +66,21 @@
   <cols>
     <col min="2" max="2" width="6.3515625" customWidth="true"/>
     <col min="3" max="3" width="4.2890625" customWidth="true"/>
-    <col min="4" max="4" width="13.35546875" customWidth="true"/>
+    <col min="4" max="4" width="13.3515625" customWidth="true"/>
     <col min="5" max="5" width="9.94140625" customWidth="true"/>
     <col min="6" max="6" width="7.71484375" customWidth="true"/>
     <col min="7" max="7" width="3.3359375" customWidth="true"/>
-    <col min="8" max="8" width="17.59765625" customWidth="true"/>
+    <col min="8" max="8" width="17.53515625" customWidth="true"/>
     <col min="9" max="9" width="9.01953125" customWidth="true"/>
     <col min="10" max="10" width="3.62890625" customWidth="true"/>
     <col min="11" max="11" width="17.29296875" customWidth="true"/>
     <col min="12" max="12" width="4.9765625" customWidth="true"/>
     <col min="13" max="13" width="4.9375" customWidth="true"/>
-    <col min="14" max="14" width="16.61328125" customWidth="true"/>
+    <col min="14" max="14" width="17.015625" customWidth="true"/>
     <col min="15" max="15" width="6.6171875" customWidth="true"/>
     <col min="16" max="16" width="16.5234375" customWidth="true"/>
     <col min="17" max="17" width="11.0390625" customWidth="true"/>
-    <col min="18" max="18" width="17.78125" customWidth="true"/>
+    <col min="18" max="18" width="17.7734375" customWidth="true"/>
     <col min="19" max="19" width="9.18359375" customWidth="true"/>
     <col min="20" max="20" width="3.26171875" customWidth="true"/>
     <col min="21" max="21" width="0.76953125" customWidth="true"/>
@@ -101,7 +101,7 @@
     <col min="36" max="36" width="4.12890625" customWidth="true"/>
     <col min="37" max="37" width="3.046875" customWidth="true"/>
     <col min="38" max="38" width="6.7109375" customWidth="true"/>
-    <col min="39" max="39" width="17.78125" customWidth="true"/>
+    <col min="39" max="39" width="17.7734375" customWidth="true"/>
     <col min="40" max="40" width="0.76953125" customWidth="true"/>
     <col min="41" max="41" width="0.76953125" customWidth="true"/>
     <col min="42" max="42" width="0.76953125" customWidth="true"/>
@@ -32938,7 +32938,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -32963,7 +32963,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -33038,12 +33038,12 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
@@ -33058,17 +33058,17 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t/>
+          <t>8050.0</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
@@ -33310,7 +33310,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -33335,7 +33335,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -33410,12 +33410,12 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
@@ -33430,17 +33430,17 @@
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t/>
+          <t>7750.0</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
@@ -33682,7 +33682,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -33707,7 +33707,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -33782,12 +33782,12 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
@@ -33802,17 +33802,17 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t/>
+          <t>8850.0</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
@@ -39634,7 +39634,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -39659,7 +39659,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -39734,12 +39734,12 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
@@ -39754,17 +39754,17 @@
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t/>
+          <t>6750.0</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
@@ -41122,7 +41122,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -41147,7 +41147,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -41222,12 +41222,12 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr">
@@ -41242,17 +41242,17 @@
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
@@ -41494,7 +41494,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -41594,12 +41594,12 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
@@ -41614,12 +41614,12 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -41866,7 +41866,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -41891,7 +41891,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -41966,12 +41966,12 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
@@ -41986,17 +41986,17 @@
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
@@ -42238,7 +42238,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -42263,7 +42263,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -42338,12 +42338,12 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
@@ -42358,17 +42358,17 @@
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t/>
+          <t>8550.0</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
@@ -43354,7 +43354,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -43379,7 +43379,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -43454,12 +43454,12 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
@@ -43474,17 +43474,17 @@
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t/>
+          <t>8850.0</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
@@ -43726,7 +43726,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -43751,7 +43751,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -43826,12 +43826,12 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
@@ -43846,17 +43846,17 @@
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t/>
+          <t>500.0</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
@@ -44098,7 +44098,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -44123,7 +44123,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -44198,12 +44198,12 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
@@ -44218,17 +44218,17 @@
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t/>
+          <t>8050.0</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
@@ -45586,7 +45586,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -45611,7 +45611,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -45686,12 +45686,12 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI123" t="inlineStr">
@@ -45706,17 +45706,17 @@
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL123" t="inlineStr">
         <is>
-          <t/>
+          <t>9150.0</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t/>
+          <t>21-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
@@ -45958,7 +45958,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -46058,12 +46058,12 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
@@ -46078,12 +46078,12 @@
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
         <is>
-          <t/>
+          <t>9150.0</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -46330,310 +46330,4774 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>108607082636</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>0899053000000002</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>MELINDHA BADE</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>9989075944</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL125" t="inlineStr">
+        <is>
+          <t>9150.0</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE125" t="inlineStr">
+        <is>
+          <t>19852</t>
+        </is>
+      </c>
+      <c r="BF125" t="inlineStr">
+        <is>
+          <t>262887,264390</t>
+        </is>
+      </c>
+      <c r="BG125" t="inlineStr">
+        <is>
+          <t>2037,2043</t>
+        </is>
+      </c>
+      <c r="BH125" t="inlineStr">
+        <is>
+          <t>nine thousand one hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI125" t="inlineStr">
+        <is>
+          <t>17149</t>
+        </is>
+      </c>
+      <c r="BJ125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU125" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>11000317632924</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1763689095</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>8550.00</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 07:09:43</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
           <t>NRNS</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>108607082636</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P125" t="inlineStr">
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>108608161209</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>ASHWATH ADITHYA MUNUBARTHI</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>9908906244</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE126" t="inlineStr">
+        <is>
+          <t>18659</t>
+        </is>
+      </c>
+      <c r="BF126" t="inlineStr">
+        <is>
+          <t>262404,264014</t>
+        </is>
+      </c>
+      <c r="BG126" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="BH126" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI126" t="inlineStr">
+        <is>
+          <t>16492</t>
+        </is>
+      </c>
+      <c r="BJ126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU126" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>11000317631984</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1763689095</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>8550.00</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 07:10:51</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>108608164995</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>ASHWATH ADITHYA MUNUBARTHI</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>9908906244</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE127" t="inlineStr">
+        <is>
+          <t>18659</t>
+        </is>
+      </c>
+      <c r="BF127" t="inlineStr">
+        <is>
+          <t>262404,264014</t>
+        </is>
+      </c>
+      <c r="BG127" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="BH127" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI127" t="inlineStr">
+        <is>
+          <t>16492</t>
+        </is>
+      </c>
+      <c r="BJ127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU127" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>11000317632962</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1763689095</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>8550.00</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 07:11:30</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>108608167999</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>ASHWATH ADITHYA MUNUBARTHI</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>9908906244</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE128" t="inlineStr">
+        <is>
+          <t>18659</t>
+        </is>
+      </c>
+      <c r="BF128" t="inlineStr">
+        <is>
+          <t>262404,264014</t>
+        </is>
+      </c>
+      <c r="BG128" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="BH128" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI128" t="inlineStr">
+        <is>
+          <t>16492</t>
+        </is>
+      </c>
+      <c r="BJ128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO128" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU128" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>11000317644277</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1763696190</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>17800.00</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 09:13:00</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>122941457741</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>MAHENDRA NAIDU VANJARI</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>9440280157</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT129" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE129" t="inlineStr">
+        <is>
+          <t>19009</t>
+        </is>
+      </c>
+      <c r="BF129" t="inlineStr">
+        <is>
+          <t>262983,264486,266136</t>
+        </is>
+      </c>
+      <c r="BG129" t="inlineStr">
+        <is>
+          <t>2037,2043,2051</t>
+        </is>
+      </c>
+      <c r="BH129" t="inlineStr">
+        <is>
+          <t>seventeen thousand eight hundred</t>
+        </is>
+      </c>
+      <c r="BI129" t="inlineStr">
+        <is>
+          <t>15898</t>
+        </is>
+      </c>
+      <c r="BJ129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO129" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU129" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>11000317644277</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1763696190</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>17300.00</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 09:13:00</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>122941457741</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>0899053000000004</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>MAHENDRA NAIDU VANJARI</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>9440280157</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE130" t="inlineStr">
+        <is>
+          <t>19009</t>
+        </is>
+      </c>
+      <c r="BF130" t="inlineStr">
+        <is>
+          <t>262983,264486,266136</t>
+        </is>
+      </c>
+      <c r="BG130" t="inlineStr">
+        <is>
+          <t>2037,2043,2051</t>
+        </is>
+      </c>
+      <c r="BH130" t="inlineStr">
+        <is>
+          <t>seventeen thousand eight hundred</t>
+        </is>
+      </c>
+      <c r="BI130" t="inlineStr">
+        <is>
+          <t>15898</t>
+        </is>
+      </c>
+      <c r="BJ130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO130" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU130" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>11000317644277</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1763696190</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 09:13:00</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>122941457741</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
         <is>
           <t>0899053000000002</t>
         </is>
       </c>
-      <c r="Q125" t="inlineStr">
+      <c r="Q131" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S125" t="inlineStr">
+      <c r="R131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
         <is>
           <t>MERCHANT</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr">
+      <c r="T131" t="inlineStr">
         <is>
           <t>UPI</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>MELINDHA BADE</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
+      <c r="U131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>MAHENDRA NAIDU VANJARI</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
         <is>
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>9989075944</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>9440280157</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ125" t="inlineStr">
+      <c r="AJ131" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AP125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AT125" t="inlineStr">
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT131" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
         </is>
       </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AW125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BA125" t="inlineStr">
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
         <is>
           <t>UPI</t>
         </is>
       </c>
-      <c r="BB125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BC125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BD125" t="inlineStr">
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD131" t="inlineStr">
         <is>
           <t>REGULAR</t>
         </is>
       </c>
-      <c r="BE125" t="inlineStr">
-        <is>
-          <t>19852</t>
-        </is>
-      </c>
-      <c r="BF125" t="inlineStr">
-        <is>
-          <t>262887,264390</t>
-        </is>
-      </c>
-      <c r="BG125" t="inlineStr">
-        <is>
-          <t>2037,2043</t>
-        </is>
-      </c>
-      <c r="BH125" t="inlineStr">
-        <is>
-          <t>nine thousand one hundred fifty</t>
-        </is>
-      </c>
-      <c r="BI125" t="inlineStr">
-        <is>
-          <t>17149</t>
-        </is>
-      </c>
-      <c r="BJ125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BK125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BL125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BM125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BN125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BO125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BP125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BQ125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BR125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BS125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BT125" t="inlineStr">
+      <c r="BE131" t="inlineStr">
+        <is>
+          <t>19009</t>
+        </is>
+      </c>
+      <c r="BF131" t="inlineStr">
+        <is>
+          <t>262983,264486,266136</t>
+        </is>
+      </c>
+      <c r="BG131" t="inlineStr">
+        <is>
+          <t>2037,2043,2051</t>
+        </is>
+      </c>
+      <c r="BH131" t="inlineStr">
+        <is>
+          <t>seventeen thousand eight hundred</t>
+        </is>
+      </c>
+      <c r="BI131" t="inlineStr">
+        <is>
+          <t>15898</t>
+        </is>
+      </c>
+      <c r="BJ131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO131" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT131" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BU125" t="inlineStr">
+      <c r="BU131" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="BV125" t="inlineStr">
+      <c r="BV131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>11000317657466</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1763702116</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>8850.00</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 10:45:33</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>404578383859</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>VENKATA VIGNESWARI SAI VINYA BOTTA</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>6303433178</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE132" t="inlineStr">
+        <is>
+          <t>18918</t>
+        </is>
+      </c>
+      <c r="BF132" t="inlineStr">
+        <is>
+          <t>262741,264244</t>
+        </is>
+      </c>
+      <c r="BG132" t="inlineStr">
+        <is>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="BH132" t="inlineStr">
+        <is>
+          <t>eight thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI132" t="inlineStr">
+        <is>
+          <t>15538</t>
+        </is>
+      </c>
+      <c r="BJ132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO132" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU132" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>11000317657543</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>1763702195</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>11250.00</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 10:46:49</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>079146114128</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>GNANA VIGNESWARI SAI CHANDRIKA BOTTA</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>6303433178</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE133" t="inlineStr">
+        <is>
+          <t>19244</t>
+        </is>
+      </c>
+      <c r="BF133" t="inlineStr">
+        <is>
+          <t>263048,264551</t>
+        </is>
+      </c>
+      <c r="BG133" t="inlineStr">
+        <is>
+          <t>2037,2044</t>
+        </is>
+      </c>
+      <c r="BH133" t="inlineStr">
+        <is>
+          <t>eleven thousand two hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI133" t="inlineStr">
+        <is>
+          <t>14873</t>
+        </is>
+      </c>
+      <c r="BJ133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO133" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU133" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>11000317657543</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>1763702195</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>10750.00</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 10:46:49</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>079146114128</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>0899053000000003</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>GNANA VIGNESWARI SAI CHANDRIKA BOTTA</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>6303433178</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT134" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE134" t="inlineStr">
+        <is>
+          <t>19244</t>
+        </is>
+      </c>
+      <c r="BF134" t="inlineStr">
+        <is>
+          <t>263048,264551</t>
+        </is>
+      </c>
+      <c r="BG134" t="inlineStr">
+        <is>
+          <t>2037,2044</t>
+        </is>
+      </c>
+      <c r="BH134" t="inlineStr">
+        <is>
+          <t>eleven thousand two hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI134" t="inlineStr">
+        <is>
+          <t>14873</t>
+        </is>
+      </c>
+      <c r="BJ134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO134" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU134" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>11000317657543</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>1763702195</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 10:46:49</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>079146114128</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>0899053000000002</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>GNANA VIGNESWARI SAI CHANDRIKA BOTTA</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>6303433178</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT135" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE135" t="inlineStr">
+        <is>
+          <t>19244</t>
+        </is>
+      </c>
+      <c r="BF135" t="inlineStr">
+        <is>
+          <t>263048,264551</t>
+        </is>
+      </c>
+      <c r="BG135" t="inlineStr">
+        <is>
+          <t>2037,2044</t>
+        </is>
+      </c>
+      <c r="BH135" t="inlineStr">
+        <is>
+          <t>eleven thousand two hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI135" t="inlineStr">
+        <is>
+          <t>14873</t>
+        </is>
+      </c>
+      <c r="BJ135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO135" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU135" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>11000317695213</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1763715904</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 14:41:57</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>BANK OF BARODA FSS</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>101202532591839096</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>701931</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>STATE BANK OF INDIA</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>RAYASAM SRI VARNIKA</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>7382913422</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>XXXXXXXXXXXX1989</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT136" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>RUPAY</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE136" t="inlineStr">
+        <is>
+          <t>19483</t>
+        </is>
+      </c>
+      <c r="BF136" t="inlineStr">
+        <is>
+          <t>264879</t>
+        </is>
+      </c>
+      <c r="BG136" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="BH136" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI136" t="inlineStr">
+        <is>
+          <t>15096</t>
+        </is>
+      </c>
+      <c r="BJ136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT136" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="BU136" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>11000317719673</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>1763728005</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 17:59:17</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>108611639217</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>GAUTAM MOOGI</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>7207505036</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE137" t="inlineStr">
+        <is>
+          <t>18360</t>
+        </is>
+      </c>
+      <c r="BF137" t="inlineStr">
+        <is>
+          <t>265368</t>
+        </is>
+      </c>
+      <c r="BG137" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH137" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI137" t="inlineStr">
+        <is>
+          <t>16992</t>
+        </is>
+      </c>
+      <c r="BJ137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU137" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV137" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -66,15 +66,15 @@
   <cols>
     <col min="2" max="2" width="6.3515625" customWidth="true"/>
     <col min="3" max="3" width="4.2890625" customWidth="true"/>
-    <col min="4" max="4" width="13.20703125" customWidth="true"/>
+    <col min="4" max="4" width="13.16015625" customWidth="true"/>
     <col min="5" max="5" width="9.94140625" customWidth="true"/>
-    <col min="6" max="6" width="7.56640625" customWidth="true"/>
+    <col min="6" max="6" width="8.06640625" customWidth="true"/>
     <col min="7" max="7" width="3.3359375" customWidth="true"/>
     <col min="8" max="8" width="17.578125" customWidth="true"/>
     <col min="9" max="9" width="9.01953125" customWidth="true"/>
     <col min="10" max="10" width="3.62890625" customWidth="true"/>
     <col min="11" max="11" width="17.29296875" customWidth="true"/>
-    <col min="12" max="12" width="4.9765625" customWidth="true"/>
+    <col min="12" max="12" width="10.80859375" customWidth="true"/>
     <col min="13" max="13" width="4.9375" customWidth="true"/>
     <col min="14" max="14" width="17.015625" customWidth="true"/>
     <col min="15" max="15" width="11.546875" customWidth="true"/>
@@ -100,7 +100,7 @@
     <col min="35" max="35" width="4.12890625" customWidth="true"/>
     <col min="36" max="36" width="4.12890625" customWidth="true"/>
     <col min="37" max="37" width="3.046875" customWidth="true"/>
-    <col min="38" max="38" width="6.52734375" customWidth="true"/>
+    <col min="38" max="38" width="6.55078125" customWidth="true"/>
     <col min="39" max="39" width="17.7734375" customWidth="true"/>
     <col min="40" max="40" width="0.76953125" customWidth="true"/>
     <col min="41" max="41" width="0.76953125" customWidth="true"/>
@@ -120,8 +120,8 @@
     <col min="55" max="55" width="0.76953125" customWidth="true"/>
     <col min="56" max="56" width="7.86328125" customWidth="true"/>
     <col min="57" max="57" width="5.75" customWidth="true"/>
-    <col min="58" max="58" width="18.2265625" customWidth="true"/>
-    <col min="59" max="59" width="12.6171875" customWidth="true"/>
+    <col min="58" max="58" width="18.29296875" customWidth="true"/>
+    <col min="59" max="59" width="13.0234375" customWidth="true"/>
     <col min="60" max="60" width="29.51171875" customWidth="true"/>
     <col min="61" max="61" width="5.328125" customWidth="true"/>
     <col min="62" max="62" width="0.76953125" customWidth="true"/>
@@ -47446,7 +47446,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -47471,7 +47471,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -47546,12 +47546,12 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
@@ -47566,17 +47566,17 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t/>
+          <t>8550.0</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
@@ -47818,7 +47818,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -47843,7 +47843,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -47918,12 +47918,12 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
@@ -47938,17 +47938,17 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t/>
+          <t>17800.0</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
@@ -48190,7 +48190,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -48290,12 +48290,12 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
@@ -48310,12 +48310,12 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t/>
+          <t>17800.0</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -48562,7 +48562,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -48587,7 +48587,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -48662,12 +48662,12 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
@@ -48682,17 +48682,17 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t/>
+          <t>17800.0</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
@@ -48934,7 +48934,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -48959,7 +48959,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -49034,12 +49034,12 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
@@ -49054,17 +49054,17 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t/>
+          <t>8850.0</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
@@ -49306,7 +49306,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -49331,7 +49331,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -49406,12 +49406,12 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
@@ -49426,17 +49426,17 @@
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
@@ -49678,7 +49678,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -49778,12 +49778,12 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
@@ -49798,12 +49798,12 @@
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM134" t="inlineStr">
@@ -50050,7 +50050,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -50075,7 +50075,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -50150,12 +50150,12 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI135" t="inlineStr">
@@ -50170,17 +50170,17 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
@@ -50422,7 +50422,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -50522,12 +50522,12 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
@@ -50542,12 +50542,12 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t/>
+          <t>11350.0</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
@@ -50794,7 +50794,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -50819,7 +50819,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -50894,12 +50894,12 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
@@ -50914,17 +50914,17 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t/>
+          <t>7750.0</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
@@ -51166,7 +51166,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -51191,7 +51191,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -51266,12 +51266,12 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
@@ -51286,17 +51286,17 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
         <is>
-          <t/>
+          <t>8550.0</t>
         </is>
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
@@ -52654,7 +52654,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -52679,7 +52679,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -52754,12 +52754,12 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
@@ -52774,17 +52774,17 @@
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t/>
+          <t>8550.0</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
@@ -53026,7 +53026,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -53051,7 +53051,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -53126,12 +53126,12 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
@@ -53146,17 +53146,17 @@
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t/>
+          <t>9150.0</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
@@ -53398,7 +53398,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -53498,12 +53498,12 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI144" t="inlineStr">
@@ -53518,12 +53518,12 @@
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL144" t="inlineStr">
         <is>
-          <t/>
+          <t>9150.0</t>
         </is>
       </c>
       <c r="AM144" t="inlineStr">
@@ -53770,7 +53770,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -53795,7 +53795,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
@@ -53870,12 +53870,12 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
@@ -53890,17 +53890,17 @@
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t/>
+          <t>9150.0</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
@@ -54137,12 +54137,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Force Success</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -54167,7 +54167,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -54242,12 +54242,12 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
@@ -54262,17 +54262,17 @@
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
@@ -54509,12 +54509,12 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Force Success</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -54614,12 +54614,12 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
@@ -54634,12 +54634,12 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -54881,12 +54881,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Force Success</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -54911,7 +54911,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -54986,12 +54986,12 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
@@ -55006,17 +55006,17 @@
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
@@ -55258,7 +55258,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -55283,7 +55283,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -55358,12 +55358,12 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
@@ -55378,17 +55378,17 @@
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
         <is>
-          <t/>
+          <t>8250.0</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
@@ -55630,7 +55630,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -55655,7 +55655,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -55730,12 +55730,12 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
@@ -55750,17 +55750,17 @@
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t/>
+          <t>8250.0</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
@@ -57490,7 +57490,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -57515,7 +57515,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -57590,12 +57590,12 @@
       </c>
       <c r="AG155" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
@@ -57610,17 +57610,17 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
         <is>
-          <t/>
+          <t>8250.0</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
@@ -57862,7 +57862,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -57887,7 +57887,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -57962,12 +57962,12 @@
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI156" t="inlineStr">
@@ -57982,17 +57982,17 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
@@ -58234,7 +58234,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -58334,12 +58334,12 @@
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI157" t="inlineStr">
@@ -58354,12 +58354,12 @@
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
@@ -58606,7 +58606,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -58631,7 +58631,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
@@ -58706,12 +58706,12 @@
       </c>
       <c r="AG158" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI158" t="inlineStr">
@@ -58726,17 +58726,17 @@
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL158" t="inlineStr">
         <is>
-          <t/>
+          <t>11250.0</t>
         </is>
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
@@ -59350,7 +59350,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -59375,7 +59375,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
@@ -59450,12 +59450,12 @@
       </c>
       <c r="AG160" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI160" t="inlineStr">
@@ -59470,17 +59470,17 @@
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL160" t="inlineStr">
         <is>
-          <t/>
+          <t>6750.0</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
@@ -59722,7 +59722,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -59747,7 +59747,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
@@ -59822,12 +59822,12 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI161" t="inlineStr">
@@ -59842,17 +59842,17 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t/>
+          <t>8050.0</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
@@ -60466,7 +60466,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -60491,7 +60491,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
@@ -60566,12 +60566,12 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI163" t="inlineStr">
@@ -60586,17 +60586,17 @@
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
         <is>
-          <t/>
+          <t>8250.0</t>
         </is>
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t/>
+          <t>24-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
@@ -61142,6 +61142,2982 @@
         </is>
       </c>
       <c r="BV164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>11000317917995</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>1763951385</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 08:01:40</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>108625745822</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>DHARMAVARAPU CHANDANA RAMYA</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>8374970989</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT165" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD165" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE165" t="inlineStr">
+        <is>
+          <t>19571</t>
+        </is>
+      </c>
+      <c r="BF165" t="inlineStr">
+        <is>
+          <t>264841</t>
+        </is>
+      </c>
+      <c r="BG165" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="BH165" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI165" t="inlineStr">
+        <is>
+          <t>14160</t>
+        </is>
+      </c>
+      <c r="BJ165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU165" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>11000317919152</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>1763951723</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>11850.00</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 08:07:11</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>108625767984</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>DHARMAVARAPU MADHULICA SRI</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>8374970989</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT166" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD166" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE166" t="inlineStr">
+        <is>
+          <t>19336</t>
+        </is>
+      </c>
+      <c r="BF166" t="inlineStr">
+        <is>
+          <t>263218,264721</t>
+        </is>
+      </c>
+      <c r="BG166" t="inlineStr">
+        <is>
+          <t>2037,2045</t>
+        </is>
+      </c>
+      <c r="BH166" t="inlineStr">
+        <is>
+          <t>eleven thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI166" t="inlineStr">
+        <is>
+          <t>14511</t>
+        </is>
+      </c>
+      <c r="BJ166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU166" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>11000317919152</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>1763951723</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 08:07:11</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>108625767984</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>0899053000000003</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>DHARMAVARAPU MADHULICA SRI</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>8374970989</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD167" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE167" t="inlineStr">
+        <is>
+          <t>19336</t>
+        </is>
+      </c>
+      <c r="BF167" t="inlineStr">
+        <is>
+          <t>263218,264721</t>
+        </is>
+      </c>
+      <c r="BG167" t="inlineStr">
+        <is>
+          <t>2037,2045</t>
+        </is>
+      </c>
+      <c r="BH167" t="inlineStr">
+        <is>
+          <t>eleven thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI167" t="inlineStr">
+        <is>
+          <t>14511</t>
+        </is>
+      </c>
+      <c r="BJ167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU167" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>11000317919152</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>1763951723</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 08:07:11</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>108625767984</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>0899053000000002</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>DHARMAVARAPU MADHULICA SRI</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>8374970989</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD168" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE168" t="inlineStr">
+        <is>
+          <t>19336</t>
+        </is>
+      </c>
+      <c r="BF168" t="inlineStr">
+        <is>
+          <t>263218,264721</t>
+        </is>
+      </c>
+      <c r="BG168" t="inlineStr">
+        <is>
+          <t>2037,2045</t>
+        </is>
+      </c>
+      <c r="BH168" t="inlineStr">
+        <is>
+          <t>eleven thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI168" t="inlineStr">
+        <is>
+          <t>14511</t>
+        </is>
+      </c>
+      <c r="BJ168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU168" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>11000317919499</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>1763952416</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 08:19:39</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>108625814663</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>PANDRANKI BHAVITHA SRI</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>6301729629</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT169" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD169" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE169" t="inlineStr">
+        <is>
+          <t>18038</t>
+        </is>
+      </c>
+      <c r="BF169" t="inlineStr">
+        <is>
+          <t>263436</t>
+        </is>
+      </c>
+      <c r="BG169" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="BH169" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI169" t="inlineStr">
+        <is>
+          <t>17103</t>
+        </is>
+      </c>
+      <c r="BJ169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU169" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>11000317934837</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1763959817</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>22000.00</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 10:20:54</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>694416410395</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>MOHAMMAD AFZAL</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>9885519010</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT170" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD170" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE170" t="inlineStr">
+        <is>
+          <t>19319</t>
+        </is>
+      </c>
+      <c r="BF170" t="inlineStr">
+        <is>
+          <t>263145,264648,266298</t>
+        </is>
+      </c>
+      <c r="BG170" t="inlineStr">
+        <is>
+          <t>2037,2044,2052</t>
+        </is>
+      </c>
+      <c r="BH170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">twenty two thousand </t>
+        </is>
+      </c>
+      <c r="BI170" t="inlineStr">
+        <is>
+          <t>16067</t>
+        </is>
+      </c>
+      <c r="BJ170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO170" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU170" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>11000317934837</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>1763959817</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>21500.00</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 10:20:54</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>694416410395</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>0899053000000003</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>MOHAMMAD AFZAL</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>9885519010</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT171" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD171" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE171" t="inlineStr">
+        <is>
+          <t>19319</t>
+        </is>
+      </c>
+      <c r="BF171" t="inlineStr">
+        <is>
+          <t>263145,264648,266298</t>
+        </is>
+      </c>
+      <c r="BG171" t="inlineStr">
+        <is>
+          <t>2037,2044,2052</t>
+        </is>
+      </c>
+      <c r="BH171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">twenty two thousand </t>
+        </is>
+      </c>
+      <c r="BI171" t="inlineStr">
+        <is>
+          <t>16067</t>
+        </is>
+      </c>
+      <c r="BJ171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO171" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU171" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>11000317934837</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>1763959817</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 10:20:54</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>694416410395</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>0899053000000002</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>MOHAMMAD AFZAL</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>9885519010</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD172" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE172" t="inlineStr">
+        <is>
+          <t>19319</t>
+        </is>
+      </c>
+      <c r="BF172" t="inlineStr">
+        <is>
+          <t>263145,264648,266298</t>
+        </is>
+      </c>
+      <c r="BG172" t="inlineStr">
+        <is>
+          <t>2037,2044,2052</t>
+        </is>
+      </c>
+      <c r="BH172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">twenty two thousand </t>
+        </is>
+      </c>
+      <c r="BI172" t="inlineStr">
+        <is>
+          <t>16067</t>
+        </is>
+      </c>
+      <c r="BJ172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO172" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU172" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV172" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -66,7 +66,7 @@
   <cols>
     <col min="2" max="2" width="6.3515625" customWidth="true"/>
     <col min="3" max="3" width="4.2890625" customWidth="true"/>
-    <col min="4" max="4" width="13.16015625" customWidth="true"/>
+    <col min="4" max="4" width="13.296875" customWidth="true"/>
     <col min="5" max="5" width="9.94140625" customWidth="true"/>
     <col min="6" max="6" width="8.06640625" customWidth="true"/>
     <col min="7" max="7" width="3.3359375" customWidth="true"/>
@@ -100,7 +100,7 @@
     <col min="35" max="35" width="4.12890625" customWidth="true"/>
     <col min="36" max="36" width="4.12890625" customWidth="true"/>
     <col min="37" max="37" width="3.046875" customWidth="true"/>
-    <col min="38" max="38" width="6.55078125" customWidth="true"/>
+    <col min="38" max="38" width="7.0625" customWidth="true"/>
     <col min="39" max="39" width="17.7734375" customWidth="true"/>
     <col min="40" max="40" width="0.76953125" customWidth="true"/>
     <col min="41" max="41" width="0.76953125" customWidth="true"/>
@@ -122,7 +122,7 @@
     <col min="57" max="57" width="5.75" customWidth="true"/>
     <col min="58" max="58" width="18.29296875" customWidth="true"/>
     <col min="59" max="59" width="13.0234375" customWidth="true"/>
-    <col min="60" max="60" width="29.51171875" customWidth="true"/>
+    <col min="60" max="60" width="25.96875" customWidth="true"/>
     <col min="61" max="61" width="5.328125" customWidth="true"/>
     <col min="62" max="62" width="0.76953125" customWidth="true"/>
     <col min="63" max="63" width="0.76953125" customWidth="true"/>
@@ -61210,7 +61210,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -61310,12 +61310,12 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI165" t="inlineStr">
@@ -61330,12 +61330,12 @@
       </c>
       <c r="AK165" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL165" t="inlineStr">
         <is>
-          <t/>
+          <t>11350.0</t>
         </is>
       </c>
       <c r="AM165" t="inlineStr">
@@ -61582,7 +61582,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -61607,7 +61607,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t/>
+          <t>25-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -61682,12 +61682,12 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI166" t="inlineStr">
@@ -61702,17 +61702,17 @@
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr">
         <is>
-          <t/>
+          <t>11850.0</t>
         </is>
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t/>
+          <t>25-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
@@ -61954,7 +61954,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -62054,12 +62054,12 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
@@ -62074,12 +62074,12 @@
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t/>
+          <t>11850.0</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
@@ -62326,7 +62326,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -62351,7 +62351,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t/>
+          <t>25-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
@@ -62426,12 +62426,12 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI168" t="inlineStr">
@@ -62446,17 +62446,17 @@
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL168" t="inlineStr">
         <is>
-          <t/>
+          <t>11850.0</t>
         </is>
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t/>
+          <t>25-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
@@ -62698,7 +62698,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -62723,7 +62723,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t/>
+          <t>25-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
@@ -62798,12 +62798,12 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI169" t="inlineStr">
@@ -62818,17 +62818,17 @@
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL169" t="inlineStr">
         <is>
-          <t/>
+          <t>6750.0</t>
         </is>
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t/>
+          <t>25-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
@@ -63070,7 +63070,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -63095,7 +63095,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t/>
+          <t>25-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -63170,12 +63170,12 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI170" t="inlineStr">
@@ -63190,17 +63190,17 @@
       </c>
       <c r="AK170" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL170" t="inlineStr">
         <is>
-          <t/>
+          <t>22000.0</t>
         </is>
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t/>
+          <t>25-Nov-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
@@ -63442,7 +63442,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -63542,12 +63542,12 @@
       </c>
       <c r="AG171" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI171" t="inlineStr">
@@ -63562,12 +63562,12 @@
       </c>
       <c r="AK171" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL171" t="inlineStr">
         <is>
-          <t/>
+          <t>22000.0</t>
         </is>
       </c>
       <c r="AM171" t="inlineStr">
@@ -63814,310 +63814,2542 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>694416410395</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>0899053000000002</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>MOHAMMAD AFZAL</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>9885519010</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr">
+        <is>
+          <t>22000.0</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD172" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE172" t="inlineStr">
+        <is>
+          <t>19319</t>
+        </is>
+      </c>
+      <c r="BF172" t="inlineStr">
+        <is>
+          <t>263145,264648,266298</t>
+        </is>
+      </c>
+      <c r="BG172" t="inlineStr">
+        <is>
+          <t>2037,2044,2052</t>
+        </is>
+      </c>
+      <c r="BH172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">twenty two thousand </t>
+        </is>
+      </c>
+      <c r="BI172" t="inlineStr">
+        <is>
+          <t>16067</t>
+        </is>
+      </c>
+      <c r="BJ172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO172" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU172" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>11000318061560</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>1764041529</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>8850.00</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 09:02:25</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>285283553470</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>GANTEDA CHERISHMA</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>9676361548</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>8850.0</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD173" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE173" t="inlineStr">
+        <is>
+          <t>18789</t>
+        </is>
+      </c>
+      <c r="BF173" t="inlineStr">
+        <is>
+          <t>262103,264102</t>
+        </is>
+      </c>
+      <c r="BG173" t="inlineStr">
+        <is>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="BH173" t="inlineStr">
+        <is>
+          <t>eight thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI173" t="inlineStr">
+        <is>
+          <t>16555</t>
+        </is>
+      </c>
+      <c r="BJ173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO173" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU173" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>11000318091639</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>1764052436</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>8550.00</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 12:04:15</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>514342923427</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>BOMMIDI BALA SURYA BHUVAN</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>6300875193</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>8550.0</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT174" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD174" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE174" t="inlineStr">
+        <is>
+          <t>18543</t>
+        </is>
+      </c>
+      <c r="BF174" t="inlineStr">
+        <is>
+          <t>262382,264003</t>
+        </is>
+      </c>
+      <c r="BG174" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="BH174" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI174" t="inlineStr">
+        <is>
+          <t>15863</t>
+        </is>
+      </c>
+      <c r="BJ174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO174" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU174" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>11000318101749</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>1764055278</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 12:51:53</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
           <t>NRNS</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>694416410395</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>0899053000000002</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>569503756623</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S172" t="inlineStr">
+      <c r="R175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
         <is>
           <t>MERCHANT</t>
         </is>
       </c>
-      <c r="T172" t="inlineStr">
+      <c r="T175" t="inlineStr">
         <is>
           <t>UPI</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>MOHAMMAD AFZAL</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
+      <c r="U175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>PALAKONDA PUDARJUN</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
         <is>
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>9885519010</t>
-        </is>
-      </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>9493856632</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ172" t="inlineStr">
+      <c r="AJ175" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AP172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AT172" t="inlineStr">
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD175" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE175" t="inlineStr">
+        <is>
+          <t>20005</t>
+        </is>
+      </c>
+      <c r="BF175" t="inlineStr">
+        <is>
+          <t>265045</t>
+        </is>
+      </c>
+      <c r="BG175" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH175" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI175" t="inlineStr">
+        <is>
+          <t>17295</t>
+        </is>
+      </c>
+      <c r="BJ175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO175" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU175" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>11000318159831</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1764079329</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 19:32:34</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>569509465610</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>PALAKONDA PUDARJUN</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>9493856632</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL176" t="inlineStr">
+        <is>
+          <t>6750.0</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT176" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
         </is>
       </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AW172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AX172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AY172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AZ172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BA172" t="inlineStr">
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
         <is>
           <t>UPI</t>
         </is>
       </c>
-      <c r="BB172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BC172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BD172" t="inlineStr">
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD176" t="inlineStr">
         <is>
           <t>REGULAR</t>
         </is>
       </c>
-      <c r="BE172" t="inlineStr">
-        <is>
-          <t>19319</t>
-        </is>
-      </c>
-      <c r="BF172" t="inlineStr">
-        <is>
-          <t>263145,264648,266298</t>
-        </is>
-      </c>
-      <c r="BG172" t="inlineStr">
-        <is>
-          <t>2037,2044,2052</t>
-        </is>
-      </c>
-      <c r="BH172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">twenty two thousand </t>
-        </is>
-      </c>
-      <c r="BI172" t="inlineStr">
-        <is>
-          <t>16067</t>
-        </is>
-      </c>
-      <c r="BJ172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BK172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BL172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BM172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BN172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BO172" t="inlineStr">
+      <c r="BE176" t="inlineStr">
+        <is>
+          <t>20005</t>
+        </is>
+      </c>
+      <c r="BF176" t="inlineStr">
+        <is>
+          <t>265045</t>
+        </is>
+      </c>
+      <c r="BG176" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH176" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI176" t="inlineStr">
+        <is>
+          <t>17295</t>
+        </is>
+      </c>
+      <c r="BJ176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO176" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>
       </c>
-      <c r="BP172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BQ172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BR172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BS172" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BT172" t="inlineStr">
+      <c r="BP176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT176" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BU172" t="inlineStr">
+      <c r="BU176" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="BV172" t="inlineStr">
+      <c r="BV176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>11000318238042</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1764142579</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 13:06:35</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>779334795869</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>BOTTA V K SAMTHOSHI VARSHITHA</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>9059927162</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT177" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD177" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE177" t="inlineStr">
+        <is>
+          <t>19597</t>
+        </is>
+      </c>
+      <c r="BF177" t="inlineStr">
+        <is>
+          <t>261864</t>
+        </is>
+      </c>
+      <c r="BG177" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="BH177" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI177" t="inlineStr">
+        <is>
+          <t>16196</t>
+        </is>
+      </c>
+      <c r="BJ177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO177" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU177" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>11000318238143</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1764142689</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>10750.00</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 13:08:30</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>640249767855</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>BOTTA RAM VIGNESH SANTHOSH SAI RISHIK</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>9059927162</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT178" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD178" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE178" t="inlineStr">
+        <is>
+          <t>19186</t>
+        </is>
+      </c>
+      <c r="BF178" t="inlineStr">
+        <is>
+          <t>261642</t>
+        </is>
+      </c>
+      <c r="BG178" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="BH178" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI178" t="inlineStr">
+        <is>
+          <t>14874</t>
+        </is>
+      </c>
+      <c r="BJ178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO178" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU178" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV178" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -65674,7 +65674,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -65774,12 +65774,12 @@
       </c>
       <c r="AG177" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
@@ -65794,12 +65794,12 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t/>
+          <t>11350.0</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
@@ -66046,7 +66046,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -66146,12 +66146,12 @@
       </c>
       <c r="AG178" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI178" t="inlineStr">
@@ -66166,12 +66166,12 @@
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL178" t="inlineStr">
         <is>
-          <t/>
+          <t>10750.0</t>
         </is>
       </c>
       <c r="AM178" t="inlineStr">

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -66355,6 +66355,378 @@
         </is>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>11000318681594</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1764510946</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>30-Nov-2025 19:27:04</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>253593820489</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>01-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>KOMMANABOINA SOHAM KRISHNA</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>7013724701</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>6750.0</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>01-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT179" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA179" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD179" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE179" t="inlineStr">
+        <is>
+          <t>18069</t>
+        </is>
+      </c>
+      <c r="BF179" t="inlineStr">
+        <is>
+          <t>265116</t>
+        </is>
+      </c>
+      <c r="BG179" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH179" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI179" t="inlineStr">
+        <is>
+          <t>16915</t>
+        </is>
+      </c>
+      <c r="BJ179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO179" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU179" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -88,7 +88,7 @@
     <col min="23" max="23" width="0.76953125" customWidth="true"/>
     <col min="24" max="24" width="34.45703125" customWidth="true"/>
     <col min="25" max="25" width="20.16015625" customWidth="true"/>
-    <col min="26" max="26" width="10.4375" customWidth="true"/>
+    <col min="26" max="26" width="10.421875" customWidth="true"/>
     <col min="27" max="27" width="0.76953125" customWidth="true"/>
     <col min="28" max="28" width="0.76953125" customWidth="true"/>
     <col min="29" max="29" width="16.08203125" customWidth="true"/>
@@ -66727,6 +66727,1494 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>11000318889672</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1764649784</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>02-Dec-2025 10:00:57</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>108676570140</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>BANALA VAIBHAV</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>9248863180</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT180" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA180" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB180" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD180" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE180" t="inlineStr">
+        <is>
+          <t>19562</t>
+        </is>
+      </c>
+      <c r="BF180" t="inlineStr">
+        <is>
+          <t>266565</t>
+        </is>
+      </c>
+      <c r="BG180" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH180" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI180" t="inlineStr">
+        <is>
+          <t>15962</t>
+        </is>
+      </c>
+      <c r="BJ180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU180" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>11000318908193</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1764654572</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>02-Dec-2025 11:20:56</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>108677067517</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>HEYAN RUUDRA RAPOL</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>9991367333</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT181" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA181" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB181" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD181" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE181" t="inlineStr">
+        <is>
+          <t>20016</t>
+        </is>
+      </c>
+      <c r="BF181" t="inlineStr">
+        <is>
+          <t>265830</t>
+        </is>
+      </c>
+      <c r="BG181" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH181" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI181" t="inlineStr">
+        <is>
+          <t>17307</t>
+        </is>
+      </c>
+      <c r="BJ181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU181" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>11000318907761</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>1764654572</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>02-Dec-2025 11:23:13</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>108677081867</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>HEYAN RUUDRA RAPOL</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>9991367333</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT182" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA182" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD182" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE182" t="inlineStr">
+        <is>
+          <t>20016</t>
+        </is>
+      </c>
+      <c r="BF182" t="inlineStr">
+        <is>
+          <t>265830</t>
+        </is>
+      </c>
+      <c r="BG182" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH182" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI182" t="inlineStr">
+        <is>
+          <t>17307</t>
+        </is>
+      </c>
+      <c r="BJ182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU182" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>11000318911315</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>1764655338</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>02-Dec-2025 11:34:49</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>108677160277</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>SHAIK REHAN SIDDIQUE</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>7569535771</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT183" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA183" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB183" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD183" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE183" t="inlineStr">
+        <is>
+          <t>19879</t>
+        </is>
+      </c>
+      <c r="BF183" t="inlineStr">
+        <is>
+          <t>265139</t>
+        </is>
+      </c>
+      <c r="BG183" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH183" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI183" t="inlineStr">
+        <is>
+          <t>17164</t>
+        </is>
+      </c>
+      <c r="BJ183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU183" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -80,18 +80,18 @@
     <col min="15" max="15" width="11.546875" customWidth="true"/>
     <col min="16" max="16" width="16.5234375" customWidth="true"/>
     <col min="17" max="17" width="11.0390625" customWidth="true"/>
-    <col min="18" max="18" width="17.7734375" customWidth="true"/>
+    <col min="18" max="18" width="17.74609375" customWidth="true"/>
     <col min="19" max="19" width="9.18359375" customWidth="true"/>
     <col min="20" max="20" width="6.296875" customWidth="true"/>
     <col min="21" max="21" width="0.76953125" customWidth="true"/>
-    <col min="22" max="22" width="17.1640625" customWidth="true"/>
+    <col min="22" max="22" width="17.09375" customWidth="true"/>
     <col min="23" max="23" width="0.76953125" customWidth="true"/>
     <col min="24" max="24" width="34.45703125" customWidth="true"/>
     <col min="25" max="25" width="20.16015625" customWidth="true"/>
     <col min="26" max="26" width="10.421875" customWidth="true"/>
     <col min="27" max="27" width="0.76953125" customWidth="true"/>
     <col min="28" max="28" width="0.76953125" customWidth="true"/>
-    <col min="29" max="29" width="16.08203125" customWidth="true"/>
+    <col min="29" max="29" width="15.64453125" customWidth="true"/>
     <col min="30" max="30" width="0.76953125" customWidth="true"/>
     <col min="31" max="31" width="0.76953125" customWidth="true"/>
     <col min="32" max="32" width="0.76953125" customWidth="true"/>
@@ -101,7 +101,7 @@
     <col min="36" max="36" width="4.12890625" customWidth="true"/>
     <col min="37" max="37" width="3.046875" customWidth="true"/>
     <col min="38" max="38" width="7.0625" customWidth="true"/>
-    <col min="39" max="39" width="17.7734375" customWidth="true"/>
+    <col min="39" max="39" width="17.74609375" customWidth="true"/>
     <col min="40" max="40" width="0.76953125" customWidth="true"/>
     <col min="41" max="41" width="0.76953125" customWidth="true"/>
     <col min="42" max="42" width="0.76953125" customWidth="true"/>
@@ -66790,7 +66790,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -66890,12 +66890,12 @@
       </c>
       <c r="AG180" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI180" t="inlineStr">
@@ -66910,12 +66910,12 @@
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
         <is>
-          <t/>
+          <t>11350.0</t>
         </is>
       </c>
       <c r="AM180" t="inlineStr">
@@ -67534,7 +67534,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -67559,7 +67559,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t/>
+          <t>03-Dec-2025 00:00:00</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -67634,12 +67634,12 @@
       </c>
       <c r="AG182" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
@@ -67654,17 +67654,17 @@
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t/>
+          <t>8350.0</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t/>
+          <t>03-Dec-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
@@ -68210,6 +68210,750 @@
         </is>
       </c>
       <c r="BV183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>11000319087080</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>1764746759</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>03-Dec-2025 12:56:10</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>104049297773</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>04-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>DIMILI GAGAN RISHIT</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>9493942534</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL184" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>04-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT184" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD184" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE184" t="inlineStr">
+        <is>
+          <t>19915</t>
+        </is>
+      </c>
+      <c r="BF184" t="inlineStr">
+        <is>
+          <t>265222</t>
+        </is>
+      </c>
+      <c r="BG184" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH184" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI184" t="inlineStr">
+        <is>
+          <t>17201</t>
+        </is>
+      </c>
+      <c r="BJ184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO184" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU184" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>11000319277676</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>1764851203</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>04-Dec-2025 17:57:16</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>571789451692</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>PERARAPU RESHMI SRI THANVI</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>9573851290</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT185" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA185" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD185" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE185" t="inlineStr">
+        <is>
+          <t>18767</t>
+        </is>
+      </c>
+      <c r="BF185" t="inlineStr">
+        <is>
+          <t>265790</t>
+        </is>
+      </c>
+      <c r="BG185" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH185" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI185" t="inlineStr">
+        <is>
+          <t>16147</t>
+        </is>
+      </c>
+      <c r="BJ185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO185" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU185" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV185" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -68650,7 +68650,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -68675,7 +68675,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t/>
+          <t>05-Dec-2025 00:00:00</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
@@ -68750,12 +68750,12 @@
       </c>
       <c r="AG185" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AI185" t="inlineStr">
@@ -68770,17 +68770,17 @@
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t/>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AL185" t="inlineStr">
         <is>
-          <t/>
+          <t>8350.0</t>
         </is>
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t/>
+          <t>05-Dec-2025 00:00:00</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -66,7 +66,7 @@
   <cols>
     <col min="2" max="2" width="6.3515625" customWidth="true"/>
     <col min="3" max="3" width="4.2890625" customWidth="true"/>
-    <col min="4" max="4" width="13.296875" customWidth="true"/>
+    <col min="4" max="4" width="13.3671875" customWidth="true"/>
     <col min="5" max="5" width="9.94140625" customWidth="true"/>
     <col min="6" max="6" width="8.06640625" customWidth="true"/>
     <col min="7" max="7" width="3.3359375" customWidth="true"/>
@@ -119,7 +119,7 @@
     <col min="54" max="54" width="39.1171875" customWidth="true"/>
     <col min="55" max="55" width="0.76953125" customWidth="true"/>
     <col min="56" max="56" width="7.86328125" customWidth="true"/>
-    <col min="57" max="57" width="5.75" customWidth="true"/>
+    <col min="57" max="57" width="5.72265625" customWidth="true"/>
     <col min="58" max="58" width="18.29296875" customWidth="true"/>
     <col min="59" max="59" width="13.0234375" customWidth="true"/>
     <col min="60" max="60" width="25.96875" customWidth="true"/>
@@ -68959,6 +68959,2982 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>11000319489481</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>1764992505</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>06-Dec-2025 09:13:44</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>108703956088</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>PILAKA VINISHA REDDY</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>9505890135</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT186" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA186" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD186" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE186" t="inlineStr">
+        <is>
+          <t>18805</t>
+        </is>
+      </c>
+      <c r="BF186" t="inlineStr">
+        <is>
+          <t>265779</t>
+        </is>
+      </c>
+      <c r="BG186" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH186" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI186" t="inlineStr">
+        <is>
+          <t>15762</t>
+        </is>
+      </c>
+      <c r="BJ186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BU186" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>11000319490500</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>1764992795</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>06-Dec-2025 09:17:33</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>108703980088</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>PILAKA VINISHA REDDY</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>9505890135</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr">
+        <is>
+          <t>8350.0</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT187" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA187" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD187" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE187" t="inlineStr">
+        <is>
+          <t>18805</t>
+        </is>
+      </c>
+      <c r="BF187" t="inlineStr">
+        <is>
+          <t>265779</t>
+        </is>
+      </c>
+      <c r="BG187" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH187" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI187" t="inlineStr">
+        <is>
+          <t>15762</t>
+        </is>
+      </c>
+      <c r="BJ187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BU187" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>11000319686064</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>1765123332</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>8050.00</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>07-Dec-2025 21:32:51</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>213323909356</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>MYLABATHULA MEDHANSH</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>9949134987</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL188" t="inlineStr">
+        <is>
+          <t>8050.0</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT188" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA188" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB188" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD188" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE188" t="inlineStr">
+        <is>
+          <t>18624</t>
+        </is>
+      </c>
+      <c r="BF188" t="inlineStr">
+        <is>
+          <t>265707</t>
+        </is>
+      </c>
+      <c r="BG188" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="BH188" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI188" t="inlineStr">
+        <is>
+          <t>15868</t>
+        </is>
+      </c>
+      <c r="BJ188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO188" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU188" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>11000319714346</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>1765163266</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 08:39:19</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>108716525550</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>SHAIK FARHEEN</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>9652279329</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT189" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD189" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE189" t="inlineStr">
+        <is>
+          <t>18907</t>
+        </is>
+      </c>
+      <c r="BF189" t="inlineStr">
+        <is>
+          <t>265963</t>
+        </is>
+      </c>
+      <c r="BG189" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH189" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI189" t="inlineStr">
+        <is>
+          <t>15533</t>
+        </is>
+      </c>
+      <c r="BJ189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU189" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>11000319714742</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>1765163798</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 08:47:16</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>108716565885</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>SHAIK FARHEEN</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>9652279329</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT190" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD190" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE190" t="inlineStr">
+        <is>
+          <t>18907</t>
+        </is>
+      </c>
+      <c r="BF190" t="inlineStr">
+        <is>
+          <t>265963</t>
+        </is>
+      </c>
+      <c r="BG190" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH190" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI190" t="inlineStr">
+        <is>
+          <t>15533</t>
+        </is>
+      </c>
+      <c r="BJ190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU190" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>11000319809148</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>1765188111</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 15:32:58</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>108719254095</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>09-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>SHAIK FARHEEN</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>9652279329</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL191" t="inlineStr">
+        <is>
+          <t>8350.0</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>09-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT191" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA191" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD191" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE191" t="inlineStr">
+        <is>
+          <t>18907</t>
+        </is>
+      </c>
+      <c r="BF191" t="inlineStr">
+        <is>
+          <t>265963</t>
+        </is>
+      </c>
+      <c r="BG191" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH191" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI191" t="inlineStr">
+        <is>
+          <t>15533</t>
+        </is>
+      </c>
+      <c r="BJ191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU191" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>11000319830227</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>1765195873</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>13500.00</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 17:41:36</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>108720127204</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>BORA LYDIA</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>6309196999</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT192" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA192" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD192" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE192" t="inlineStr">
+        <is>
+          <t>19894</t>
+        </is>
+      </c>
+      <c r="BF192" t="inlineStr">
+        <is>
+          <t>264985,266635</t>
+        </is>
+      </c>
+      <c r="BG192" t="inlineStr">
+        <is>
+          <t>2047,2055</t>
+        </is>
+      </c>
+      <c r="BH192" t="inlineStr">
+        <is>
+          <t>thirteen thousand five hundred</t>
+        </is>
+      </c>
+      <c r="BI192" t="inlineStr">
+        <is>
+          <t>17179</t>
+        </is>
+      </c>
+      <c r="BJ192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU192" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>11000319830313</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>1765195873</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 17:43:10</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>108720139585</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>09-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>BORA LYDIA</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>6309196999</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL193" t="inlineStr">
+        <is>
+          <t>6750.0</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>09-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT193" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA193" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD193" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE193" t="inlineStr">
+        <is>
+          <t>19894</t>
+        </is>
+      </c>
+      <c r="BF193" t="inlineStr">
+        <is>
+          <t>264985</t>
+        </is>
+      </c>
+      <c r="BG193" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH193" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI193" t="inlineStr">
+        <is>
+          <t>17179</t>
+        </is>
+      </c>
+      <c r="BJ193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU193" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -66,8 +66,8 @@
   <cols>
     <col min="2" max="2" width="6.3515625" customWidth="true"/>
     <col min="3" max="3" width="4.2890625" customWidth="true"/>
-    <col min="4" max="4" width="13.3671875" customWidth="true"/>
-    <col min="5" max="5" width="9.94140625" customWidth="true"/>
+    <col min="4" max="4" width="13.7890625" customWidth="true"/>
+    <col min="5" max="5" width="9.93359375" customWidth="true"/>
     <col min="6" max="6" width="8.06640625" customWidth="true"/>
     <col min="7" max="7" width="3.3359375" customWidth="true"/>
     <col min="8" max="8" width="17.578125" customWidth="true"/>
@@ -76,8 +76,8 @@
     <col min="11" max="11" width="17.29296875" customWidth="true"/>
     <col min="12" max="12" width="10.80859375" customWidth="true"/>
     <col min="13" max="13" width="4.9375" customWidth="true"/>
-    <col min="14" max="14" width="17.015625" customWidth="true"/>
-    <col min="15" max="15" width="11.546875" customWidth="true"/>
+    <col min="14" max="14" width="17.5625" customWidth="true"/>
+    <col min="15" max="15" width="11.625" customWidth="true"/>
     <col min="16" max="16" width="16.5234375" customWidth="true"/>
     <col min="17" max="17" width="11.0390625" customWidth="true"/>
     <col min="18" max="18" width="17.74609375" customWidth="true"/>
@@ -86,12 +86,12 @@
     <col min="21" max="21" width="0.76953125" customWidth="true"/>
     <col min="22" max="22" width="17.09375" customWidth="true"/>
     <col min="23" max="23" width="0.76953125" customWidth="true"/>
-    <col min="24" max="24" width="34.45703125" customWidth="true"/>
+    <col min="24" max="24" width="33.59375" customWidth="true"/>
     <col min="25" max="25" width="20.16015625" customWidth="true"/>
     <col min="26" max="26" width="10.421875" customWidth="true"/>
     <col min="27" max="27" width="0.76953125" customWidth="true"/>
     <col min="28" max="28" width="0.76953125" customWidth="true"/>
-    <col min="29" max="29" width="15.64453125" customWidth="true"/>
+    <col min="29" max="29" width="16.04296875" customWidth="true"/>
     <col min="30" max="30" width="0.76953125" customWidth="true"/>
     <col min="31" max="31" width="0.76953125" customWidth="true"/>
     <col min="32" max="32" width="0.76953125" customWidth="true"/>
@@ -71935,6 +71935,9678 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>11000340117361</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>1765517263</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>12-Dec-2025 10:57:59</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>534655013098</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>RONGALI JASMIKA</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>7793910192</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL194" t="inlineStr">
+        <is>
+          <t>6750.0</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT194" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD194" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE194" t="inlineStr">
+        <is>
+          <t>19849</t>
+        </is>
+      </c>
+      <c r="BF194" t="inlineStr">
+        <is>
+          <t>265097</t>
+        </is>
+      </c>
+      <c r="BG194" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH194" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI194" t="inlineStr">
+        <is>
+          <t>17146</t>
+        </is>
+      </c>
+      <c r="BJ194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO194" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU194" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>11000340117427</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>1765517323</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>8050.00</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>12-Dec-2025 10:58:54</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>571217384715</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>RONGALI YERNI VENKATA RAKESH</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>7793910192</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL195" t="inlineStr">
+        <is>
+          <t>8050.0</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT195" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD195" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE195" t="inlineStr">
+        <is>
+          <t>19850</t>
+        </is>
+      </c>
+      <c r="BF195" t="inlineStr">
+        <is>
+          <t>265556</t>
+        </is>
+      </c>
+      <c r="BG195" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="BH195" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI195" t="inlineStr">
+        <is>
+          <t>17147</t>
+        </is>
+      </c>
+      <c r="BJ195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO195" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU195" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>11000340161581</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>1765532834</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>8050.00</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>12-Dec-2025 15:19:14</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>108745991711</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>AKKURADA VARUN</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>8500847900</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL196" t="inlineStr">
+        <is>
+          <t>8050.0</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT196" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD196" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE196" t="inlineStr">
+        <is>
+          <t>20089</t>
+        </is>
+      </c>
+      <c r="BF196" t="inlineStr">
+        <is>
+          <t>268484</t>
+        </is>
+      </c>
+      <c r="BG196" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="BH196" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI196" t="inlineStr">
+        <is>
+          <t>17370</t>
+        </is>
+      </c>
+      <c r="BJ196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU196" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>11000340240544</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>1765601703</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>10750.00</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>13-Dec-2025 10:25:13</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>790303117843</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>GOGALAMANDA ASHWIN</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>9133615133</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr">
+        <is>
+          <t>10750.0</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT197" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD197" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE197" t="inlineStr">
+        <is>
+          <t>20064</t>
+        </is>
+      </c>
+      <c r="BF197" t="inlineStr">
+        <is>
+          <t>266318</t>
+        </is>
+      </c>
+      <c r="BG197" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="BH197" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI197" t="inlineStr">
+        <is>
+          <t>17336</t>
+        </is>
+      </c>
+      <c r="BJ197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO197" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU197" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>11000340278660</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>1765619596</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>13-Dec-2025 15:24:28</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>397896712035</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>397896712035</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>EVAAN CHODAM</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>7995919129</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL198" t="inlineStr">
+        <is>
+          <t>6750.0</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT198" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD198" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE198" t="inlineStr">
+        <is>
+          <t>20086</t>
+        </is>
+      </c>
+      <c r="BF198" t="inlineStr">
+        <is>
+          <t>268470</t>
+        </is>
+      </c>
+      <c r="BG198" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH198" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI198" t="inlineStr">
+        <is>
+          <t>17367</t>
+        </is>
+      </c>
+      <c r="BJ198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO198" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU198" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>11000340453923</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>1765779979</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>8650.00</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 11:57:08</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>231872222125</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>MAHENDRA REDDY GUDLA</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>9948345552</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL199" t="inlineStr">
+        <is>
+          <t>8650.0</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT199" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD199" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE199" t="inlineStr">
+        <is>
+          <t>19010</t>
+        </is>
+      </c>
+      <c r="BF199" t="inlineStr">
+        <is>
+          <t>266145</t>
+        </is>
+      </c>
+      <c r="BG199" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH199" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI199" t="inlineStr">
+        <is>
+          <t>16796</t>
+        </is>
+      </c>
+      <c r="BJ199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO199" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU199" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>11000340456018</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>1765780062</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 11:58:00</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>717946201991</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>16-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>YASHWANTH REDDY GUDLA</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>9948345552</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL200" t="inlineStr">
+        <is>
+          <t>8350.0</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>16-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT200" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD200" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE200" t="inlineStr">
+        <is>
+          <t>18786</t>
+        </is>
+      </c>
+      <c r="BF200" t="inlineStr">
+        <is>
+          <t>265832</t>
+        </is>
+      </c>
+      <c r="BG200" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH200" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI200" t="inlineStr">
+        <is>
+          <t>16797</t>
+        </is>
+      </c>
+      <c r="BJ200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO200" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT200" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU200" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>11000340619866</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>1765866976</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>16-Dec-2025 12:06:31</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>690206926885</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>17-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>HARIPRIYA RAVADA</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>6305148581</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>17-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT201" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD201" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE201" t="inlineStr">
+        <is>
+          <t>18341</t>
+        </is>
+      </c>
+      <c r="BF201" t="inlineStr">
+        <is>
+          <t>265338</t>
+        </is>
+      </c>
+      <c r="BG201" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH201" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI201" t="inlineStr">
+        <is>
+          <t>16936</t>
+        </is>
+      </c>
+      <c r="BJ201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO201" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT201" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU201" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>11000340759102</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>1765955387</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>10750.00</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>17-Dec-2025 12:40:11</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>794450161070</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>RANVITHA SEERA</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>7095076706</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>10750.0</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT202" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD202" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE202" t="inlineStr">
+        <is>
+          <t>19168</t>
+        </is>
+      </c>
+      <c r="BF202" t="inlineStr">
+        <is>
+          <t>266241</t>
+        </is>
+      </c>
+      <c r="BG202" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="BH202" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI202" t="inlineStr">
+        <is>
+          <t>16906</t>
+        </is>
+      </c>
+      <c r="BJ202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO202" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT202" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU202" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>11000340813371</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>1765980521</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>17-Dec-2025 19:39:33</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>108780945784</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>VINAYAK KUMAR</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>7396170082</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT203" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD203" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE203" t="inlineStr">
+        <is>
+          <t>18292</t>
+        </is>
+      </c>
+      <c r="BF203" t="inlineStr">
+        <is>
+          <t>265434</t>
+        </is>
+      </c>
+      <c r="BG203" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH203" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI203" t="inlineStr">
+        <is>
+          <t>16937</t>
+        </is>
+      </c>
+      <c r="BJ203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT203" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU203" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>11000340878141</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>1766039017</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 12:09:57</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>297705735742</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>KEERTHANA MUDDA</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>9573036376</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>11350.0</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT204" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA204" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD204" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE204" t="inlineStr">
+        <is>
+          <t>19519</t>
+        </is>
+      </c>
+      <c r="BF204" t="inlineStr">
+        <is>
+          <t>266531</t>
+        </is>
+      </c>
+      <c r="BG204" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH204" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI204" t="inlineStr">
+        <is>
+          <t>15621</t>
+        </is>
+      </c>
+      <c r="BJ204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO204" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT204" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU204" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>11000340919232</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>1766057697</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 17:07:06</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>108787285351</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>19-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>SAI SRAVAN PATNAYAK</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>7337422112</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL205" t="inlineStr">
+        <is>
+          <t>6750.0</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>19-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT205" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA205" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB205" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD205" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE205" t="inlineStr">
+        <is>
+          <t>18066</t>
+        </is>
+      </c>
+      <c r="BF205" t="inlineStr">
+        <is>
+          <t>265129</t>
+        </is>
+      </c>
+      <c r="BG205" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH205" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI205" t="inlineStr">
+        <is>
+          <t>16914</t>
+        </is>
+      </c>
+      <c r="BJ205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT205" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU205" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>11000340940536</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>1766070034</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>8050.00</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 20:31:47</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>BANK OF BARODA FSS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>101202535235054940</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>547580</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>19-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>CANARA BANK</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>GANIREDDY ANUHYA</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>9848537189</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>XXXXXXXXXXXX9882</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>8050.0</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>19-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT206" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA206" t="inlineStr">
+        <is>
+          <t>RUPAY</t>
+        </is>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD206" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE206" t="inlineStr">
+        <is>
+          <t>18375</t>
+        </is>
+      </c>
+      <c r="BF206" t="inlineStr">
+        <is>
+          <t>265457</t>
+        </is>
+      </c>
+      <c r="BG206" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="BH206" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI206" t="inlineStr">
+        <is>
+          <t>16552</t>
+        </is>
+      </c>
+      <c r="BJ206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT206" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU206" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>11000342204411</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>1767145208</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>8050.00</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>31-Dec-2025 07:37:12</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>067115244586</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>GOLAGANI RITHIK NANDHAN</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>9393123464</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>8050.0</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT207" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD207" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE207" t="inlineStr">
+        <is>
+          <t>18667</t>
+        </is>
+      </c>
+      <c r="BF207" t="inlineStr">
+        <is>
+          <t>265672</t>
+        </is>
+      </c>
+      <c r="BG207" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="BH207" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI207" t="inlineStr">
+        <is>
+          <t>15824</t>
+        </is>
+      </c>
+      <c r="BJ207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO207" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU207" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>11000342307101</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>1767189156</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>31-Dec-2025 19:23:00</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>108881246730</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>REYANA SRIJITH</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>9985925345</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT208" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD208" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE208" t="inlineStr">
+        <is>
+          <t>19902</t>
+        </is>
+      </c>
+      <c r="BF208" t="inlineStr">
+        <is>
+          <t>265340</t>
+        </is>
+      </c>
+      <c r="BG208" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH208" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI208" t="inlineStr">
+        <is>
+          <t>17188</t>
+        </is>
+      </c>
+      <c r="BJ208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU208" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>11000342315290</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>1767193550</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>31-Dec-2025 20:40:26</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>108881815622</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>KARRI ABHINAY CHARVIK</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>9177965994</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL209" t="inlineStr">
+        <is>
+          <t>8350.0</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT209" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD209" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE209" t="inlineStr">
+        <is>
+          <t>18807</t>
+        </is>
+      </c>
+      <c r="BF209" t="inlineStr">
+        <is>
+          <t>267483</t>
+        </is>
+      </c>
+      <c r="BG209" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH209" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI209" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="BJ209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU209" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>11000342341005</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>1767238144</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 09:00:50</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>108884026898</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>KADAJARI ESHAN ESWAR</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>9885130099</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL210" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT210" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD210" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE210" t="inlineStr">
+        <is>
+          <t>18273</t>
+        </is>
+      </c>
+      <c r="BF210" t="inlineStr">
+        <is>
+          <t>265390</t>
+        </is>
+      </c>
+      <c r="BG210" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH210" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI210" t="inlineStr">
+        <is>
+          <t>16974</t>
+        </is>
+      </c>
+      <c r="BJ210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT210" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU210" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>11000342354253</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>1767244559</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 10:46:18</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>104639698103</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>VARTIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>8369239788</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL211" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT211" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD211" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE211" t="inlineStr">
+        <is>
+          <t>19931</t>
+        </is>
+      </c>
+      <c r="BF211" t="inlineStr">
+        <is>
+          <t>265205</t>
+        </is>
+      </c>
+      <c r="BG211" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH211" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI211" t="inlineStr">
+        <is>
+          <t>17219</t>
+        </is>
+      </c>
+      <c r="BJ211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO211" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT211" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU211" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>11000342590071</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>1767355353</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 17:33:21</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>108896145112</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>03-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>CHENNA JAIKAR ABHIMANYU</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>8074712848</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL212" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>03-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT212" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD212" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE212" t="inlineStr">
+        <is>
+          <t>19925</t>
+        </is>
+      </c>
+      <c r="BF212" t="inlineStr">
+        <is>
+          <t>265220</t>
+        </is>
+      </c>
+      <c r="BG212" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH212" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI212" t="inlineStr">
+        <is>
+          <t>17211</t>
+        </is>
+      </c>
+      <c r="BJ212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT212" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU212" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>11000342590128</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>1767355490</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 17:35:15</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>108896159648</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>03-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>CHENNA JAIKAR ABHIMANYU</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>8074712848</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL213" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>03-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT213" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD213" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE213" t="inlineStr">
+        <is>
+          <t>19925</t>
+        </is>
+      </c>
+      <c r="BF213" t="inlineStr">
+        <is>
+          <t>266870</t>
+        </is>
+      </c>
+      <c r="BG213" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH213" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI213" t="inlineStr">
+        <is>
+          <t>17211</t>
+        </is>
+      </c>
+      <c r="BJ213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT213" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU213" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>11000342680749</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>1767419107</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>03-Jan-2026 11:15:36</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>600378887759</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>05-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>SAANVI SAHOO</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>8309736856</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL214" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>05-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT214" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA214" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB214" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD214" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE214" t="inlineStr">
+        <is>
+          <t>20077</t>
+        </is>
+      </c>
+      <c r="BF214" t="inlineStr">
+        <is>
+          <t>268294</t>
+        </is>
+      </c>
+      <c r="BG214" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH214" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI214" t="inlineStr">
+        <is>
+          <t>17358</t>
+        </is>
+      </c>
+      <c r="BJ214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO214" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT214" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU214" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>11000343253696</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>1767678695</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>06-Jan-2026 11:22:49</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>108922656285</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>GAYATRI PHANISRI SATHWIKA YEDIDA</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>7032420256</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT215" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD215" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE215" t="inlineStr">
+        <is>
+          <t>18149</t>
+        </is>
+      </c>
+      <c r="BF215" t="inlineStr">
+        <is>
+          <t>265207</t>
+        </is>
+      </c>
+      <c r="BG215" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH215" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI215" t="inlineStr">
+        <is>
+          <t>16675</t>
+        </is>
+      </c>
+      <c r="BJ215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT215" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU215" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>11000343525514</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>1767755445</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>15500.00</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>07-Jan-2026 08:41:12</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>279709918647</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>08-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>POTNURU YELEENA</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>8374132397</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL216" t="inlineStr">
+        <is>
+          <t>15500.0</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>08-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT216" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD216" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE216" t="inlineStr">
+        <is>
+          <t>18352</t>
+        </is>
+      </c>
+      <c r="BF216" t="inlineStr">
+        <is>
+          <t>265332,266982</t>
+        </is>
+      </c>
+      <c r="BG216" t="inlineStr">
+        <is>
+          <t>2048,2056</t>
+        </is>
+      </c>
+      <c r="BH216" t="inlineStr">
+        <is>
+          <t>fifteen thousand five hundred</t>
+        </is>
+      </c>
+      <c r="BI216" t="inlineStr">
+        <is>
+          <t>16507</t>
+        </is>
+      </c>
+      <c r="BJ216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO216" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT216" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU216" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>11000343669593</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>1767785538</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>8650.00</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>07-Jan-2026 17:04:48</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>691063181825</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>SUGGI VENKATA SAI VISHNU VARDHAN</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>8500793683</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>8650.0</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT217" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD217" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE217" t="inlineStr">
+        <is>
+          <t>19146</t>
+        </is>
+      </c>
+      <c r="BF217" t="inlineStr">
+        <is>
+          <t>266163</t>
+        </is>
+      </c>
+      <c r="BG217" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH217" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI217" t="inlineStr">
+        <is>
+          <t>16894</t>
+        </is>
+      </c>
+      <c r="BJ217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO217" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT217" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU217" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>11000344284124</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>1768016812</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>10-Jan-2026 09:17:42</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>108951978498</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>EDUBILLI MAHASWIN</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>9618641662</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT218" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD218" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE218" t="inlineStr">
+        <is>
+          <t>19988</t>
+        </is>
+      </c>
+      <c r="BF218" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="BG218" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH218" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI218" t="inlineStr">
+        <is>
+          <t>17277</t>
+        </is>
+      </c>
+      <c r="BJ218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT218" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU218" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>11000344283491</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>1768017067</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>10-Jan-2026 09:21:38</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>108952003059</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>EDUBILLI MAHASWIN</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>9618641662</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT219" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD219" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE219" t="inlineStr">
+        <is>
+          <t>19988</t>
+        </is>
+      </c>
+      <c r="BF219" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="BG219" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH219" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI219" t="inlineStr">
+        <is>
+          <t>17277</t>
+        </is>
+      </c>
+      <c r="BJ219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT219" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU219" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -67,10 +67,10 @@
     <col min="2" max="2" width="6.3515625" customWidth="true"/>
     <col min="3" max="3" width="4.2890625" customWidth="true"/>
     <col min="4" max="4" width="13.7890625" customWidth="true"/>
-    <col min="5" max="5" width="9.93359375" customWidth="true"/>
+    <col min="5" max="5" width="9.96484375" customWidth="true"/>
     <col min="6" max="6" width="8.06640625" customWidth="true"/>
     <col min="7" max="7" width="3.3359375" customWidth="true"/>
-    <col min="8" max="8" width="17.578125" customWidth="true"/>
+    <col min="8" max="8" width="17.5703125" customWidth="true"/>
     <col min="9" max="9" width="9.01953125" customWidth="true"/>
     <col min="10" max="10" width="3.62890625" customWidth="true"/>
     <col min="11" max="11" width="17.29296875" customWidth="true"/>
@@ -84,11 +84,11 @@
     <col min="19" max="19" width="9.18359375" customWidth="true"/>
     <col min="20" max="20" width="6.296875" customWidth="true"/>
     <col min="21" max="21" width="0.76953125" customWidth="true"/>
-    <col min="22" max="22" width="17.09375" customWidth="true"/>
+    <col min="22" max="22" width="17.1640625" customWidth="true"/>
     <col min="23" max="23" width="0.76953125" customWidth="true"/>
-    <col min="24" max="24" width="33.59375" customWidth="true"/>
+    <col min="24" max="24" width="33.453125" customWidth="true"/>
     <col min="25" max="25" width="20.16015625" customWidth="true"/>
-    <col min="26" max="26" width="10.421875" customWidth="true"/>
+    <col min="26" max="26" width="10.41015625" customWidth="true"/>
     <col min="27" max="27" width="0.76953125" customWidth="true"/>
     <col min="28" max="28" width="0.76953125" customWidth="true"/>
     <col min="29" max="29" width="16.04296875" customWidth="true"/>
@@ -122,7 +122,7 @@
     <col min="57" max="57" width="5.72265625" customWidth="true"/>
     <col min="58" max="58" width="18.29296875" customWidth="true"/>
     <col min="59" max="59" width="13.0234375" customWidth="true"/>
-    <col min="60" max="60" width="25.96875" customWidth="true"/>
+    <col min="60" max="60" width="26.29296875" customWidth="true"/>
     <col min="61" max="61" width="5.328125" customWidth="true"/>
     <col min="62" max="62" width="0.76953125" customWidth="true"/>
     <col min="63" max="63" width="0.76953125" customWidth="true"/>
@@ -134,7 +134,7 @@
     <col min="69" max="69" width="0.76953125" customWidth="true"/>
     <col min="70" max="70" width="0.76953125" customWidth="true"/>
     <col min="71" max="71" width="0.76953125" customWidth="true"/>
-    <col min="72" max="72" width="3.203125" customWidth="true"/>
+    <col min="72" max="72" width="1.8203125" customWidth="true"/>
     <col min="73" max="73" width="2.91015625" customWidth="true"/>
     <col min="74" max="74" width="1.3828125" customWidth="true"/>
   </cols>
@@ -81298,310 +81298,8494 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>108952003059</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>12-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>EDUBILLI MAHASWIN</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>9618641662</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL219" t="inlineStr">
+        <is>
+          <t>6750.0</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>12-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT219" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD219" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE219" t="inlineStr">
+        <is>
+          <t>19988</t>
+        </is>
+      </c>
+      <c r="BF219" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="BG219" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH219" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI219" t="inlineStr">
+        <is>
+          <t>17277</t>
+        </is>
+      </c>
+      <c r="BJ219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT219" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU219" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>11000344351903</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>1768027227</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>10-Jan-2026 12:11:32</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>108953138415</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>12-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>SILUGURI CHIYAN ESHAN VARMA</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>8639375454</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL220" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM220" t="inlineStr">
+        <is>
+          <t>12-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT220" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD220" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE220" t="inlineStr">
+        <is>
+          <t>19975</t>
+        </is>
+      </c>
+      <c r="BF220" t="inlineStr">
+        <is>
+          <t>265274</t>
+        </is>
+      </c>
+      <c r="BG220" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH220" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI220" t="inlineStr">
+        <is>
+          <t>17264</t>
+        </is>
+      </c>
+      <c r="BJ220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU220" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>11000344353254</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>1768027340</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>10-Jan-2026 12:14:02</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>108953157494</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>12-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>SILUGURI CHIYAN ESHAN VARMA</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>8639375454</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL221" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>12-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT221" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD221" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE221" t="inlineStr">
+        <is>
+          <t>19975</t>
+        </is>
+      </c>
+      <c r="BF221" t="inlineStr">
+        <is>
+          <t>266924</t>
+        </is>
+      </c>
+      <c r="BG221" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH221" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI221" t="inlineStr">
+        <is>
+          <t>17264</t>
+        </is>
+      </c>
+      <c r="BJ221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU221" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>11000345560684</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>1768629091</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>17-Jan-2026 11:25:23</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>BANK OF BARODA FSS</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
           <t>NRNS</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>108952003059</t>
-        </is>
-      </c>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P219" t="inlineStr">
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>101202601785336502</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
         <is>
           <t>100000036600</t>
         </is>
       </c>
-      <c r="Q219" t="inlineStr">
+      <c r="Q222" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S219" t="inlineStr">
+      <c r="R222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
         <is>
           <t>MERCHANT</t>
         </is>
       </c>
-      <c r="T219" t="inlineStr">
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>UNION BANK OF INDIA</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>PIRATI RISHIKESH VENKATA SAI</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>9985572139</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>XXXXXXXXXXXX1294</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>RUPAY</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD222" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE222" t="inlineStr">
+        <is>
+          <t>19505</t>
+        </is>
+      </c>
+      <c r="BF222" t="inlineStr">
+        <is>
+          <t>266608</t>
+        </is>
+      </c>
+      <c r="BG222" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH222" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI222" t="inlineStr">
+        <is>
+          <t>14569</t>
+        </is>
+      </c>
+      <c r="BJ222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU222" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>11000345855138</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>1768769044</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 02:15:04</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>109013707860</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
         <is>
           <t>UPI</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>EDUBILLI MAHASWIN</t>
-        </is>
-      </c>
-      <c r="Y219" t="inlineStr">
+      <c r="U223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>VEDITHI ARPANA CHANDRA</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
         <is>
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>9618641662</t>
-        </is>
-      </c>
-      <c r="AA219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>9959307771</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ219" t="inlineStr">
+      <c r="AJ223" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AP219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AT219" t="inlineStr">
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT223" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD223" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE223" t="inlineStr">
+        <is>
+          <t>18863</t>
+        </is>
+      </c>
+      <c r="BF223" t="inlineStr">
+        <is>
+          <t>267586</t>
+        </is>
+      </c>
+      <c r="BG223" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH223" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI223" t="inlineStr">
+        <is>
+          <t>15938</t>
+        </is>
+      </c>
+      <c r="BJ223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU223" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>11000345867539</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>1768790106</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>8050.00</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 08:07:08</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>109014543218</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>DWARAMPUDI BHUVAN REDDY</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>9505754523</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL224" t="inlineStr">
+        <is>
+          <t>8050.0</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT224" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
         </is>
       </c>
-      <c r="AU219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AW219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AX219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AY219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AZ219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BA219" t="inlineStr">
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
         <is>
           <t>UPI</t>
         </is>
       </c>
-      <c r="BB219" t="inlineStr">
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD224" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE224" t="inlineStr">
+        <is>
+          <t>18393</t>
+        </is>
+      </c>
+      <c r="BF224" t="inlineStr">
+        <is>
+          <t>267111</t>
+        </is>
+      </c>
+      <c r="BG224" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH224" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI224" t="inlineStr">
+        <is>
+          <t>16686</t>
+        </is>
+      </c>
+      <c r="BJ224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU224" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>11000345867589</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>1768790317</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 08:09:06</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>109014551659</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>DWARAMPUDI MOKSHITA</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>9505754523</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL225" t="inlineStr">
+        <is>
+          <t>6750.0</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT225" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
-      <c r="BC219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BD219" t="inlineStr">
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD225" t="inlineStr">
         <is>
           <t>REGULAR</t>
         </is>
       </c>
-      <c r="BE219" t="inlineStr">
-        <is>
-          <t>19988</t>
-        </is>
-      </c>
-      <c r="BF219" t="inlineStr">
-        <is>
-          <t>265125</t>
-        </is>
-      </c>
-      <c r="BG219" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="BH219" t="inlineStr">
+      <c r="BE225" t="inlineStr">
+        <is>
+          <t>19890</t>
+        </is>
+      </c>
+      <c r="BF225" t="inlineStr">
+        <is>
+          <t>266639</t>
+        </is>
+      </c>
+      <c r="BG225" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH225" t="inlineStr">
         <is>
           <t>six thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="BI219" t="inlineStr">
-        <is>
-          <t>17277</t>
-        </is>
-      </c>
-      <c r="BJ219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BK219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BL219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BM219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BN219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BO219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BP219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BQ219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BR219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BS219" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="BT219" t="inlineStr">
+      <c r="BI225" t="inlineStr">
+        <is>
+          <t>17175</t>
+        </is>
+      </c>
+      <c r="BJ225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT225" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BU219" t="inlineStr">
+      <c r="BU225" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="BV219" t="inlineStr">
+      <c r="BV225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>11000345916088</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>1768799896</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 10:57:18</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>464738387430</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>SUVVARI JAIDEEP</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>7386363690</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL226" t="inlineStr">
+        <is>
+          <t>7750.0</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT226" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD226" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE226" t="inlineStr">
+        <is>
+          <t>20024</t>
+        </is>
+      </c>
+      <c r="BF226" t="inlineStr">
+        <is>
+          <t>265253</t>
+        </is>
+      </c>
+      <c r="BG226" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH226" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI226" t="inlineStr">
+        <is>
+          <t>17316</t>
+        </is>
+      </c>
+      <c r="BJ226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO226" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU226" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>11000346179829</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>1768841237</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>8650.00</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 22:18:56</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>899357782103</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>GANTEDA NIKHIL RAJ</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>9676361548</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL227" t="inlineStr">
+        <is>
+          <t>8650.0</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT227" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD227" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE227" t="inlineStr">
+        <is>
+          <t>19096</t>
+        </is>
+      </c>
+      <c r="BF227" t="inlineStr">
+        <is>
+          <t>266126</t>
+        </is>
+      </c>
+      <c r="BG227" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH227" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI227" t="inlineStr">
+        <is>
+          <t>16313</t>
+        </is>
+      </c>
+      <c r="BJ227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO227" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU227" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>11000346395565</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>1768911627</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 17:50:43</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>306068999759</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>21-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>GANTEDA CHERISHMA</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>9676361548</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL228" t="inlineStr">
+        <is>
+          <t>8350.0</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>21-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT228" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD228" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE228" t="inlineStr">
+        <is>
+          <t>18789</t>
+        </is>
+      </c>
+      <c r="BF228" t="inlineStr">
+        <is>
+          <t>265752</t>
+        </is>
+      </c>
+      <c r="BG228" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH228" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI228" t="inlineStr">
+        <is>
+          <t>16555</t>
+        </is>
+      </c>
+      <c r="BJ228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO228" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU228" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>11000346500624</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>1768966997</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>21-Jan-2026 09:15:52</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>109028539732</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>DEDEEPYA MERUGUMALLA</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>8801427880</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT229" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA229" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB229" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD229" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE229" t="inlineStr">
+        <is>
+          <t>18297</t>
+        </is>
+      </c>
+      <c r="BF229" t="inlineStr">
+        <is>
+          <t>266953</t>
+        </is>
+      </c>
+      <c r="BG229" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH229" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI229" t="inlineStr">
+        <is>
+          <t>16636</t>
+        </is>
+      </c>
+      <c r="BJ229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT229" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU229" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>11000346525369</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>1768973323</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>8050.00</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>21-Jan-2026 11:00:25</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>655956291842</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>SIMMA REGINA</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>9949129798</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL230" t="inlineStr">
+        <is>
+          <t>8050.0</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT230" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD230" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE230" t="inlineStr">
+        <is>
+          <t>19979</t>
+        </is>
+      </c>
+      <c r="BF230" t="inlineStr">
+        <is>
+          <t>265502</t>
+        </is>
+      </c>
+      <c r="BG230" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="BH230" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI230" t="inlineStr">
+        <is>
+          <t>17268</t>
+        </is>
+      </c>
+      <c r="BJ230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO230" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU230" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>11000346568106</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>1768978763</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>8650.00</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>21-Jan-2026 12:31:04</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>109029876457</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>AAROHI DASARI</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>9848982155</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL231" t="inlineStr">
+        <is>
+          <t>8650.0</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT231" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD231" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE231" t="inlineStr">
+        <is>
+          <t>19022</t>
+        </is>
+      </c>
+      <c r="BF231" t="inlineStr">
+        <is>
+          <t>266033</t>
+        </is>
+      </c>
+      <c r="BG231" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH231" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI231" t="inlineStr">
+        <is>
+          <t>15765</t>
+        </is>
+      </c>
+      <c r="BJ231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU231" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>11000346670581</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>1769048719</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 07:56:13</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>136130932845</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>CHINTAPALLI CHATHAN SWAROOP</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>9985304942</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL232" t="inlineStr">
+        <is>
+          <t>11350.0</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT232" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD232" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE232" t="inlineStr">
+        <is>
+          <t>19397</t>
+        </is>
+      </c>
+      <c r="BF232" t="inlineStr">
+        <is>
+          <t>266418</t>
+        </is>
+      </c>
+      <c r="BG232" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH232" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI232" t="inlineStr">
+        <is>
+          <t>14706</t>
+        </is>
+      </c>
+      <c r="BJ232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO232" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU232" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>11000346674063</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>1769049843</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 08:14:26</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>632058461761</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>CHINTAPALLI CHANDINI</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>9985304942</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL233" t="inlineStr">
+        <is>
+          <t>8350.0</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT233" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD233" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE233" t="inlineStr">
+        <is>
+          <t>18866</t>
+        </is>
+      </c>
+      <c r="BF233" t="inlineStr">
+        <is>
+          <t>265897</t>
+        </is>
+      </c>
+      <c r="BG233" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH233" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI233" t="inlineStr">
+        <is>
+          <t>15618</t>
+        </is>
+      </c>
+      <c r="BJ233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO233" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU233" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>11000346806094</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>1769090880</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>8050.00</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 19:45:38</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>109039770569</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>THANU SREE BHOOMIREDDY</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>9573771080</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL234" t="inlineStr">
+        <is>
+          <t>8050.0</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT234" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD234" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE234" t="inlineStr">
+        <is>
+          <t>18610</t>
+        </is>
+      </c>
+      <c r="BF234" t="inlineStr">
+        <is>
+          <t>267230</t>
+        </is>
+      </c>
+      <c r="BG234" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH234" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI234" t="inlineStr">
+        <is>
+          <t>16617</t>
+        </is>
+      </c>
+      <c r="BJ234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU234" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>11000346831268</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>1769131185</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>8350.00</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 06:50:59</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>638921959953</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>MUSKHAN KARRI</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>8019731551</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT235" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD235" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE235" t="inlineStr">
+        <is>
+          <t>18875</t>
+        </is>
+      </c>
+      <c r="BF235" t="inlineStr">
+        <is>
+          <t>267563</t>
+        </is>
+      </c>
+      <c r="BG235" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH235" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI235" t="inlineStr">
+        <is>
+          <t>15539</t>
+        </is>
+      </c>
+      <c r="BJ235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO235" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU235" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>11000346844834</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>1769140828</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 09:30:36</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>891843903115</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>SEERLA SURAJ SAI</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>9704836532</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT236" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA236" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB236" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD236" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE236" t="inlineStr">
+        <is>
+          <t>19981</t>
+        </is>
+      </c>
+      <c r="BF236" t="inlineStr">
+        <is>
+          <t>266915</t>
+        </is>
+      </c>
+      <c r="BG236" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH236" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI236" t="inlineStr">
+        <is>
+          <t>17270</t>
+        </is>
+      </c>
+      <c r="BJ236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO236" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU236" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>11000346846448</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>1769141317</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 09:40:57</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>109042639757</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>TALACHINTALA SURYA NIMROD</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>9492203981</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT237" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA237" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB237" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD237" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE237" t="inlineStr">
+        <is>
+          <t>18172</t>
+        </is>
+      </c>
+      <c r="BF237" t="inlineStr">
+        <is>
+          <t>266904</t>
+        </is>
+      </c>
+      <c r="BG237" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH237" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI237" t="inlineStr">
+        <is>
+          <t>16648</t>
+        </is>
+      </c>
+      <c r="BJ237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT237" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU237" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>11000346858020</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>1769145410</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 10:47:03</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>938830485824</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>PIRATI RISHIKESH VENKATA SAI</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>9985572139</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT238" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA238" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB238" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD238" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE238" t="inlineStr">
+        <is>
+          <t>19505</t>
+        </is>
+      </c>
+      <c r="BF238" t="inlineStr">
+        <is>
+          <t>266608</t>
+        </is>
+      </c>
+      <c r="BG238" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH238" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI238" t="inlineStr">
+        <is>
+          <t>14569</t>
+        </is>
+      </c>
+      <c r="BJ238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO238" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU238" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>11000346874934</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>1769152013</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 12:37:15</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>744495867933</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>JYOTHSNA PILAKA</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>9298052339</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT239" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA239" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB239" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD239" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE239" t="inlineStr">
+        <is>
+          <t>19518</t>
+        </is>
+      </c>
+      <c r="BF239" t="inlineStr">
+        <is>
+          <t>266530</t>
+        </is>
+      </c>
+      <c r="BG239" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH239" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI239" t="inlineStr">
+        <is>
+          <t>14741</t>
+        </is>
+      </c>
+      <c r="BJ239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO239" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT239" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU239" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>11000346878686</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>1769169337</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>22700.00</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 12:56:31</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>250331567150</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>SARIPILLI JASWITH</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>7396346993</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ240" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT240" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA240" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB240" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD240" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE240" t="inlineStr">
+        <is>
+          <t>19498</t>
+        </is>
+      </c>
+      <c r="BF240" t="inlineStr">
+        <is>
+          <t>266614,268264</t>
+        </is>
+      </c>
+      <c r="BG240" t="inlineStr">
+        <is>
+          <t>2053,2061</t>
+        </is>
+      </c>
+      <c r="BH240" t="inlineStr">
+        <is>
+          <t>twenty two thousand seven hundred</t>
+        </is>
+      </c>
+      <c r="BI240" t="inlineStr">
+        <is>
+          <t>14319</t>
+        </is>
+      </c>
+      <c r="BJ240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO240" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT240" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU240" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>11000346879346</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>1769153340</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 13:01:25</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>109044037469</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>GUDLA YAMINI</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>7799277970</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT241" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA241" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB241" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD241" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE241" t="inlineStr">
+        <is>
+          <t>19353</t>
+        </is>
+      </c>
+      <c r="BF241" t="inlineStr">
+        <is>
+          <t>266388</t>
+        </is>
+      </c>
+      <c r="BG241" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH241" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI241" t="inlineStr">
+        <is>
+          <t>14152</t>
+        </is>
+      </c>
+      <c r="BJ241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT241" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU241" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV241" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -70,15 +70,15 @@
     <col min="5" max="5" width="9.96484375" customWidth="true"/>
     <col min="6" max="6" width="8.06640625" customWidth="true"/>
     <col min="7" max="7" width="3.3359375" customWidth="true"/>
-    <col min="8" max="8" width="17.5703125" customWidth="true"/>
+    <col min="8" max="8" width="17.56640625" customWidth="true"/>
     <col min="9" max="9" width="9.01953125" customWidth="true"/>
     <col min="10" max="10" width="3.62890625" customWidth="true"/>
     <col min="11" max="11" width="17.29296875" customWidth="true"/>
-    <col min="12" max="12" width="10.80859375" customWidth="true"/>
+    <col min="12" max="12" width="4.9765625" customWidth="true"/>
     <col min="13" max="13" width="4.9375" customWidth="true"/>
     <col min="14" max="14" width="17.5625" customWidth="true"/>
     <col min="15" max="15" width="11.625" customWidth="true"/>
-    <col min="16" max="16" width="16.5234375" customWidth="true"/>
+    <col min="16" max="16" width="16.51171875" customWidth="true"/>
     <col min="17" max="17" width="11.0390625" customWidth="true"/>
     <col min="18" max="18" width="17.74609375" customWidth="true"/>
     <col min="19" max="19" width="9.18359375" customWidth="true"/>
@@ -88,7 +88,7 @@
     <col min="23" max="23" width="0.76953125" customWidth="true"/>
     <col min="24" max="24" width="33.453125" customWidth="true"/>
     <col min="25" max="25" width="20.16015625" customWidth="true"/>
-    <col min="26" max="26" width="10.41015625" customWidth="true"/>
+    <col min="26" max="26" width="10.50390625" customWidth="true"/>
     <col min="27" max="27" width="0.76953125" customWidth="true"/>
     <col min="28" max="28" width="0.76953125" customWidth="true"/>
     <col min="29" max="29" width="16.04296875" customWidth="true"/>
@@ -123,7 +123,7 @@
     <col min="58" max="58" width="18.29296875" customWidth="true"/>
     <col min="59" max="59" width="13.0234375" customWidth="true"/>
     <col min="60" max="60" width="26.29296875" customWidth="true"/>
-    <col min="61" max="61" width="5.328125" customWidth="true"/>
+    <col min="61" max="61" width="5.27734375" customWidth="true"/>
     <col min="62" max="62" width="0.76953125" customWidth="true"/>
     <col min="63" max="63" width="0.76953125" customWidth="true"/>
     <col min="64" max="64" width="0.76953125" customWidth="true"/>
@@ -89791,6 +89791,4098 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>11000346968551</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>1769224504</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 08:45:20</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>302212189815</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>MUTHABATHULA HANISHA</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>9553420014</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT242" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA242" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB242" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD242" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE242" t="inlineStr">
+        <is>
+          <t>19380</t>
+        </is>
+      </c>
+      <c r="BF242" t="inlineStr">
+        <is>
+          <t>266406</t>
+        </is>
+      </c>
+      <c r="BG242" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH242" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI242" t="inlineStr">
+        <is>
+          <t>16496</t>
+        </is>
+      </c>
+      <c r="BJ242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO242" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT242" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU242" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>11000346968962</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>1769225070</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 08:54:46</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>566245840665</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>VANUMU TRINAYANI SATYA SRI</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>9885123477</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT243" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA243" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB243" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD243" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE243" t="inlineStr">
+        <is>
+          <t>19486</t>
+        </is>
+      </c>
+      <c r="BF243" t="inlineStr">
+        <is>
+          <t>266548</t>
+        </is>
+      </c>
+      <c r="BG243" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH243" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI243" t="inlineStr">
+        <is>
+          <t>16460</t>
+        </is>
+      </c>
+      <c r="BJ243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO243" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT243" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU243" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>11000346977003</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>1769229258</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 10:04:31</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>348778801124</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>MYCHERLA SHASANK</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>7386344393</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT244" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA244" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB244" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD244" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE244" t="inlineStr">
+        <is>
+          <t>19412</t>
+        </is>
+      </c>
+      <c r="BF244" t="inlineStr">
+        <is>
+          <t>266452</t>
+        </is>
+      </c>
+      <c r="BG244" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH244" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI244" t="inlineStr">
+        <is>
+          <t>16208</t>
+        </is>
+      </c>
+      <c r="BJ244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO244" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT244" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU244" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>11000346977375</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>1769229450</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 10:08:32</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>697973343000</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>CHEBOLU ZANETA</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>9030174782</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT245" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA245" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB245" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD245" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE245" t="inlineStr">
+        <is>
+          <t>19356</t>
+        </is>
+      </c>
+      <c r="BF245" t="inlineStr">
+        <is>
+          <t>266367</t>
+        </is>
+      </c>
+      <c r="BG245" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH245" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI245" t="inlineStr">
+        <is>
+          <t>15253</t>
+        </is>
+      </c>
+      <c r="BJ245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO245" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU245" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>11000346985333</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>1769231939</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 10:49:26</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>953155834178</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>THUPAKULA AARON RAJ GANGADHAR</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>9440076171</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT246" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD246" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE246" t="inlineStr">
+        <is>
+          <t>19487</t>
+        </is>
+      </c>
+      <c r="BF246" t="inlineStr">
+        <is>
+          <t>266613</t>
+        </is>
+      </c>
+      <c r="BG246" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH246" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI246" t="inlineStr">
+        <is>
+          <t>16844</t>
+        </is>
+      </c>
+      <c r="BJ246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO246" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT246" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU246" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>11000346988908</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>1769232802</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 11:06:08</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>109049853098</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>TANYA KARNATI</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>9542378388</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT247" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA247" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB247" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD247" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE247" t="inlineStr">
+        <is>
+          <t>18229</t>
+        </is>
+      </c>
+      <c r="BF247" t="inlineStr">
+        <is>
+          <t>266951</t>
+        </is>
+      </c>
+      <c r="BG247" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH247" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI247" t="inlineStr">
+        <is>
+          <t>16955</t>
+        </is>
+      </c>
+      <c r="BJ247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT247" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU247" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>11000346993137</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>1769234416</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 11:30:33</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>432003362670</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>AKULA SIVA SURYA</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>9052828440</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT248" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA248" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB248" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD248" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE248" t="inlineStr">
+        <is>
+          <t>19459</t>
+        </is>
+      </c>
+      <c r="BF248" t="inlineStr">
+        <is>
+          <t>266435</t>
+        </is>
+      </c>
+      <c r="BG248" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH248" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI248" t="inlineStr">
+        <is>
+          <t>14541</t>
+        </is>
+      </c>
+      <c r="BJ248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO248" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU248" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>11000347001524</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>1769237723</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 12:25:49</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>744362088782</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>AFREEN BEGUM</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>8099960677</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT249" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA249" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB249" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD249" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE249" t="inlineStr">
+        <is>
+          <t>19419</t>
+        </is>
+      </c>
+      <c r="BF249" t="inlineStr">
+        <is>
+          <t>266365</t>
+        </is>
+      </c>
+      <c r="BG249" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH249" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI249" t="inlineStr">
+        <is>
+          <t>15952</t>
+        </is>
+      </c>
+      <c r="BJ249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO249" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT249" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU249" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>11000347009711</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>1769240812</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 13:19:28</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>001505087491</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>HEMANTH NAMMI</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>9502806409</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT250" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA250" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB250" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD250" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE250" t="inlineStr">
+        <is>
+          <t>19448</t>
+        </is>
+      </c>
+      <c r="BF250" t="inlineStr">
+        <is>
+          <t>266450</t>
+        </is>
+      </c>
+      <c r="BG250" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH250" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI250" t="inlineStr">
+        <is>
+          <t>14652</t>
+        </is>
+      </c>
+      <c r="BJ250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO250" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU250" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>11000347009869</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>1769240812</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>11350.00</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 13:21:28</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>557427391390</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>HEMANTH NAMMI</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>9502806409</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT251" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD251" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE251" t="inlineStr">
+        <is>
+          <t>19448</t>
+        </is>
+      </c>
+      <c r="BF251" t="inlineStr">
+        <is>
+          <t>266450</t>
+        </is>
+      </c>
+      <c r="BG251" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="BH251" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI251" t="inlineStr">
+        <is>
+          <t>14652</t>
+        </is>
+      </c>
+      <c r="BJ251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO251" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT251" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU251" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>11000347038757</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>1769251908</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>7750.00</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 16:27:44</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>109052062295</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>100000036600</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>GUNIPE NIHARIKA</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>9966262514</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT252" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD252" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE252" t="inlineStr">
+        <is>
+          <t>19893</t>
+        </is>
+      </c>
+      <c r="BF252" t="inlineStr">
+        <is>
+          <t>266835</t>
+        </is>
+      </c>
+      <c r="BG252" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH252" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI252" t="inlineStr">
+        <is>
+          <t>17178</t>
+        </is>
+      </c>
+      <c r="BJ252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU252" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV275"/>
+  <dimension ref="A1:BV289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54693,7 +54693,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N275" t="n">
@@ -54708,7 +54708,11 @@
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R275" t="inlineStr"/>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="S275" t="inlineStr">
         <is>
           <t>MERCHANT</t>
@@ -54737,17 +54741,29 @@
       <c r="AD275" t="inlineStr"/>
       <c r="AE275" t="inlineStr"/>
       <c r="AF275" t="inlineStr"/>
-      <c r="AG275" t="inlineStr"/>
-      <c r="AH275" t="inlineStr"/>
+      <c r="AG275" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI275" t="n">
         <v>0</v>
       </c>
       <c r="AJ275" t="n">
         <v>0</v>
       </c>
-      <c r="AK275" t="inlineStr"/>
-      <c r="AL275" t="inlineStr"/>
-      <c r="AM275" t="inlineStr"/>
+      <c r="AK275" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="AN275" t="inlineStr"/>
       <c r="AO275" t="inlineStr"/>
       <c r="AP275" t="inlineStr"/>
@@ -54784,11 +54800,15 @@
       <c r="BE275" t="n">
         <v>19911</v>
       </c>
-      <c r="BF275" t="n">
-        <v>266720</v>
-      </c>
-      <c r="BG275" t="n">
-        <v>2055</v>
+      <c r="BF275" t="inlineStr">
+        <is>
+          <t>266720</t>
+        </is>
+      </c>
+      <c r="BG275" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
       </c>
       <c r="BH275" t="inlineStr">
         <is>
@@ -54818,6 +54838,2658 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C276" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D276" t="n">
+        <v>11000347614077</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1769621069</v>
+      </c>
+      <c r="F276" t="n">
+        <v>10750</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 22:57:16</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>109080979496</v>
+      </c>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr"/>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr"/>
+      <c r="V276" t="inlineStr"/>
+      <c r="W276" t="inlineStr"/>
+      <c r="X276" t="inlineStr"/>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z276" t="n">
+        <v>6300436983</v>
+      </c>
+      <c r="AA276" t="inlineStr"/>
+      <c r="AB276" t="inlineStr"/>
+      <c r="AC276" t="inlineStr"/>
+      <c r="AD276" t="inlineStr"/>
+      <c r="AE276" t="inlineStr"/>
+      <c r="AF276" t="inlineStr"/>
+      <c r="AG276" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH276" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK276" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL276" t="n">
+        <v>10750</v>
+      </c>
+      <c r="AM276" t="inlineStr"/>
+      <c r="AN276" t="inlineStr"/>
+      <c r="AO276" t="inlineStr"/>
+      <c r="AP276" t="inlineStr"/>
+      <c r="AQ276" t="inlineStr"/>
+      <c r="AR276" t="inlineStr"/>
+      <c r="AS276" t="inlineStr"/>
+      <c r="AT276" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU276" t="inlineStr"/>
+      <c r="AV276" t="inlineStr"/>
+      <c r="AW276" t="inlineStr"/>
+      <c r="AX276" t="inlineStr"/>
+      <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr"/>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr"/>
+      <c r="BD276" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE276" t="n">
+        <v>19264</v>
+      </c>
+      <c r="BF276" t="inlineStr">
+        <is>
+          <t>266312</t>
+        </is>
+      </c>
+      <c r="BG276" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="BH276" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI276" t="n">
+        <v>15025</v>
+      </c>
+      <c r="BJ276" t="inlineStr"/>
+      <c r="BK276" t="inlineStr"/>
+      <c r="BL276" t="inlineStr"/>
+      <c r="BM276" t="inlineStr"/>
+      <c r="BN276" t="inlineStr"/>
+      <c r="BO276" t="inlineStr"/>
+      <c r="BP276" t="inlineStr"/>
+      <c r="BQ276" t="inlineStr"/>
+      <c r="BR276" t="inlineStr"/>
+      <c r="BS276" t="inlineStr"/>
+      <c r="BT276" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU276" t="inlineStr"/>
+      <c r="BV276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C277" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D277" t="n">
+        <v>11000347612953</v>
+      </c>
+      <c r="E277" t="n">
+        <v>1769621384</v>
+      </c>
+      <c r="F277" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 23:00:56</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>109080990486</v>
+      </c>
+      <c r="O277" t="inlineStr"/>
+      <c r="P277" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr"/>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr"/>
+      <c r="V277" t="inlineStr"/>
+      <c r="W277" t="inlineStr"/>
+      <c r="X277" t="inlineStr"/>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z277" t="n">
+        <v>6300436983</v>
+      </c>
+      <c r="AA277" t="inlineStr"/>
+      <c r="AB277" t="inlineStr"/>
+      <c r="AC277" t="inlineStr"/>
+      <c r="AD277" t="inlineStr"/>
+      <c r="AE277" t="inlineStr"/>
+      <c r="AF277" t="inlineStr"/>
+      <c r="AG277" t="inlineStr"/>
+      <c r="AH277" t="inlineStr"/>
+      <c r="AI277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK277" t="inlineStr"/>
+      <c r="AL277" t="inlineStr"/>
+      <c r="AM277" t="inlineStr"/>
+      <c r="AN277" t="inlineStr"/>
+      <c r="AO277" t="inlineStr"/>
+      <c r="AP277" t="inlineStr"/>
+      <c r="AQ277" t="inlineStr"/>
+      <c r="AR277" t="inlineStr"/>
+      <c r="AS277" t="inlineStr"/>
+      <c r="AT277" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU277" t="inlineStr"/>
+      <c r="AV277" t="inlineStr"/>
+      <c r="AW277" t="inlineStr"/>
+      <c r="AX277" t="inlineStr"/>
+      <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr"/>
+      <c r="BA277" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB277" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC277" t="inlineStr"/>
+      <c r="BD277" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE277" t="n">
+        <v>18984</v>
+      </c>
+      <c r="BF277" t="inlineStr">
+        <is>
+          <t>266061</t>
+        </is>
+      </c>
+      <c r="BG277" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH277" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI277" t="n">
+        <v>15237</v>
+      </c>
+      <c r="BJ277" t="inlineStr"/>
+      <c r="BK277" t="inlineStr"/>
+      <c r="BL277" t="inlineStr"/>
+      <c r="BM277" t="inlineStr"/>
+      <c r="BN277" t="inlineStr"/>
+      <c r="BO277" t="inlineStr"/>
+      <c r="BP277" t="inlineStr"/>
+      <c r="BQ277" t="inlineStr"/>
+      <c r="BR277" t="inlineStr"/>
+      <c r="BS277" t="inlineStr"/>
+      <c r="BT277" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU277" t="inlineStr"/>
+      <c r="BV277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C278" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D278" t="n">
+        <v>11000347616224</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1769622527</v>
+      </c>
+      <c r="F278" t="n">
+        <v>22700</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 23:22:02</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr"/>
+      <c r="P278" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr"/>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr"/>
+      <c r="V278" t="inlineStr"/>
+      <c r="W278" t="inlineStr"/>
+      <c r="X278" t="inlineStr"/>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z278" t="n">
+        <v>9494128377</v>
+      </c>
+      <c r="AA278" t="inlineStr"/>
+      <c r="AB278" t="inlineStr"/>
+      <c r="AC278" t="inlineStr"/>
+      <c r="AD278" t="inlineStr"/>
+      <c r="AE278" t="inlineStr"/>
+      <c r="AF278" t="inlineStr"/>
+      <c r="AG278" t="inlineStr"/>
+      <c r="AH278" t="inlineStr"/>
+      <c r="AI278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK278" t="inlineStr"/>
+      <c r="AL278" t="inlineStr"/>
+      <c r="AM278" t="inlineStr"/>
+      <c r="AN278" t="inlineStr"/>
+      <c r="AO278" t="inlineStr"/>
+      <c r="AP278" t="inlineStr"/>
+      <c r="AQ278" t="inlineStr"/>
+      <c r="AR278" t="inlineStr"/>
+      <c r="AS278" t="inlineStr"/>
+      <c r="AT278" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS CANCELLED BY USER</t>
+        </is>
+      </c>
+      <c r="AU278" t="inlineStr"/>
+      <c r="AV278" t="inlineStr"/>
+      <c r="AW278" t="inlineStr"/>
+      <c r="AX278" t="inlineStr"/>
+      <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr"/>
+      <c r="BA278" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB278" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC278" t="inlineStr"/>
+      <c r="BD278" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE278" t="n">
+        <v>19590</v>
+      </c>
+      <c r="BF278" t="inlineStr">
+        <is>
+          <t>264853,266503</t>
+        </is>
+      </c>
+      <c r="BG278" t="inlineStr">
+        <is>
+          <t>2045,2053</t>
+        </is>
+      </c>
+      <c r="BH278" t="inlineStr">
+        <is>
+          <t>twenty two thousand seven hundred</t>
+        </is>
+      </c>
+      <c r="BI278" t="n">
+        <v>14179</v>
+      </c>
+      <c r="BJ278" t="inlineStr"/>
+      <c r="BK278" t="inlineStr"/>
+      <c r="BL278" t="inlineStr"/>
+      <c r="BM278" t="inlineStr"/>
+      <c r="BN278" t="inlineStr"/>
+      <c r="BO278" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP278" t="inlineStr"/>
+      <c r="BQ278" t="inlineStr"/>
+      <c r="BR278" t="inlineStr"/>
+      <c r="BS278" t="inlineStr"/>
+      <c r="BT278" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU278" t="inlineStr"/>
+      <c r="BV278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C279" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D279" t="n">
+        <v>11000347616233</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1769622527</v>
+      </c>
+      <c r="F279" t="n">
+        <v>22700</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 23:22:31</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>232254793834</v>
+      </c>
+      <c r="O279" t="inlineStr"/>
+      <c r="P279" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr"/>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr"/>
+      <c r="V279" t="inlineStr"/>
+      <c r="W279" t="inlineStr"/>
+      <c r="X279" t="inlineStr"/>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr"/>
+      <c r="AA279" t="inlineStr"/>
+      <c r="AB279" t="inlineStr"/>
+      <c r="AC279" t="inlineStr"/>
+      <c r="AD279" t="inlineStr"/>
+      <c r="AE279" t="inlineStr"/>
+      <c r="AF279" t="inlineStr"/>
+      <c r="AG279" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH279" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK279" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL279" t="n">
+        <v>22700</v>
+      </c>
+      <c r="AM279" t="inlineStr"/>
+      <c r="AN279" t="inlineStr"/>
+      <c r="AO279" t="inlineStr"/>
+      <c r="AP279" t="inlineStr"/>
+      <c r="AQ279" t="inlineStr"/>
+      <c r="AR279" t="inlineStr"/>
+      <c r="AS279" t="inlineStr"/>
+      <c r="AT279" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU279" t="inlineStr"/>
+      <c r="AV279" t="inlineStr"/>
+      <c r="AW279" t="inlineStr"/>
+      <c r="AX279" t="inlineStr"/>
+      <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr"/>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr"/>
+      <c r="BD279" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE279" t="n">
+        <v>19590</v>
+      </c>
+      <c r="BF279" t="inlineStr">
+        <is>
+          <t>264853,266503</t>
+        </is>
+      </c>
+      <c r="BG279" t="inlineStr">
+        <is>
+          <t>2045,2053</t>
+        </is>
+      </c>
+      <c r="BH279" t="inlineStr">
+        <is>
+          <t>twenty two thousand seven hundred</t>
+        </is>
+      </c>
+      <c r="BI279" t="n">
+        <v>14179</v>
+      </c>
+      <c r="BJ279" t="inlineStr"/>
+      <c r="BK279" t="inlineStr"/>
+      <c r="BL279" t="inlineStr"/>
+      <c r="BM279" t="inlineStr"/>
+      <c r="BN279" t="inlineStr"/>
+      <c r="BO279" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP279" t="inlineStr"/>
+      <c r="BQ279" t="inlineStr"/>
+      <c r="BR279" t="inlineStr"/>
+      <c r="BS279" t="inlineStr"/>
+      <c r="BT279" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU279" t="inlineStr"/>
+      <c r="BV279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C280" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D280" t="n">
+        <v>11000347619670</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1769632447</v>
+      </c>
+      <c r="F280" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 02:05:03</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>109081256624</v>
+      </c>
+      <c r="O280" t="inlineStr"/>
+      <c r="P280" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr"/>
+      <c r="V280" t="inlineStr"/>
+      <c r="W280" t="inlineStr"/>
+      <c r="X280" t="inlineStr"/>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z280" t="n">
+        <v>9959307771</v>
+      </c>
+      <c r="AA280" t="inlineStr"/>
+      <c r="AB280" t="inlineStr"/>
+      <c r="AC280" t="inlineStr"/>
+      <c r="AD280" t="inlineStr"/>
+      <c r="AE280" t="inlineStr"/>
+      <c r="AF280" t="inlineStr"/>
+      <c r="AG280" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH280" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK280" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL280" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM280" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN280" t="inlineStr"/>
+      <c r="AO280" t="inlineStr"/>
+      <c r="AP280" t="inlineStr"/>
+      <c r="AQ280" t="inlineStr"/>
+      <c r="AR280" t="inlineStr"/>
+      <c r="AS280" t="inlineStr"/>
+      <c r="AT280" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU280" t="inlineStr"/>
+      <c r="AV280" t="inlineStr"/>
+      <c r="AW280" t="inlineStr"/>
+      <c r="AX280" t="inlineStr"/>
+      <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr"/>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr"/>
+      <c r="BD280" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE280" t="n">
+        <v>18863</v>
+      </c>
+      <c r="BF280" t="inlineStr">
+        <is>
+          <t>267586</t>
+        </is>
+      </c>
+      <c r="BG280" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH280" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI280" t="n">
+        <v>15938</v>
+      </c>
+      <c r="BJ280" t="inlineStr"/>
+      <c r="BK280" t="inlineStr"/>
+      <c r="BL280" t="inlineStr"/>
+      <c r="BM280" t="inlineStr"/>
+      <c r="BN280" t="inlineStr"/>
+      <c r="BO280" t="inlineStr"/>
+      <c r="BP280" t="inlineStr"/>
+      <c r="BQ280" t="inlineStr"/>
+      <c r="BR280" t="inlineStr"/>
+      <c r="BS280" t="inlineStr"/>
+      <c r="BT280" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU280" t="inlineStr"/>
+      <c r="BV280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C281" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D281" t="n">
+        <v>11000347624524</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1769653866</v>
+      </c>
+      <c r="F281" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 08:02:15</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>109082072826</v>
+      </c>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr"/>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
+      <c r="W281" t="inlineStr"/>
+      <c r="X281" t="inlineStr"/>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr"/>
+      <c r="AA281" t="inlineStr"/>
+      <c r="AB281" t="inlineStr"/>
+      <c r="AC281" t="inlineStr"/>
+      <c r="AD281" t="inlineStr"/>
+      <c r="AE281" t="inlineStr"/>
+      <c r="AF281" t="inlineStr"/>
+      <c r="AG281" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH281" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK281" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL281" t="n">
+        <v>8650</v>
+      </c>
+      <c r="AM281" t="inlineStr"/>
+      <c r="AN281" t="inlineStr"/>
+      <c r="AO281" t="inlineStr"/>
+      <c r="AP281" t="inlineStr"/>
+      <c r="AQ281" t="inlineStr"/>
+      <c r="AR281" t="inlineStr"/>
+      <c r="AS281" t="inlineStr"/>
+      <c r="AT281" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU281" t="inlineStr"/>
+      <c r="AV281" t="inlineStr"/>
+      <c r="AW281" t="inlineStr"/>
+      <c r="AX281" t="inlineStr"/>
+      <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr"/>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr"/>
+      <c r="BD281" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE281" t="n">
+        <v>18984</v>
+      </c>
+      <c r="BF281" t="inlineStr">
+        <is>
+          <t>266061</t>
+        </is>
+      </c>
+      <c r="BG281" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH281" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI281" t="n">
+        <v>15237</v>
+      </c>
+      <c r="BJ281" t="inlineStr"/>
+      <c r="BK281" t="inlineStr"/>
+      <c r="BL281" t="inlineStr"/>
+      <c r="BM281" t="inlineStr"/>
+      <c r="BN281" t="inlineStr"/>
+      <c r="BO281" t="inlineStr"/>
+      <c r="BP281" t="inlineStr"/>
+      <c r="BQ281" t="inlineStr"/>
+      <c r="BR281" t="inlineStr"/>
+      <c r="BS281" t="inlineStr"/>
+      <c r="BT281" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU281" t="inlineStr"/>
+      <c r="BV281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C282" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D282" t="n">
+        <v>11000347664770</v>
+      </c>
+      <c r="E282" t="n">
+        <v>1769666904</v>
+      </c>
+      <c r="F282" t="n">
+        <v>24650</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 11:39:27</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HDFC Bank </t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr"/>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr"/>
+      <c r="V282" t="inlineStr"/>
+      <c r="W282" t="inlineStr"/>
+      <c r="X282" t="inlineStr"/>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z282" t="n">
+        <v>9573851290</v>
+      </c>
+      <c r="AA282" t="inlineStr"/>
+      <c r="AB282" t="inlineStr"/>
+      <c r="AC282" t="inlineStr"/>
+      <c r="AD282" t="inlineStr"/>
+      <c r="AE282" t="inlineStr"/>
+      <c r="AF282" t="inlineStr"/>
+      <c r="AG282" t="inlineStr"/>
+      <c r="AH282" t="inlineStr"/>
+      <c r="AI282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK282" t="inlineStr"/>
+      <c r="AL282" t="inlineStr"/>
+      <c r="AM282" t="inlineStr"/>
+      <c r="AN282" t="inlineStr"/>
+      <c r="AO282" t="inlineStr"/>
+      <c r="AP282" t="inlineStr"/>
+      <c r="AQ282" t="inlineStr"/>
+      <c r="AR282" t="inlineStr"/>
+      <c r="AS282" t="inlineStr"/>
+      <c r="AT282" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU282" t="inlineStr"/>
+      <c r="AV282" t="inlineStr"/>
+      <c r="AW282" t="inlineStr"/>
+      <c r="AX282" t="inlineStr"/>
+      <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr"/>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr"/>
+      <c r="BD282" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE282" t="n">
+        <v>18502</v>
+      </c>
+      <c r="BF282" t="inlineStr">
+        <is>
+          <t>262506,263894,265544,267194</t>
+        </is>
+      </c>
+      <c r="BG282" t="inlineStr">
+        <is>
+          <t>2037,2041,2049,2057</t>
+        </is>
+      </c>
+      <c r="BH282" t="inlineStr">
+        <is>
+          <t>twenty four thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI282" t="n">
+        <v>16148</v>
+      </c>
+      <c r="BJ282" t="inlineStr"/>
+      <c r="BK282" t="inlineStr"/>
+      <c r="BL282" t="inlineStr"/>
+      <c r="BM282" t="inlineStr"/>
+      <c r="BN282" t="inlineStr"/>
+      <c r="BO282" t="inlineStr"/>
+      <c r="BP282" t="inlineStr"/>
+      <c r="BQ282" t="inlineStr"/>
+      <c r="BR282" t="inlineStr"/>
+      <c r="BS282" t="inlineStr"/>
+      <c r="BT282" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU282" t="inlineStr"/>
+      <c r="BV282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C283" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D283" t="n">
+        <v>11000347665261</v>
+      </c>
+      <c r="E283" t="n">
+        <v>1769667026</v>
+      </c>
+      <c r="F283" t="n">
+        <v>24650</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 11:43:37</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>109083484020</v>
+      </c>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr"/>
+      <c r="V283" t="inlineStr"/>
+      <c r="W283" t="inlineStr"/>
+      <c r="X283" t="inlineStr"/>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z283" t="n">
+        <v>9573851290</v>
+      </c>
+      <c r="AA283" t="inlineStr"/>
+      <c r="AB283" t="inlineStr"/>
+      <c r="AC283" t="inlineStr"/>
+      <c r="AD283" t="inlineStr"/>
+      <c r="AE283" t="inlineStr"/>
+      <c r="AF283" t="inlineStr"/>
+      <c r="AG283" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH283" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK283" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL283" t="n">
+        <v>24650</v>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN283" t="inlineStr"/>
+      <c r="AO283" t="inlineStr"/>
+      <c r="AP283" t="inlineStr"/>
+      <c r="AQ283" t="inlineStr"/>
+      <c r="AR283" t="inlineStr"/>
+      <c r="AS283" t="inlineStr"/>
+      <c r="AT283" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU283" t="inlineStr"/>
+      <c r="AV283" t="inlineStr"/>
+      <c r="AW283" t="inlineStr"/>
+      <c r="AX283" t="inlineStr"/>
+      <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr"/>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr"/>
+      <c r="BD283" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE283" t="n">
+        <v>18502</v>
+      </c>
+      <c r="BF283" t="inlineStr">
+        <is>
+          <t>262506,263894,265544,267194</t>
+        </is>
+      </c>
+      <c r="BG283" t="inlineStr">
+        <is>
+          <t>2037,2041,2049,2057</t>
+        </is>
+      </c>
+      <c r="BH283" t="inlineStr">
+        <is>
+          <t>twenty four thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI283" t="n">
+        <v>16148</v>
+      </c>
+      <c r="BJ283" t="inlineStr"/>
+      <c r="BK283" t="inlineStr"/>
+      <c r="BL283" t="inlineStr"/>
+      <c r="BM283" t="inlineStr"/>
+      <c r="BN283" t="inlineStr"/>
+      <c r="BO283" t="inlineStr"/>
+      <c r="BP283" t="inlineStr"/>
+      <c r="BQ283" t="inlineStr"/>
+      <c r="BR283" t="inlineStr"/>
+      <c r="BS283" t="inlineStr"/>
+      <c r="BT283" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU283" t="inlineStr"/>
+      <c r="BV283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C284" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D284" t="n">
+        <v>11000347667143</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1769667469</v>
+      </c>
+      <c r="F284" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 11:48:21</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>109083513527</v>
+      </c>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr"/>
+      <c r="V284" t="inlineStr"/>
+      <c r="W284" t="inlineStr"/>
+      <c r="X284" t="inlineStr"/>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z284" t="n">
+        <v>9573851290</v>
+      </c>
+      <c r="AA284" t="inlineStr"/>
+      <c r="AB284" t="inlineStr"/>
+      <c r="AC284" t="inlineStr"/>
+      <c r="AD284" t="inlineStr"/>
+      <c r="AE284" t="inlineStr"/>
+      <c r="AF284" t="inlineStr"/>
+      <c r="AG284" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH284" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK284" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL284" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM284" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN284" t="inlineStr"/>
+      <c r="AO284" t="inlineStr"/>
+      <c r="AP284" t="inlineStr"/>
+      <c r="AQ284" t="inlineStr"/>
+      <c r="AR284" t="inlineStr"/>
+      <c r="AS284" t="inlineStr"/>
+      <c r="AT284" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU284" t="inlineStr"/>
+      <c r="AV284" t="inlineStr"/>
+      <c r="AW284" t="inlineStr"/>
+      <c r="AX284" t="inlineStr"/>
+      <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr"/>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr"/>
+      <c r="BD284" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE284" t="n">
+        <v>18767</v>
+      </c>
+      <c r="BF284" t="inlineStr">
+        <is>
+          <t>267440</t>
+        </is>
+      </c>
+      <c r="BG284" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH284" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI284" t="n">
+        <v>16147</v>
+      </c>
+      <c r="BJ284" t="inlineStr"/>
+      <c r="BK284" t="inlineStr"/>
+      <c r="BL284" t="inlineStr"/>
+      <c r="BM284" t="inlineStr"/>
+      <c r="BN284" t="inlineStr"/>
+      <c r="BO284" t="inlineStr"/>
+      <c r="BP284" t="inlineStr"/>
+      <c r="BQ284" t="inlineStr"/>
+      <c r="BR284" t="inlineStr"/>
+      <c r="BS284" t="inlineStr"/>
+      <c r="BT284" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU284" t="inlineStr"/>
+      <c r="BV284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C285" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D285" t="n">
+        <v>11000347735867</v>
+      </c>
+      <c r="E285" t="n">
+        <v>1769693071</v>
+      </c>
+      <c r="F285" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 18:54:47</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>639543409302</v>
+      </c>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr"/>
+      <c r="V285" t="inlineStr"/>
+      <c r="W285" t="inlineStr"/>
+      <c r="X285" t="inlineStr"/>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z285" t="n">
+        <v>8985833952</v>
+      </c>
+      <c r="AA285" t="inlineStr"/>
+      <c r="AB285" t="inlineStr"/>
+      <c r="AC285" t="inlineStr"/>
+      <c r="AD285" t="inlineStr"/>
+      <c r="AE285" t="inlineStr"/>
+      <c r="AF285" t="inlineStr"/>
+      <c r="AG285" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH285" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK285" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL285" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM285" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN285" t="inlineStr"/>
+      <c r="AO285" t="inlineStr"/>
+      <c r="AP285" t="inlineStr"/>
+      <c r="AQ285" t="inlineStr"/>
+      <c r="AR285" t="inlineStr"/>
+      <c r="AS285" t="inlineStr"/>
+      <c r="AT285" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU285" t="inlineStr"/>
+      <c r="AV285" t="inlineStr"/>
+      <c r="AW285" t="inlineStr"/>
+      <c r="AX285" t="inlineStr"/>
+      <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr"/>
+      <c r="BA285" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB285" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC285" t="inlineStr"/>
+      <c r="BD285" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE285" t="n">
+        <v>19924</v>
+      </c>
+      <c r="BF285" t="inlineStr">
+        <is>
+          <t>266780</t>
+        </is>
+      </c>
+      <c r="BG285" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH285" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI285" t="n">
+        <v>17210</v>
+      </c>
+      <c r="BJ285" t="inlineStr"/>
+      <c r="BK285" t="inlineStr"/>
+      <c r="BL285" t="inlineStr"/>
+      <c r="BM285" t="inlineStr"/>
+      <c r="BN285" t="inlineStr"/>
+      <c r="BO285" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP285" t="inlineStr"/>
+      <c r="BQ285" t="inlineStr"/>
+      <c r="BR285" t="inlineStr"/>
+      <c r="BS285" t="inlineStr"/>
+      <c r="BT285" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU285" t="inlineStr"/>
+      <c r="BV285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C286" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D286" t="n">
+        <v>11000347805222</v>
+      </c>
+      <c r="E286" t="n">
+        <v>1769748539</v>
+      </c>
+      <c r="F286" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 10:20:21</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>782823183812</v>
+      </c>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr"/>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr"/>
+      <c r="V286" t="inlineStr"/>
+      <c r="W286" t="inlineStr"/>
+      <c r="X286" t="inlineStr"/>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z286" t="n">
+        <v>8500847900</v>
+      </c>
+      <c r="AA286" t="inlineStr"/>
+      <c r="AB286" t="inlineStr"/>
+      <c r="AC286" t="inlineStr"/>
+      <c r="AD286" t="inlineStr"/>
+      <c r="AE286" t="inlineStr"/>
+      <c r="AF286" t="inlineStr"/>
+      <c r="AG286" t="inlineStr"/>
+      <c r="AH286" t="inlineStr"/>
+      <c r="AI286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK286" t="inlineStr"/>
+      <c r="AL286" t="inlineStr"/>
+      <c r="AM286" t="inlineStr"/>
+      <c r="AN286" t="inlineStr"/>
+      <c r="AO286" t="inlineStr"/>
+      <c r="AP286" t="inlineStr"/>
+      <c r="AQ286" t="inlineStr"/>
+      <c r="AR286" t="inlineStr"/>
+      <c r="AS286" t="inlineStr"/>
+      <c r="AT286" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU286" t="inlineStr"/>
+      <c r="AV286" t="inlineStr"/>
+      <c r="AW286" t="inlineStr"/>
+      <c r="AX286" t="inlineStr"/>
+      <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr"/>
+      <c r="BA286" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB286" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC286" t="inlineStr"/>
+      <c r="BD286" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE286" t="n">
+        <v>20089</v>
+      </c>
+      <c r="BF286" t="inlineStr">
+        <is>
+          <t>268485</t>
+        </is>
+      </c>
+      <c r="BG286" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH286" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI286" t="n">
+        <v>17370</v>
+      </c>
+      <c r="BJ286" t="inlineStr"/>
+      <c r="BK286" t="inlineStr"/>
+      <c r="BL286" t="inlineStr"/>
+      <c r="BM286" t="inlineStr"/>
+      <c r="BN286" t="inlineStr"/>
+      <c r="BO286" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP286" t="inlineStr"/>
+      <c r="BQ286" t="inlineStr"/>
+      <c r="BR286" t="inlineStr"/>
+      <c r="BS286" t="inlineStr"/>
+      <c r="BT286" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU286" t="inlineStr"/>
+      <c r="BV286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C287" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D287" t="n">
+        <v>11000347904277</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1769778846</v>
+      </c>
+      <c r="F287" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 18:44:42</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>109092842968</v>
+      </c>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr"/>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr"/>
+      <c r="V287" t="inlineStr"/>
+      <c r="W287" t="inlineStr"/>
+      <c r="X287" t="inlineStr"/>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z287" t="n">
+        <v>9866667129</v>
+      </c>
+      <c r="AA287" t="inlineStr"/>
+      <c r="AB287" t="inlineStr"/>
+      <c r="AC287" t="inlineStr"/>
+      <c r="AD287" t="inlineStr"/>
+      <c r="AE287" t="inlineStr"/>
+      <c r="AF287" t="inlineStr"/>
+      <c r="AG287" t="inlineStr"/>
+      <c r="AH287" t="inlineStr"/>
+      <c r="AI287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK287" t="inlineStr"/>
+      <c r="AL287" t="inlineStr"/>
+      <c r="AM287" t="inlineStr"/>
+      <c r="AN287" t="inlineStr"/>
+      <c r="AO287" t="inlineStr"/>
+      <c r="AP287" t="inlineStr"/>
+      <c r="AQ287" t="inlineStr"/>
+      <c r="AR287" t="inlineStr"/>
+      <c r="AS287" t="inlineStr"/>
+      <c r="AT287" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU287" t="inlineStr"/>
+      <c r="AV287" t="inlineStr"/>
+      <c r="AW287" t="inlineStr"/>
+      <c r="AX287" t="inlineStr"/>
+      <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr"/>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr"/>
+      <c r="BD287" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE287" t="n">
+        <v>18184</v>
+      </c>
+      <c r="BF287" t="inlineStr">
+        <is>
+          <t>265154</t>
+        </is>
+      </c>
+      <c r="BG287" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH287" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI287" t="n">
+        <v>16710</v>
+      </c>
+      <c r="BJ287" t="inlineStr"/>
+      <c r="BK287" t="inlineStr"/>
+      <c r="BL287" t="inlineStr"/>
+      <c r="BM287" t="inlineStr"/>
+      <c r="BN287" t="inlineStr"/>
+      <c r="BO287" t="inlineStr"/>
+      <c r="BP287" t="inlineStr"/>
+      <c r="BQ287" t="inlineStr"/>
+      <c r="BR287" t="inlineStr"/>
+      <c r="BS287" t="inlineStr"/>
+      <c r="BT287" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU287" t="inlineStr"/>
+      <c r="BV287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C288" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D288" t="n">
+        <v>11000347945459</v>
+      </c>
+      <c r="E288" t="n">
+        <v>1769793554</v>
+      </c>
+      <c r="F288" t="n">
+        <v>10750</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 22:49:30</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>603044734989</v>
+      </c>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr"/>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr"/>
+      <c r="V288" t="inlineStr"/>
+      <c r="W288" t="inlineStr"/>
+      <c r="X288" t="inlineStr"/>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z288" t="n">
+        <v>9701751097</v>
+      </c>
+      <c r="AA288" t="inlineStr"/>
+      <c r="AB288" t="inlineStr"/>
+      <c r="AC288" t="inlineStr"/>
+      <c r="AD288" t="inlineStr"/>
+      <c r="AE288" t="inlineStr"/>
+      <c r="AF288" t="inlineStr"/>
+      <c r="AG288" t="inlineStr"/>
+      <c r="AH288" t="inlineStr"/>
+      <c r="AI288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK288" t="inlineStr"/>
+      <c r="AL288" t="inlineStr"/>
+      <c r="AM288" t="inlineStr"/>
+      <c r="AN288" t="inlineStr"/>
+      <c r="AO288" t="inlineStr"/>
+      <c r="AP288" t="inlineStr"/>
+      <c r="AQ288" t="inlineStr"/>
+      <c r="AR288" t="inlineStr"/>
+      <c r="AS288" t="inlineStr"/>
+      <c r="AT288" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU288" t="inlineStr"/>
+      <c r="AV288" t="inlineStr"/>
+      <c r="AW288" t="inlineStr"/>
+      <c r="AX288" t="inlineStr"/>
+      <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr"/>
+      <c r="BA288" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB288" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC288" t="inlineStr"/>
+      <c r="BD288" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE288" t="n">
+        <v>19153</v>
+      </c>
+      <c r="BF288" t="inlineStr">
+        <is>
+          <t>266251</t>
+        </is>
+      </c>
+      <c r="BG288" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="BH288" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI288" t="n">
+        <v>17061</v>
+      </c>
+      <c r="BJ288" t="inlineStr"/>
+      <c r="BK288" t="inlineStr"/>
+      <c r="BL288" t="inlineStr"/>
+      <c r="BM288" t="inlineStr"/>
+      <c r="BN288" t="inlineStr"/>
+      <c r="BO288" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP288" t="inlineStr"/>
+      <c r="BQ288" t="inlineStr"/>
+      <c r="BR288" t="inlineStr"/>
+      <c r="BS288" t="inlineStr"/>
+      <c r="BT288" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU288" t="inlineStr"/>
+      <c r="BV288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C289" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D289" t="n">
+        <v>11000347957233</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1769821248</v>
+      </c>
+      <c r="F289" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 06:31:28</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>629938220235</v>
+      </c>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr"/>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr"/>
+      <c r="V289" t="inlineStr"/>
+      <c r="W289" t="inlineStr"/>
+      <c r="X289" t="inlineStr"/>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z289" t="n">
+        <v>9866667129</v>
+      </c>
+      <c r="AA289" t="inlineStr"/>
+      <c r="AB289" t="inlineStr"/>
+      <c r="AC289" t="inlineStr"/>
+      <c r="AD289" t="inlineStr"/>
+      <c r="AE289" t="inlineStr"/>
+      <c r="AF289" t="inlineStr"/>
+      <c r="AG289" t="inlineStr"/>
+      <c r="AH289" t="inlineStr"/>
+      <c r="AI289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK289" t="inlineStr"/>
+      <c r="AL289" t="inlineStr"/>
+      <c r="AM289" t="inlineStr"/>
+      <c r="AN289" t="inlineStr"/>
+      <c r="AO289" t="inlineStr"/>
+      <c r="AP289" t="inlineStr"/>
+      <c r="AQ289" t="inlineStr"/>
+      <c r="AR289" t="inlineStr"/>
+      <c r="AS289" t="inlineStr"/>
+      <c r="AT289" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU289" t="inlineStr"/>
+      <c r="AV289" t="inlineStr"/>
+      <c r="AW289" t="inlineStr"/>
+      <c r="AX289" t="inlineStr"/>
+      <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr"/>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr"/>
+      <c r="BD289" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE289" t="n">
+        <v>18184</v>
+      </c>
+      <c r="BF289" t="inlineStr">
+        <is>
+          <t>265154</t>
+        </is>
+      </c>
+      <c r="BG289" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH289" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI289" t="n">
+        <v>16710</v>
+      </c>
+      <c r="BJ289" t="inlineStr"/>
+      <c r="BK289" t="inlineStr"/>
+      <c r="BL289" t="inlineStr"/>
+      <c r="BM289" t="inlineStr"/>
+      <c r="BN289" t="inlineStr"/>
+      <c r="BO289" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP289" t="inlineStr"/>
+      <c r="BQ289" t="inlineStr"/>
+      <c r="BR289" t="inlineStr"/>
+      <c r="BS289" t="inlineStr"/>
+      <c r="BT289" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU289" t="inlineStr"/>
+      <c r="BV289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV289"/>
+  <dimension ref="A1:BV292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56803,7 +56803,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N286" t="n">
@@ -56847,16 +56847,24 @@
       <c r="AD286" t="inlineStr"/>
       <c r="AE286" t="inlineStr"/>
       <c r="AF286" t="inlineStr"/>
-      <c r="AG286" t="inlineStr"/>
-      <c r="AH286" t="inlineStr"/>
+      <c r="AG286" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH286" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI286" t="n">
         <v>0</v>
       </c>
       <c r="AJ286" t="n">
         <v>0</v>
       </c>
-      <c r="AK286" t="inlineStr"/>
-      <c r="AL286" t="inlineStr"/>
+      <c r="AK286" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL286" t="n">
+        <v>8050</v>
+      </c>
       <c r="AM286" t="inlineStr"/>
       <c r="AN286" t="inlineStr"/>
       <c r="AO286" t="inlineStr"/>
@@ -57171,7 +57179,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N288" t="n">
@@ -57215,16 +57223,24 @@
       <c r="AD288" t="inlineStr"/>
       <c r="AE288" t="inlineStr"/>
       <c r="AF288" t="inlineStr"/>
-      <c r="AG288" t="inlineStr"/>
-      <c r="AH288" t="inlineStr"/>
+      <c r="AG288" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH288" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI288" t="n">
         <v>0</v>
       </c>
       <c r="AJ288" t="n">
         <v>0</v>
       </c>
-      <c r="AK288" t="inlineStr"/>
-      <c r="AL288" t="inlineStr"/>
+      <c r="AK288" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL288" t="n">
+        <v>10750</v>
+      </c>
       <c r="AM288" t="inlineStr"/>
       <c r="AN288" t="inlineStr"/>
       <c r="AO288" t="inlineStr"/>
@@ -57490,6 +57506,560 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C290" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D290" t="n">
+        <v>11000347959832</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1769825328</v>
+      </c>
+      <c r="F290" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 07:38:56</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>837422109593</v>
+      </c>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr"/>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr"/>
+      <c r="V290" t="inlineStr"/>
+      <c r="W290" t="inlineStr"/>
+      <c r="X290" t="inlineStr"/>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z290" t="n">
+        <v>9866667129</v>
+      </c>
+      <c r="AA290" t="inlineStr"/>
+      <c r="AB290" t="inlineStr"/>
+      <c r="AC290" t="inlineStr"/>
+      <c r="AD290" t="inlineStr"/>
+      <c r="AE290" t="inlineStr"/>
+      <c r="AF290" t="inlineStr"/>
+      <c r="AG290" t="inlineStr"/>
+      <c r="AH290" t="inlineStr"/>
+      <c r="AI290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK290" t="inlineStr"/>
+      <c r="AL290" t="inlineStr"/>
+      <c r="AM290" t="inlineStr"/>
+      <c r="AN290" t="inlineStr"/>
+      <c r="AO290" t="inlineStr"/>
+      <c r="AP290" t="inlineStr"/>
+      <c r="AQ290" t="inlineStr"/>
+      <c r="AR290" t="inlineStr"/>
+      <c r="AS290" t="inlineStr"/>
+      <c r="AT290" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU290" t="inlineStr"/>
+      <c r="AV290" t="inlineStr"/>
+      <c r="AW290" t="inlineStr"/>
+      <c r="AX290" t="inlineStr"/>
+      <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr"/>
+      <c r="BA290" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB290" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC290" t="inlineStr"/>
+      <c r="BD290" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE290" t="n">
+        <v>18184</v>
+      </c>
+      <c r="BF290" t="inlineStr">
+        <is>
+          <t>265154</t>
+        </is>
+      </c>
+      <c r="BG290" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="BH290" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI290" t="n">
+        <v>16710</v>
+      </c>
+      <c r="BJ290" t="inlineStr"/>
+      <c r="BK290" t="inlineStr"/>
+      <c r="BL290" t="inlineStr"/>
+      <c r="BM290" t="inlineStr"/>
+      <c r="BN290" t="inlineStr"/>
+      <c r="BO290" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP290" t="inlineStr"/>
+      <c r="BQ290" t="inlineStr"/>
+      <c r="BR290" t="inlineStr"/>
+      <c r="BS290" t="inlineStr"/>
+      <c r="BT290" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU290" t="inlineStr"/>
+      <c r="BV290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C291" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D291" t="n">
+        <v>11000347994515</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1769839734</v>
+      </c>
+      <c r="F291" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 11:39:53</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>109096550984</v>
+      </c>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr"/>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr"/>
+      <c r="V291" t="inlineStr"/>
+      <c r="W291" t="inlineStr"/>
+      <c r="X291" t="inlineStr"/>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z291" t="n">
+        <v>7396170082</v>
+      </c>
+      <c r="AA291" t="inlineStr"/>
+      <c r="AB291" t="inlineStr"/>
+      <c r="AC291" t="inlineStr"/>
+      <c r="AD291" t="inlineStr"/>
+      <c r="AE291" t="inlineStr"/>
+      <c r="AF291" t="inlineStr"/>
+      <c r="AG291" t="inlineStr"/>
+      <c r="AH291" t="inlineStr"/>
+      <c r="AI291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK291" t="inlineStr"/>
+      <c r="AL291" t="inlineStr"/>
+      <c r="AM291" t="inlineStr"/>
+      <c r="AN291" t="inlineStr"/>
+      <c r="AO291" t="inlineStr"/>
+      <c r="AP291" t="inlineStr"/>
+      <c r="AQ291" t="inlineStr"/>
+      <c r="AR291" t="inlineStr"/>
+      <c r="AS291" t="inlineStr"/>
+      <c r="AT291" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU291" t="inlineStr"/>
+      <c r="AV291" t="inlineStr"/>
+      <c r="AW291" t="inlineStr"/>
+      <c r="AX291" t="inlineStr"/>
+      <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr"/>
+      <c r="BA291" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB291" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC291" t="inlineStr"/>
+      <c r="BD291" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE291" t="n">
+        <v>18292</v>
+      </c>
+      <c r="BF291" t="inlineStr">
+        <is>
+          <t>267084</t>
+        </is>
+      </c>
+      <c r="BG291" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH291" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI291" t="n">
+        <v>16937</v>
+      </c>
+      <c r="BJ291" t="inlineStr"/>
+      <c r="BK291" t="inlineStr"/>
+      <c r="BL291" t="inlineStr"/>
+      <c r="BM291" t="inlineStr"/>
+      <c r="BN291" t="inlineStr"/>
+      <c r="BO291" t="inlineStr"/>
+      <c r="BP291" t="inlineStr"/>
+      <c r="BQ291" t="inlineStr"/>
+      <c r="BR291" t="inlineStr"/>
+      <c r="BS291" t="inlineStr"/>
+      <c r="BT291" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU291" t="inlineStr"/>
+      <c r="BV291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C292" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D292" t="n">
+        <v>11000348002801</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1769842304</v>
+      </c>
+      <c r="F292" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 12:22:53</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>603137988475</v>
+      </c>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr"/>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr"/>
+      <c r="V292" t="inlineStr"/>
+      <c r="W292" t="inlineStr"/>
+      <c r="X292" t="inlineStr"/>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z292" t="n">
+        <v>9676727222</v>
+      </c>
+      <c r="AA292" t="inlineStr"/>
+      <c r="AB292" t="inlineStr"/>
+      <c r="AC292" t="inlineStr"/>
+      <c r="AD292" t="inlineStr"/>
+      <c r="AE292" t="inlineStr"/>
+      <c r="AF292" t="inlineStr"/>
+      <c r="AG292" t="inlineStr"/>
+      <c r="AH292" t="inlineStr"/>
+      <c r="AI292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK292" t="inlineStr"/>
+      <c r="AL292" t="inlineStr"/>
+      <c r="AM292" t="inlineStr"/>
+      <c r="AN292" t="inlineStr"/>
+      <c r="AO292" t="inlineStr"/>
+      <c r="AP292" t="inlineStr"/>
+      <c r="AQ292" t="inlineStr"/>
+      <c r="AR292" t="inlineStr"/>
+      <c r="AS292" t="inlineStr"/>
+      <c r="AT292" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU292" t="inlineStr"/>
+      <c r="AV292" t="inlineStr"/>
+      <c r="AW292" t="inlineStr"/>
+      <c r="AX292" t="inlineStr"/>
+      <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr"/>
+      <c r="BA292" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB292" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC292" t="inlineStr"/>
+      <c r="BD292" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE292" t="n">
+        <v>20005</v>
+      </c>
+      <c r="BF292" t="inlineStr">
+        <is>
+          <t>266695</t>
+        </is>
+      </c>
+      <c r="BG292" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH292" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI292" t="n">
+        <v>17295</v>
+      </c>
+      <c r="BJ292" t="inlineStr"/>
+      <c r="BK292" t="inlineStr"/>
+      <c r="BL292" t="inlineStr"/>
+      <c r="BM292" t="inlineStr"/>
+      <c r="BN292" t="inlineStr"/>
+      <c r="BO292" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP292" t="inlineStr"/>
+      <c r="BQ292" t="inlineStr"/>
+      <c r="BR292" t="inlineStr"/>
+      <c r="BS292" t="inlineStr"/>
+      <c r="BT292" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU292" t="inlineStr"/>
+      <c r="BV292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV292"/>
+  <dimension ref="A1:BV308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56803,7 +56803,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N286" t="n">
@@ -56818,7 +56818,11 @@
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R286" t="inlineStr"/>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="S286" t="inlineStr">
         <is>
           <t>MERCHANT</t>
@@ -56865,7 +56869,11 @@
       <c r="AL286" t="n">
         <v>8050</v>
       </c>
-      <c r="AM286" t="inlineStr"/>
+      <c r="AM286" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="AN286" t="inlineStr"/>
       <c r="AO286" t="inlineStr"/>
       <c r="AP286" t="inlineStr"/>
@@ -57745,7 +57753,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N291" t="n">
@@ -57760,7 +57768,11 @@
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R291" t="inlineStr"/>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="S291" t="inlineStr">
         <is>
           <t>MERCHANT</t>
@@ -57789,17 +57801,29 @@
       <c r="AD291" t="inlineStr"/>
       <c r="AE291" t="inlineStr"/>
       <c r="AF291" t="inlineStr"/>
-      <c r="AG291" t="inlineStr"/>
-      <c r="AH291" t="inlineStr"/>
+      <c r="AG291" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH291" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI291" t="n">
         <v>0</v>
       </c>
       <c r="AJ291" t="n">
         <v>0</v>
       </c>
-      <c r="AK291" t="inlineStr"/>
-      <c r="AL291" t="inlineStr"/>
-      <c r="AM291" t="inlineStr"/>
+      <c r="AK291" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL291" t="n">
+        <v>7750</v>
+      </c>
+      <c r="AM291" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="AN291" t="inlineStr"/>
       <c r="AO291" t="inlineStr"/>
       <c r="AP291" t="inlineStr"/>
@@ -57927,7 +57951,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N292" t="n">
@@ -57942,7 +57966,11 @@
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R292" t="inlineStr"/>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="S292" t="inlineStr">
         <is>
           <t>MERCHANT</t>
@@ -57971,17 +57999,29 @@
       <c r="AD292" t="inlineStr"/>
       <c r="AE292" t="inlineStr"/>
       <c r="AF292" t="inlineStr"/>
-      <c r="AG292" t="inlineStr"/>
-      <c r="AH292" t="inlineStr"/>
+      <c r="AG292" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH292" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI292" t="n">
         <v>0</v>
       </c>
       <c r="AJ292" t="n">
         <v>0</v>
       </c>
-      <c r="AK292" t="inlineStr"/>
-      <c r="AL292" t="inlineStr"/>
-      <c r="AM292" t="inlineStr"/>
+      <c r="AK292" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL292" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM292" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="AN292" t="inlineStr"/>
       <c r="AO292" t="inlineStr"/>
       <c r="AP292" t="inlineStr"/>
@@ -58060,6 +58100,3112 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C293" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D293" t="n">
+        <v>11000348058030</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1769863383</v>
+      </c>
+      <c r="F293" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 18:13:43</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>109099158804</v>
+      </c>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr"/>
+      <c r="V293" t="inlineStr"/>
+      <c r="W293" t="inlineStr"/>
+      <c r="X293" t="inlineStr"/>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z293" t="n">
+        <v>9582803185</v>
+      </c>
+      <c r="AA293" t="inlineStr"/>
+      <c r="AB293" t="inlineStr"/>
+      <c r="AC293" t="inlineStr"/>
+      <c r="AD293" t="inlineStr"/>
+      <c r="AE293" t="inlineStr"/>
+      <c r="AF293" t="inlineStr"/>
+      <c r="AG293" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH293" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK293" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL293" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM293" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN293" t="inlineStr"/>
+      <c r="AO293" t="inlineStr"/>
+      <c r="AP293" t="inlineStr"/>
+      <c r="AQ293" t="inlineStr"/>
+      <c r="AR293" t="inlineStr"/>
+      <c r="AS293" t="inlineStr"/>
+      <c r="AT293" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU293" t="inlineStr"/>
+      <c r="AV293" t="inlineStr"/>
+      <c r="AW293" t="inlineStr"/>
+      <c r="AX293" t="inlineStr"/>
+      <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr"/>
+      <c r="BA293" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB293" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC293" t="inlineStr"/>
+      <c r="BD293" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE293" t="n">
+        <v>18689</v>
+      </c>
+      <c r="BF293" t="inlineStr">
+        <is>
+          <t>267419</t>
+        </is>
+      </c>
+      <c r="BG293" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH293" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI293" t="n">
+        <v>16975</v>
+      </c>
+      <c r="BJ293" t="inlineStr"/>
+      <c r="BK293" t="inlineStr"/>
+      <c r="BL293" t="inlineStr"/>
+      <c r="BM293" t="inlineStr"/>
+      <c r="BN293" t="inlineStr"/>
+      <c r="BO293" t="inlineStr"/>
+      <c r="BP293" t="inlineStr"/>
+      <c r="BQ293" t="inlineStr"/>
+      <c r="BR293" t="inlineStr"/>
+      <c r="BS293" t="inlineStr"/>
+      <c r="BT293" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU293" t="inlineStr"/>
+      <c r="BV293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C294" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D294" t="n">
+        <v>11000348058210</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1769863602</v>
+      </c>
+      <c r="F294" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 18:17:11</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>109099182132</v>
+      </c>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr"/>
+      <c r="V294" t="inlineStr"/>
+      <c r="W294" t="inlineStr"/>
+      <c r="X294" t="inlineStr"/>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z294" t="n">
+        <v>9582803185</v>
+      </c>
+      <c r="AA294" t="inlineStr"/>
+      <c r="AB294" t="inlineStr"/>
+      <c r="AC294" t="inlineStr"/>
+      <c r="AD294" t="inlineStr"/>
+      <c r="AE294" t="inlineStr"/>
+      <c r="AF294" t="inlineStr"/>
+      <c r="AG294" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH294" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK294" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL294" t="n">
+        <v>8050</v>
+      </c>
+      <c r="AM294" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN294" t="inlineStr"/>
+      <c r="AO294" t="inlineStr"/>
+      <c r="AP294" t="inlineStr"/>
+      <c r="AQ294" t="inlineStr"/>
+      <c r="AR294" t="inlineStr"/>
+      <c r="AS294" t="inlineStr"/>
+      <c r="AT294" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU294" t="inlineStr"/>
+      <c r="AV294" t="inlineStr"/>
+      <c r="AW294" t="inlineStr"/>
+      <c r="AX294" t="inlineStr"/>
+      <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr"/>
+      <c r="BA294" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB294" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC294" t="inlineStr"/>
+      <c r="BD294" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE294" t="n">
+        <v>19917</v>
+      </c>
+      <c r="BF294" t="inlineStr">
+        <is>
+          <t>267156</t>
+        </is>
+      </c>
+      <c r="BG294" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH294" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI294" t="n">
+        <v>17203</v>
+      </c>
+      <c r="BJ294" t="inlineStr"/>
+      <c r="BK294" t="inlineStr"/>
+      <c r="BL294" t="inlineStr"/>
+      <c r="BM294" t="inlineStr"/>
+      <c r="BN294" t="inlineStr"/>
+      <c r="BO294" t="inlineStr"/>
+      <c r="BP294" t="inlineStr"/>
+      <c r="BQ294" t="inlineStr"/>
+      <c r="BR294" t="inlineStr"/>
+      <c r="BS294" t="inlineStr"/>
+      <c r="BT294" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU294" t="inlineStr"/>
+      <c r="BV294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D295" t="n">
+        <v>11000348075456</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1769873832</v>
+      </c>
+      <c r="F295" t="n">
+        <v>17200</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 21:10:07</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>211520585120</v>
+      </c>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr"/>
+      <c r="V295" t="inlineStr"/>
+      <c r="W295" t="inlineStr"/>
+      <c r="X295" t="inlineStr"/>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z295" t="n">
+        <v>9494128377</v>
+      </c>
+      <c r="AA295" t="inlineStr"/>
+      <c r="AB295" t="inlineStr"/>
+      <c r="AC295" t="inlineStr"/>
+      <c r="AD295" t="inlineStr"/>
+      <c r="AE295" t="inlineStr"/>
+      <c r="AF295" t="inlineStr"/>
+      <c r="AG295" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH295" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK295" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL295" t="n">
+        <v>17200</v>
+      </c>
+      <c r="AM295" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN295" t="inlineStr"/>
+      <c r="AO295" t="inlineStr"/>
+      <c r="AP295" t="inlineStr"/>
+      <c r="AQ295" t="inlineStr"/>
+      <c r="AR295" t="inlineStr"/>
+      <c r="AS295" t="inlineStr"/>
+      <c r="AT295" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU295" t="inlineStr"/>
+      <c r="AV295" t="inlineStr"/>
+      <c r="AW295" t="inlineStr"/>
+      <c r="AX295" t="inlineStr"/>
+      <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr"/>
+      <c r="BA295" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB295" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC295" t="inlineStr"/>
+      <c r="BD295" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE295" t="n">
+        <v>18708</v>
+      </c>
+      <c r="BF295" t="inlineStr">
+        <is>
+          <t>262434,264169,265819</t>
+        </is>
+      </c>
+      <c r="BG295" t="inlineStr">
+        <is>
+          <t>2037,2042,2050</t>
+        </is>
+      </c>
+      <c r="BH295" t="inlineStr">
+        <is>
+          <t>seventeen thousand two hundred</t>
+        </is>
+      </c>
+      <c r="BI295" t="n">
+        <v>15610</v>
+      </c>
+      <c r="BJ295" t="inlineStr"/>
+      <c r="BK295" t="inlineStr"/>
+      <c r="BL295" t="inlineStr"/>
+      <c r="BM295" t="inlineStr"/>
+      <c r="BN295" t="inlineStr"/>
+      <c r="BO295" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP295" t="inlineStr"/>
+      <c r="BQ295" t="inlineStr"/>
+      <c r="BR295" t="inlineStr"/>
+      <c r="BS295" t="inlineStr"/>
+      <c r="BT295" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU295" t="inlineStr"/>
+      <c r="BV295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C296" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D296" t="n">
+        <v>11000348084444</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1769878103</v>
+      </c>
+      <c r="F296" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 22:18:47</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>261849315319</v>
+      </c>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr"/>
+      <c r="V296" t="inlineStr"/>
+      <c r="W296" t="inlineStr"/>
+      <c r="X296" t="inlineStr"/>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z296" t="n">
+        <v>9959734686</v>
+      </c>
+      <c r="AA296" t="inlineStr"/>
+      <c r="AB296" t="inlineStr"/>
+      <c r="AC296" t="inlineStr"/>
+      <c r="AD296" t="inlineStr"/>
+      <c r="AE296" t="inlineStr"/>
+      <c r="AF296" t="inlineStr"/>
+      <c r="AG296" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH296" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK296" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL296" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM296" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN296" t="inlineStr"/>
+      <c r="AO296" t="inlineStr"/>
+      <c r="AP296" t="inlineStr"/>
+      <c r="AQ296" t="inlineStr"/>
+      <c r="AR296" t="inlineStr"/>
+      <c r="AS296" t="inlineStr"/>
+      <c r="AT296" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU296" t="inlineStr"/>
+      <c r="AV296" t="inlineStr"/>
+      <c r="AW296" t="inlineStr"/>
+      <c r="AX296" t="inlineStr"/>
+      <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr"/>
+      <c r="BA296" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB296" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC296" t="inlineStr"/>
+      <c r="BD296" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE296" t="n">
+        <v>20008</v>
+      </c>
+      <c r="BF296" t="inlineStr">
+        <is>
+          <t>263349</t>
+        </is>
+      </c>
+      <c r="BG296" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="BH296" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI296" t="n">
+        <v>17299</v>
+      </c>
+      <c r="BJ296" t="inlineStr"/>
+      <c r="BK296" t="inlineStr"/>
+      <c r="BL296" t="inlineStr"/>
+      <c r="BM296" t="inlineStr"/>
+      <c r="BN296" t="inlineStr"/>
+      <c r="BO296" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP296" t="inlineStr"/>
+      <c r="BQ296" t="inlineStr"/>
+      <c r="BR296" t="inlineStr"/>
+      <c r="BS296" t="inlineStr"/>
+      <c r="BT296" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU296" t="inlineStr"/>
+      <c r="BV296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C297" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D297" t="n">
+        <v>11000348259685</v>
+      </c>
+      <c r="E297" t="n">
+        <v>1770007167</v>
+      </c>
+      <c r="F297" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 10:10:12</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N297" t="n">
+        <v>109110162417</v>
+      </c>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr"/>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr"/>
+      <c r="V297" t="inlineStr"/>
+      <c r="W297" t="inlineStr"/>
+      <c r="X297" t="inlineStr"/>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z297" t="n">
+        <v>6300436983</v>
+      </c>
+      <c r="AA297" t="inlineStr"/>
+      <c r="AB297" t="inlineStr"/>
+      <c r="AC297" t="inlineStr"/>
+      <c r="AD297" t="inlineStr"/>
+      <c r="AE297" t="inlineStr"/>
+      <c r="AF297" t="inlineStr"/>
+      <c r="AG297" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH297" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK297" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL297" t="n">
+        <v>8650</v>
+      </c>
+      <c r="AM297" t="inlineStr"/>
+      <c r="AN297" t="inlineStr"/>
+      <c r="AO297" t="inlineStr"/>
+      <c r="AP297" t="inlineStr"/>
+      <c r="AQ297" t="inlineStr"/>
+      <c r="AR297" t="inlineStr"/>
+      <c r="AS297" t="inlineStr"/>
+      <c r="AT297" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU297" t="inlineStr"/>
+      <c r="AV297" t="inlineStr"/>
+      <c r="AW297" t="inlineStr"/>
+      <c r="AX297" t="inlineStr"/>
+      <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr"/>
+      <c r="BA297" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB297" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC297" t="inlineStr"/>
+      <c r="BD297" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE297" t="n">
+        <v>18984</v>
+      </c>
+      <c r="BF297" t="inlineStr">
+        <is>
+          <t>268309</t>
+        </is>
+      </c>
+      <c r="BG297" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="BH297" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI297" t="n">
+        <v>15237</v>
+      </c>
+      <c r="BJ297" t="inlineStr"/>
+      <c r="BK297" t="inlineStr"/>
+      <c r="BL297" t="inlineStr"/>
+      <c r="BM297" t="inlineStr"/>
+      <c r="BN297" t="inlineStr"/>
+      <c r="BO297" t="inlineStr"/>
+      <c r="BP297" t="inlineStr"/>
+      <c r="BQ297" t="inlineStr"/>
+      <c r="BR297" t="inlineStr"/>
+      <c r="BS297" t="inlineStr"/>
+      <c r="BT297" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU297" t="inlineStr"/>
+      <c r="BV297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C298" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D298" t="n">
+        <v>11000348259812</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1770007283</v>
+      </c>
+      <c r="F298" t="n">
+        <v>10750</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 10:11:47</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N298" t="n">
+        <v>109110173919</v>
+      </c>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr"/>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr"/>
+      <c r="V298" t="inlineStr"/>
+      <c r="W298" t="inlineStr"/>
+      <c r="X298" t="inlineStr"/>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z298" t="n">
+        <v>6300436983</v>
+      </c>
+      <c r="AA298" t="inlineStr"/>
+      <c r="AB298" t="inlineStr"/>
+      <c r="AC298" t="inlineStr"/>
+      <c r="AD298" t="inlineStr"/>
+      <c r="AE298" t="inlineStr"/>
+      <c r="AF298" t="inlineStr"/>
+      <c r="AG298" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH298" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK298" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL298" t="n">
+        <v>10750</v>
+      </c>
+      <c r="AM298" t="inlineStr"/>
+      <c r="AN298" t="inlineStr"/>
+      <c r="AO298" t="inlineStr"/>
+      <c r="AP298" t="inlineStr"/>
+      <c r="AQ298" t="inlineStr"/>
+      <c r="AR298" t="inlineStr"/>
+      <c r="AS298" t="inlineStr"/>
+      <c r="AT298" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU298" t="inlineStr"/>
+      <c r="AV298" t="inlineStr"/>
+      <c r="AW298" t="inlineStr"/>
+      <c r="AX298" t="inlineStr"/>
+      <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr"/>
+      <c r="BA298" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB298" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC298" t="inlineStr"/>
+      <c r="BD298" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE298" t="n">
+        <v>19264</v>
+      </c>
+      <c r="BF298" t="inlineStr">
+        <is>
+          <t>268649</t>
+        </is>
+      </c>
+      <c r="BG298" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="BH298" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI298" t="n">
+        <v>15025</v>
+      </c>
+      <c r="BJ298" t="inlineStr"/>
+      <c r="BK298" t="inlineStr"/>
+      <c r="BL298" t="inlineStr"/>
+      <c r="BM298" t="inlineStr"/>
+      <c r="BN298" t="inlineStr"/>
+      <c r="BO298" t="inlineStr"/>
+      <c r="BP298" t="inlineStr"/>
+      <c r="BQ298" t="inlineStr"/>
+      <c r="BR298" t="inlineStr"/>
+      <c r="BS298" t="inlineStr"/>
+      <c r="BT298" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU298" t="inlineStr"/>
+      <c r="BV298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C299" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D299" t="n">
+        <v>11000348263733</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1770007955</v>
+      </c>
+      <c r="F299" t="n">
+        <v>16100</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 10:24:11</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N299" t="n">
+        <v>109110252989</v>
+      </c>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr"/>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr"/>
+      <c r="V299" t="inlineStr"/>
+      <c r="W299" t="inlineStr"/>
+      <c r="X299" t="inlineStr"/>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z299" t="n">
+        <v>8919560551</v>
+      </c>
+      <c r="AA299" t="inlineStr"/>
+      <c r="AB299" t="inlineStr"/>
+      <c r="AC299" t="inlineStr"/>
+      <c r="AD299" t="inlineStr"/>
+      <c r="AE299" t="inlineStr"/>
+      <c r="AF299" t="inlineStr"/>
+      <c r="AG299" t="inlineStr"/>
+      <c r="AH299" t="inlineStr"/>
+      <c r="AI299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK299" t="inlineStr"/>
+      <c r="AL299" t="inlineStr"/>
+      <c r="AM299" t="inlineStr"/>
+      <c r="AN299" t="inlineStr"/>
+      <c r="AO299" t="inlineStr"/>
+      <c r="AP299" t="inlineStr"/>
+      <c r="AQ299" t="inlineStr"/>
+      <c r="AR299" t="inlineStr"/>
+      <c r="AS299" t="inlineStr"/>
+      <c r="AT299" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU299" t="inlineStr"/>
+      <c r="AV299" t="inlineStr"/>
+      <c r="AW299" t="inlineStr"/>
+      <c r="AX299" t="inlineStr"/>
+      <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr"/>
+      <c r="BA299" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB299" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC299" t="inlineStr"/>
+      <c r="BD299" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE299" t="n">
+        <v>18526</v>
+      </c>
+      <c r="BF299" t="inlineStr">
+        <is>
+          <t>265609,267259</t>
+        </is>
+      </c>
+      <c r="BG299" t="inlineStr">
+        <is>
+          <t>2049,2057</t>
+        </is>
+      </c>
+      <c r="BH299" t="inlineStr">
+        <is>
+          <t>sixteen thousand one hundred</t>
+        </is>
+      </c>
+      <c r="BI299" t="n">
+        <v>16983</v>
+      </c>
+      <c r="BJ299" t="inlineStr"/>
+      <c r="BK299" t="inlineStr"/>
+      <c r="BL299" t="inlineStr"/>
+      <c r="BM299" t="inlineStr"/>
+      <c r="BN299" t="inlineStr"/>
+      <c r="BO299" t="inlineStr"/>
+      <c r="BP299" t="inlineStr"/>
+      <c r="BQ299" t="inlineStr"/>
+      <c r="BR299" t="inlineStr"/>
+      <c r="BS299" t="inlineStr"/>
+      <c r="BT299" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU299" t="inlineStr"/>
+      <c r="BV299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C300" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D300" t="n">
+        <v>11000348272865</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1770010319</v>
+      </c>
+      <c r="F300" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 11:03:20</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N300" t="n">
+        <v>109110496570</v>
+      </c>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr"/>
+      <c r="V300" t="inlineStr"/>
+      <c r="W300" t="inlineStr"/>
+      <c r="X300" t="inlineStr"/>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z300" t="n">
+        <v>6301729629</v>
+      </c>
+      <c r="AA300" t="inlineStr"/>
+      <c r="AB300" t="inlineStr"/>
+      <c r="AC300" t="inlineStr"/>
+      <c r="AD300" t="inlineStr"/>
+      <c r="AE300" t="inlineStr"/>
+      <c r="AF300" t="inlineStr"/>
+      <c r="AG300" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH300" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK300" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL300" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM300" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN300" t="inlineStr"/>
+      <c r="AO300" t="inlineStr"/>
+      <c r="AP300" t="inlineStr"/>
+      <c r="AQ300" t="inlineStr"/>
+      <c r="AR300" t="inlineStr"/>
+      <c r="AS300" t="inlineStr"/>
+      <c r="AT300" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU300" t="inlineStr"/>
+      <c r="AV300" t="inlineStr"/>
+      <c r="AW300" t="inlineStr"/>
+      <c r="AX300" t="inlineStr"/>
+      <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr"/>
+      <c r="BA300" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB300" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC300" t="inlineStr"/>
+      <c r="BD300" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE300" t="n">
+        <v>18038</v>
+      </c>
+      <c r="BF300" t="inlineStr">
+        <is>
+          <t>265086</t>
+        </is>
+      </c>
+      <c r="BG300" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="BH300" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI300" t="n">
+        <v>17103</v>
+      </c>
+      <c r="BJ300" t="inlineStr"/>
+      <c r="BK300" t="inlineStr"/>
+      <c r="BL300" t="inlineStr"/>
+      <c r="BM300" t="inlineStr"/>
+      <c r="BN300" t="inlineStr"/>
+      <c r="BO300" t="inlineStr"/>
+      <c r="BP300" t="inlineStr"/>
+      <c r="BQ300" t="inlineStr"/>
+      <c r="BR300" t="inlineStr"/>
+      <c r="BS300" t="inlineStr"/>
+      <c r="BT300" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU300" t="inlineStr"/>
+      <c r="BV300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C301" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D301" t="n">
+        <v>11000348296762</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1770015969</v>
+      </c>
+      <c r="F301" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 12:37:32</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N301" t="n">
+        <v>603396699255</v>
+      </c>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr"/>
+      <c r="V301" t="inlineStr"/>
+      <c r="W301" t="inlineStr"/>
+      <c r="X301" t="inlineStr"/>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z301" t="n">
+        <v>9030736744</v>
+      </c>
+      <c r="AA301" t="inlineStr"/>
+      <c r="AB301" t="inlineStr"/>
+      <c r="AC301" t="inlineStr"/>
+      <c r="AD301" t="inlineStr"/>
+      <c r="AE301" t="inlineStr"/>
+      <c r="AF301" t="inlineStr"/>
+      <c r="AG301" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH301" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK301" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL301" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM301" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN301" t="inlineStr"/>
+      <c r="AO301" t="inlineStr"/>
+      <c r="AP301" t="inlineStr"/>
+      <c r="AQ301" t="inlineStr"/>
+      <c r="AR301" t="inlineStr"/>
+      <c r="AS301" t="inlineStr"/>
+      <c r="AT301" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU301" t="inlineStr"/>
+      <c r="AV301" t="inlineStr"/>
+      <c r="AW301" t="inlineStr"/>
+      <c r="AX301" t="inlineStr"/>
+      <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr"/>
+      <c r="BA301" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB301" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC301" t="inlineStr"/>
+      <c r="BD301" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE301" t="n">
+        <v>19989</v>
+      </c>
+      <c r="BF301" t="inlineStr">
+        <is>
+          <t>266791</t>
+        </is>
+      </c>
+      <c r="BG301" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH301" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI301" t="n">
+        <v>17278</v>
+      </c>
+      <c r="BJ301" t="inlineStr"/>
+      <c r="BK301" t="inlineStr"/>
+      <c r="BL301" t="inlineStr"/>
+      <c r="BM301" t="inlineStr"/>
+      <c r="BN301" t="inlineStr"/>
+      <c r="BO301" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP301" t="inlineStr"/>
+      <c r="BQ301" t="inlineStr"/>
+      <c r="BR301" t="inlineStr"/>
+      <c r="BS301" t="inlineStr"/>
+      <c r="BT301" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU301" t="inlineStr"/>
+      <c r="BV301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C302" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D302" t="n">
+        <v>11000348300433</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1770016889</v>
+      </c>
+      <c r="F302" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 12:51:55</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N302" t="n">
+        <v>109111170783</v>
+      </c>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
+      <c r="W302" t="inlineStr"/>
+      <c r="X302" t="inlineStr"/>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z302" t="n">
+        <v>8919560551</v>
+      </c>
+      <c r="AA302" t="inlineStr"/>
+      <c r="AB302" t="inlineStr"/>
+      <c r="AC302" t="inlineStr"/>
+      <c r="AD302" t="inlineStr"/>
+      <c r="AE302" t="inlineStr"/>
+      <c r="AF302" t="inlineStr"/>
+      <c r="AG302" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH302" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK302" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL302" t="n">
+        <v>8050</v>
+      </c>
+      <c r="AM302" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN302" t="inlineStr"/>
+      <c r="AO302" t="inlineStr"/>
+      <c r="AP302" t="inlineStr"/>
+      <c r="AQ302" t="inlineStr"/>
+      <c r="AR302" t="inlineStr"/>
+      <c r="AS302" t="inlineStr"/>
+      <c r="AT302" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU302" t="inlineStr"/>
+      <c r="AV302" t="inlineStr"/>
+      <c r="AW302" t="inlineStr"/>
+      <c r="AX302" t="inlineStr"/>
+      <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr"/>
+      <c r="BA302" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB302" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC302" t="inlineStr"/>
+      <c r="BD302" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE302" t="n">
+        <v>18526</v>
+      </c>
+      <c r="BF302" t="inlineStr">
+        <is>
+          <t>265609</t>
+        </is>
+      </c>
+      <c r="BG302" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="BH302" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI302" t="n">
+        <v>16983</v>
+      </c>
+      <c r="BJ302" t="inlineStr"/>
+      <c r="BK302" t="inlineStr"/>
+      <c r="BL302" t="inlineStr"/>
+      <c r="BM302" t="inlineStr"/>
+      <c r="BN302" t="inlineStr"/>
+      <c r="BO302" t="inlineStr"/>
+      <c r="BP302" t="inlineStr"/>
+      <c r="BQ302" t="inlineStr"/>
+      <c r="BR302" t="inlineStr"/>
+      <c r="BS302" t="inlineStr"/>
+      <c r="BT302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU302" t="inlineStr"/>
+      <c r="BV302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D303" t="n">
+        <v>11000348327211</v>
+      </c>
+      <c r="E303" t="n">
+        <v>1770024680</v>
+      </c>
+      <c r="F303" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 15:01:40</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N303" t="n">
+        <v>109112112619</v>
+      </c>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr"/>
+      <c r="V303" t="inlineStr"/>
+      <c r="W303" t="inlineStr"/>
+      <c r="X303" t="inlineStr"/>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z303" t="n">
+        <v>8919560551</v>
+      </c>
+      <c r="AA303" t="inlineStr"/>
+      <c r="AB303" t="inlineStr"/>
+      <c r="AC303" t="inlineStr"/>
+      <c r="AD303" t="inlineStr"/>
+      <c r="AE303" t="inlineStr"/>
+      <c r="AF303" t="inlineStr"/>
+      <c r="AG303" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH303" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK303" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL303" t="n">
+        <v>8050</v>
+      </c>
+      <c r="AM303" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN303" t="inlineStr"/>
+      <c r="AO303" t="inlineStr"/>
+      <c r="AP303" t="inlineStr"/>
+      <c r="AQ303" t="inlineStr"/>
+      <c r="AR303" t="inlineStr"/>
+      <c r="AS303" t="inlineStr"/>
+      <c r="AT303" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU303" t="inlineStr"/>
+      <c r="AV303" t="inlineStr"/>
+      <c r="AW303" t="inlineStr"/>
+      <c r="AX303" t="inlineStr"/>
+      <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr"/>
+      <c r="BA303" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB303" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC303" t="inlineStr"/>
+      <c r="BD303" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE303" t="n">
+        <v>18526</v>
+      </c>
+      <c r="BF303" t="inlineStr">
+        <is>
+          <t>267259</t>
+        </is>
+      </c>
+      <c r="BG303" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH303" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI303" t="n">
+        <v>16983</v>
+      </c>
+      <c r="BJ303" t="inlineStr"/>
+      <c r="BK303" t="inlineStr"/>
+      <c r="BL303" t="inlineStr"/>
+      <c r="BM303" t="inlineStr"/>
+      <c r="BN303" t="inlineStr"/>
+      <c r="BO303" t="inlineStr"/>
+      <c r="BP303" t="inlineStr"/>
+      <c r="BQ303" t="inlineStr"/>
+      <c r="BR303" t="inlineStr"/>
+      <c r="BS303" t="inlineStr"/>
+      <c r="BT303" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU303" t="inlineStr"/>
+      <c r="BV303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C304" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D304" t="n">
+        <v>11000348327327</v>
+      </c>
+      <c r="E304" t="n">
+        <v>1770024758</v>
+      </c>
+      <c r="F304" t="n">
+        <v>15500</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 15:03:03</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N304" t="n">
+        <v>109112123447</v>
+      </c>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr"/>
+      <c r="V304" t="inlineStr"/>
+      <c r="W304" t="inlineStr"/>
+      <c r="X304" t="inlineStr"/>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z304" t="n">
+        <v>8919560551</v>
+      </c>
+      <c r="AA304" t="inlineStr"/>
+      <c r="AB304" t="inlineStr"/>
+      <c r="AC304" t="inlineStr"/>
+      <c r="AD304" t="inlineStr"/>
+      <c r="AE304" t="inlineStr"/>
+      <c r="AF304" t="inlineStr"/>
+      <c r="AG304" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH304" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK304" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>15500</v>
+      </c>
+      <c r="AM304" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN304" t="inlineStr"/>
+      <c r="AO304" t="inlineStr"/>
+      <c r="AP304" t="inlineStr"/>
+      <c r="AQ304" t="inlineStr"/>
+      <c r="AR304" t="inlineStr"/>
+      <c r="AS304" t="inlineStr"/>
+      <c r="AT304" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU304" t="inlineStr"/>
+      <c r="AV304" t="inlineStr"/>
+      <c r="AW304" t="inlineStr"/>
+      <c r="AX304" t="inlineStr"/>
+      <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr"/>
+      <c r="BA304" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB304" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC304" t="inlineStr"/>
+      <c r="BD304" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE304" t="n">
+        <v>18142</v>
+      </c>
+      <c r="BF304" t="inlineStr">
+        <is>
+          <t>265260,266910</t>
+        </is>
+      </c>
+      <c r="BG304" t="inlineStr">
+        <is>
+          <t>2048,2056</t>
+        </is>
+      </c>
+      <c r="BH304" t="inlineStr">
+        <is>
+          <t>fifteen thousand five hundred</t>
+        </is>
+      </c>
+      <c r="BI304" t="n">
+        <v>16981</v>
+      </c>
+      <c r="BJ304" t="inlineStr"/>
+      <c r="BK304" t="inlineStr"/>
+      <c r="BL304" t="inlineStr"/>
+      <c r="BM304" t="inlineStr"/>
+      <c r="BN304" t="inlineStr"/>
+      <c r="BO304" t="inlineStr"/>
+      <c r="BP304" t="inlineStr"/>
+      <c r="BQ304" t="inlineStr"/>
+      <c r="BR304" t="inlineStr"/>
+      <c r="BS304" t="inlineStr"/>
+      <c r="BT304" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU304" t="inlineStr"/>
+      <c r="BV304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D305" t="n">
+        <v>11000348365273</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1770038166</v>
+      </c>
+      <c r="F305" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 18:47:03</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N305" t="n">
+        <v>109113635360</v>
+      </c>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr"/>
+      <c r="V305" t="inlineStr"/>
+      <c r="W305" t="inlineStr"/>
+      <c r="X305" t="inlineStr"/>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z305" t="n">
+        <v>9177919989</v>
+      </c>
+      <c r="AA305" t="inlineStr"/>
+      <c r="AB305" t="inlineStr"/>
+      <c r="AC305" t="inlineStr"/>
+      <c r="AD305" t="inlineStr"/>
+      <c r="AE305" t="inlineStr"/>
+      <c r="AF305" t="inlineStr"/>
+      <c r="AG305" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH305" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK305" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL305" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM305" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN305" t="inlineStr"/>
+      <c r="AO305" t="inlineStr"/>
+      <c r="AP305" t="inlineStr"/>
+      <c r="AQ305" t="inlineStr"/>
+      <c r="AR305" t="inlineStr"/>
+      <c r="AS305" t="inlineStr"/>
+      <c r="AT305" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU305" t="inlineStr"/>
+      <c r="AV305" t="inlineStr"/>
+      <c r="AW305" t="inlineStr"/>
+      <c r="AX305" t="inlineStr"/>
+      <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr"/>
+      <c r="BA305" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB305" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC305" t="inlineStr"/>
+      <c r="BD305" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE305" t="n">
+        <v>18940</v>
+      </c>
+      <c r="BF305" t="inlineStr">
+        <is>
+          <t>267616</t>
+        </is>
+      </c>
+      <c r="BG305" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH305" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI305" t="n">
+        <v>16046</v>
+      </c>
+      <c r="BJ305" t="inlineStr"/>
+      <c r="BK305" t="inlineStr"/>
+      <c r="BL305" t="inlineStr"/>
+      <c r="BM305" t="inlineStr"/>
+      <c r="BN305" t="inlineStr"/>
+      <c r="BO305" t="inlineStr"/>
+      <c r="BP305" t="inlineStr"/>
+      <c r="BQ305" t="inlineStr"/>
+      <c r="BR305" t="inlineStr"/>
+      <c r="BS305" t="inlineStr"/>
+      <c r="BT305" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU305" t="inlineStr"/>
+      <c r="BV305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C306" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D306" t="n">
+        <v>11000348393006</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1770049673</v>
+      </c>
+      <c r="F306" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 21:58:11</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr"/>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr"/>
+      <c r="V306" t="inlineStr"/>
+      <c r="W306" t="inlineStr"/>
+      <c r="X306" t="inlineStr"/>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z306" t="n">
+        <v>8801427880</v>
+      </c>
+      <c r="AA306" t="inlineStr"/>
+      <c r="AB306" t="inlineStr"/>
+      <c r="AC306" t="inlineStr"/>
+      <c r="AD306" t="inlineStr"/>
+      <c r="AE306" t="inlineStr"/>
+      <c r="AF306" t="inlineStr"/>
+      <c r="AG306" t="inlineStr"/>
+      <c r="AH306" t="inlineStr"/>
+      <c r="AI306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK306" t="inlineStr"/>
+      <c r="AL306" t="inlineStr"/>
+      <c r="AM306" t="inlineStr"/>
+      <c r="AN306" t="inlineStr"/>
+      <c r="AO306" t="inlineStr"/>
+      <c r="AP306" t="inlineStr"/>
+      <c r="AQ306" t="inlineStr"/>
+      <c r="AR306" t="inlineStr"/>
+      <c r="AS306" t="inlineStr"/>
+      <c r="AT306" t="inlineStr">
+        <is>
+          <t>BQR TRANSACTION IS TIMED OUT</t>
+        </is>
+      </c>
+      <c r="AU306" t="inlineStr"/>
+      <c r="AV306" t="inlineStr"/>
+      <c r="AW306" t="inlineStr"/>
+      <c r="AX306" t="inlineStr"/>
+      <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr"/>
+      <c r="BA306" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB306" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC306" t="inlineStr"/>
+      <c r="BD306" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE306" t="n">
+        <v>18443</v>
+      </c>
+      <c r="BF306" t="inlineStr">
+        <is>
+          <t>267167</t>
+        </is>
+      </c>
+      <c r="BG306" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH306" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI306" t="n">
+        <v>16308</v>
+      </c>
+      <c r="BJ306" t="inlineStr"/>
+      <c r="BK306" t="inlineStr"/>
+      <c r="BL306" t="inlineStr"/>
+      <c r="BM306" t="inlineStr"/>
+      <c r="BN306" t="inlineStr"/>
+      <c r="BO306" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP306" t="inlineStr"/>
+      <c r="BQ306" t="inlineStr"/>
+      <c r="BR306" t="inlineStr"/>
+      <c r="BS306" t="inlineStr"/>
+      <c r="BT306" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU306" t="inlineStr"/>
+      <c r="BV306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C307" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D307" t="n">
+        <v>11000348471340</v>
+      </c>
+      <c r="E307" t="n">
+        <v>1770101732</v>
+      </c>
+      <c r="F307" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 12:28:23</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N307" t="n">
+        <v>109118392390</v>
+      </c>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr"/>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr"/>
+      <c r="V307" t="inlineStr"/>
+      <c r="W307" t="inlineStr"/>
+      <c r="X307" t="inlineStr"/>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z307" t="n">
+        <v>9989075944</v>
+      </c>
+      <c r="AA307" t="inlineStr"/>
+      <c r="AB307" t="inlineStr"/>
+      <c r="AC307" t="inlineStr"/>
+      <c r="AD307" t="inlineStr"/>
+      <c r="AE307" t="inlineStr"/>
+      <c r="AF307" t="inlineStr"/>
+      <c r="AG307" t="inlineStr"/>
+      <c r="AH307" t="inlineStr"/>
+      <c r="AI307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK307" t="inlineStr"/>
+      <c r="AL307" t="inlineStr"/>
+      <c r="AM307" t="inlineStr"/>
+      <c r="AN307" t="inlineStr"/>
+      <c r="AO307" t="inlineStr"/>
+      <c r="AP307" t="inlineStr"/>
+      <c r="AQ307" t="inlineStr"/>
+      <c r="AR307" t="inlineStr"/>
+      <c r="AS307" t="inlineStr"/>
+      <c r="AT307" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU307" t="inlineStr"/>
+      <c r="AV307" t="inlineStr"/>
+      <c r="AW307" t="inlineStr"/>
+      <c r="AX307" t="inlineStr"/>
+      <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr"/>
+      <c r="BA307" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB307" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC307" t="inlineStr"/>
+      <c r="BD307" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE307" t="n">
+        <v>19852</v>
+      </c>
+      <c r="BF307" t="inlineStr">
+        <is>
+          <t>266040</t>
+        </is>
+      </c>
+      <c r="BG307" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH307" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI307" t="n">
+        <v>17149</v>
+      </c>
+      <c r="BJ307" t="inlineStr"/>
+      <c r="BK307" t="inlineStr"/>
+      <c r="BL307" t="inlineStr"/>
+      <c r="BM307" t="inlineStr"/>
+      <c r="BN307" t="inlineStr"/>
+      <c r="BO307" t="inlineStr"/>
+      <c r="BP307" t="inlineStr"/>
+      <c r="BQ307" t="inlineStr"/>
+      <c r="BR307" t="inlineStr"/>
+      <c r="BS307" t="inlineStr"/>
+      <c r="BT307" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU307" t="inlineStr"/>
+      <c r="BV307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C308" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D308" t="n">
+        <v>11000348551835</v>
+      </c>
+      <c r="E308" t="n">
+        <v>1770132067</v>
+      </c>
+      <c r="F308" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 20:53:32</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N308" t="n">
+        <v>337099556372</v>
+      </c>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr"/>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr"/>
+      <c r="V308" t="inlineStr"/>
+      <c r="W308" t="inlineStr"/>
+      <c r="X308" t="inlineStr"/>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z308" t="n">
+        <v>7207505036</v>
+      </c>
+      <c r="AA308" t="inlineStr"/>
+      <c r="AB308" t="inlineStr"/>
+      <c r="AC308" t="inlineStr"/>
+      <c r="AD308" t="inlineStr"/>
+      <c r="AE308" t="inlineStr"/>
+      <c r="AF308" t="inlineStr"/>
+      <c r="AG308" t="inlineStr"/>
+      <c r="AH308" t="inlineStr"/>
+      <c r="AI308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK308" t="inlineStr"/>
+      <c r="AL308" t="inlineStr"/>
+      <c r="AM308" t="inlineStr"/>
+      <c r="AN308" t="inlineStr"/>
+      <c r="AO308" t="inlineStr"/>
+      <c r="AP308" t="inlineStr"/>
+      <c r="AQ308" t="inlineStr"/>
+      <c r="AR308" t="inlineStr"/>
+      <c r="AS308" t="inlineStr"/>
+      <c r="AT308" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU308" t="inlineStr"/>
+      <c r="AV308" t="inlineStr"/>
+      <c r="AW308" t="inlineStr"/>
+      <c r="AX308" t="inlineStr"/>
+      <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr"/>
+      <c r="BA308" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB308" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC308" t="inlineStr"/>
+      <c r="BD308" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE308" t="n">
+        <v>18360</v>
+      </c>
+      <c r="BF308" t="inlineStr">
+        <is>
+          <t>267018</t>
+        </is>
+      </c>
+      <c r="BG308" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH308" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI308" t="n">
+        <v>16992</v>
+      </c>
+      <c r="BJ308" t="inlineStr"/>
+      <c r="BK308" t="inlineStr"/>
+      <c r="BL308" t="inlineStr"/>
+      <c r="BM308" t="inlineStr"/>
+      <c r="BN308" t="inlineStr"/>
+      <c r="BO308" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP308" t="inlineStr"/>
+      <c r="BQ308" t="inlineStr"/>
+      <c r="BR308" t="inlineStr"/>
+      <c r="BS308" t="inlineStr"/>
+      <c r="BT308" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU308" t="inlineStr"/>
+      <c r="BV308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV308"/>
+  <dimension ref="A1:BV312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60891,7 +60891,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N307" t="n">
@@ -60935,16 +60935,24 @@
       <c r="AD307" t="inlineStr"/>
       <c r="AE307" t="inlineStr"/>
       <c r="AF307" t="inlineStr"/>
-      <c r="AG307" t="inlineStr"/>
-      <c r="AH307" t="inlineStr"/>
+      <c r="AG307" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH307" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI307" t="n">
         <v>0</v>
       </c>
       <c r="AJ307" t="n">
         <v>0</v>
       </c>
-      <c r="AK307" t="inlineStr"/>
-      <c r="AL307" t="inlineStr"/>
+      <c r="AK307" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>8650</v>
+      </c>
       <c r="AM307" t="inlineStr"/>
       <c r="AN307" t="inlineStr"/>
       <c r="AO307" t="inlineStr"/>
@@ -61073,7 +61081,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N308" t="n">
@@ -61088,7 +61096,11 @@
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R308" t="inlineStr"/>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="S308" t="inlineStr">
         <is>
           <t>MERCHANT</t>
@@ -61117,17 +61129,29 @@
       <c r="AD308" t="inlineStr"/>
       <c r="AE308" t="inlineStr"/>
       <c r="AF308" t="inlineStr"/>
-      <c r="AG308" t="inlineStr"/>
-      <c r="AH308" t="inlineStr"/>
+      <c r="AG308" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH308" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI308" t="n">
         <v>0</v>
       </c>
       <c r="AJ308" t="n">
         <v>0</v>
       </c>
-      <c r="AK308" t="inlineStr"/>
-      <c r="AL308" t="inlineStr"/>
-      <c r="AM308" t="inlineStr"/>
+      <c r="AK308" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL308" t="n">
+        <v>7750</v>
+      </c>
+      <c r="AM308" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="AN308" t="inlineStr"/>
       <c r="AO308" t="inlineStr"/>
       <c r="AP308" t="inlineStr"/>
@@ -61206,6 +61230,742 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C309" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D309" t="n">
+        <v>11000348575099</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1770168829</v>
+      </c>
+      <c r="F309" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 07:05:09</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N309" t="n">
+        <v>109123051045</v>
+      </c>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr"/>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr"/>
+      <c r="V309" t="inlineStr"/>
+      <c r="W309" t="inlineStr"/>
+      <c r="X309" t="inlineStr"/>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z309" t="n">
+        <v>9991367333</v>
+      </c>
+      <c r="AA309" t="inlineStr"/>
+      <c r="AB309" t="inlineStr"/>
+      <c r="AC309" t="inlineStr"/>
+      <c r="AD309" t="inlineStr"/>
+      <c r="AE309" t="inlineStr"/>
+      <c r="AF309" t="inlineStr"/>
+      <c r="AG309" t="inlineStr"/>
+      <c r="AH309" t="inlineStr"/>
+      <c r="AI309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK309" t="inlineStr"/>
+      <c r="AL309" t="inlineStr"/>
+      <c r="AM309" t="inlineStr"/>
+      <c r="AN309" t="inlineStr"/>
+      <c r="AO309" t="inlineStr"/>
+      <c r="AP309" t="inlineStr"/>
+      <c r="AQ309" t="inlineStr"/>
+      <c r="AR309" t="inlineStr"/>
+      <c r="AS309" t="inlineStr"/>
+      <c r="AT309" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU309" t="inlineStr"/>
+      <c r="AV309" t="inlineStr"/>
+      <c r="AW309" t="inlineStr"/>
+      <c r="AX309" t="inlineStr"/>
+      <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr"/>
+      <c r="BA309" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB309" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC309" t="inlineStr"/>
+      <c r="BD309" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE309" t="n">
+        <v>20016</v>
+      </c>
+      <c r="BF309" t="inlineStr">
+        <is>
+          <t>267480</t>
+        </is>
+      </c>
+      <c r="BG309" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH309" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI309" t="n">
+        <v>17307</v>
+      </c>
+      <c r="BJ309" t="inlineStr"/>
+      <c r="BK309" t="inlineStr"/>
+      <c r="BL309" t="inlineStr"/>
+      <c r="BM309" t="inlineStr"/>
+      <c r="BN309" t="inlineStr"/>
+      <c r="BO309" t="inlineStr"/>
+      <c r="BP309" t="inlineStr"/>
+      <c r="BQ309" t="inlineStr"/>
+      <c r="BR309" t="inlineStr"/>
+      <c r="BS309" t="inlineStr"/>
+      <c r="BT309" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU309" t="inlineStr"/>
+      <c r="BV309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C310" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D310" t="n">
+        <v>11000348596178</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1770179127</v>
+      </c>
+      <c r="F310" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 09:56:04</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N310" t="n">
+        <v>496896024593</v>
+      </c>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr"/>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr"/>
+      <c r="V310" t="inlineStr"/>
+      <c r="W310" t="inlineStr"/>
+      <c r="X310" t="inlineStr"/>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z310" t="n">
+        <v>8885883431</v>
+      </c>
+      <c r="AA310" t="inlineStr"/>
+      <c r="AB310" t="inlineStr"/>
+      <c r="AC310" t="inlineStr"/>
+      <c r="AD310" t="inlineStr"/>
+      <c r="AE310" t="inlineStr"/>
+      <c r="AF310" t="inlineStr"/>
+      <c r="AG310" t="inlineStr"/>
+      <c r="AH310" t="inlineStr"/>
+      <c r="AI310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK310" t="inlineStr"/>
+      <c r="AL310" t="inlineStr"/>
+      <c r="AM310" t="inlineStr"/>
+      <c r="AN310" t="inlineStr"/>
+      <c r="AO310" t="inlineStr"/>
+      <c r="AP310" t="inlineStr"/>
+      <c r="AQ310" t="inlineStr"/>
+      <c r="AR310" t="inlineStr"/>
+      <c r="AS310" t="inlineStr"/>
+      <c r="AT310" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU310" t="inlineStr"/>
+      <c r="AV310" t="inlineStr"/>
+      <c r="AW310" t="inlineStr"/>
+      <c r="AX310" t="inlineStr"/>
+      <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr"/>
+      <c r="BA310" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB310" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC310" t="inlineStr"/>
+      <c r="BD310" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE310" t="n">
+        <v>18960</v>
+      </c>
+      <c r="BF310" t="inlineStr">
+        <is>
+          <t>267577</t>
+        </is>
+      </c>
+      <c r="BG310" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH310" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI310" t="n">
+        <v>17069</v>
+      </c>
+      <c r="BJ310" t="inlineStr"/>
+      <c r="BK310" t="inlineStr"/>
+      <c r="BL310" t="inlineStr"/>
+      <c r="BM310" t="inlineStr"/>
+      <c r="BN310" t="inlineStr"/>
+      <c r="BO310" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP310" t="inlineStr"/>
+      <c r="BQ310" t="inlineStr"/>
+      <c r="BR310" t="inlineStr"/>
+      <c r="BS310" t="inlineStr"/>
+      <c r="BT310" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU310" t="inlineStr"/>
+      <c r="BV310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C311" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D311" t="n">
+        <v>11000348597736</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1770179690</v>
+      </c>
+      <c r="F311" t="n">
+        <v>11350</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 10:05:07</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N311" t="n">
+        <v>230527479236</v>
+      </c>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr"/>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr"/>
+      <c r="V311" t="inlineStr"/>
+      <c r="W311" t="inlineStr"/>
+      <c r="X311" t="inlineStr"/>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z311" t="n">
+        <v>7893025312</v>
+      </c>
+      <c r="AA311" t="inlineStr"/>
+      <c r="AB311" t="inlineStr"/>
+      <c r="AC311" t="inlineStr"/>
+      <c r="AD311" t="inlineStr"/>
+      <c r="AE311" t="inlineStr"/>
+      <c r="AF311" t="inlineStr"/>
+      <c r="AG311" t="inlineStr"/>
+      <c r="AH311" t="inlineStr"/>
+      <c r="AI311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK311" t="inlineStr"/>
+      <c r="AL311" t="inlineStr"/>
+      <c r="AM311" t="inlineStr"/>
+      <c r="AN311" t="inlineStr"/>
+      <c r="AO311" t="inlineStr"/>
+      <c r="AP311" t="inlineStr"/>
+      <c r="AQ311" t="inlineStr"/>
+      <c r="AR311" t="inlineStr"/>
+      <c r="AS311" t="inlineStr"/>
+      <c r="AT311" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU311" t="inlineStr"/>
+      <c r="AV311" t="inlineStr"/>
+      <c r="AW311" t="inlineStr"/>
+      <c r="AX311" t="inlineStr"/>
+      <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr"/>
+      <c r="BA311" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB311" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC311" t="inlineStr"/>
+      <c r="BD311" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE311" t="n">
+        <v>19462</v>
+      </c>
+      <c r="BF311" t="inlineStr">
+        <is>
+          <t>268164</t>
+        </is>
+      </c>
+      <c r="BG311" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="BH311" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI311" t="n">
+        <v>15728</v>
+      </c>
+      <c r="BJ311" t="inlineStr"/>
+      <c r="BK311" t="inlineStr"/>
+      <c r="BL311" t="inlineStr"/>
+      <c r="BM311" t="inlineStr"/>
+      <c r="BN311" t="inlineStr"/>
+      <c r="BO311" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP311" t="inlineStr"/>
+      <c r="BQ311" t="inlineStr"/>
+      <c r="BR311" t="inlineStr"/>
+      <c r="BS311" t="inlineStr"/>
+      <c r="BT311" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU311" t="inlineStr"/>
+      <c r="BV311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C312" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D312" t="n">
+        <v>11000348724700</v>
+      </c>
+      <c r="E312" t="n">
+        <v>1770226187</v>
+      </c>
+      <c r="F312" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 23:05:27</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N312" t="n">
+        <v>109128651847</v>
+      </c>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr"/>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr"/>
+      <c r="V312" t="inlineStr"/>
+      <c r="W312" t="inlineStr"/>
+      <c r="X312" t="inlineStr"/>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z312" t="n">
+        <v>9849969449</v>
+      </c>
+      <c r="AA312" t="inlineStr"/>
+      <c r="AB312" t="inlineStr"/>
+      <c r="AC312" t="inlineStr"/>
+      <c r="AD312" t="inlineStr"/>
+      <c r="AE312" t="inlineStr"/>
+      <c r="AF312" t="inlineStr"/>
+      <c r="AG312" t="inlineStr"/>
+      <c r="AH312" t="inlineStr"/>
+      <c r="AI312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK312" t="inlineStr"/>
+      <c r="AL312" t="inlineStr"/>
+      <c r="AM312" t="inlineStr"/>
+      <c r="AN312" t="inlineStr"/>
+      <c r="AO312" t="inlineStr"/>
+      <c r="AP312" t="inlineStr"/>
+      <c r="AQ312" t="inlineStr"/>
+      <c r="AR312" t="inlineStr"/>
+      <c r="AS312" t="inlineStr"/>
+      <c r="AT312" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU312" t="inlineStr"/>
+      <c r="AV312" t="inlineStr"/>
+      <c r="AW312" t="inlineStr"/>
+      <c r="AX312" t="inlineStr"/>
+      <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr"/>
+      <c r="BA312" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB312" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC312" t="inlineStr"/>
+      <c r="BD312" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE312" t="n">
+        <v>18766</v>
+      </c>
+      <c r="BF312" t="inlineStr">
+        <is>
+          <t>265813</t>
+        </is>
+      </c>
+      <c r="BG312" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH312" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI312" t="n">
+        <v>15541</v>
+      </c>
+      <c r="BJ312" t="inlineStr"/>
+      <c r="BK312" t="inlineStr"/>
+      <c r="BL312" t="inlineStr"/>
+      <c r="BM312" t="inlineStr"/>
+      <c r="BN312" t="inlineStr"/>
+      <c r="BO312" t="inlineStr"/>
+      <c r="BP312" t="inlineStr"/>
+      <c r="BQ312" t="inlineStr"/>
+      <c r="BR312" t="inlineStr"/>
+      <c r="BS312" t="inlineStr"/>
+      <c r="BT312" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU312" t="inlineStr"/>
+      <c r="BV312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -61283,7 +61283,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N309" t="n">
@@ -61298,7 +61298,11 @@
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R309" t="inlineStr"/>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>05-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="S309" t="inlineStr">
         <is>
           <t>MERCHANT</t>
@@ -61327,17 +61331,29 @@
       <c r="AD309" t="inlineStr"/>
       <c r="AE309" t="inlineStr"/>
       <c r="AF309" t="inlineStr"/>
-      <c r="AG309" t="inlineStr"/>
-      <c r="AH309" t="inlineStr"/>
+      <c r="AG309" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH309" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI309" t="n">
         <v>0</v>
       </c>
       <c r="AJ309" t="n">
         <v>0</v>
       </c>
-      <c r="AK309" t="inlineStr"/>
-      <c r="AL309" t="inlineStr"/>
-      <c r="AM309" t="inlineStr"/>
+      <c r="AK309" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL309" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM309" t="inlineStr">
+        <is>
+          <t>05-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="AN309" t="inlineStr"/>
       <c r="AO309" t="inlineStr"/>
       <c r="AP309" t="inlineStr"/>
@@ -61465,7 +61481,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N310" t="n">
@@ -61480,7 +61496,11 @@
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R310" t="inlineStr"/>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>05-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="S310" t="inlineStr">
         <is>
           <t>MERCHANT</t>
@@ -61509,17 +61529,29 @@
       <c r="AD310" t="inlineStr"/>
       <c r="AE310" t="inlineStr"/>
       <c r="AF310" t="inlineStr"/>
-      <c r="AG310" t="inlineStr"/>
-      <c r="AH310" t="inlineStr"/>
+      <c r="AG310" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH310" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI310" t="n">
         <v>0</v>
       </c>
       <c r="AJ310" t="n">
         <v>0</v>
       </c>
-      <c r="AK310" t="inlineStr"/>
-      <c r="AL310" t="inlineStr"/>
-      <c r="AM310" t="inlineStr"/>
+      <c r="AK310" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL310" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM310" t="inlineStr">
+        <is>
+          <t>05-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="AN310" t="inlineStr"/>
       <c r="AO310" t="inlineStr"/>
       <c r="AP310" t="inlineStr"/>
@@ -61651,7 +61683,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N311" t="n">
@@ -61695,16 +61727,24 @@
       <c r="AD311" t="inlineStr"/>
       <c r="AE311" t="inlineStr"/>
       <c r="AF311" t="inlineStr"/>
-      <c r="AG311" t="inlineStr"/>
-      <c r="AH311" t="inlineStr"/>
+      <c r="AG311" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH311" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI311" t="n">
         <v>0</v>
       </c>
       <c r="AJ311" t="n">
         <v>0</v>
       </c>
-      <c r="AK311" t="inlineStr"/>
-      <c r="AL311" t="inlineStr"/>
+      <c r="AK311" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL311" t="n">
+        <v>11350</v>
+      </c>
       <c r="AM311" t="inlineStr"/>
       <c r="AN311" t="inlineStr"/>
       <c r="AO311" t="inlineStr"/>
@@ -61837,7 +61877,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N312" t="n">
@@ -61852,7 +61892,11 @@
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R312" t="inlineStr"/>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>05-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="S312" t="inlineStr">
         <is>
           <t>MERCHANT</t>
@@ -61881,17 +61925,29 @@
       <c r="AD312" t="inlineStr"/>
       <c r="AE312" t="inlineStr"/>
       <c r="AF312" t="inlineStr"/>
-      <c r="AG312" t="inlineStr"/>
-      <c r="AH312" t="inlineStr"/>
+      <c r="AG312" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH312" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI312" t="n">
         <v>0</v>
       </c>
       <c r="AJ312" t="n">
         <v>0</v>
       </c>
-      <c r="AK312" t="inlineStr"/>
-      <c r="AL312" t="inlineStr"/>
-      <c r="AM312" t="inlineStr"/>
+      <c r="AK312" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL312" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM312" t="inlineStr">
+        <is>
+          <t>05-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="AN312" t="inlineStr"/>
       <c r="AO312" t="inlineStr"/>
       <c r="AP312" t="inlineStr"/>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV312"/>
+  <dimension ref="A1:BV317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62022,6 +62022,942 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C313" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D313" t="n">
+        <v>11000348990079</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1770372650</v>
+      </c>
+      <c r="F313" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>06-Feb-2026 15:42:50</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N313" t="n">
+        <v>696631043153</v>
+      </c>
+      <c r="O313" t="inlineStr"/>
+      <c r="P313" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>07-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr"/>
+      <c r="V313" t="inlineStr"/>
+      <c r="W313" t="inlineStr"/>
+      <c r="X313" t="inlineStr"/>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z313" t="n">
+        <v>9542502425</v>
+      </c>
+      <c r="AA313" t="inlineStr"/>
+      <c r="AB313" t="inlineStr"/>
+      <c r="AC313" t="inlineStr"/>
+      <c r="AD313" t="inlineStr"/>
+      <c r="AE313" t="inlineStr"/>
+      <c r="AF313" t="inlineStr"/>
+      <c r="AG313" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH313" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK313" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL313" t="n">
+        <v>8050</v>
+      </c>
+      <c r="AM313" t="inlineStr">
+        <is>
+          <t>07-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN313" t="inlineStr"/>
+      <c r="AO313" t="inlineStr"/>
+      <c r="AP313" t="inlineStr"/>
+      <c r="AQ313" t="inlineStr"/>
+      <c r="AR313" t="inlineStr"/>
+      <c r="AS313" t="inlineStr"/>
+      <c r="AT313" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU313" t="inlineStr"/>
+      <c r="AV313" t="inlineStr"/>
+      <c r="AW313" t="inlineStr"/>
+      <c r="AX313" t="inlineStr"/>
+      <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr"/>
+      <c r="BA313" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB313" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC313" t="inlineStr"/>
+      <c r="BD313" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE313" t="n">
+        <v>18422</v>
+      </c>
+      <c r="BF313" t="inlineStr">
+        <is>
+          <t>267145</t>
+        </is>
+      </c>
+      <c r="BG313" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH313" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI313" t="n">
+        <v>16400</v>
+      </c>
+      <c r="BJ313" t="inlineStr"/>
+      <c r="BK313" t="inlineStr"/>
+      <c r="BL313" t="inlineStr"/>
+      <c r="BM313" t="inlineStr"/>
+      <c r="BN313" t="inlineStr"/>
+      <c r="BO313" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP313" t="inlineStr"/>
+      <c r="BQ313" t="inlineStr"/>
+      <c r="BR313" t="inlineStr"/>
+      <c r="BS313" t="inlineStr"/>
+      <c r="BT313" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU313" t="inlineStr"/>
+      <c r="BV313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C314" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D314" t="n">
+        <v>11000349086368</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1770445075</v>
+      </c>
+      <c r="F314" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>07-Feb-2026 11:49:02</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N314" t="n">
+        <v>109145651654</v>
+      </c>
+      <c r="O314" t="inlineStr"/>
+      <c r="P314" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr"/>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr"/>
+      <c r="V314" t="inlineStr"/>
+      <c r="W314" t="inlineStr"/>
+      <c r="X314" t="inlineStr"/>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z314" t="n">
+        <v>9505890135</v>
+      </c>
+      <c r="AA314" t="inlineStr"/>
+      <c r="AB314" t="inlineStr"/>
+      <c r="AC314" t="inlineStr"/>
+      <c r="AD314" t="inlineStr"/>
+      <c r="AE314" t="inlineStr"/>
+      <c r="AF314" t="inlineStr"/>
+      <c r="AG314" t="inlineStr"/>
+      <c r="AH314" t="inlineStr"/>
+      <c r="AI314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK314" t="inlineStr"/>
+      <c r="AL314" t="inlineStr"/>
+      <c r="AM314" t="inlineStr"/>
+      <c r="AN314" t="inlineStr"/>
+      <c r="AO314" t="inlineStr"/>
+      <c r="AP314" t="inlineStr"/>
+      <c r="AQ314" t="inlineStr"/>
+      <c r="AR314" t="inlineStr"/>
+      <c r="AS314" t="inlineStr"/>
+      <c r="AT314" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU314" t="inlineStr"/>
+      <c r="AV314" t="inlineStr"/>
+      <c r="AW314" t="inlineStr"/>
+      <c r="AX314" t="inlineStr"/>
+      <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr"/>
+      <c r="BA314" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB314" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC314" t="inlineStr"/>
+      <c r="BD314" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE314" t="n">
+        <v>18805</v>
+      </c>
+      <c r="BF314" t="inlineStr">
+        <is>
+          <t>267429</t>
+        </is>
+      </c>
+      <c r="BG314" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH314" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI314" t="n">
+        <v>15762</v>
+      </c>
+      <c r="BJ314" t="inlineStr"/>
+      <c r="BK314" t="inlineStr"/>
+      <c r="BL314" t="inlineStr"/>
+      <c r="BM314" t="inlineStr"/>
+      <c r="BN314" t="inlineStr"/>
+      <c r="BO314" t="inlineStr"/>
+      <c r="BP314" t="inlineStr"/>
+      <c r="BQ314" t="inlineStr"/>
+      <c r="BR314" t="inlineStr"/>
+      <c r="BS314" t="inlineStr"/>
+      <c r="BT314" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU314" t="inlineStr"/>
+      <c r="BV314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C315" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D315" t="n">
+        <v>11000349179233</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1770528801</v>
+      </c>
+      <c r="F315" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>08-Feb-2026 11:04:35</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HDFC Bank </t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr"/>
+      <c r="P315" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr"/>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr"/>
+      <c r="V315" t="inlineStr"/>
+      <c r="W315" t="inlineStr"/>
+      <c r="X315" t="inlineStr"/>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z315" t="n">
+        <v>6305761566</v>
+      </c>
+      <c r="AA315" t="inlineStr"/>
+      <c r="AB315" t="inlineStr"/>
+      <c r="AC315" t="inlineStr"/>
+      <c r="AD315" t="inlineStr"/>
+      <c r="AE315" t="inlineStr"/>
+      <c r="AF315" t="inlineStr"/>
+      <c r="AG315" t="inlineStr"/>
+      <c r="AH315" t="inlineStr"/>
+      <c r="AI315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK315" t="inlineStr"/>
+      <c r="AL315" t="inlineStr"/>
+      <c r="AM315" t="inlineStr"/>
+      <c r="AN315" t="inlineStr"/>
+      <c r="AO315" t="inlineStr"/>
+      <c r="AP315" t="inlineStr"/>
+      <c r="AQ315" t="inlineStr"/>
+      <c r="AR315" t="inlineStr"/>
+      <c r="AS315" t="inlineStr"/>
+      <c r="AT315" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU315" t="inlineStr"/>
+      <c r="AV315" t="inlineStr"/>
+      <c r="AW315" t="inlineStr"/>
+      <c r="AX315" t="inlineStr"/>
+      <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr"/>
+      <c r="BA315" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="BB315" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC315" t="inlineStr"/>
+      <c r="BD315" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE315" t="n">
+        <v>19972</v>
+      </c>
+      <c r="BF315" t="inlineStr">
+        <is>
+          <t>265869</t>
+        </is>
+      </c>
+      <c r="BG315" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH315" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI315" t="n">
+        <v>17260</v>
+      </c>
+      <c r="BJ315" t="inlineStr"/>
+      <c r="BK315" t="inlineStr"/>
+      <c r="BL315" t="inlineStr"/>
+      <c r="BM315" t="inlineStr"/>
+      <c r="BN315" t="inlineStr"/>
+      <c r="BO315" t="inlineStr"/>
+      <c r="BP315" t="inlineStr"/>
+      <c r="BQ315" t="inlineStr"/>
+      <c r="BR315" t="inlineStr"/>
+      <c r="BS315" t="inlineStr"/>
+      <c r="BT315" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU315" t="inlineStr"/>
+      <c r="BV315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C316" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D316" t="n">
+        <v>11000349188445</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1770534277</v>
+      </c>
+      <c r="F316" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>08-Feb-2026 12:35:23</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>773499900668</v>
+      </c>
+      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr"/>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr"/>
+      <c r="V316" t="inlineStr"/>
+      <c r="W316" t="inlineStr"/>
+      <c r="X316" t="inlineStr"/>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z316" t="n">
+        <v>9985965602</v>
+      </c>
+      <c r="AA316" t="inlineStr"/>
+      <c r="AB316" t="inlineStr"/>
+      <c r="AC316" t="inlineStr"/>
+      <c r="AD316" t="inlineStr"/>
+      <c r="AE316" t="inlineStr"/>
+      <c r="AF316" t="inlineStr"/>
+      <c r="AG316" t="inlineStr"/>
+      <c r="AH316" t="inlineStr"/>
+      <c r="AI316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK316" t="inlineStr"/>
+      <c r="AL316" t="inlineStr"/>
+      <c r="AM316" t="inlineStr"/>
+      <c r="AN316" t="inlineStr"/>
+      <c r="AO316" t="inlineStr"/>
+      <c r="AP316" t="inlineStr"/>
+      <c r="AQ316" t="inlineStr"/>
+      <c r="AR316" t="inlineStr"/>
+      <c r="AS316" t="inlineStr"/>
+      <c r="AT316" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU316" t="inlineStr"/>
+      <c r="AV316" t="inlineStr"/>
+      <c r="AW316" t="inlineStr"/>
+      <c r="AX316" t="inlineStr"/>
+      <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr"/>
+      <c r="BA316" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB316" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC316" t="inlineStr"/>
+      <c r="BD316" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE316" t="n">
+        <v>19941</v>
+      </c>
+      <c r="BF316" t="inlineStr">
+        <is>
+          <t>267541</t>
+        </is>
+      </c>
+      <c r="BG316" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH316" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI316" t="n">
+        <v>17229</v>
+      </c>
+      <c r="BJ316" t="inlineStr"/>
+      <c r="BK316" t="inlineStr"/>
+      <c r="BL316" t="inlineStr"/>
+      <c r="BM316" t="inlineStr"/>
+      <c r="BN316" t="inlineStr"/>
+      <c r="BO316" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP316" t="inlineStr"/>
+      <c r="BQ316" t="inlineStr"/>
+      <c r="BR316" t="inlineStr"/>
+      <c r="BS316" t="inlineStr"/>
+      <c r="BT316" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU316" t="inlineStr"/>
+      <c r="BV316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C317" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D317" t="n">
+        <v>11000349199255</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1770541823</v>
+      </c>
+      <c r="F317" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>08-Feb-2026 14:40:50</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>89695506546</v>
+      </c>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr"/>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr"/>
+      <c r="V317" t="inlineStr"/>
+      <c r="W317" t="inlineStr"/>
+      <c r="X317" t="inlineStr"/>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z317" t="n">
+        <v>9866955786</v>
+      </c>
+      <c r="AA317" t="inlineStr"/>
+      <c r="AB317" t="inlineStr"/>
+      <c r="AC317" t="inlineStr"/>
+      <c r="AD317" t="inlineStr"/>
+      <c r="AE317" t="inlineStr"/>
+      <c r="AF317" t="inlineStr"/>
+      <c r="AG317" t="inlineStr"/>
+      <c r="AH317" t="inlineStr"/>
+      <c r="AI317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK317" t="inlineStr"/>
+      <c r="AL317" t="inlineStr"/>
+      <c r="AM317" t="inlineStr"/>
+      <c r="AN317" t="inlineStr"/>
+      <c r="AO317" t="inlineStr"/>
+      <c r="AP317" t="inlineStr"/>
+      <c r="AQ317" t="inlineStr"/>
+      <c r="AR317" t="inlineStr"/>
+      <c r="AS317" t="inlineStr"/>
+      <c r="AT317" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU317" t="inlineStr"/>
+      <c r="AV317" t="inlineStr"/>
+      <c r="AW317" t="inlineStr"/>
+      <c r="AX317" t="inlineStr"/>
+      <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr"/>
+      <c r="BA317" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB317" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC317" t="inlineStr"/>
+      <c r="BD317" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE317" t="n">
+        <v>18265</v>
+      </c>
+      <c r="BF317" t="inlineStr">
+        <is>
+          <t>267000</t>
+        </is>
+      </c>
+      <c r="BG317" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH317" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI317" t="n">
+        <v>16342</v>
+      </c>
+      <c r="BJ317" t="inlineStr"/>
+      <c r="BK317" t="inlineStr"/>
+      <c r="BL317" t="inlineStr"/>
+      <c r="BM317" t="inlineStr"/>
+      <c r="BN317" t="inlineStr"/>
+      <c r="BO317" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP317" t="inlineStr"/>
+      <c r="BQ317" t="inlineStr"/>
+      <c r="BR317" t="inlineStr"/>
+      <c r="BS317" t="inlineStr"/>
+      <c r="BT317" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU317" t="inlineStr"/>
+      <c r="BV317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV312"/>
+  <dimension ref="A1:BV335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62022,6 +62022,4506 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C313" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D313" t="n">
+        <v>11000348990079</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1770372650</v>
+      </c>
+      <c r="F313" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>06-Feb-2026 15:42:50</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N313" t="n">
+        <v>696631043153</v>
+      </c>
+      <c r="O313" t="inlineStr"/>
+      <c r="P313" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>07-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr"/>
+      <c r="V313" t="inlineStr"/>
+      <c r="W313" t="inlineStr"/>
+      <c r="X313" t="inlineStr"/>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z313" t="n">
+        <v>9542502425</v>
+      </c>
+      <c r="AA313" t="inlineStr"/>
+      <c r="AB313" t="inlineStr"/>
+      <c r="AC313" t="inlineStr"/>
+      <c r="AD313" t="inlineStr"/>
+      <c r="AE313" t="inlineStr"/>
+      <c r="AF313" t="inlineStr"/>
+      <c r="AG313" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH313" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK313" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL313" t="n">
+        <v>8050</v>
+      </c>
+      <c r="AM313" t="inlineStr">
+        <is>
+          <t>07-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN313" t="inlineStr"/>
+      <c r="AO313" t="inlineStr"/>
+      <c r="AP313" t="inlineStr"/>
+      <c r="AQ313" t="inlineStr"/>
+      <c r="AR313" t="inlineStr"/>
+      <c r="AS313" t="inlineStr"/>
+      <c r="AT313" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU313" t="inlineStr"/>
+      <c r="AV313" t="inlineStr"/>
+      <c r="AW313" t="inlineStr"/>
+      <c r="AX313" t="inlineStr"/>
+      <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr"/>
+      <c r="BA313" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB313" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC313" t="inlineStr"/>
+      <c r="BD313" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE313" t="n">
+        <v>18422</v>
+      </c>
+      <c r="BF313" t="inlineStr">
+        <is>
+          <t>267145</t>
+        </is>
+      </c>
+      <c r="BG313" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH313" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI313" t="n">
+        <v>16400</v>
+      </c>
+      <c r="BJ313" t="inlineStr"/>
+      <c r="BK313" t="inlineStr"/>
+      <c r="BL313" t="inlineStr"/>
+      <c r="BM313" t="inlineStr"/>
+      <c r="BN313" t="inlineStr"/>
+      <c r="BO313" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP313" t="inlineStr"/>
+      <c r="BQ313" t="inlineStr"/>
+      <c r="BR313" t="inlineStr"/>
+      <c r="BS313" t="inlineStr"/>
+      <c r="BT313" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU313" t="inlineStr"/>
+      <c r="BV313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C314" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D314" t="n">
+        <v>11000349086368</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1770445075</v>
+      </c>
+      <c r="F314" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>07-Feb-2026 11:49:02</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N314" t="n">
+        <v>109145651654</v>
+      </c>
+      <c r="O314" t="inlineStr"/>
+      <c r="P314" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr"/>
+      <c r="V314" t="inlineStr"/>
+      <c r="W314" t="inlineStr"/>
+      <c r="X314" t="inlineStr"/>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z314" t="n">
+        <v>9505890135</v>
+      </c>
+      <c r="AA314" t="inlineStr"/>
+      <c r="AB314" t="inlineStr"/>
+      <c r="AC314" t="inlineStr"/>
+      <c r="AD314" t="inlineStr"/>
+      <c r="AE314" t="inlineStr"/>
+      <c r="AF314" t="inlineStr"/>
+      <c r="AG314" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH314" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK314" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL314" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM314" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN314" t="inlineStr"/>
+      <c r="AO314" t="inlineStr"/>
+      <c r="AP314" t="inlineStr"/>
+      <c r="AQ314" t="inlineStr"/>
+      <c r="AR314" t="inlineStr"/>
+      <c r="AS314" t="inlineStr"/>
+      <c r="AT314" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU314" t="inlineStr"/>
+      <c r="AV314" t="inlineStr"/>
+      <c r="AW314" t="inlineStr"/>
+      <c r="AX314" t="inlineStr"/>
+      <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr"/>
+      <c r="BA314" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB314" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC314" t="inlineStr"/>
+      <c r="BD314" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE314" t="n">
+        <v>18805</v>
+      </c>
+      <c r="BF314" t="inlineStr">
+        <is>
+          <t>267429</t>
+        </is>
+      </c>
+      <c r="BG314" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH314" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI314" t="n">
+        <v>15762</v>
+      </c>
+      <c r="BJ314" t="inlineStr"/>
+      <c r="BK314" t="inlineStr"/>
+      <c r="BL314" t="inlineStr"/>
+      <c r="BM314" t="inlineStr"/>
+      <c r="BN314" t="inlineStr"/>
+      <c r="BO314" t="inlineStr"/>
+      <c r="BP314" t="inlineStr"/>
+      <c r="BQ314" t="inlineStr"/>
+      <c r="BR314" t="inlineStr"/>
+      <c r="BS314" t="inlineStr"/>
+      <c r="BT314" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU314" t="inlineStr"/>
+      <c r="BV314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C315" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D315" t="n">
+        <v>11000349179233</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1770528801</v>
+      </c>
+      <c r="F315" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>08-Feb-2026 11:04:35</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HDFC Bank </t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr"/>
+      <c r="P315" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr"/>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr"/>
+      <c r="V315" t="inlineStr"/>
+      <c r="W315" t="inlineStr"/>
+      <c r="X315" t="inlineStr"/>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z315" t="n">
+        <v>6305761566</v>
+      </c>
+      <c r="AA315" t="inlineStr"/>
+      <c r="AB315" t="inlineStr"/>
+      <c r="AC315" t="inlineStr"/>
+      <c r="AD315" t="inlineStr"/>
+      <c r="AE315" t="inlineStr"/>
+      <c r="AF315" t="inlineStr"/>
+      <c r="AG315" t="inlineStr"/>
+      <c r="AH315" t="inlineStr"/>
+      <c r="AI315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK315" t="inlineStr"/>
+      <c r="AL315" t="inlineStr"/>
+      <c r="AM315" t="inlineStr"/>
+      <c r="AN315" t="inlineStr"/>
+      <c r="AO315" t="inlineStr"/>
+      <c r="AP315" t="inlineStr"/>
+      <c r="AQ315" t="inlineStr"/>
+      <c r="AR315" t="inlineStr"/>
+      <c r="AS315" t="inlineStr"/>
+      <c r="AT315" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU315" t="inlineStr"/>
+      <c r="AV315" t="inlineStr"/>
+      <c r="AW315" t="inlineStr"/>
+      <c r="AX315" t="inlineStr"/>
+      <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr"/>
+      <c r="BA315" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="BB315" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC315" t="inlineStr"/>
+      <c r="BD315" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE315" t="n">
+        <v>19972</v>
+      </c>
+      <c r="BF315" t="inlineStr">
+        <is>
+          <t>265869</t>
+        </is>
+      </c>
+      <c r="BG315" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH315" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI315" t="n">
+        <v>17260</v>
+      </c>
+      <c r="BJ315" t="inlineStr"/>
+      <c r="BK315" t="inlineStr"/>
+      <c r="BL315" t="inlineStr"/>
+      <c r="BM315" t="inlineStr"/>
+      <c r="BN315" t="inlineStr"/>
+      <c r="BO315" t="inlineStr"/>
+      <c r="BP315" t="inlineStr"/>
+      <c r="BQ315" t="inlineStr"/>
+      <c r="BR315" t="inlineStr"/>
+      <c r="BS315" t="inlineStr"/>
+      <c r="BT315" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU315" t="inlineStr"/>
+      <c r="BV315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C316" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D316" t="n">
+        <v>11000349188445</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1770534277</v>
+      </c>
+      <c r="F316" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>08-Feb-2026 12:35:23</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>773499900668</v>
+      </c>
+      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr"/>
+      <c r="V316" t="inlineStr"/>
+      <c r="W316" t="inlineStr"/>
+      <c r="X316" t="inlineStr"/>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z316" t="n">
+        <v>9985965602</v>
+      </c>
+      <c r="AA316" t="inlineStr"/>
+      <c r="AB316" t="inlineStr"/>
+      <c r="AC316" t="inlineStr"/>
+      <c r="AD316" t="inlineStr"/>
+      <c r="AE316" t="inlineStr"/>
+      <c r="AF316" t="inlineStr"/>
+      <c r="AG316" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH316" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK316" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL316" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM316" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN316" t="inlineStr"/>
+      <c r="AO316" t="inlineStr"/>
+      <c r="AP316" t="inlineStr"/>
+      <c r="AQ316" t="inlineStr"/>
+      <c r="AR316" t="inlineStr"/>
+      <c r="AS316" t="inlineStr"/>
+      <c r="AT316" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU316" t="inlineStr"/>
+      <c r="AV316" t="inlineStr"/>
+      <c r="AW316" t="inlineStr"/>
+      <c r="AX316" t="inlineStr"/>
+      <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr"/>
+      <c r="BA316" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB316" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC316" t="inlineStr"/>
+      <c r="BD316" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE316" t="n">
+        <v>19941</v>
+      </c>
+      <c r="BF316" t="inlineStr">
+        <is>
+          <t>267541</t>
+        </is>
+      </c>
+      <c r="BG316" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH316" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI316" t="n">
+        <v>17229</v>
+      </c>
+      <c r="BJ316" t="inlineStr"/>
+      <c r="BK316" t="inlineStr"/>
+      <c r="BL316" t="inlineStr"/>
+      <c r="BM316" t="inlineStr"/>
+      <c r="BN316" t="inlineStr"/>
+      <c r="BO316" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP316" t="inlineStr"/>
+      <c r="BQ316" t="inlineStr"/>
+      <c r="BR316" t="inlineStr"/>
+      <c r="BS316" t="inlineStr"/>
+      <c r="BT316" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU316" t="inlineStr"/>
+      <c r="BV316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C317" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D317" t="n">
+        <v>11000349199255</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1770541823</v>
+      </c>
+      <c r="F317" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>08-Feb-2026 14:40:50</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>89695506546</v>
+      </c>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr"/>
+      <c r="V317" t="inlineStr"/>
+      <c r="W317" t="inlineStr"/>
+      <c r="X317" t="inlineStr"/>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z317" t="n">
+        <v>9866955786</v>
+      </c>
+      <c r="AA317" t="inlineStr"/>
+      <c r="AB317" t="inlineStr"/>
+      <c r="AC317" t="inlineStr"/>
+      <c r="AD317" t="inlineStr"/>
+      <c r="AE317" t="inlineStr"/>
+      <c r="AF317" t="inlineStr"/>
+      <c r="AG317" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH317" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK317" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL317" t="n">
+        <v>7750</v>
+      </c>
+      <c r="AM317" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN317" t="inlineStr"/>
+      <c r="AO317" t="inlineStr"/>
+      <c r="AP317" t="inlineStr"/>
+      <c r="AQ317" t="inlineStr"/>
+      <c r="AR317" t="inlineStr"/>
+      <c r="AS317" t="inlineStr"/>
+      <c r="AT317" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU317" t="inlineStr"/>
+      <c r="AV317" t="inlineStr"/>
+      <c r="AW317" t="inlineStr"/>
+      <c r="AX317" t="inlineStr"/>
+      <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr"/>
+      <c r="BA317" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB317" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC317" t="inlineStr"/>
+      <c r="BD317" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE317" t="n">
+        <v>18265</v>
+      </c>
+      <c r="BF317" t="inlineStr">
+        <is>
+          <t>267000</t>
+        </is>
+      </c>
+      <c r="BG317" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH317" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI317" t="n">
+        <v>16342</v>
+      </c>
+      <c r="BJ317" t="inlineStr"/>
+      <c r="BK317" t="inlineStr"/>
+      <c r="BL317" t="inlineStr"/>
+      <c r="BM317" t="inlineStr"/>
+      <c r="BN317" t="inlineStr"/>
+      <c r="BO317" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP317" t="inlineStr"/>
+      <c r="BQ317" t="inlineStr"/>
+      <c r="BR317" t="inlineStr"/>
+      <c r="BS317" t="inlineStr"/>
+      <c r="BT317" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU317" t="inlineStr"/>
+      <c r="BV317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C318" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D318" t="n">
+        <v>11000349411873</v>
+      </c>
+      <c r="E318" t="n">
+        <v>1770653541</v>
+      </c>
+      <c r="F318" t="n">
+        <v>10750</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 21:45:01</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>109162276900</v>
+      </c>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr"/>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr"/>
+      <c r="V318" t="inlineStr"/>
+      <c r="W318" t="inlineStr"/>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>GURRALA RUSHABH NARAYAN</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z318" t="n">
+        <v>9704995001</v>
+      </c>
+      <c r="AA318" t="inlineStr"/>
+      <c r="AB318" t="inlineStr"/>
+      <c r="AC318" t="inlineStr"/>
+      <c r="AD318" t="inlineStr"/>
+      <c r="AE318" t="inlineStr"/>
+      <c r="AF318" t="inlineStr"/>
+      <c r="AG318" t="inlineStr"/>
+      <c r="AH318" t="inlineStr"/>
+      <c r="AI318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK318" t="inlineStr"/>
+      <c r="AL318" t="inlineStr"/>
+      <c r="AM318" t="inlineStr"/>
+      <c r="AN318" t="inlineStr"/>
+      <c r="AO318" t="inlineStr"/>
+      <c r="AP318" t="inlineStr"/>
+      <c r="AQ318" t="inlineStr"/>
+      <c r="AR318" t="inlineStr"/>
+      <c r="AS318" t="inlineStr"/>
+      <c r="AT318" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AU318" t="inlineStr"/>
+      <c r="AV318" t="inlineStr"/>
+      <c r="AW318" t="inlineStr"/>
+      <c r="AX318" t="inlineStr"/>
+      <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr"/>
+      <c r="BA318" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB318" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC318" t="inlineStr"/>
+      <c r="BD318" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE318" t="n">
+        <v>19325</v>
+      </c>
+      <c r="BF318" t="inlineStr">
+        <is>
+          <t>268659</t>
+        </is>
+      </c>
+      <c r="BG318" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="BH318" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI318" t="n">
+        <v>16052</v>
+      </c>
+      <c r="BJ318" t="inlineStr"/>
+      <c r="BK318" t="inlineStr"/>
+      <c r="BL318" t="inlineStr"/>
+      <c r="BM318" t="inlineStr"/>
+      <c r="BN318" t="inlineStr"/>
+      <c r="BO318" t="inlineStr"/>
+      <c r="BP318" t="inlineStr"/>
+      <c r="BQ318" t="inlineStr"/>
+      <c r="BR318" t="inlineStr"/>
+      <c r="BS318" t="inlineStr"/>
+      <c r="BT318" t="n">
+        <v>34</v>
+      </c>
+      <c r="BU318" t="inlineStr"/>
+      <c r="BV318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C319" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D319" t="n">
+        <v>11000349412641</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1770653878</v>
+      </c>
+      <c r="F319" t="n">
+        <v>10750</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 21:49:08</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>109162303649</v>
+      </c>
+      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr"/>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr"/>
+      <c r="V319" t="inlineStr"/>
+      <c r="W319" t="inlineStr"/>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>GURRALA RUSHABH NARAYAN</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z319" t="n">
+        <v>9704995001</v>
+      </c>
+      <c r="AA319" t="inlineStr"/>
+      <c r="AB319" t="inlineStr"/>
+      <c r="AC319" t="inlineStr"/>
+      <c r="AD319" t="inlineStr"/>
+      <c r="AE319" t="inlineStr"/>
+      <c r="AF319" t="inlineStr"/>
+      <c r="AG319" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH319" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK319" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL319" t="n">
+        <v>10750</v>
+      </c>
+      <c r="AM319" t="inlineStr"/>
+      <c r="AN319" t="inlineStr"/>
+      <c r="AO319" t="inlineStr"/>
+      <c r="AP319" t="inlineStr"/>
+      <c r="AQ319" t="inlineStr"/>
+      <c r="AR319" t="inlineStr"/>
+      <c r="AS319" t="inlineStr"/>
+      <c r="AT319" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU319" t="inlineStr"/>
+      <c r="AV319" t="inlineStr"/>
+      <c r="AW319" t="inlineStr"/>
+      <c r="AX319" t="inlineStr"/>
+      <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr"/>
+      <c r="BA319" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB319" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC319" t="inlineStr"/>
+      <c r="BD319" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE319" t="n">
+        <v>19325</v>
+      </c>
+      <c r="BF319" t="inlineStr">
+        <is>
+          <t>268659</t>
+        </is>
+      </c>
+      <c r="BG319" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="BH319" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI319" t="n">
+        <v>16052</v>
+      </c>
+      <c r="BJ319" t="inlineStr"/>
+      <c r="BK319" t="inlineStr"/>
+      <c r="BL319" t="inlineStr"/>
+      <c r="BM319" t="inlineStr"/>
+      <c r="BN319" t="inlineStr"/>
+      <c r="BO319" t="inlineStr"/>
+      <c r="BP319" t="inlineStr"/>
+      <c r="BQ319" t="inlineStr"/>
+      <c r="BR319" t="inlineStr"/>
+      <c r="BS319" t="inlineStr"/>
+      <c r="BT319" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU319" t="inlineStr"/>
+      <c r="BV319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C320" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D320" t="n">
+        <v>11000349433264</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1770688284</v>
+      </c>
+      <c r="F320" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>10-Feb-2026 07:23:05</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N320" t="n">
+        <v>109163767115</v>
+      </c>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr"/>
+      <c r="V320" t="inlineStr"/>
+      <c r="W320" t="inlineStr"/>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>VELAMALA LAKSHITHA</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z320" t="n">
+        <v>8886569151</v>
+      </c>
+      <c r="AA320" t="inlineStr"/>
+      <c r="AB320" t="inlineStr"/>
+      <c r="AC320" t="inlineStr"/>
+      <c r="AD320" t="inlineStr"/>
+      <c r="AE320" t="inlineStr"/>
+      <c r="AF320" t="inlineStr"/>
+      <c r="AG320" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH320" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK320" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL320" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM320" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN320" t="inlineStr"/>
+      <c r="AO320" t="inlineStr"/>
+      <c r="AP320" t="inlineStr"/>
+      <c r="AQ320" t="inlineStr"/>
+      <c r="AR320" t="inlineStr"/>
+      <c r="AS320" t="inlineStr"/>
+      <c r="AT320" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU320" t="inlineStr"/>
+      <c r="AV320" t="inlineStr"/>
+      <c r="AW320" t="inlineStr"/>
+      <c r="AX320" t="inlineStr"/>
+      <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr"/>
+      <c r="BA320" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB320" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC320" t="inlineStr"/>
+      <c r="BD320" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE320" t="n">
+        <v>18687</v>
+      </c>
+      <c r="BF320" t="inlineStr">
+        <is>
+          <t>265804</t>
+        </is>
+      </c>
+      <c r="BG320" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="BH320" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI320" t="n">
+        <v>16167</v>
+      </c>
+      <c r="BJ320" t="inlineStr"/>
+      <c r="BK320" t="inlineStr"/>
+      <c r="BL320" t="inlineStr"/>
+      <c r="BM320" t="inlineStr"/>
+      <c r="BN320" t="inlineStr"/>
+      <c r="BO320" t="inlineStr"/>
+      <c r="BP320" t="inlineStr"/>
+      <c r="BQ320" t="inlineStr"/>
+      <c r="BR320" t="inlineStr"/>
+      <c r="BS320" t="inlineStr"/>
+      <c r="BT320" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU320" t="inlineStr"/>
+      <c r="BV320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C321" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D321" t="n">
+        <v>11000349550616</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1770723058</v>
+      </c>
+      <c r="F321" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>10-Feb-2026 17:03:05</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>109167537406</v>
+      </c>
+      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr"/>
+      <c r="V321" t="inlineStr"/>
+      <c r="W321" t="inlineStr"/>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>RETOJI HRIDAYANSH VICTOR</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z321" t="n">
+        <v>9395553084</v>
+      </c>
+      <c r="AA321" t="inlineStr"/>
+      <c r="AB321" t="inlineStr"/>
+      <c r="AC321" t="inlineStr"/>
+      <c r="AD321" t="inlineStr"/>
+      <c r="AE321" t="inlineStr"/>
+      <c r="AF321" t="inlineStr"/>
+      <c r="AG321" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH321" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK321" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL321" t="n">
+        <v>8050</v>
+      </c>
+      <c r="AM321" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN321" t="inlineStr"/>
+      <c r="AO321" t="inlineStr"/>
+      <c r="AP321" t="inlineStr"/>
+      <c r="AQ321" t="inlineStr"/>
+      <c r="AR321" t="inlineStr"/>
+      <c r="AS321" t="inlineStr"/>
+      <c r="AT321" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU321" t="inlineStr"/>
+      <c r="AV321" t="inlineStr"/>
+      <c r="AW321" t="inlineStr"/>
+      <c r="AX321" t="inlineStr"/>
+      <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr"/>
+      <c r="BA321" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB321" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC321" t="inlineStr"/>
+      <c r="BD321" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE321" t="n">
+        <v>18469</v>
+      </c>
+      <c r="BF321" t="inlineStr">
+        <is>
+          <t>265534</t>
+        </is>
+      </c>
+      <c r="BG321" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="BH321" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI321" t="n">
+        <v>16353</v>
+      </c>
+      <c r="BJ321" t="inlineStr"/>
+      <c r="BK321" t="inlineStr"/>
+      <c r="BL321" t="inlineStr"/>
+      <c r="BM321" t="inlineStr"/>
+      <c r="BN321" t="inlineStr"/>
+      <c r="BO321" t="inlineStr"/>
+      <c r="BP321" t="inlineStr"/>
+      <c r="BQ321" t="inlineStr"/>
+      <c r="BR321" t="inlineStr"/>
+      <c r="BS321" t="inlineStr"/>
+      <c r="BT321" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU321" t="inlineStr"/>
+      <c r="BV321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C322" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D322" t="n">
+        <v>11000349611971</v>
+      </c>
+      <c r="E322" t="n">
+        <v>1770776081</v>
+      </c>
+      <c r="F322" t="n">
+        <v>16700</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 07:45:40</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N322" t="n">
+        <v>109170679443</v>
+      </c>
+      <c r="O322" t="inlineStr"/>
+      <c r="P322" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>12-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr"/>
+      <c r="V322" t="inlineStr"/>
+      <c r="W322" t="inlineStr"/>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>SIDDI SHANMUKHA SAI MANI DEEPANSH</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z322" t="n">
+        <v>6305761566</v>
+      </c>
+      <c r="AA322" t="inlineStr"/>
+      <c r="AB322" t="inlineStr"/>
+      <c r="AC322" t="inlineStr"/>
+      <c r="AD322" t="inlineStr"/>
+      <c r="AE322" t="inlineStr"/>
+      <c r="AF322" t="inlineStr"/>
+      <c r="AG322" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH322" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK322" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL322" t="n">
+        <v>16700</v>
+      </c>
+      <c r="AM322" t="inlineStr">
+        <is>
+          <t>12-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN322" t="inlineStr"/>
+      <c r="AO322" t="inlineStr"/>
+      <c r="AP322" t="inlineStr"/>
+      <c r="AQ322" t="inlineStr"/>
+      <c r="AR322" t="inlineStr"/>
+      <c r="AS322" t="inlineStr"/>
+      <c r="AT322" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU322" t="inlineStr"/>
+      <c r="AV322" t="inlineStr"/>
+      <c r="AW322" t="inlineStr"/>
+      <c r="AX322" t="inlineStr"/>
+      <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr"/>
+      <c r="BA322" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB322" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC322" t="inlineStr"/>
+      <c r="BD322" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE322" t="n">
+        <v>19972</v>
+      </c>
+      <c r="BF322" t="inlineStr">
+        <is>
+          <t>265869,267519</t>
+        </is>
+      </c>
+      <c r="BG322" t="inlineStr">
+        <is>
+          <t>2050,2058</t>
+        </is>
+      </c>
+      <c r="BH322" t="inlineStr">
+        <is>
+          <t>sixteen thousand seven hundred</t>
+        </is>
+      </c>
+      <c r="BI322" t="n">
+        <v>17260</v>
+      </c>
+      <c r="BJ322" t="inlineStr"/>
+      <c r="BK322" t="inlineStr"/>
+      <c r="BL322" t="inlineStr"/>
+      <c r="BM322" t="inlineStr"/>
+      <c r="BN322" t="inlineStr"/>
+      <c r="BO322" t="inlineStr"/>
+      <c r="BP322" t="inlineStr"/>
+      <c r="BQ322" t="inlineStr"/>
+      <c r="BR322" t="inlineStr"/>
+      <c r="BS322" t="inlineStr"/>
+      <c r="BT322" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU322" t="inlineStr"/>
+      <c r="BV322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C323" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D323" t="n">
+        <v>11000349612523</v>
+      </c>
+      <c r="E323" t="n">
+        <v>1770776819</v>
+      </c>
+      <c r="F323" t="n">
+        <v>21500</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 08:00:22</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N323" t="n">
+        <v>109170756189</v>
+      </c>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr"/>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr"/>
+      <c r="V323" t="inlineStr"/>
+      <c r="W323" t="inlineStr"/>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>SIDDI SHANMUKHA SESA SAI DHANUSH</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z323" t="n">
+        <v>6305761566</v>
+      </c>
+      <c r="AA323" t="inlineStr"/>
+      <c r="AB323" t="inlineStr"/>
+      <c r="AC323" t="inlineStr"/>
+      <c r="AD323" t="inlineStr"/>
+      <c r="AE323" t="inlineStr"/>
+      <c r="AF323" t="inlineStr"/>
+      <c r="AG323" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH323" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK323" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL323" t="n">
+        <v>21500</v>
+      </c>
+      <c r="AM323" t="inlineStr"/>
+      <c r="AN323" t="inlineStr"/>
+      <c r="AO323" t="inlineStr"/>
+      <c r="AP323" t="inlineStr"/>
+      <c r="AQ323" t="inlineStr"/>
+      <c r="AR323" t="inlineStr"/>
+      <c r="AS323" t="inlineStr"/>
+      <c r="AT323" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU323" t="inlineStr"/>
+      <c r="AV323" t="inlineStr"/>
+      <c r="AW323" t="inlineStr"/>
+      <c r="AX323" t="inlineStr"/>
+      <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr"/>
+      <c r="BA323" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB323" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC323" t="inlineStr"/>
+      <c r="BD323" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE323" t="n">
+        <v>19971</v>
+      </c>
+      <c r="BF323" t="inlineStr">
+        <is>
+          <t>266353,268690</t>
+        </is>
+      </c>
+      <c r="BG323" t="inlineStr">
+        <is>
+          <t>2052,2062</t>
+        </is>
+      </c>
+      <c r="BH323" t="inlineStr">
+        <is>
+          <t>twenty one thousand five hundred</t>
+        </is>
+      </c>
+      <c r="BI323" t="n">
+        <v>17259</v>
+      </c>
+      <c r="BJ323" t="inlineStr"/>
+      <c r="BK323" t="inlineStr"/>
+      <c r="BL323" t="inlineStr"/>
+      <c r="BM323" t="inlineStr"/>
+      <c r="BN323" t="inlineStr"/>
+      <c r="BO323" t="inlineStr"/>
+      <c r="BP323" t="inlineStr"/>
+      <c r="BQ323" t="inlineStr"/>
+      <c r="BR323" t="inlineStr"/>
+      <c r="BS323" t="inlineStr"/>
+      <c r="BT323" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU323" t="inlineStr"/>
+      <c r="BV323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C324" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D324" t="n">
+        <v>11000349933934</v>
+      </c>
+      <c r="E324" t="n">
+        <v>1770951465</v>
+      </c>
+      <c r="F324" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 08:29:21</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N324" t="n">
+        <v>456479327537</v>
+      </c>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr"/>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr"/>
+      <c r="V324" t="inlineStr"/>
+      <c r="W324" t="inlineStr"/>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>RAKESH NAMMI</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z324" t="n">
+        <v>9502806409</v>
+      </c>
+      <c r="AA324" t="inlineStr"/>
+      <c r="AB324" t="inlineStr"/>
+      <c r="AC324" t="inlineStr"/>
+      <c r="AD324" t="inlineStr"/>
+      <c r="AE324" t="inlineStr"/>
+      <c r="AF324" t="inlineStr"/>
+      <c r="AG324" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH324" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK324" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL324" t="n">
+        <v>8650</v>
+      </c>
+      <c r="AM324" t="inlineStr"/>
+      <c r="AN324" t="inlineStr"/>
+      <c r="AO324" t="inlineStr"/>
+      <c r="AP324" t="inlineStr"/>
+      <c r="AQ324" t="inlineStr"/>
+      <c r="AR324" t="inlineStr"/>
+      <c r="AS324" t="inlineStr"/>
+      <c r="AT324" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU324" t="inlineStr"/>
+      <c r="AV324" t="inlineStr"/>
+      <c r="AW324" t="inlineStr"/>
+      <c r="AX324" t="inlineStr"/>
+      <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr"/>
+      <c r="BA324" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB324" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC324" t="inlineStr"/>
+      <c r="BD324" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE324" t="n">
+        <v>19097</v>
+      </c>
+      <c r="BF324" t="inlineStr">
+        <is>
+          <t>268335</t>
+        </is>
+      </c>
+      <c r="BG324" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="BH324" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI324" t="n">
+        <v>16615</v>
+      </c>
+      <c r="BJ324" t="inlineStr"/>
+      <c r="BK324" t="inlineStr"/>
+      <c r="BL324" t="inlineStr"/>
+      <c r="BM324" t="inlineStr"/>
+      <c r="BN324" t="inlineStr"/>
+      <c r="BO324" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP324" t="inlineStr"/>
+      <c r="BQ324" t="inlineStr"/>
+      <c r="BR324" t="inlineStr"/>
+      <c r="BS324" t="inlineStr"/>
+      <c r="BT324" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU324" t="inlineStr"/>
+      <c r="BV324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C325" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D325" t="n">
+        <v>11000349933992</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1770951642</v>
+      </c>
+      <c r="F325" t="n">
+        <v>11350</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 08:30:55</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N325" t="n">
+        <v>186282312824</v>
+      </c>
+      <c r="O325" t="inlineStr"/>
+      <c r="P325" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr"/>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr"/>
+      <c r="V325" t="inlineStr"/>
+      <c r="W325" t="inlineStr"/>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>HEMANTH NAMMI</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z325" t="n">
+        <v>9502806409</v>
+      </c>
+      <c r="AA325" t="inlineStr"/>
+      <c r="AB325" t="inlineStr"/>
+      <c r="AC325" t="inlineStr"/>
+      <c r="AD325" t="inlineStr"/>
+      <c r="AE325" t="inlineStr"/>
+      <c r="AF325" t="inlineStr"/>
+      <c r="AG325" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH325" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI325" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ325" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK325" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL325" t="n">
+        <v>11350</v>
+      </c>
+      <c r="AM325" t="inlineStr"/>
+      <c r="AN325" t="inlineStr"/>
+      <c r="AO325" t="inlineStr"/>
+      <c r="AP325" t="inlineStr"/>
+      <c r="AQ325" t="inlineStr"/>
+      <c r="AR325" t="inlineStr"/>
+      <c r="AS325" t="inlineStr"/>
+      <c r="AT325" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU325" t="inlineStr"/>
+      <c r="AV325" t="inlineStr"/>
+      <c r="AW325" t="inlineStr"/>
+      <c r="AX325" t="inlineStr"/>
+      <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr"/>
+      <c r="BA325" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB325" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC325" t="inlineStr"/>
+      <c r="BD325" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE325" t="n">
+        <v>19448</v>
+      </c>
+      <c r="BF325" t="inlineStr">
+        <is>
+          <t>268100</t>
+        </is>
+      </c>
+      <c r="BG325" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="BH325" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI325" t="n">
+        <v>14652</v>
+      </c>
+      <c r="BJ325" t="inlineStr"/>
+      <c r="BK325" t="inlineStr"/>
+      <c r="BL325" t="inlineStr"/>
+      <c r="BM325" t="inlineStr"/>
+      <c r="BN325" t="inlineStr"/>
+      <c r="BO325" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP325" t="inlineStr"/>
+      <c r="BQ325" t="inlineStr"/>
+      <c r="BR325" t="inlineStr"/>
+      <c r="BS325" t="inlineStr"/>
+      <c r="BT325" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU325" t="inlineStr"/>
+      <c r="BV325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C326" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D326" t="n">
+        <v>11000349945161</v>
+      </c>
+      <c r="E326" t="n">
+        <v>1770955661</v>
+      </c>
+      <c r="F326" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 09:38:08</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N326" t="n">
+        <v>834632436491</v>
+      </c>
+      <c r="O326" t="n">
+        <v>834632436491</v>
+      </c>
+      <c r="P326" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>16-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr"/>
+      <c r="V326" t="inlineStr"/>
+      <c r="W326" t="inlineStr"/>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>EVAAN CHODAM</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z326" t="n">
+        <v>7995919129</v>
+      </c>
+      <c r="AA326" t="inlineStr"/>
+      <c r="AB326" t="inlineStr"/>
+      <c r="AC326" t="inlineStr"/>
+      <c r="AD326" t="inlineStr"/>
+      <c r="AE326" t="inlineStr"/>
+      <c r="AF326" t="inlineStr"/>
+      <c r="AG326" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH326" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK326" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL326" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM326" t="inlineStr">
+        <is>
+          <t>16-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN326" t="inlineStr"/>
+      <c r="AO326" t="inlineStr"/>
+      <c r="AP326" t="inlineStr"/>
+      <c r="AQ326" t="inlineStr"/>
+      <c r="AR326" t="inlineStr"/>
+      <c r="AS326" t="inlineStr"/>
+      <c r="AT326" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU326" t="inlineStr"/>
+      <c r="AV326" t="inlineStr"/>
+      <c r="AW326" t="inlineStr"/>
+      <c r="AX326" t="inlineStr"/>
+      <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr"/>
+      <c r="BA326" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB326" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC326" t="inlineStr"/>
+      <c r="BD326" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE326" t="n">
+        <v>20086</v>
+      </c>
+      <c r="BF326" t="inlineStr">
+        <is>
+          <t>268471</t>
+        </is>
+      </c>
+      <c r="BG326" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH326" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI326" t="n">
+        <v>17367</v>
+      </c>
+      <c r="BJ326" t="inlineStr"/>
+      <c r="BK326" t="inlineStr"/>
+      <c r="BL326" t="inlineStr"/>
+      <c r="BM326" t="inlineStr"/>
+      <c r="BN326" t="inlineStr"/>
+      <c r="BO326" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP326" t="inlineStr"/>
+      <c r="BQ326" t="inlineStr"/>
+      <c r="BR326" t="inlineStr"/>
+      <c r="BS326" t="inlineStr"/>
+      <c r="BT326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU326" t="inlineStr"/>
+      <c r="BV326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C327" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D327" t="n">
+        <v>11000350039137</v>
+      </c>
+      <c r="E327" t="n">
+        <v>1770986795</v>
+      </c>
+      <c r="F327" t="n">
+        <v>11350</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 18:17:23</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr"/>
+      <c r="P327" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr"/>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr"/>
+      <c r="V327" t="inlineStr"/>
+      <c r="W327" t="inlineStr"/>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>AFREEN BEGUM</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z327" t="n">
+        <v>8099960677</v>
+      </c>
+      <c r="AA327" t="inlineStr"/>
+      <c r="AB327" t="inlineStr"/>
+      <c r="AC327" t="inlineStr"/>
+      <c r="AD327" t="inlineStr"/>
+      <c r="AE327" t="inlineStr"/>
+      <c r="AF327" t="inlineStr"/>
+      <c r="AG327" t="inlineStr"/>
+      <c r="AH327" t="inlineStr"/>
+      <c r="AI327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK327" t="inlineStr"/>
+      <c r="AL327" t="inlineStr"/>
+      <c r="AM327" t="inlineStr"/>
+      <c r="AN327" t="inlineStr"/>
+      <c r="AO327" t="inlineStr"/>
+      <c r="AP327" t="inlineStr"/>
+      <c r="AQ327" t="inlineStr"/>
+      <c r="AR327" t="inlineStr"/>
+      <c r="AS327" t="inlineStr"/>
+      <c r="AT327" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS CANCELLED BY USER</t>
+        </is>
+      </c>
+      <c r="AU327" t="inlineStr"/>
+      <c r="AV327" t="inlineStr"/>
+      <c r="AW327" t="inlineStr"/>
+      <c r="AX327" t="inlineStr"/>
+      <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr"/>
+      <c r="BA327" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB327" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC327" t="inlineStr"/>
+      <c r="BD327" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE327" t="n">
+        <v>19419</v>
+      </c>
+      <c r="BF327" t="inlineStr">
+        <is>
+          <t>268015</t>
+        </is>
+      </c>
+      <c r="BG327" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="BH327" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI327" t="n">
+        <v>15952</v>
+      </c>
+      <c r="BJ327" t="inlineStr"/>
+      <c r="BK327" t="inlineStr"/>
+      <c r="BL327" t="inlineStr"/>
+      <c r="BM327" t="inlineStr"/>
+      <c r="BN327" t="inlineStr"/>
+      <c r="BO327" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP327" t="inlineStr"/>
+      <c r="BQ327" t="inlineStr"/>
+      <c r="BR327" t="inlineStr"/>
+      <c r="BS327" t="inlineStr"/>
+      <c r="BT327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU327" t="inlineStr"/>
+      <c r="BV327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C328" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D328" t="n">
+        <v>11000350040172</v>
+      </c>
+      <c r="E328" t="n">
+        <v>1770986795</v>
+      </c>
+      <c r="F328" t="n">
+        <v>11350</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 18:18:42</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N328" t="n">
+        <v>321558195549</v>
+      </c>
+      <c r="O328" t="inlineStr"/>
+      <c r="P328" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr"/>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr"/>
+      <c r="V328" t="inlineStr"/>
+      <c r="W328" t="inlineStr"/>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>AFREEN BEGUM</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z328" t="n">
+        <v>8099960677</v>
+      </c>
+      <c r="AA328" t="inlineStr"/>
+      <c r="AB328" t="inlineStr"/>
+      <c r="AC328" t="inlineStr"/>
+      <c r="AD328" t="inlineStr"/>
+      <c r="AE328" t="inlineStr"/>
+      <c r="AF328" t="inlineStr"/>
+      <c r="AG328" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH328" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK328" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL328" t="n">
+        <v>11350</v>
+      </c>
+      <c r="AM328" t="inlineStr"/>
+      <c r="AN328" t="inlineStr"/>
+      <c r="AO328" t="inlineStr"/>
+      <c r="AP328" t="inlineStr"/>
+      <c r="AQ328" t="inlineStr"/>
+      <c r="AR328" t="inlineStr"/>
+      <c r="AS328" t="inlineStr"/>
+      <c r="AT328" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU328" t="inlineStr"/>
+      <c r="AV328" t="inlineStr"/>
+      <c r="AW328" t="inlineStr"/>
+      <c r="AX328" t="inlineStr"/>
+      <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr"/>
+      <c r="BA328" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB328" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC328" t="inlineStr"/>
+      <c r="BD328" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE328" t="n">
+        <v>19419</v>
+      </c>
+      <c r="BF328" t="inlineStr">
+        <is>
+          <t>268015</t>
+        </is>
+      </c>
+      <c r="BG328" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="BH328" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI328" t="n">
+        <v>15952</v>
+      </c>
+      <c r="BJ328" t="inlineStr"/>
+      <c r="BK328" t="inlineStr"/>
+      <c r="BL328" t="inlineStr"/>
+      <c r="BM328" t="inlineStr"/>
+      <c r="BN328" t="inlineStr"/>
+      <c r="BO328" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP328" t="inlineStr"/>
+      <c r="BQ328" t="inlineStr"/>
+      <c r="BR328" t="inlineStr"/>
+      <c r="BS328" t="inlineStr"/>
+      <c r="BT328" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU328" t="inlineStr"/>
+      <c r="BV328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C329" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D329" t="n">
+        <v>11000350074923</v>
+      </c>
+      <c r="E329" t="n">
+        <v>1771037293</v>
+      </c>
+      <c r="F329" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>14-Feb-2026 08:18:57</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N329" t="n">
+        <v>597298866691</v>
+      </c>
+      <c r="O329" t="inlineStr"/>
+      <c r="P329" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr"/>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr"/>
+      <c r="V329" t="inlineStr"/>
+      <c r="W329" t="inlineStr"/>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>GOLAGANI GEETHANJALI</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z329" t="n">
+        <v>9393123464</v>
+      </c>
+      <c r="AA329" t="inlineStr"/>
+      <c r="AB329" t="inlineStr"/>
+      <c r="AC329" t="inlineStr"/>
+      <c r="AD329" t="inlineStr"/>
+      <c r="AE329" t="inlineStr"/>
+      <c r="AF329" t="inlineStr"/>
+      <c r="AG329" t="inlineStr"/>
+      <c r="AH329" t="inlineStr"/>
+      <c r="AI329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK329" t="inlineStr"/>
+      <c r="AL329" t="inlineStr"/>
+      <c r="AM329" t="inlineStr"/>
+      <c r="AN329" t="inlineStr"/>
+      <c r="AO329" t="inlineStr"/>
+      <c r="AP329" t="inlineStr"/>
+      <c r="AQ329" t="inlineStr"/>
+      <c r="AR329" t="inlineStr"/>
+      <c r="AS329" t="inlineStr"/>
+      <c r="AT329" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU329" t="inlineStr"/>
+      <c r="AV329" t="inlineStr"/>
+      <c r="AW329" t="inlineStr"/>
+      <c r="AX329" t="inlineStr"/>
+      <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr"/>
+      <c r="BA329" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB329" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC329" t="inlineStr"/>
+      <c r="BD329" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE329" t="n">
+        <v>19026</v>
+      </c>
+      <c r="BF329" t="inlineStr">
+        <is>
+          <t>266050</t>
+        </is>
+      </c>
+      <c r="BG329" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH329" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI329" t="n">
+        <v>15009</v>
+      </c>
+      <c r="BJ329" t="inlineStr"/>
+      <c r="BK329" t="inlineStr"/>
+      <c r="BL329" t="inlineStr"/>
+      <c r="BM329" t="inlineStr"/>
+      <c r="BN329" t="inlineStr"/>
+      <c r="BO329" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP329" t="inlineStr"/>
+      <c r="BQ329" t="inlineStr"/>
+      <c r="BR329" t="inlineStr"/>
+      <c r="BS329" t="inlineStr"/>
+      <c r="BT329" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU329" t="inlineStr"/>
+      <c r="BV329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C330" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D330" t="n">
+        <v>11000350074991</v>
+      </c>
+      <c r="E330" t="n">
+        <v>1771037293</v>
+      </c>
+      <c r="F330" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>14-Feb-2026 08:20:30</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N330" t="n">
+        <v>998731603885</v>
+      </c>
+      <c r="O330" t="inlineStr"/>
+      <c r="P330" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr"/>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr"/>
+      <c r="V330" t="inlineStr"/>
+      <c r="W330" t="inlineStr"/>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>GOLAGANI GEETHANJALI</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z330" t="n">
+        <v>9393123464</v>
+      </c>
+      <c r="AA330" t="inlineStr"/>
+      <c r="AB330" t="inlineStr"/>
+      <c r="AC330" t="inlineStr"/>
+      <c r="AD330" t="inlineStr"/>
+      <c r="AE330" t="inlineStr"/>
+      <c r="AF330" t="inlineStr"/>
+      <c r="AG330" t="inlineStr"/>
+      <c r="AH330" t="inlineStr"/>
+      <c r="AI330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK330" t="inlineStr"/>
+      <c r="AL330" t="inlineStr"/>
+      <c r="AM330" t="inlineStr"/>
+      <c r="AN330" t="inlineStr"/>
+      <c r="AO330" t="inlineStr"/>
+      <c r="AP330" t="inlineStr"/>
+      <c r="AQ330" t="inlineStr"/>
+      <c r="AR330" t="inlineStr"/>
+      <c r="AS330" t="inlineStr"/>
+      <c r="AT330" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU330" t="inlineStr"/>
+      <c r="AV330" t="inlineStr"/>
+      <c r="AW330" t="inlineStr"/>
+      <c r="AX330" t="inlineStr"/>
+      <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr"/>
+      <c r="BA330" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB330" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC330" t="inlineStr"/>
+      <c r="BD330" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE330" t="n">
+        <v>19026</v>
+      </c>
+      <c r="BF330" t="inlineStr">
+        <is>
+          <t>266050</t>
+        </is>
+      </c>
+      <c r="BG330" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH330" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI330" t="n">
+        <v>15009</v>
+      </c>
+      <c r="BJ330" t="inlineStr"/>
+      <c r="BK330" t="inlineStr"/>
+      <c r="BL330" t="inlineStr"/>
+      <c r="BM330" t="inlineStr"/>
+      <c r="BN330" t="inlineStr"/>
+      <c r="BO330" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP330" t="inlineStr"/>
+      <c r="BQ330" t="inlineStr"/>
+      <c r="BR330" t="inlineStr"/>
+      <c r="BS330" t="inlineStr"/>
+      <c r="BT330" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU330" t="inlineStr"/>
+      <c r="BV330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C331" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D331" t="n">
+        <v>11000350075558</v>
+      </c>
+      <c r="E331" t="n">
+        <v>1771037667</v>
+      </c>
+      <c r="F331" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>14-Feb-2026 08:24:58</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N331" t="n">
+        <v>759841106307</v>
+      </c>
+      <c r="O331" t="inlineStr"/>
+      <c r="P331" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr"/>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr"/>
+      <c r="V331" t="inlineStr"/>
+      <c r="W331" t="inlineStr"/>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>GOLAGANI GEETHANJALI</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z331" t="n">
+        <v>9393123464</v>
+      </c>
+      <c r="AA331" t="inlineStr"/>
+      <c r="AB331" t="inlineStr"/>
+      <c r="AC331" t="inlineStr"/>
+      <c r="AD331" t="inlineStr"/>
+      <c r="AE331" t="inlineStr"/>
+      <c r="AF331" t="inlineStr"/>
+      <c r="AG331" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH331" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK331" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL331" t="n">
+        <v>8650</v>
+      </c>
+      <c r="AM331" t="inlineStr"/>
+      <c r="AN331" t="inlineStr"/>
+      <c r="AO331" t="inlineStr"/>
+      <c r="AP331" t="inlineStr"/>
+      <c r="AQ331" t="inlineStr"/>
+      <c r="AR331" t="inlineStr"/>
+      <c r="AS331" t="inlineStr"/>
+      <c r="AT331" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU331" t="inlineStr"/>
+      <c r="AV331" t="inlineStr"/>
+      <c r="AW331" t="inlineStr"/>
+      <c r="AX331" t="inlineStr"/>
+      <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr"/>
+      <c r="BA331" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB331" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC331" t="inlineStr"/>
+      <c r="BD331" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE331" t="n">
+        <v>19026</v>
+      </c>
+      <c r="BF331" t="inlineStr">
+        <is>
+          <t>266050</t>
+        </is>
+      </c>
+      <c r="BG331" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH331" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI331" t="n">
+        <v>15009</v>
+      </c>
+      <c r="BJ331" t="inlineStr"/>
+      <c r="BK331" t="inlineStr"/>
+      <c r="BL331" t="inlineStr"/>
+      <c r="BM331" t="inlineStr"/>
+      <c r="BN331" t="inlineStr"/>
+      <c r="BO331" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP331" t="inlineStr"/>
+      <c r="BQ331" t="inlineStr"/>
+      <c r="BR331" t="inlineStr"/>
+      <c r="BS331" t="inlineStr"/>
+      <c r="BT331" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU331" t="inlineStr"/>
+      <c r="BV331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C332" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D332" t="n">
+        <v>11000350432476</v>
+      </c>
+      <c r="E332" t="n">
+        <v>1771299354</v>
+      </c>
+      <c r="F332" t="n">
+        <v>11350</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>17-Feb-2026 09:06:11</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N332" t="n">
+        <v>387026729931</v>
+      </c>
+      <c r="O332" t="inlineStr"/>
+      <c r="P332" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr"/>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr"/>
+      <c r="V332" t="inlineStr"/>
+      <c r="W332" t="inlineStr"/>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>KORUKONDA KALYANI</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z332" t="n">
+        <v>9885668424</v>
+      </c>
+      <c r="AA332" t="inlineStr"/>
+      <c r="AB332" t="inlineStr"/>
+      <c r="AC332" t="inlineStr"/>
+      <c r="AD332" t="inlineStr"/>
+      <c r="AE332" t="inlineStr"/>
+      <c r="AF332" t="inlineStr"/>
+      <c r="AG332" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH332" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI332" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ332" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK332" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL332" t="n">
+        <v>11350</v>
+      </c>
+      <c r="AM332" t="inlineStr"/>
+      <c r="AN332" t="inlineStr"/>
+      <c r="AO332" t="inlineStr"/>
+      <c r="AP332" t="inlineStr"/>
+      <c r="AQ332" t="inlineStr"/>
+      <c r="AR332" t="inlineStr"/>
+      <c r="AS332" t="inlineStr"/>
+      <c r="AT332" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU332" t="inlineStr"/>
+      <c r="AV332" t="inlineStr"/>
+      <c r="AW332" t="inlineStr"/>
+      <c r="AX332" t="inlineStr"/>
+      <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr"/>
+      <c r="BA332" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB332" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC332" t="inlineStr"/>
+      <c r="BD332" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE332" t="n">
+        <v>19580</v>
+      </c>
+      <c r="BF332" t="inlineStr">
+        <is>
+          <t>268160</t>
+        </is>
+      </c>
+      <c r="BG332" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="BH332" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI332" t="n">
+        <v>15095</v>
+      </c>
+      <c r="BJ332" t="inlineStr"/>
+      <c r="BK332" t="inlineStr"/>
+      <c r="BL332" t="inlineStr"/>
+      <c r="BM332" t="inlineStr"/>
+      <c r="BN332" t="inlineStr"/>
+      <c r="BO332" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP332" t="inlineStr"/>
+      <c r="BQ332" t="inlineStr"/>
+      <c r="BR332" t="inlineStr"/>
+      <c r="BS332" t="inlineStr"/>
+      <c r="BT332" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU332" t="inlineStr"/>
+      <c r="BV332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C333" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D333" t="n">
+        <v>11000350603509</v>
+      </c>
+      <c r="E333" t="n">
+        <v>1771391968</v>
+      </c>
+      <c r="F333" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>18-Feb-2026 10:49:40</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N333" t="n">
+        <v>821324645171</v>
+      </c>
+      <c r="O333" t="inlineStr"/>
+      <c r="P333" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr"/>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr"/>
+      <c r="V333" t="inlineStr"/>
+      <c r="W333" t="inlineStr"/>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>RAKESH NAMMI</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z333" t="n">
+        <v>9502806409</v>
+      </c>
+      <c r="AA333" t="inlineStr"/>
+      <c r="AB333" t="inlineStr"/>
+      <c r="AC333" t="inlineStr"/>
+      <c r="AD333" t="inlineStr"/>
+      <c r="AE333" t="inlineStr"/>
+      <c r="AF333" t="inlineStr"/>
+      <c r="AG333" t="inlineStr"/>
+      <c r="AH333" t="inlineStr"/>
+      <c r="AI333" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ333" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK333" t="inlineStr"/>
+      <c r="AL333" t="inlineStr"/>
+      <c r="AM333" t="inlineStr"/>
+      <c r="AN333" t="inlineStr"/>
+      <c r="AO333" t="inlineStr"/>
+      <c r="AP333" t="inlineStr"/>
+      <c r="AQ333" t="inlineStr"/>
+      <c r="AR333" t="inlineStr"/>
+      <c r="AS333" t="inlineStr"/>
+      <c r="AT333" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU333" t="inlineStr"/>
+      <c r="AV333" t="inlineStr"/>
+      <c r="AW333" t="inlineStr"/>
+      <c r="AX333" t="inlineStr"/>
+      <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr"/>
+      <c r="BA333" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB333" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC333" t="inlineStr"/>
+      <c r="BD333" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE333" t="n">
+        <v>19097</v>
+      </c>
+      <c r="BF333" t="inlineStr">
+        <is>
+          <t>266170</t>
+        </is>
+      </c>
+      <c r="BG333" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH333" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI333" t="n">
+        <v>16615</v>
+      </c>
+      <c r="BJ333" t="inlineStr"/>
+      <c r="BK333" t="inlineStr"/>
+      <c r="BL333" t="inlineStr"/>
+      <c r="BM333" t="inlineStr"/>
+      <c r="BN333" t="inlineStr"/>
+      <c r="BO333" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP333" t="inlineStr"/>
+      <c r="BQ333" t="inlineStr"/>
+      <c r="BR333" t="inlineStr"/>
+      <c r="BS333" t="inlineStr"/>
+      <c r="BT333" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU333" t="inlineStr"/>
+      <c r="BV333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C334" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D334" t="n">
+        <v>11000350731551</v>
+      </c>
+      <c r="E334" t="n">
+        <v>1771425670</v>
+      </c>
+      <c r="F334" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>18-Feb-2026 20:11:30</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N334" t="n">
+        <v>163162136750</v>
+      </c>
+      <c r="O334" t="inlineStr"/>
+      <c r="P334" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr"/>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr"/>
+      <c r="V334" t="inlineStr"/>
+      <c r="W334" t="inlineStr"/>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>CHINTAPALLI CHANDINI</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z334" t="n">
+        <v>9985304942</v>
+      </c>
+      <c r="AA334" t="inlineStr"/>
+      <c r="AB334" t="inlineStr"/>
+      <c r="AC334" t="inlineStr"/>
+      <c r="AD334" t="inlineStr"/>
+      <c r="AE334" t="inlineStr"/>
+      <c r="AF334" t="inlineStr"/>
+      <c r="AG334" t="inlineStr"/>
+      <c r="AH334" t="inlineStr"/>
+      <c r="AI334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK334" t="inlineStr"/>
+      <c r="AL334" t="inlineStr"/>
+      <c r="AM334" t="inlineStr"/>
+      <c r="AN334" t="inlineStr"/>
+      <c r="AO334" t="inlineStr"/>
+      <c r="AP334" t="inlineStr"/>
+      <c r="AQ334" t="inlineStr"/>
+      <c r="AR334" t="inlineStr"/>
+      <c r="AS334" t="inlineStr"/>
+      <c r="AT334" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU334" t="inlineStr"/>
+      <c r="AV334" t="inlineStr"/>
+      <c r="AW334" t="inlineStr"/>
+      <c r="AX334" t="inlineStr"/>
+      <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr"/>
+      <c r="BA334" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB334" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC334" t="inlineStr"/>
+      <c r="BD334" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE334" t="n">
+        <v>18866</v>
+      </c>
+      <c r="BF334" t="inlineStr">
+        <is>
+          <t>267547</t>
+        </is>
+      </c>
+      <c r="BG334" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH334" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI334" t="n">
+        <v>15618</v>
+      </c>
+      <c r="BJ334" t="inlineStr"/>
+      <c r="BK334" t="inlineStr"/>
+      <c r="BL334" t="inlineStr"/>
+      <c r="BM334" t="inlineStr"/>
+      <c r="BN334" t="inlineStr"/>
+      <c r="BO334" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP334" t="inlineStr"/>
+      <c r="BQ334" t="inlineStr"/>
+      <c r="BR334" t="inlineStr"/>
+      <c r="BS334" t="inlineStr"/>
+      <c r="BT334" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU334" t="inlineStr"/>
+      <c r="BV334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C335" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D335" t="n">
+        <v>11000350731636</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1771425769</v>
+      </c>
+      <c r="F335" t="n">
+        <v>11350</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>18-Feb-2026 20:13:07</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N335" t="n">
+        <v>842044167452</v>
+      </c>
+      <c r="O335" t="inlineStr"/>
+      <c r="P335" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr"/>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr"/>
+      <c r="V335" t="inlineStr"/>
+      <c r="W335" t="inlineStr"/>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>CHINTAPALLI CHATHAN SWAROOP</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z335" t="n">
+        <v>9985304942</v>
+      </c>
+      <c r="AA335" t="inlineStr"/>
+      <c r="AB335" t="inlineStr"/>
+      <c r="AC335" t="inlineStr"/>
+      <c r="AD335" t="inlineStr"/>
+      <c r="AE335" t="inlineStr"/>
+      <c r="AF335" t="inlineStr"/>
+      <c r="AG335" t="inlineStr"/>
+      <c r="AH335" t="inlineStr"/>
+      <c r="AI335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK335" t="inlineStr"/>
+      <c r="AL335" t="inlineStr"/>
+      <c r="AM335" t="inlineStr"/>
+      <c r="AN335" t="inlineStr"/>
+      <c r="AO335" t="inlineStr"/>
+      <c r="AP335" t="inlineStr"/>
+      <c r="AQ335" t="inlineStr"/>
+      <c r="AR335" t="inlineStr"/>
+      <c r="AS335" t="inlineStr"/>
+      <c r="AT335" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU335" t="inlineStr"/>
+      <c r="AV335" t="inlineStr"/>
+      <c r="AW335" t="inlineStr"/>
+      <c r="AX335" t="inlineStr"/>
+      <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr"/>
+      <c r="BA335" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB335" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC335" t="inlineStr"/>
+      <c r="BD335" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE335" t="n">
+        <v>19397</v>
+      </c>
+      <c r="BF335" t="inlineStr">
+        <is>
+          <t>268068</t>
+        </is>
+      </c>
+      <c r="BG335" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="BH335" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI335" t="n">
+        <v>14706</v>
+      </c>
+      <c r="BJ335" t="inlineStr"/>
+      <c r="BK335" t="inlineStr"/>
+      <c r="BL335" t="inlineStr"/>
+      <c r="BM335" t="inlineStr"/>
+      <c r="BN335" t="inlineStr"/>
+      <c r="BO335" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP335" t="inlineStr"/>
+      <c r="BQ335" t="inlineStr"/>
+      <c r="BR335" t="inlineStr"/>
+      <c r="BS335" t="inlineStr"/>
+      <c r="BT335" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU335" t="inlineStr"/>
+      <c r="BV335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV335"/>
+  <dimension ref="A1:BV369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66005,7 +66005,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N333" t="n">
@@ -66053,16 +66053,24 @@
       <c r="AD333" t="inlineStr"/>
       <c r="AE333" t="inlineStr"/>
       <c r="AF333" t="inlineStr"/>
-      <c r="AG333" t="inlineStr"/>
-      <c r="AH333" t="inlineStr"/>
+      <c r="AG333" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH333" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI333" t="n">
         <v>0</v>
       </c>
       <c r="AJ333" t="n">
         <v>0</v>
       </c>
-      <c r="AK333" t="inlineStr"/>
-      <c r="AL333" t="inlineStr"/>
+      <c r="AK333" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL333" t="n">
+        <v>8650</v>
+      </c>
       <c r="AM333" t="inlineStr"/>
       <c r="AN333" t="inlineStr"/>
       <c r="AO333" t="inlineStr"/>
@@ -66195,7 +66203,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="N334" t="n">
@@ -66210,7 +66218,11 @@
           <t>SIBL0000899</t>
         </is>
       </c>
-      <c r="R334" t="inlineStr"/>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>20-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="S334" t="inlineStr">
         <is>
           <t>MERCHANT</t>
@@ -66243,17 +66255,29 @@
       <c r="AD334" t="inlineStr"/>
       <c r="AE334" t="inlineStr"/>
       <c r="AF334" t="inlineStr"/>
-      <c r="AG334" t="inlineStr"/>
-      <c r="AH334" t="inlineStr"/>
+      <c r="AG334" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH334" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI334" t="n">
         <v>0</v>
       </c>
       <c r="AJ334" t="n">
         <v>0</v>
       </c>
-      <c r="AK334" t="inlineStr"/>
-      <c r="AL334" t="inlineStr"/>
-      <c r="AM334" t="inlineStr"/>
+      <c r="AK334" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL334" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM334" t="inlineStr">
+        <is>
+          <t>20-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="AN334" t="inlineStr"/>
       <c r="AO334" t="inlineStr"/>
       <c r="AP334" t="inlineStr"/>
@@ -66385,7 +66409,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="N335" t="n">
@@ -66433,16 +66457,24 @@
       <c r="AD335" t="inlineStr"/>
       <c r="AE335" t="inlineStr"/>
       <c r="AF335" t="inlineStr"/>
-      <c r="AG335" t="inlineStr"/>
-      <c r="AH335" t="inlineStr"/>
+      <c r="AG335" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH335" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AI335" t="n">
         <v>0</v>
       </c>
       <c r="AJ335" t="n">
         <v>0</v>
       </c>
-      <c r="AK335" t="inlineStr"/>
-      <c r="AL335" t="inlineStr"/>
+      <c r="AK335" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL335" t="n">
+        <v>11350</v>
+      </c>
       <c r="AM335" t="inlineStr"/>
       <c r="AN335" t="inlineStr"/>
       <c r="AO335" t="inlineStr"/>
@@ -66522,6 +66554,6742 @@
         </is>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C336" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D336" t="n">
+        <v>11000350963982</v>
+      </c>
+      <c r="E336" t="n">
+        <v>1771554340</v>
+      </c>
+      <c r="F336" t="n">
+        <v>10750</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>20-Feb-2026 07:56:35</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N336" t="n">
+        <v>109227319525</v>
+      </c>
+      <c r="O336" t="inlineStr"/>
+      <c r="P336" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr"/>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr"/>
+      <c r="V336" t="inlineStr"/>
+      <c r="W336" t="inlineStr"/>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>SHAIK GOUSIA NASRIN</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z336" t="n">
+        <v>7207749584</v>
+      </c>
+      <c r="AA336" t="inlineStr"/>
+      <c r="AB336" t="inlineStr"/>
+      <c r="AC336" t="inlineStr"/>
+      <c r="AD336" t="inlineStr"/>
+      <c r="AE336" t="inlineStr"/>
+      <c r="AF336" t="inlineStr"/>
+      <c r="AG336" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH336" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI336" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ336" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK336" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL336" t="n">
+        <v>10750</v>
+      </c>
+      <c r="AM336" t="inlineStr"/>
+      <c r="AN336" t="inlineStr"/>
+      <c r="AO336" t="inlineStr"/>
+      <c r="AP336" t="inlineStr"/>
+      <c r="AQ336" t="inlineStr"/>
+      <c r="AR336" t="inlineStr"/>
+      <c r="AS336" t="inlineStr"/>
+      <c r="AT336" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU336" t="inlineStr"/>
+      <c r="AV336" t="inlineStr"/>
+      <c r="AW336" t="inlineStr"/>
+      <c r="AX336" t="inlineStr"/>
+      <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr"/>
+      <c r="BA336" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB336" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC336" t="inlineStr"/>
+      <c r="BD336" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE336" t="n">
+        <v>19200</v>
+      </c>
+      <c r="BF336" t="inlineStr">
+        <is>
+          <t>266268</t>
+        </is>
+      </c>
+      <c r="BG336" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="BH336" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI336" t="n">
+        <v>14888</v>
+      </c>
+      <c r="BJ336" t="inlineStr"/>
+      <c r="BK336" t="inlineStr"/>
+      <c r="BL336" t="inlineStr"/>
+      <c r="BM336" t="inlineStr"/>
+      <c r="BN336" t="inlineStr"/>
+      <c r="BO336" t="inlineStr"/>
+      <c r="BP336" t="inlineStr"/>
+      <c r="BQ336" t="inlineStr"/>
+      <c r="BR336" t="inlineStr"/>
+      <c r="BS336" t="inlineStr"/>
+      <c r="BT336" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU336" t="inlineStr"/>
+      <c r="BV336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C337" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D337" t="n">
+        <v>11000351187164</v>
+      </c>
+      <c r="E337" t="n">
+        <v>1771744152</v>
+      </c>
+      <c r="F337" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>22-Feb-2026 12:39:56</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N337" t="n">
+        <v>109240823792</v>
+      </c>
+      <c r="O337" t="inlineStr"/>
+      <c r="P337" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr"/>
+      <c r="V337" t="inlineStr"/>
+      <c r="W337" t="inlineStr"/>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>REYANA SRIJITH</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z337" t="n">
+        <v>9985925345</v>
+      </c>
+      <c r="AA337" t="inlineStr"/>
+      <c r="AB337" t="inlineStr"/>
+      <c r="AC337" t="inlineStr"/>
+      <c r="AD337" t="inlineStr"/>
+      <c r="AE337" t="inlineStr"/>
+      <c r="AF337" t="inlineStr"/>
+      <c r="AG337" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH337" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI337" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ337" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK337" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL337" t="n">
+        <v>7750</v>
+      </c>
+      <c r="AM337" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN337" t="inlineStr"/>
+      <c r="AO337" t="inlineStr"/>
+      <c r="AP337" t="inlineStr"/>
+      <c r="AQ337" t="inlineStr"/>
+      <c r="AR337" t="inlineStr"/>
+      <c r="AS337" t="inlineStr"/>
+      <c r="AT337" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU337" t="inlineStr"/>
+      <c r="AV337" t="inlineStr"/>
+      <c r="AW337" t="inlineStr"/>
+      <c r="AX337" t="inlineStr"/>
+      <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr"/>
+      <c r="BA337" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB337" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC337" t="inlineStr"/>
+      <c r="BD337" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE337" t="n">
+        <v>19902</v>
+      </c>
+      <c r="BF337" t="inlineStr">
+        <is>
+          <t>266990</t>
+        </is>
+      </c>
+      <c r="BG337" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH337" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI337" t="n">
+        <v>17188</v>
+      </c>
+      <c r="BJ337" t="inlineStr"/>
+      <c r="BK337" t="inlineStr"/>
+      <c r="BL337" t="inlineStr"/>
+      <c r="BM337" t="inlineStr"/>
+      <c r="BN337" t="inlineStr"/>
+      <c r="BO337" t="inlineStr"/>
+      <c r="BP337" t="inlineStr"/>
+      <c r="BQ337" t="inlineStr"/>
+      <c r="BR337" t="inlineStr"/>
+      <c r="BS337" t="inlineStr"/>
+      <c r="BT337" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU337" t="inlineStr"/>
+      <c r="BV337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C338" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D338" t="n">
+        <v>11000351225842</v>
+      </c>
+      <c r="E338" t="n">
+        <v>1771778816</v>
+      </c>
+      <c r="F338" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>22-Feb-2026 22:18:36</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr"/>
+      <c r="P338" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr"/>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr"/>
+      <c r="V338" t="inlineStr"/>
+      <c r="W338" t="inlineStr"/>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>GANIREDDY AISHWARYA</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z338" t="n">
+        <v>6302459147</v>
+      </c>
+      <c r="AA338" t="inlineStr"/>
+      <c r="AB338" t="inlineStr"/>
+      <c r="AC338" t="inlineStr"/>
+      <c r="AD338" t="inlineStr"/>
+      <c r="AE338" t="inlineStr"/>
+      <c r="AF338" t="inlineStr"/>
+      <c r="AG338" t="inlineStr"/>
+      <c r="AH338" t="inlineStr"/>
+      <c r="AI338" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ338" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK338" t="inlineStr"/>
+      <c r="AL338" t="inlineStr"/>
+      <c r="AM338" t="inlineStr"/>
+      <c r="AN338" t="inlineStr"/>
+      <c r="AO338" t="inlineStr"/>
+      <c r="AP338" t="inlineStr"/>
+      <c r="AQ338" t="inlineStr"/>
+      <c r="AR338" t="inlineStr"/>
+      <c r="AS338" t="inlineStr"/>
+      <c r="AT338" t="inlineStr">
+        <is>
+          <t>BQR TRANSACTION IS TIMED OUT</t>
+        </is>
+      </c>
+      <c r="AU338" t="inlineStr"/>
+      <c r="AV338" t="inlineStr"/>
+      <c r="AW338" t="inlineStr"/>
+      <c r="AX338" t="inlineStr"/>
+      <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr"/>
+      <c r="BA338" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB338" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC338" t="inlineStr"/>
+      <c r="BD338" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE338" t="n">
+        <v>19023</v>
+      </c>
+      <c r="BF338" t="inlineStr">
+        <is>
+          <t>266049</t>
+        </is>
+      </c>
+      <c r="BG338" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH338" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI338" t="n">
+        <v>16056</v>
+      </c>
+      <c r="BJ338" t="inlineStr"/>
+      <c r="BK338" t="inlineStr"/>
+      <c r="BL338" t="inlineStr"/>
+      <c r="BM338" t="inlineStr"/>
+      <c r="BN338" t="inlineStr"/>
+      <c r="BO338" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP338" t="inlineStr"/>
+      <c r="BQ338" t="inlineStr"/>
+      <c r="BR338" t="inlineStr"/>
+      <c r="BS338" t="inlineStr"/>
+      <c r="BT338" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU338" t="inlineStr"/>
+      <c r="BV338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C339" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D339" t="n">
+        <v>11000351226381</v>
+      </c>
+      <c r="E339" t="n">
+        <v>1771778816</v>
+      </c>
+      <c r="F339" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>22-Feb-2026 22:22:18</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N339" t="n">
+        <v>302542306467</v>
+      </c>
+      <c r="O339" t="n">
+        <v>302542306467</v>
+      </c>
+      <c r="P339" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr"/>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr"/>
+      <c r="V339" t="inlineStr"/>
+      <c r="W339" t="inlineStr"/>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>GANIREDDY AISHWARYA</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z339" t="n">
+        <v>6302459147</v>
+      </c>
+      <c r="AA339" t="inlineStr"/>
+      <c r="AB339" t="inlineStr"/>
+      <c r="AC339" t="inlineStr"/>
+      <c r="AD339" t="inlineStr"/>
+      <c r="AE339" t="inlineStr"/>
+      <c r="AF339" t="inlineStr"/>
+      <c r="AG339" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH339" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI339" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ339" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK339" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL339" t="n">
+        <v>8650</v>
+      </c>
+      <c r="AM339" t="inlineStr"/>
+      <c r="AN339" t="inlineStr"/>
+      <c r="AO339" t="inlineStr"/>
+      <c r="AP339" t="inlineStr"/>
+      <c r="AQ339" t="inlineStr"/>
+      <c r="AR339" t="inlineStr"/>
+      <c r="AS339" t="inlineStr"/>
+      <c r="AT339" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU339" t="inlineStr"/>
+      <c r="AV339" t="inlineStr"/>
+      <c r="AW339" t="inlineStr"/>
+      <c r="AX339" t="inlineStr"/>
+      <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr"/>
+      <c r="BA339" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB339" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC339" t="inlineStr"/>
+      <c r="BD339" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE339" t="n">
+        <v>19023</v>
+      </c>
+      <c r="BF339" t="inlineStr">
+        <is>
+          <t>266049</t>
+        </is>
+      </c>
+      <c r="BG339" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="BH339" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI339" t="n">
+        <v>16056</v>
+      </c>
+      <c r="BJ339" t="inlineStr"/>
+      <c r="BK339" t="inlineStr"/>
+      <c r="BL339" t="inlineStr"/>
+      <c r="BM339" t="inlineStr"/>
+      <c r="BN339" t="inlineStr"/>
+      <c r="BO339" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP339" t="inlineStr"/>
+      <c r="BQ339" t="inlineStr"/>
+      <c r="BR339" t="inlineStr"/>
+      <c r="BS339" t="inlineStr"/>
+      <c r="BT339" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU339" t="inlineStr"/>
+      <c r="BV339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C340" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D340" t="n">
+        <v>11000351228098</v>
+      </c>
+      <c r="E340" t="n">
+        <v>1771779418</v>
+      </c>
+      <c r="F340" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>22-Feb-2026 22:46:16</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N340" t="n">
+        <v>640262345476</v>
+      </c>
+      <c r="O340" t="n">
+        <v>640262345476</v>
+      </c>
+      <c r="P340" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr"/>
+      <c r="V340" t="inlineStr"/>
+      <c r="W340" t="inlineStr"/>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>GANIREDDY ANUHYA</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z340" t="n">
+        <v>9848537189</v>
+      </c>
+      <c r="AA340" t="inlineStr"/>
+      <c r="AB340" t="inlineStr"/>
+      <c r="AC340" t="inlineStr"/>
+      <c r="AD340" t="inlineStr"/>
+      <c r="AE340" t="inlineStr"/>
+      <c r="AF340" t="inlineStr"/>
+      <c r="AG340" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH340" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI340" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ340" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK340" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL340" t="n">
+        <v>8050</v>
+      </c>
+      <c r="AM340" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN340" t="inlineStr"/>
+      <c r="AO340" t="inlineStr"/>
+      <c r="AP340" t="inlineStr"/>
+      <c r="AQ340" t="inlineStr"/>
+      <c r="AR340" t="inlineStr"/>
+      <c r="AS340" t="inlineStr"/>
+      <c r="AT340" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU340" t="inlineStr"/>
+      <c r="AV340" t="inlineStr"/>
+      <c r="AW340" t="inlineStr"/>
+      <c r="AX340" t="inlineStr"/>
+      <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr"/>
+      <c r="BA340" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB340" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC340" t="inlineStr"/>
+      <c r="BD340" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE340" t="n">
+        <v>18375</v>
+      </c>
+      <c r="BF340" t="inlineStr">
+        <is>
+          <t>267107</t>
+        </is>
+      </c>
+      <c r="BG340" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH340" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI340" t="n">
+        <v>16552</v>
+      </c>
+      <c r="BJ340" t="inlineStr"/>
+      <c r="BK340" t="inlineStr"/>
+      <c r="BL340" t="inlineStr"/>
+      <c r="BM340" t="inlineStr"/>
+      <c r="BN340" t="inlineStr"/>
+      <c r="BO340" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP340" t="inlineStr"/>
+      <c r="BQ340" t="inlineStr"/>
+      <c r="BR340" t="inlineStr"/>
+      <c r="BS340" t="inlineStr"/>
+      <c r="BT340" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU340" t="inlineStr"/>
+      <c r="BV340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C341" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D341" t="n">
+        <v>11000351269193</v>
+      </c>
+      <c r="E341" t="n">
+        <v>1771825072</v>
+      </c>
+      <c r="F341" t="n">
+        <v>11350</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 11:09:23</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N341" t="n">
+        <v>109246378284</v>
+      </c>
+      <c r="O341" t="inlineStr"/>
+      <c r="P341" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr"/>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr"/>
+      <c r="V341" t="inlineStr"/>
+      <c r="W341" t="inlineStr"/>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>MYCHERLA SHASANK</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z341" t="n">
+        <v>7386344393</v>
+      </c>
+      <c r="AA341" t="inlineStr"/>
+      <c r="AB341" t="inlineStr"/>
+      <c r="AC341" t="inlineStr"/>
+      <c r="AD341" t="inlineStr"/>
+      <c r="AE341" t="inlineStr"/>
+      <c r="AF341" t="inlineStr"/>
+      <c r="AG341" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH341" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI341" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ341" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK341" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL341" t="n">
+        <v>11350</v>
+      </c>
+      <c r="AM341" t="inlineStr"/>
+      <c r="AN341" t="inlineStr"/>
+      <c r="AO341" t="inlineStr"/>
+      <c r="AP341" t="inlineStr"/>
+      <c r="AQ341" t="inlineStr"/>
+      <c r="AR341" t="inlineStr"/>
+      <c r="AS341" t="inlineStr"/>
+      <c r="AT341" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU341" t="inlineStr"/>
+      <c r="AV341" t="inlineStr"/>
+      <c r="AW341" t="inlineStr"/>
+      <c r="AX341" t="inlineStr"/>
+      <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr"/>
+      <c r="BA341" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB341" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC341" t="inlineStr"/>
+      <c r="BD341" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE341" t="n">
+        <v>19412</v>
+      </c>
+      <c r="BF341" t="inlineStr">
+        <is>
+          <t>268102</t>
+        </is>
+      </c>
+      <c r="BG341" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="BH341" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI341" t="n">
+        <v>16208</v>
+      </c>
+      <c r="BJ341" t="inlineStr"/>
+      <c r="BK341" t="inlineStr"/>
+      <c r="BL341" t="inlineStr"/>
+      <c r="BM341" t="inlineStr"/>
+      <c r="BN341" t="inlineStr"/>
+      <c r="BO341" t="inlineStr"/>
+      <c r="BP341" t="inlineStr"/>
+      <c r="BQ341" t="inlineStr"/>
+      <c r="BR341" t="inlineStr"/>
+      <c r="BS341" t="inlineStr"/>
+      <c r="BT341" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU341" t="inlineStr"/>
+      <c r="BV341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C342" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D342" t="n">
+        <v>11000351328822</v>
+      </c>
+      <c r="E342" t="n">
+        <v>1771848461</v>
+      </c>
+      <c r="F342" t="n">
+        <v>10750</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 17:39:15</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N342" t="n">
+        <v>109248745854</v>
+      </c>
+      <c r="O342" t="inlineStr"/>
+      <c r="P342" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr"/>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr"/>
+      <c r="V342" t="inlineStr"/>
+      <c r="W342" t="inlineStr"/>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>RANVITHA SEERA</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z342" t="n">
+        <v>7095076706</v>
+      </c>
+      <c r="AA342" t="inlineStr"/>
+      <c r="AB342" t="inlineStr"/>
+      <c r="AC342" t="inlineStr"/>
+      <c r="AD342" t="inlineStr"/>
+      <c r="AE342" t="inlineStr"/>
+      <c r="AF342" t="inlineStr"/>
+      <c r="AG342" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH342" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK342" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL342" t="n">
+        <v>10750</v>
+      </c>
+      <c r="AM342" t="inlineStr"/>
+      <c r="AN342" t="inlineStr"/>
+      <c r="AO342" t="inlineStr"/>
+      <c r="AP342" t="inlineStr"/>
+      <c r="AQ342" t="inlineStr"/>
+      <c r="AR342" t="inlineStr"/>
+      <c r="AS342" t="inlineStr"/>
+      <c r="AT342" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU342" t="inlineStr"/>
+      <c r="AV342" t="inlineStr"/>
+      <c r="AW342" t="inlineStr"/>
+      <c r="AX342" t="inlineStr"/>
+      <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr"/>
+      <c r="BA342" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB342" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="BC342" t="inlineStr"/>
+      <c r="BD342" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE342" t="n">
+        <v>19168</v>
+      </c>
+      <c r="BF342" t="inlineStr">
+        <is>
+          <t>268578</t>
+        </is>
+      </c>
+      <c r="BG342" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="BH342" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI342" t="n">
+        <v>16906</v>
+      </c>
+      <c r="BJ342" t="inlineStr"/>
+      <c r="BK342" t="inlineStr"/>
+      <c r="BL342" t="inlineStr"/>
+      <c r="BM342" t="inlineStr"/>
+      <c r="BN342" t="inlineStr"/>
+      <c r="BO342" t="inlineStr"/>
+      <c r="BP342" t="inlineStr"/>
+      <c r="BQ342" t="inlineStr"/>
+      <c r="BR342" t="inlineStr"/>
+      <c r="BS342" t="inlineStr"/>
+      <c r="BT342" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU342" t="inlineStr"/>
+      <c r="BV342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C343" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D343" t="n">
+        <v>11000351453145</v>
+      </c>
+      <c r="E343" t="n">
+        <v>1771934170</v>
+      </c>
+      <c r="F343" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>24-Feb-2026 17:26:28</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N343" t="n">
+        <v>929800159168</v>
+      </c>
+      <c r="O343" t="n">
+        <v>929800159168</v>
+      </c>
+      <c r="P343" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr"/>
+      <c r="V343" t="inlineStr"/>
+      <c r="W343" t="inlineStr"/>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>VINDYA SOWDALA</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z343" t="n">
+        <v>7075489300</v>
+      </c>
+      <c r="AA343" t="inlineStr"/>
+      <c r="AB343" t="inlineStr"/>
+      <c r="AC343" t="inlineStr"/>
+      <c r="AD343" t="inlineStr"/>
+      <c r="AE343" t="inlineStr"/>
+      <c r="AF343" t="inlineStr"/>
+      <c r="AG343" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH343" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI343" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ343" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK343" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL343" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM343" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN343" t="inlineStr"/>
+      <c r="AO343" t="inlineStr"/>
+      <c r="AP343" t="inlineStr"/>
+      <c r="AQ343" t="inlineStr"/>
+      <c r="AR343" t="inlineStr"/>
+      <c r="AS343" t="inlineStr"/>
+      <c r="AT343" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU343" t="inlineStr"/>
+      <c r="AV343" t="inlineStr"/>
+      <c r="AW343" t="inlineStr"/>
+      <c r="AX343" t="inlineStr"/>
+      <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr"/>
+      <c r="BA343" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB343" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC343" t="inlineStr"/>
+      <c r="BD343" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE343" t="n">
+        <v>18095</v>
+      </c>
+      <c r="BF343" t="inlineStr">
+        <is>
+          <t>266761</t>
+        </is>
+      </c>
+      <c r="BG343" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH343" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI343" t="n">
+        <v>17099</v>
+      </c>
+      <c r="BJ343" t="inlineStr"/>
+      <c r="BK343" t="inlineStr"/>
+      <c r="BL343" t="inlineStr"/>
+      <c r="BM343" t="inlineStr"/>
+      <c r="BN343" t="inlineStr"/>
+      <c r="BO343" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP343" t="inlineStr"/>
+      <c r="BQ343" t="inlineStr"/>
+      <c r="BR343" t="inlineStr"/>
+      <c r="BS343" t="inlineStr"/>
+      <c r="BT343" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU343" t="inlineStr"/>
+      <c r="BV343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C344" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D344" t="n">
+        <v>11000351454113</v>
+      </c>
+      <c r="E344" t="n">
+        <v>1771934227</v>
+      </c>
+      <c r="F344" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>24-Feb-2026 17:27:19</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N344" t="n">
+        <v>555789383766</v>
+      </c>
+      <c r="O344" t="n">
+        <v>555789383766</v>
+      </c>
+      <c r="P344" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr"/>
+      <c r="V344" t="inlineStr"/>
+      <c r="W344" t="inlineStr"/>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>BHAVIYSA SOWDALA</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z344" t="n">
+        <v>7075489300</v>
+      </c>
+      <c r="AA344" t="inlineStr"/>
+      <c r="AB344" t="inlineStr"/>
+      <c r="AC344" t="inlineStr"/>
+      <c r="AD344" t="inlineStr"/>
+      <c r="AE344" t="inlineStr"/>
+      <c r="AF344" t="inlineStr"/>
+      <c r="AG344" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH344" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI344" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ344" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK344" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL344" t="n">
+        <v>8050</v>
+      </c>
+      <c r="AM344" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN344" t="inlineStr"/>
+      <c r="AO344" t="inlineStr"/>
+      <c r="AP344" t="inlineStr"/>
+      <c r="AQ344" t="inlineStr"/>
+      <c r="AR344" t="inlineStr"/>
+      <c r="AS344" t="inlineStr"/>
+      <c r="AT344" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU344" t="inlineStr"/>
+      <c r="AV344" t="inlineStr"/>
+      <c r="AW344" t="inlineStr"/>
+      <c r="AX344" t="inlineStr"/>
+      <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr"/>
+      <c r="BA344" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB344" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC344" t="inlineStr"/>
+      <c r="BD344" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE344" t="n">
+        <v>18638</v>
+      </c>
+      <c r="BF344" t="inlineStr">
+        <is>
+          <t>267297</t>
+        </is>
+      </c>
+      <c r="BG344" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH344" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI344" t="n">
+        <v>17100</v>
+      </c>
+      <c r="BJ344" t="inlineStr"/>
+      <c r="BK344" t="inlineStr"/>
+      <c r="BL344" t="inlineStr"/>
+      <c r="BM344" t="inlineStr"/>
+      <c r="BN344" t="inlineStr"/>
+      <c r="BO344" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP344" t="inlineStr"/>
+      <c r="BQ344" t="inlineStr"/>
+      <c r="BR344" t="inlineStr"/>
+      <c r="BS344" t="inlineStr"/>
+      <c r="BT344" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU344" t="inlineStr"/>
+      <c r="BV344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C345" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D345" t="n">
+        <v>11000351479569</v>
+      </c>
+      <c r="E345" t="n">
+        <v>1771953532</v>
+      </c>
+      <c r="F345" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>24-Feb-2026 22:50:26</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N345" t="n">
+        <v>145208162</v>
+      </c>
+      <c r="O345" t="n">
+        <v>145208162</v>
+      </c>
+      <c r="P345" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr"/>
+      <c r="V345" t="inlineStr"/>
+      <c r="W345" t="inlineStr"/>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>BORA LYDIA</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z345" t="n">
+        <v>6309196999</v>
+      </c>
+      <c r="AA345" t="inlineStr"/>
+      <c r="AB345" t="inlineStr"/>
+      <c r="AC345" t="inlineStr"/>
+      <c r="AD345" t="inlineStr"/>
+      <c r="AE345" t="inlineStr"/>
+      <c r="AF345" t="inlineStr"/>
+      <c r="AG345" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH345" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK345" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL345" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM345" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN345" t="inlineStr"/>
+      <c r="AO345" t="inlineStr"/>
+      <c r="AP345" t="inlineStr"/>
+      <c r="AQ345" t="inlineStr"/>
+      <c r="AR345" t="inlineStr"/>
+      <c r="AS345" t="inlineStr"/>
+      <c r="AT345" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU345" t="inlineStr"/>
+      <c r="AV345" t="inlineStr"/>
+      <c r="AW345" t="inlineStr"/>
+      <c r="AX345" t="inlineStr"/>
+      <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr"/>
+      <c r="BA345" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB345" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC345" t="inlineStr"/>
+      <c r="BD345" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE345" t="n">
+        <v>19894</v>
+      </c>
+      <c r="BF345" t="inlineStr">
+        <is>
+          <t>266635</t>
+        </is>
+      </c>
+      <c r="BG345" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH345" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI345" t="n">
+        <v>17179</v>
+      </c>
+      <c r="BJ345" t="inlineStr"/>
+      <c r="BK345" t="inlineStr"/>
+      <c r="BL345" t="inlineStr"/>
+      <c r="BM345" t="inlineStr"/>
+      <c r="BN345" t="inlineStr"/>
+      <c r="BO345" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP345" t="inlineStr"/>
+      <c r="BQ345" t="inlineStr"/>
+      <c r="BR345" t="inlineStr"/>
+      <c r="BS345" t="inlineStr"/>
+      <c r="BT345" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU345" t="inlineStr"/>
+      <c r="BV345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C346" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D346" t="n">
+        <v>11000351595092</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1772034489</v>
+      </c>
+      <c r="F346" t="n">
+        <v>25550</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 21:19:38</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N346" t="n">
+        <v>109262506265</v>
+      </c>
+      <c r="O346" t="inlineStr"/>
+      <c r="P346" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>26-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr"/>
+      <c r="V346" t="inlineStr"/>
+      <c r="W346" t="inlineStr"/>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>TANDU ROSARY ANTHONY</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z346" t="n">
+        <v>9492868687</v>
+      </c>
+      <c r="AA346" t="inlineStr"/>
+      <c r="AB346" t="inlineStr"/>
+      <c r="AC346" t="inlineStr"/>
+      <c r="AD346" t="inlineStr"/>
+      <c r="AE346" t="inlineStr"/>
+      <c r="AF346" t="inlineStr"/>
+      <c r="AG346" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH346" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI346" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ346" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK346" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL346" t="n">
+        <v>25550</v>
+      </c>
+      <c r="AM346" t="inlineStr">
+        <is>
+          <t>26-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN346" t="inlineStr"/>
+      <c r="AO346" t="inlineStr"/>
+      <c r="AP346" t="inlineStr"/>
+      <c r="AQ346" t="inlineStr"/>
+      <c r="AR346" t="inlineStr"/>
+      <c r="AS346" t="inlineStr"/>
+      <c r="AT346" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU346" t="inlineStr"/>
+      <c r="AV346" t="inlineStr"/>
+      <c r="AW346" t="inlineStr"/>
+      <c r="AX346" t="inlineStr"/>
+      <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr"/>
+      <c r="BA346" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB346" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC346" t="inlineStr"/>
+      <c r="BD346" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE346" t="n">
+        <v>18727</v>
+      </c>
+      <c r="BF346" t="inlineStr">
+        <is>
+          <t>261176,262330,264151,265801</t>
+        </is>
+      </c>
+      <c r="BG346" t="inlineStr">
+        <is>
+          <t>2033,2037,2042,2050</t>
+        </is>
+      </c>
+      <c r="BH346" t="inlineStr">
+        <is>
+          <t>twenty five thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI346" t="n">
+        <v>16120</v>
+      </c>
+      <c r="BJ346" t="inlineStr"/>
+      <c r="BK346" t="inlineStr"/>
+      <c r="BL346" t="inlineStr"/>
+      <c r="BM346" t="inlineStr"/>
+      <c r="BN346" t="inlineStr"/>
+      <c r="BO346" t="inlineStr"/>
+      <c r="BP346" t="inlineStr"/>
+      <c r="BQ346" t="inlineStr"/>
+      <c r="BR346" t="inlineStr"/>
+      <c r="BS346" t="inlineStr"/>
+      <c r="BT346" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU346" t="inlineStr"/>
+      <c r="BV346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C347" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D347" t="n">
+        <v>11000351694708</v>
+      </c>
+      <c r="E347" t="n">
+        <v>1772103829</v>
+      </c>
+      <c r="F347" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>26-Feb-2026 16:35:02</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N347" t="n">
+        <v>109267256087</v>
+      </c>
+      <c r="O347" t="inlineStr"/>
+      <c r="P347" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>27-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr"/>
+      <c r="V347" t="inlineStr"/>
+      <c r="W347" t="inlineStr"/>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>OMMI NIDHISH NANDAN</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z347" t="n">
+        <v>8008110591</v>
+      </c>
+      <c r="AA347" t="inlineStr"/>
+      <c r="AB347" t="inlineStr"/>
+      <c r="AC347" t="inlineStr"/>
+      <c r="AD347" t="inlineStr"/>
+      <c r="AE347" t="inlineStr"/>
+      <c r="AF347" t="inlineStr"/>
+      <c r="AG347" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH347" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK347" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL347" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM347" t="inlineStr">
+        <is>
+          <t>27-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN347" t="inlineStr"/>
+      <c r="AO347" t="inlineStr"/>
+      <c r="AP347" t="inlineStr"/>
+      <c r="AQ347" t="inlineStr"/>
+      <c r="AR347" t="inlineStr"/>
+      <c r="AS347" t="inlineStr"/>
+      <c r="AT347" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU347" t="inlineStr"/>
+      <c r="AV347" t="inlineStr"/>
+      <c r="AW347" t="inlineStr"/>
+      <c r="AX347" t="inlineStr"/>
+      <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr"/>
+      <c r="BA347" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB347" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC347" t="inlineStr"/>
+      <c r="BD347" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE347" t="n">
+        <v>18105</v>
+      </c>
+      <c r="BF347" t="inlineStr">
+        <is>
+          <t>266784</t>
+        </is>
+      </c>
+      <c r="BG347" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH347" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI347" t="n">
+        <v>16977</v>
+      </c>
+      <c r="BJ347" t="inlineStr"/>
+      <c r="BK347" t="inlineStr"/>
+      <c r="BL347" t="inlineStr"/>
+      <c r="BM347" t="inlineStr"/>
+      <c r="BN347" t="inlineStr"/>
+      <c r="BO347" t="inlineStr"/>
+      <c r="BP347" t="inlineStr"/>
+      <c r="BQ347" t="inlineStr"/>
+      <c r="BR347" t="inlineStr"/>
+      <c r="BS347" t="inlineStr"/>
+      <c r="BT347" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU347" t="inlineStr"/>
+      <c r="BV347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C348" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D348" t="n">
+        <v>11000351725842</v>
+      </c>
+      <c r="E348" t="n">
+        <v>1772119422</v>
+      </c>
+      <c r="F348" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>26-Feb-2026 20:59:33</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N348" t="n">
+        <v>109268695191</v>
+      </c>
+      <c r="O348" t="inlineStr"/>
+      <c r="P348" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>27-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr"/>
+      <c r="V348" t="inlineStr"/>
+      <c r="W348" t="inlineStr"/>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>AADHVIK DADIRAO</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z348" t="n">
+        <v>7075570737</v>
+      </c>
+      <c r="AA348" t="inlineStr"/>
+      <c r="AB348" t="inlineStr"/>
+      <c r="AC348" t="inlineStr"/>
+      <c r="AD348" t="inlineStr"/>
+      <c r="AE348" t="inlineStr"/>
+      <c r="AF348" t="inlineStr"/>
+      <c r="AG348" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH348" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK348" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL348" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM348" t="inlineStr">
+        <is>
+          <t>27-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN348" t="inlineStr"/>
+      <c r="AO348" t="inlineStr"/>
+      <c r="AP348" t="inlineStr"/>
+      <c r="AQ348" t="inlineStr"/>
+      <c r="AR348" t="inlineStr"/>
+      <c r="AS348" t="inlineStr"/>
+      <c r="AT348" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU348" t="inlineStr"/>
+      <c r="AV348" t="inlineStr"/>
+      <c r="AW348" t="inlineStr"/>
+      <c r="AX348" t="inlineStr"/>
+      <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr"/>
+      <c r="BA348" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB348" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC348" t="inlineStr"/>
+      <c r="BD348" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE348" t="n">
+        <v>18096</v>
+      </c>
+      <c r="BF348" t="inlineStr">
+        <is>
+          <t>266773</t>
+        </is>
+      </c>
+      <c r="BG348" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH348" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI348" t="n">
+        <v>17105</v>
+      </c>
+      <c r="BJ348" t="inlineStr"/>
+      <c r="BK348" t="inlineStr"/>
+      <c r="BL348" t="inlineStr"/>
+      <c r="BM348" t="inlineStr"/>
+      <c r="BN348" t="inlineStr"/>
+      <c r="BO348" t="inlineStr"/>
+      <c r="BP348" t="inlineStr"/>
+      <c r="BQ348" t="inlineStr"/>
+      <c r="BR348" t="inlineStr"/>
+      <c r="BS348" t="inlineStr"/>
+      <c r="BT348" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU348" t="inlineStr"/>
+      <c r="BV348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C349" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D349" t="n">
+        <v>11000351864684</v>
+      </c>
+      <c r="E349" t="n">
+        <v>1772201239</v>
+      </c>
+      <c r="F349" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>27-Feb-2026 19:37:49</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N349" t="n">
+        <v>605864009197</v>
+      </c>
+      <c r="O349" t="inlineStr"/>
+      <c r="P349" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr"/>
+      <c r="V349" t="inlineStr"/>
+      <c r="W349" t="inlineStr"/>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>VARTIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z349" t="n">
+        <v>8369239788</v>
+      </c>
+      <c r="AA349" t="inlineStr"/>
+      <c r="AB349" t="inlineStr"/>
+      <c r="AC349" t="inlineStr"/>
+      <c r="AD349" t="inlineStr"/>
+      <c r="AE349" t="inlineStr"/>
+      <c r="AF349" t="inlineStr"/>
+      <c r="AG349" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH349" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI349" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ349" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK349" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL349" t="n">
+        <v>7750</v>
+      </c>
+      <c r="AM349" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN349" t="inlineStr"/>
+      <c r="AO349" t="inlineStr"/>
+      <c r="AP349" t="inlineStr"/>
+      <c r="AQ349" t="inlineStr"/>
+      <c r="AR349" t="inlineStr"/>
+      <c r="AS349" t="inlineStr"/>
+      <c r="AT349" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU349" t="inlineStr"/>
+      <c r="AV349" t="inlineStr"/>
+      <c r="AW349" t="inlineStr"/>
+      <c r="AX349" t="inlineStr"/>
+      <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr"/>
+      <c r="BA349" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB349" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC349" t="inlineStr"/>
+      <c r="BD349" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE349" t="n">
+        <v>19931</v>
+      </c>
+      <c r="BF349" t="inlineStr">
+        <is>
+          <t>266855</t>
+        </is>
+      </c>
+      <c r="BG349" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH349" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI349" t="n">
+        <v>17219</v>
+      </c>
+      <c r="BJ349" t="inlineStr"/>
+      <c r="BK349" t="inlineStr"/>
+      <c r="BL349" t="inlineStr"/>
+      <c r="BM349" t="inlineStr"/>
+      <c r="BN349" t="inlineStr"/>
+      <c r="BO349" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP349" t="inlineStr"/>
+      <c r="BQ349" t="inlineStr"/>
+      <c r="BR349" t="inlineStr"/>
+      <c r="BS349" t="inlineStr"/>
+      <c r="BT349" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU349" t="inlineStr"/>
+      <c r="BV349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C350" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D350" t="n">
+        <v>11000351905585</v>
+      </c>
+      <c r="E350" t="n">
+        <v>1772244241</v>
+      </c>
+      <c r="F350" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 07:35:09</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N350" t="n">
+        <v>109277483982</v>
+      </c>
+      <c r="O350" t="inlineStr"/>
+      <c r="P350" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr"/>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr"/>
+      <c r="V350" t="inlineStr"/>
+      <c r="W350" t="inlineStr"/>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>DODDI THANSHITHA</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z350" t="n">
+        <v>6281864352</v>
+      </c>
+      <c r="AA350" t="inlineStr"/>
+      <c r="AB350" t="inlineStr"/>
+      <c r="AC350" t="inlineStr"/>
+      <c r="AD350" t="inlineStr"/>
+      <c r="AE350" t="inlineStr"/>
+      <c r="AF350" t="inlineStr"/>
+      <c r="AG350" t="inlineStr"/>
+      <c r="AH350" t="inlineStr"/>
+      <c r="AI350" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ350" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK350" t="inlineStr"/>
+      <c r="AL350" t="inlineStr"/>
+      <c r="AM350" t="inlineStr"/>
+      <c r="AN350" t="inlineStr"/>
+      <c r="AO350" t="inlineStr"/>
+      <c r="AP350" t="inlineStr"/>
+      <c r="AQ350" t="inlineStr"/>
+      <c r="AR350" t="inlineStr"/>
+      <c r="AS350" t="inlineStr"/>
+      <c r="AT350" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU350" t="inlineStr"/>
+      <c r="AV350" t="inlineStr"/>
+      <c r="AW350" t="inlineStr"/>
+      <c r="AX350" t="inlineStr"/>
+      <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr"/>
+      <c r="BA350" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB350" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC350" t="inlineStr"/>
+      <c r="BD350" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE350" t="n">
+        <v>18092</v>
+      </c>
+      <c r="BF350" t="inlineStr">
+        <is>
+          <t>266719</t>
+        </is>
+      </c>
+      <c r="BG350" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH350" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI350" t="n">
+        <v>16997</v>
+      </c>
+      <c r="BJ350" t="inlineStr"/>
+      <c r="BK350" t="inlineStr"/>
+      <c r="BL350" t="inlineStr"/>
+      <c r="BM350" t="inlineStr"/>
+      <c r="BN350" t="inlineStr"/>
+      <c r="BO350" t="inlineStr"/>
+      <c r="BP350" t="inlineStr"/>
+      <c r="BQ350" t="inlineStr"/>
+      <c r="BR350" t="inlineStr"/>
+      <c r="BS350" t="inlineStr"/>
+      <c r="BT350" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU350" t="inlineStr"/>
+      <c r="BV350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C351" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D351" t="n">
+        <v>11000351909240</v>
+      </c>
+      <c r="E351" t="n">
+        <v>1772246973</v>
+      </c>
+      <c r="F351" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 08:20:07</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N351" t="n">
+        <v>40471991429</v>
+      </c>
+      <c r="O351" t="inlineStr"/>
+      <c r="P351" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr"/>
+      <c r="V351" t="inlineStr"/>
+      <c r="W351" t="inlineStr"/>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>YASHWANTH REDDY GUDLA</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z351" t="n">
+        <v>9948345552</v>
+      </c>
+      <c r="AA351" t="inlineStr"/>
+      <c r="AB351" t="inlineStr"/>
+      <c r="AC351" t="inlineStr"/>
+      <c r="AD351" t="inlineStr"/>
+      <c r="AE351" t="inlineStr"/>
+      <c r="AF351" t="inlineStr"/>
+      <c r="AG351" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH351" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK351" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL351" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM351" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN351" t="inlineStr"/>
+      <c r="AO351" t="inlineStr"/>
+      <c r="AP351" t="inlineStr"/>
+      <c r="AQ351" t="inlineStr"/>
+      <c r="AR351" t="inlineStr"/>
+      <c r="AS351" t="inlineStr"/>
+      <c r="AT351" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU351" t="inlineStr"/>
+      <c r="AV351" t="inlineStr"/>
+      <c r="AW351" t="inlineStr"/>
+      <c r="AX351" t="inlineStr"/>
+      <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr"/>
+      <c r="BA351" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB351" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC351" t="inlineStr"/>
+      <c r="BD351" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE351" t="n">
+        <v>18786</v>
+      </c>
+      <c r="BF351" t="inlineStr">
+        <is>
+          <t>267482</t>
+        </is>
+      </c>
+      <c r="BG351" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH351" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI351" t="n">
+        <v>16797</v>
+      </c>
+      <c r="BJ351" t="inlineStr"/>
+      <c r="BK351" t="inlineStr"/>
+      <c r="BL351" t="inlineStr"/>
+      <c r="BM351" t="inlineStr"/>
+      <c r="BN351" t="inlineStr"/>
+      <c r="BO351" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP351" t="inlineStr"/>
+      <c r="BQ351" t="inlineStr"/>
+      <c r="BR351" t="inlineStr"/>
+      <c r="BS351" t="inlineStr"/>
+      <c r="BT351" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU351" t="inlineStr"/>
+      <c r="BV351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C352" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D352" t="n">
+        <v>11000351910047</v>
+      </c>
+      <c r="E352" t="n">
+        <v>1772247054</v>
+      </c>
+      <c r="F352" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 08:21:04</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="N352" t="n">
+        <v>146763616167</v>
+      </c>
+      <c r="O352" t="inlineStr"/>
+      <c r="P352" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr"/>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr"/>
+      <c r="V352" t="inlineStr"/>
+      <c r="W352" t="inlineStr"/>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>MAHENDRA REDDY GUDLA</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z352" t="n">
+        <v>9948345552</v>
+      </c>
+      <c r="AA352" t="inlineStr"/>
+      <c r="AB352" t="inlineStr"/>
+      <c r="AC352" t="inlineStr"/>
+      <c r="AD352" t="inlineStr"/>
+      <c r="AE352" t="inlineStr"/>
+      <c r="AF352" t="inlineStr"/>
+      <c r="AG352" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH352" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK352" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL352" t="n">
+        <v>8650</v>
+      </c>
+      <c r="AM352" t="inlineStr"/>
+      <c r="AN352" t="inlineStr"/>
+      <c r="AO352" t="inlineStr"/>
+      <c r="AP352" t="inlineStr"/>
+      <c r="AQ352" t="inlineStr"/>
+      <c r="AR352" t="inlineStr"/>
+      <c r="AS352" t="inlineStr"/>
+      <c r="AT352" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU352" t="inlineStr"/>
+      <c r="AV352" t="inlineStr"/>
+      <c r="AW352" t="inlineStr"/>
+      <c r="AX352" t="inlineStr"/>
+      <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr"/>
+      <c r="BA352" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB352" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC352" t="inlineStr"/>
+      <c r="BD352" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE352" t="n">
+        <v>19010</v>
+      </c>
+      <c r="BF352" t="inlineStr">
+        <is>
+          <t>268450</t>
+        </is>
+      </c>
+      <c r="BG352" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="BH352" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI352" t="n">
+        <v>16796</v>
+      </c>
+      <c r="BJ352" t="inlineStr"/>
+      <c r="BK352" t="inlineStr"/>
+      <c r="BL352" t="inlineStr"/>
+      <c r="BM352" t="inlineStr"/>
+      <c r="BN352" t="inlineStr"/>
+      <c r="BO352" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP352" t="inlineStr"/>
+      <c r="BQ352" t="inlineStr"/>
+      <c r="BR352" t="inlineStr"/>
+      <c r="BS352" t="inlineStr"/>
+      <c r="BT352" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU352" t="inlineStr"/>
+      <c r="BV352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C353" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D353" t="n">
+        <v>11000351925096</v>
+      </c>
+      <c r="E353" t="n">
+        <v>1772254577</v>
+      </c>
+      <c r="F353" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 10:27:22</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N353" t="n">
+        <v>866758700772</v>
+      </c>
+      <c r="O353" t="inlineStr"/>
+      <c r="P353" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr"/>
+      <c r="V353" t="inlineStr"/>
+      <c r="W353" t="inlineStr"/>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>DUVVU BHARGAVA SRI SAI</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z353" t="n">
+        <v>9502247535</v>
+      </c>
+      <c r="AA353" t="inlineStr"/>
+      <c r="AB353" t="inlineStr"/>
+      <c r="AC353" t="inlineStr"/>
+      <c r="AD353" t="inlineStr"/>
+      <c r="AE353" t="inlineStr"/>
+      <c r="AF353" t="inlineStr"/>
+      <c r="AG353" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH353" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK353" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL353" t="n">
+        <v>8350</v>
+      </c>
+      <c r="AM353" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN353" t="inlineStr"/>
+      <c r="AO353" t="inlineStr"/>
+      <c r="AP353" t="inlineStr"/>
+      <c r="AQ353" t="inlineStr"/>
+      <c r="AR353" t="inlineStr"/>
+      <c r="AS353" t="inlineStr"/>
+      <c r="AT353" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU353" t="inlineStr"/>
+      <c r="AV353" t="inlineStr"/>
+      <c r="AW353" t="inlineStr"/>
+      <c r="AX353" t="inlineStr"/>
+      <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr"/>
+      <c r="BA353" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB353" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC353" t="inlineStr"/>
+      <c r="BD353" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE353" t="n">
+        <v>18964</v>
+      </c>
+      <c r="BF353" t="inlineStr">
+        <is>
+          <t>267620</t>
+        </is>
+      </c>
+      <c r="BG353" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH353" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI353" t="n">
+        <v>16036</v>
+      </c>
+      <c r="BJ353" t="inlineStr"/>
+      <c r="BK353" t="inlineStr"/>
+      <c r="BL353" t="inlineStr"/>
+      <c r="BM353" t="inlineStr"/>
+      <c r="BN353" t="inlineStr"/>
+      <c r="BO353" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP353" t="inlineStr"/>
+      <c r="BQ353" t="inlineStr"/>
+      <c r="BR353" t="inlineStr"/>
+      <c r="BS353" t="inlineStr"/>
+      <c r="BT353" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU353" t="inlineStr"/>
+      <c r="BV353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C354" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D354" t="n">
+        <v>11000351924775</v>
+      </c>
+      <c r="E354" t="n">
+        <v>1772254681</v>
+      </c>
+      <c r="F354" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 10:28:45</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N354" t="n">
+        <v>920094640606</v>
+      </c>
+      <c r="O354" t="inlineStr"/>
+      <c r="P354" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr"/>
+      <c r="V354" t="inlineStr"/>
+      <c r="W354" t="inlineStr"/>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>DUVVU MAHALAKSHMI</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z354" t="n">
+        <v>9502247535</v>
+      </c>
+      <c r="AA354" t="inlineStr"/>
+      <c r="AB354" t="inlineStr"/>
+      <c r="AC354" t="inlineStr"/>
+      <c r="AD354" t="inlineStr"/>
+      <c r="AE354" t="inlineStr"/>
+      <c r="AF354" t="inlineStr"/>
+      <c r="AG354" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH354" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI354" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ354" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK354" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL354" t="n">
+        <v>8050</v>
+      </c>
+      <c r="AM354" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN354" t="inlineStr"/>
+      <c r="AO354" t="inlineStr"/>
+      <c r="AP354" t="inlineStr"/>
+      <c r="AQ354" t="inlineStr"/>
+      <c r="AR354" t="inlineStr"/>
+      <c r="AS354" t="inlineStr"/>
+      <c r="AT354" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU354" t="inlineStr"/>
+      <c r="AV354" t="inlineStr"/>
+      <c r="AW354" t="inlineStr"/>
+      <c r="AX354" t="inlineStr"/>
+      <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr"/>
+      <c r="BA354" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB354" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC354" t="inlineStr"/>
+      <c r="BD354" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE354" t="n">
+        <v>18522</v>
+      </c>
+      <c r="BF354" t="inlineStr">
+        <is>
+          <t>265602</t>
+        </is>
+      </c>
+      <c r="BG354" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="BH354" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI354" t="n">
+        <v>16020</v>
+      </c>
+      <c r="BJ354" t="inlineStr"/>
+      <c r="BK354" t="inlineStr"/>
+      <c r="BL354" t="inlineStr"/>
+      <c r="BM354" t="inlineStr"/>
+      <c r="BN354" t="inlineStr"/>
+      <c r="BO354" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP354" t="inlineStr"/>
+      <c r="BQ354" t="inlineStr"/>
+      <c r="BR354" t="inlineStr"/>
+      <c r="BS354" t="inlineStr"/>
+      <c r="BT354" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU354" t="inlineStr"/>
+      <c r="BV354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C355" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D355" t="n">
+        <v>11000351924821</v>
+      </c>
+      <c r="E355" t="n">
+        <v>1772254751</v>
+      </c>
+      <c r="F355" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 10:29:22</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N355" t="n">
+        <v>891768471043</v>
+      </c>
+      <c r="O355" t="inlineStr"/>
+      <c r="P355" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr"/>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr"/>
+      <c r="V355" t="inlineStr"/>
+      <c r="W355" t="inlineStr"/>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>DUVVU MAHALAKSHMI</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z355" t="n">
+        <v>9502247535</v>
+      </c>
+      <c r="AA355" t="inlineStr"/>
+      <c r="AB355" t="inlineStr"/>
+      <c r="AC355" t="inlineStr"/>
+      <c r="AD355" t="inlineStr"/>
+      <c r="AE355" t="inlineStr"/>
+      <c r="AF355" t="inlineStr"/>
+      <c r="AG355" t="inlineStr"/>
+      <c r="AH355" t="inlineStr"/>
+      <c r="AI355" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ355" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK355" t="inlineStr"/>
+      <c r="AL355" t="inlineStr"/>
+      <c r="AM355" t="inlineStr"/>
+      <c r="AN355" t="inlineStr"/>
+      <c r="AO355" t="inlineStr"/>
+      <c r="AP355" t="inlineStr"/>
+      <c r="AQ355" t="inlineStr"/>
+      <c r="AR355" t="inlineStr"/>
+      <c r="AS355" t="inlineStr"/>
+      <c r="AT355" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU355" t="inlineStr"/>
+      <c r="AV355" t="inlineStr"/>
+      <c r="AW355" t="inlineStr"/>
+      <c r="AX355" t="inlineStr"/>
+      <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr"/>
+      <c r="BA355" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB355" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC355" t="inlineStr"/>
+      <c r="BD355" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE355" t="n">
+        <v>18522</v>
+      </c>
+      <c r="BF355" t="inlineStr">
+        <is>
+          <t>267252</t>
+        </is>
+      </c>
+      <c r="BG355" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH355" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI355" t="n">
+        <v>16020</v>
+      </c>
+      <c r="BJ355" t="inlineStr"/>
+      <c r="BK355" t="inlineStr"/>
+      <c r="BL355" t="inlineStr"/>
+      <c r="BM355" t="inlineStr"/>
+      <c r="BN355" t="inlineStr"/>
+      <c r="BO355" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP355" t="inlineStr"/>
+      <c r="BQ355" t="inlineStr"/>
+      <c r="BR355" t="inlineStr"/>
+      <c r="BS355" t="inlineStr"/>
+      <c r="BT355" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU355" t="inlineStr"/>
+      <c r="BV355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C356" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D356" t="n">
+        <v>11000351927021</v>
+      </c>
+      <c r="E356" t="n">
+        <v>1772254751</v>
+      </c>
+      <c r="F356" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 10:38:10</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N356" t="n">
+        <v>469507160708</v>
+      </c>
+      <c r="O356" t="inlineStr"/>
+      <c r="P356" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr"/>
+      <c r="V356" t="inlineStr"/>
+      <c r="W356" t="inlineStr"/>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>DUVVU MAHALAKSHMI</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z356" t="n">
+        <v>9502247535</v>
+      </c>
+      <c r="AA356" t="inlineStr"/>
+      <c r="AB356" t="inlineStr"/>
+      <c r="AC356" t="inlineStr"/>
+      <c r="AD356" t="inlineStr"/>
+      <c r="AE356" t="inlineStr"/>
+      <c r="AF356" t="inlineStr"/>
+      <c r="AG356" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH356" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI356" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ356" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK356" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL356" t="n">
+        <v>8050</v>
+      </c>
+      <c r="AM356" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN356" t="inlineStr"/>
+      <c r="AO356" t="inlineStr"/>
+      <c r="AP356" t="inlineStr"/>
+      <c r="AQ356" t="inlineStr"/>
+      <c r="AR356" t="inlineStr"/>
+      <c r="AS356" t="inlineStr"/>
+      <c r="AT356" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU356" t="inlineStr"/>
+      <c r="AV356" t="inlineStr"/>
+      <c r="AW356" t="inlineStr"/>
+      <c r="AX356" t="inlineStr"/>
+      <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr"/>
+      <c r="BA356" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB356" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC356" t="inlineStr"/>
+      <c r="BD356" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE356" t="n">
+        <v>18522</v>
+      </c>
+      <c r="BF356" t="inlineStr">
+        <is>
+          <t>267252</t>
+        </is>
+      </c>
+      <c r="BG356" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH356" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI356" t="n">
+        <v>16020</v>
+      </c>
+      <c r="BJ356" t="inlineStr"/>
+      <c r="BK356" t="inlineStr"/>
+      <c r="BL356" t="inlineStr"/>
+      <c r="BM356" t="inlineStr"/>
+      <c r="BN356" t="inlineStr"/>
+      <c r="BO356" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP356" t="inlineStr"/>
+      <c r="BQ356" t="inlineStr"/>
+      <c r="BR356" t="inlineStr"/>
+      <c r="BS356" t="inlineStr"/>
+      <c r="BT356" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU356" t="inlineStr"/>
+      <c r="BV356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C357" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D357" t="n">
+        <v>11000351942212</v>
+      </c>
+      <c r="E357" t="n">
+        <v>1772259825</v>
+      </c>
+      <c r="F357" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 11:55:41</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N357" t="n">
+        <v>109278991926</v>
+      </c>
+      <c r="O357" t="inlineStr"/>
+      <c r="P357" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr"/>
+      <c r="V357" t="inlineStr"/>
+      <c r="W357" t="inlineStr"/>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>SAI SRAVAN PATNAYAK</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z357" t="n">
+        <v>7337422112</v>
+      </c>
+      <c r="AA357" t="inlineStr"/>
+      <c r="AB357" t="inlineStr"/>
+      <c r="AC357" t="inlineStr"/>
+      <c r="AD357" t="inlineStr"/>
+      <c r="AE357" t="inlineStr"/>
+      <c r="AF357" t="inlineStr"/>
+      <c r="AG357" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH357" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI357" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ357" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK357" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL357" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM357" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN357" t="inlineStr"/>
+      <c r="AO357" t="inlineStr"/>
+      <c r="AP357" t="inlineStr"/>
+      <c r="AQ357" t="inlineStr"/>
+      <c r="AR357" t="inlineStr"/>
+      <c r="AS357" t="inlineStr"/>
+      <c r="AT357" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU357" t="inlineStr"/>
+      <c r="AV357" t="inlineStr"/>
+      <c r="AW357" t="inlineStr"/>
+      <c r="AX357" t="inlineStr"/>
+      <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr"/>
+      <c r="BA357" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB357" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC357" t="inlineStr"/>
+      <c r="BD357" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE357" t="n">
+        <v>18066</v>
+      </c>
+      <c r="BF357" t="inlineStr">
+        <is>
+          <t>266779</t>
+        </is>
+      </c>
+      <c r="BG357" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH357" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI357" t="n">
+        <v>16914</v>
+      </c>
+      <c r="BJ357" t="inlineStr"/>
+      <c r="BK357" t="inlineStr"/>
+      <c r="BL357" t="inlineStr"/>
+      <c r="BM357" t="inlineStr"/>
+      <c r="BN357" t="inlineStr"/>
+      <c r="BO357" t="inlineStr"/>
+      <c r="BP357" t="inlineStr"/>
+      <c r="BQ357" t="inlineStr"/>
+      <c r="BR357" t="inlineStr"/>
+      <c r="BS357" t="inlineStr"/>
+      <c r="BT357" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU357" t="inlineStr"/>
+      <c r="BV357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C358" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D358" t="n">
+        <v>11000351953158</v>
+      </c>
+      <c r="E358" t="n">
+        <v>1772263454</v>
+      </c>
+      <c r="F358" t="n">
+        <v>16100</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 12:55:32</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N358" t="n">
+        <v>109279356760</v>
+      </c>
+      <c r="O358" t="inlineStr"/>
+      <c r="P358" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr"/>
+      <c r="V358" t="inlineStr"/>
+      <c r="W358" t="inlineStr"/>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>BOMMIDI BALA SURYA BHUVAN</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z358" t="n">
+        <v>6300875193</v>
+      </c>
+      <c r="AA358" t="inlineStr"/>
+      <c r="AB358" t="inlineStr"/>
+      <c r="AC358" t="inlineStr"/>
+      <c r="AD358" t="inlineStr"/>
+      <c r="AE358" t="inlineStr"/>
+      <c r="AF358" t="inlineStr"/>
+      <c r="AG358" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH358" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI358" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ358" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK358" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL358" t="n">
+        <v>16100</v>
+      </c>
+      <c r="AM358" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN358" t="inlineStr"/>
+      <c r="AO358" t="inlineStr"/>
+      <c r="AP358" t="inlineStr"/>
+      <c r="AQ358" t="inlineStr"/>
+      <c r="AR358" t="inlineStr"/>
+      <c r="AS358" t="inlineStr"/>
+      <c r="AT358" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU358" t="inlineStr"/>
+      <c r="AV358" t="inlineStr"/>
+      <c r="AW358" t="inlineStr"/>
+      <c r="AX358" t="inlineStr"/>
+      <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr"/>
+      <c r="BA358" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB358" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC358" t="inlineStr"/>
+      <c r="BD358" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE358" t="n">
+        <v>18543</v>
+      </c>
+      <c r="BF358" t="inlineStr">
+        <is>
+          <t>265653,267303</t>
+        </is>
+      </c>
+      <c r="BG358" t="inlineStr">
+        <is>
+          <t>2049,2057</t>
+        </is>
+      </c>
+      <c r="BH358" t="inlineStr">
+        <is>
+          <t>sixteen thousand one hundred</t>
+        </is>
+      </c>
+      <c r="BI358" t="n">
+        <v>15863</v>
+      </c>
+      <c r="BJ358" t="inlineStr"/>
+      <c r="BK358" t="inlineStr"/>
+      <c r="BL358" t="inlineStr"/>
+      <c r="BM358" t="inlineStr"/>
+      <c r="BN358" t="inlineStr"/>
+      <c r="BO358" t="inlineStr"/>
+      <c r="BP358" t="inlineStr"/>
+      <c r="BQ358" t="inlineStr"/>
+      <c r="BR358" t="inlineStr"/>
+      <c r="BS358" t="inlineStr"/>
+      <c r="BT358" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU358" t="inlineStr"/>
+      <c r="BV358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C359" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D359" t="n">
+        <v>11000352070361</v>
+      </c>
+      <c r="E359" t="n">
+        <v>1772361488</v>
+      </c>
+      <c r="F359" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>01-Mar-2026 16:13:35</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>BANK OF BARODA FSS</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N359" t="n">
+        <v>1.012026060690908e+17</v>
+      </c>
+      <c r="O359" t="n">
+        <v>455738</v>
+      </c>
+      <c r="P359" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr"/>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>STATE BANK OF INDIA</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr"/>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>SAANVI SAHOO</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z359" t="n">
+        <v>8309736856</v>
+      </c>
+      <c r="AA359" t="inlineStr"/>
+      <c r="AB359" t="inlineStr"/>
+      <c r="AC359" t="inlineStr">
+        <is>
+          <t>XXXXXXXXXXXX5559</t>
+        </is>
+      </c>
+      <c r="AD359" t="inlineStr"/>
+      <c r="AE359" t="inlineStr"/>
+      <c r="AF359" t="inlineStr"/>
+      <c r="AG359" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH359" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK359" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL359" t="n">
+        <v>7750</v>
+      </c>
+      <c r="AM359" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="AN359" t="inlineStr"/>
+      <c r="AO359" t="inlineStr"/>
+      <c r="AP359" t="inlineStr"/>
+      <c r="AQ359" t="inlineStr"/>
+      <c r="AR359" t="inlineStr"/>
+      <c r="AS359" t="inlineStr"/>
+      <c r="AT359" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU359" t="inlineStr"/>
+      <c r="AV359" t="inlineStr"/>
+      <c r="AW359" t="inlineStr"/>
+      <c r="AX359" t="inlineStr"/>
+      <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr"/>
+      <c r="BA359" t="inlineStr">
+        <is>
+          <t>RUPAY</t>
+        </is>
+      </c>
+      <c r="BB359" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC359" t="inlineStr"/>
+      <c r="BD359" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE359" t="n">
+        <v>20077</v>
+      </c>
+      <c r="BF359" t="inlineStr">
+        <is>
+          <t>268295</t>
+        </is>
+      </c>
+      <c r="BG359" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH359" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI359" t="n">
+        <v>17358</v>
+      </c>
+      <c r="BJ359" t="inlineStr"/>
+      <c r="BK359" t="inlineStr"/>
+      <c r="BL359" t="inlineStr"/>
+      <c r="BM359" t="inlineStr"/>
+      <c r="BN359" t="inlineStr"/>
+      <c r="BO359" t="inlineStr"/>
+      <c r="BP359" t="inlineStr"/>
+      <c r="BQ359" t="inlineStr"/>
+      <c r="BR359" t="inlineStr"/>
+      <c r="BS359" t="inlineStr"/>
+      <c r="BT359" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU359" t="inlineStr"/>
+      <c r="BV359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C360" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D360" t="n">
+        <v>11000352121038</v>
+      </c>
+      <c r="E360" t="n">
+        <v>1772420420</v>
+      </c>
+      <c r="F360" t="n">
+        <v>8350</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 08:34:02</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N360" t="n">
+        <v>606171974859</v>
+      </c>
+      <c r="O360" t="n">
+        <v>606171974859</v>
+      </c>
+      <c r="P360" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr"/>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr"/>
+      <c r="V360" t="inlineStr"/>
+      <c r="W360" t="inlineStr"/>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>MALLA VAIBHAV SAI</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z360" t="n">
+        <v>9247311340</v>
+      </c>
+      <c r="AA360" t="inlineStr"/>
+      <c r="AB360" t="inlineStr"/>
+      <c r="AC360" t="inlineStr"/>
+      <c r="AD360" t="inlineStr"/>
+      <c r="AE360" t="inlineStr"/>
+      <c r="AF360" t="inlineStr"/>
+      <c r="AG360" t="inlineStr"/>
+      <c r="AH360" t="inlineStr"/>
+      <c r="AI360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK360" t="inlineStr"/>
+      <c r="AL360" t="inlineStr"/>
+      <c r="AM360" t="inlineStr"/>
+      <c r="AN360" t="inlineStr"/>
+      <c r="AO360" t="inlineStr"/>
+      <c r="AP360" t="inlineStr"/>
+      <c r="AQ360" t="inlineStr"/>
+      <c r="AR360" t="inlineStr"/>
+      <c r="AS360" t="inlineStr"/>
+      <c r="AT360" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU360" t="inlineStr"/>
+      <c r="AV360" t="inlineStr"/>
+      <c r="AW360" t="inlineStr"/>
+      <c r="AX360" t="inlineStr"/>
+      <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr"/>
+      <c r="BA360" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB360" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC360" t="inlineStr"/>
+      <c r="BD360" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE360" t="n">
+        <v>18978</v>
+      </c>
+      <c r="BF360" t="inlineStr">
+        <is>
+          <t>267636</t>
+        </is>
+      </c>
+      <c r="BG360" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="BH360" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI360" t="n">
+        <v>16031</v>
+      </c>
+      <c r="BJ360" t="inlineStr"/>
+      <c r="BK360" t="inlineStr"/>
+      <c r="BL360" t="inlineStr"/>
+      <c r="BM360" t="inlineStr"/>
+      <c r="BN360" t="inlineStr"/>
+      <c r="BO360" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP360" t="inlineStr"/>
+      <c r="BQ360" t="inlineStr"/>
+      <c r="BR360" t="inlineStr"/>
+      <c r="BS360" t="inlineStr"/>
+      <c r="BT360" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU360" t="inlineStr"/>
+      <c r="BV360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C361" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D361" t="n">
+        <v>11000352134464</v>
+      </c>
+      <c r="E361" t="n">
+        <v>1772424160</v>
+      </c>
+      <c r="F361" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 09:33:18</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N361" t="n">
+        <v>778077483731</v>
+      </c>
+      <c r="O361" t="inlineStr"/>
+      <c r="P361" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr"/>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr"/>
+      <c r="V361" t="inlineStr"/>
+      <c r="W361" t="inlineStr"/>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>THUTTA DHANASHVI</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z361" t="n">
+        <v>7337239208</v>
+      </c>
+      <c r="AA361" t="inlineStr"/>
+      <c r="AB361" t="inlineStr"/>
+      <c r="AC361" t="inlineStr"/>
+      <c r="AD361" t="inlineStr"/>
+      <c r="AE361" t="inlineStr"/>
+      <c r="AF361" t="inlineStr"/>
+      <c r="AG361" t="inlineStr"/>
+      <c r="AH361" t="inlineStr"/>
+      <c r="AI361" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ361" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK361" t="inlineStr"/>
+      <c r="AL361" t="inlineStr"/>
+      <c r="AM361" t="inlineStr"/>
+      <c r="AN361" t="inlineStr"/>
+      <c r="AO361" t="inlineStr"/>
+      <c r="AP361" t="inlineStr"/>
+      <c r="AQ361" t="inlineStr"/>
+      <c r="AR361" t="inlineStr"/>
+      <c r="AS361" t="inlineStr"/>
+      <c r="AT361" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU361" t="inlineStr"/>
+      <c r="AV361" t="inlineStr"/>
+      <c r="AW361" t="inlineStr"/>
+      <c r="AX361" t="inlineStr"/>
+      <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr"/>
+      <c r="BA361" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB361" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC361" t="inlineStr"/>
+      <c r="BD361" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE361" t="n">
+        <v>18339</v>
+      </c>
+      <c r="BF361" t="inlineStr">
+        <is>
+          <t>266997</t>
+        </is>
+      </c>
+      <c r="BG361" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH361" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI361" t="n">
+        <v>16927</v>
+      </c>
+      <c r="BJ361" t="inlineStr"/>
+      <c r="BK361" t="inlineStr"/>
+      <c r="BL361" t="inlineStr"/>
+      <c r="BM361" t="inlineStr"/>
+      <c r="BN361" t="inlineStr"/>
+      <c r="BO361" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP361" t="inlineStr"/>
+      <c r="BQ361" t="inlineStr"/>
+      <c r="BR361" t="inlineStr"/>
+      <c r="BS361" t="inlineStr"/>
+      <c r="BT361" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU361" t="inlineStr"/>
+      <c r="BV361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C362" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D362" t="n">
+        <v>11000352133780</v>
+      </c>
+      <c r="E362" t="n">
+        <v>1772424238</v>
+      </c>
+      <c r="F362" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 09:34:10</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N362" t="n">
+        <v>805616523520</v>
+      </c>
+      <c r="O362" t="inlineStr"/>
+      <c r="P362" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr"/>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr"/>
+      <c r="V362" t="inlineStr"/>
+      <c r="W362" t="inlineStr"/>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>THUTTA HARI CHARANI</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z362" t="n">
+        <v>7337239208</v>
+      </c>
+      <c r="AA362" t="inlineStr"/>
+      <c r="AB362" t="inlineStr"/>
+      <c r="AC362" t="inlineStr"/>
+      <c r="AD362" t="inlineStr"/>
+      <c r="AE362" t="inlineStr"/>
+      <c r="AF362" t="inlineStr"/>
+      <c r="AG362" t="inlineStr"/>
+      <c r="AH362" t="inlineStr"/>
+      <c r="AI362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK362" t="inlineStr"/>
+      <c r="AL362" t="inlineStr"/>
+      <c r="AM362" t="inlineStr"/>
+      <c r="AN362" t="inlineStr"/>
+      <c r="AO362" t="inlineStr"/>
+      <c r="AP362" t="inlineStr"/>
+      <c r="AQ362" t="inlineStr"/>
+      <c r="AR362" t="inlineStr"/>
+      <c r="AS362" t="inlineStr"/>
+      <c r="AT362" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU362" t="inlineStr"/>
+      <c r="AV362" t="inlineStr"/>
+      <c r="AW362" t="inlineStr"/>
+      <c r="AX362" t="inlineStr"/>
+      <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr"/>
+      <c r="BA362" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB362" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC362" t="inlineStr"/>
+      <c r="BD362" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE362" t="n">
+        <v>19892</v>
+      </c>
+      <c r="BF362" t="inlineStr">
+        <is>
+          <t>266661</t>
+        </is>
+      </c>
+      <c r="BG362" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH362" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI362" t="n">
+        <v>17177</v>
+      </c>
+      <c r="BJ362" t="inlineStr"/>
+      <c r="BK362" t="inlineStr"/>
+      <c r="BL362" t="inlineStr"/>
+      <c r="BM362" t="inlineStr"/>
+      <c r="BN362" t="inlineStr"/>
+      <c r="BO362" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP362" t="inlineStr"/>
+      <c r="BQ362" t="inlineStr"/>
+      <c r="BR362" t="inlineStr"/>
+      <c r="BS362" t="inlineStr"/>
+      <c r="BT362" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU362" t="inlineStr"/>
+      <c r="BV362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C363" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D363" t="n">
+        <v>11000352161115</v>
+      </c>
+      <c r="E363" t="n">
+        <v>1772431154</v>
+      </c>
+      <c r="F363" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 11:30:41</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>BANK OF BARODA FSS</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N363" t="n">
+        <v>1.01202606115622e+17</v>
+      </c>
+      <c r="O363" t="inlineStr"/>
+      <c r="P363" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr"/>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr"/>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>STATE BANK OF INDIA</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr"/>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>KADAJARI ESHAN ESWAR</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z363" t="n">
+        <v>9885130099</v>
+      </c>
+      <c r="AA363" t="inlineStr"/>
+      <c r="AB363" t="inlineStr"/>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>XXXXXXXXXXXX8821</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr"/>
+      <c r="AE363" t="inlineStr"/>
+      <c r="AF363" t="inlineStr"/>
+      <c r="AG363" t="inlineStr"/>
+      <c r="AH363" t="inlineStr"/>
+      <c r="AI363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK363" t="inlineStr"/>
+      <c r="AL363" t="inlineStr"/>
+      <c r="AM363" t="inlineStr"/>
+      <c r="AN363" t="inlineStr"/>
+      <c r="AO363" t="inlineStr"/>
+      <c r="AP363" t="inlineStr"/>
+      <c r="AQ363" t="inlineStr"/>
+      <c r="AR363" t="inlineStr"/>
+      <c r="AS363" t="inlineStr"/>
+      <c r="AT363" t="inlineStr"/>
+      <c r="AU363" t="inlineStr"/>
+      <c r="AV363" t="inlineStr"/>
+      <c r="AW363" t="inlineStr"/>
+      <c r="AX363" t="inlineStr"/>
+      <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr"/>
+      <c r="BA363" t="inlineStr">
+        <is>
+          <t>RUPAY</t>
+        </is>
+      </c>
+      <c r="BB363" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC363" t="inlineStr"/>
+      <c r="BD363" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE363" t="n">
+        <v>18273</v>
+      </c>
+      <c r="BF363" t="inlineStr">
+        <is>
+          <t>267040</t>
+        </is>
+      </c>
+      <c r="BG363" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH363" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI363" t="n">
+        <v>16974</v>
+      </c>
+      <c r="BJ363" t="inlineStr"/>
+      <c r="BK363" t="inlineStr"/>
+      <c r="BL363" t="inlineStr"/>
+      <c r="BM363" t="inlineStr"/>
+      <c r="BN363" t="inlineStr"/>
+      <c r="BO363" t="inlineStr"/>
+      <c r="BP363" t="inlineStr"/>
+      <c r="BQ363" t="inlineStr"/>
+      <c r="BR363" t="inlineStr"/>
+      <c r="BS363" t="inlineStr"/>
+      <c r="BT363" t="inlineStr"/>
+      <c r="BU363" t="inlineStr"/>
+      <c r="BV363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C364" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D364" t="n">
+        <v>11000352162203</v>
+      </c>
+      <c r="E364" t="n">
+        <v>1772431154</v>
+      </c>
+      <c r="F364" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 11:31:24</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N364" t="n">
+        <v>606128095174</v>
+      </c>
+      <c r="O364" t="n">
+        <v>606128095174</v>
+      </c>
+      <c r="P364" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr"/>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr"/>
+      <c r="V364" t="inlineStr"/>
+      <c r="W364" t="inlineStr"/>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>KADAJARI ESHAN ESWAR</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z364" t="n">
+        <v>9885130099</v>
+      </c>
+      <c r="AA364" t="inlineStr"/>
+      <c r="AB364" t="inlineStr"/>
+      <c r="AC364" t="inlineStr"/>
+      <c r="AD364" t="inlineStr"/>
+      <c r="AE364" t="inlineStr"/>
+      <c r="AF364" t="inlineStr"/>
+      <c r="AG364" t="inlineStr"/>
+      <c r="AH364" t="inlineStr"/>
+      <c r="AI364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK364" t="inlineStr"/>
+      <c r="AL364" t="inlineStr"/>
+      <c r="AM364" t="inlineStr"/>
+      <c r="AN364" t="inlineStr"/>
+      <c r="AO364" t="inlineStr"/>
+      <c r="AP364" t="inlineStr"/>
+      <c r="AQ364" t="inlineStr"/>
+      <c r="AR364" t="inlineStr"/>
+      <c r="AS364" t="inlineStr"/>
+      <c r="AT364" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="AU364" t="inlineStr"/>
+      <c r="AV364" t="inlineStr"/>
+      <c r="AW364" t="inlineStr"/>
+      <c r="AX364" t="inlineStr"/>
+      <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr"/>
+      <c r="BA364" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="BB364" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC364" t="inlineStr"/>
+      <c r="BD364" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE364" t="n">
+        <v>18273</v>
+      </c>
+      <c r="BF364" t="inlineStr">
+        <is>
+          <t>267040</t>
+        </is>
+      </c>
+      <c r="BG364" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH364" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI364" t="n">
+        <v>16974</v>
+      </c>
+      <c r="BJ364" t="inlineStr"/>
+      <c r="BK364" t="inlineStr"/>
+      <c r="BL364" t="inlineStr"/>
+      <c r="BM364" t="inlineStr"/>
+      <c r="BN364" t="inlineStr"/>
+      <c r="BO364" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+      <c r="BP364" t="inlineStr"/>
+      <c r="BQ364" t="inlineStr"/>
+      <c r="BR364" t="inlineStr"/>
+      <c r="BS364" t="inlineStr"/>
+      <c r="BT364" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU364" t="inlineStr"/>
+      <c r="BV364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C365" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D365" t="n">
+        <v>11000352172149</v>
+      </c>
+      <c r="E365" t="n">
+        <v>1772433686</v>
+      </c>
+      <c r="F365" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 12:12:45</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N365" t="n">
+        <v>201120935621</v>
+      </c>
+      <c r="O365" t="inlineStr"/>
+      <c r="P365" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr"/>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr"/>
+      <c r="V365" t="inlineStr"/>
+      <c r="W365" t="inlineStr"/>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>RONGALI JASMIKA</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z365" t="n">
+        <v>7793910192</v>
+      </c>
+      <c r="AA365" t="inlineStr"/>
+      <c r="AB365" t="inlineStr"/>
+      <c r="AC365" t="inlineStr"/>
+      <c r="AD365" t="inlineStr"/>
+      <c r="AE365" t="inlineStr"/>
+      <c r="AF365" t="inlineStr"/>
+      <c r="AG365" t="inlineStr"/>
+      <c r="AH365" t="inlineStr"/>
+      <c r="AI365" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ365" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK365" t="inlineStr"/>
+      <c r="AL365" t="inlineStr"/>
+      <c r="AM365" t="inlineStr"/>
+      <c r="AN365" t="inlineStr"/>
+      <c r="AO365" t="inlineStr"/>
+      <c r="AP365" t="inlineStr"/>
+      <c r="AQ365" t="inlineStr"/>
+      <c r="AR365" t="inlineStr"/>
+      <c r="AS365" t="inlineStr"/>
+      <c r="AT365" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU365" t="inlineStr"/>
+      <c r="AV365" t="inlineStr"/>
+      <c r="AW365" t="inlineStr"/>
+      <c r="AX365" t="inlineStr"/>
+      <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr"/>
+      <c r="BA365" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB365" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC365" t="inlineStr"/>
+      <c r="BD365" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE365" t="n">
+        <v>19849</v>
+      </c>
+      <c r="BF365" t="inlineStr">
+        <is>
+          <t>266747</t>
+        </is>
+      </c>
+      <c r="BG365" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH365" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI365" t="n">
+        <v>17146</v>
+      </c>
+      <c r="BJ365" t="inlineStr"/>
+      <c r="BK365" t="inlineStr"/>
+      <c r="BL365" t="inlineStr"/>
+      <c r="BM365" t="inlineStr"/>
+      <c r="BN365" t="inlineStr"/>
+      <c r="BO365" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP365" t="inlineStr"/>
+      <c r="BQ365" t="inlineStr"/>
+      <c r="BR365" t="inlineStr"/>
+      <c r="BS365" t="inlineStr"/>
+      <c r="BT365" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU365" t="inlineStr"/>
+      <c r="BV365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C366" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D366" t="n">
+        <v>11000352171807</v>
+      </c>
+      <c r="E366" t="n">
+        <v>1772433952</v>
+      </c>
+      <c r="F366" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 12:16:58</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N366" t="n">
+        <v>398196116938</v>
+      </c>
+      <c r="O366" t="inlineStr"/>
+      <c r="P366" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr"/>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr"/>
+      <c r="V366" t="inlineStr"/>
+      <c r="W366" t="inlineStr"/>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>RONGALI YERNI VENKATA RAKESH</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z366" t="n">
+        <v>7793910192</v>
+      </c>
+      <c r="AA366" t="inlineStr"/>
+      <c r="AB366" t="inlineStr"/>
+      <c r="AC366" t="inlineStr"/>
+      <c r="AD366" t="inlineStr"/>
+      <c r="AE366" t="inlineStr"/>
+      <c r="AF366" t="inlineStr"/>
+      <c r="AG366" t="inlineStr"/>
+      <c r="AH366" t="inlineStr"/>
+      <c r="AI366" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ366" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK366" t="inlineStr"/>
+      <c r="AL366" t="inlineStr"/>
+      <c r="AM366" t="inlineStr"/>
+      <c r="AN366" t="inlineStr"/>
+      <c r="AO366" t="inlineStr"/>
+      <c r="AP366" t="inlineStr"/>
+      <c r="AQ366" t="inlineStr"/>
+      <c r="AR366" t="inlineStr"/>
+      <c r="AS366" t="inlineStr"/>
+      <c r="AT366" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU366" t="inlineStr"/>
+      <c r="AV366" t="inlineStr"/>
+      <c r="AW366" t="inlineStr"/>
+      <c r="AX366" t="inlineStr"/>
+      <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr"/>
+      <c r="BA366" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB366" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC366" t="inlineStr"/>
+      <c r="BD366" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE366" t="n">
+        <v>19850</v>
+      </c>
+      <c r="BF366" t="inlineStr">
+        <is>
+          <t>267206</t>
+        </is>
+      </c>
+      <c r="BG366" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="BH366" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="BI366" t="n">
+        <v>17147</v>
+      </c>
+      <c r="BJ366" t="inlineStr"/>
+      <c r="BK366" t="inlineStr"/>
+      <c r="BL366" t="inlineStr"/>
+      <c r="BM366" t="inlineStr"/>
+      <c r="BN366" t="inlineStr"/>
+      <c r="BO366" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP366" t="inlineStr"/>
+      <c r="BQ366" t="inlineStr"/>
+      <c r="BR366" t="inlineStr"/>
+      <c r="BS366" t="inlineStr"/>
+      <c r="BT366" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU366" t="inlineStr"/>
+      <c r="BV366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C367" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D367" t="n">
+        <v>11000352181791</v>
+      </c>
+      <c r="E367" t="n">
+        <v>1772436554</v>
+      </c>
+      <c r="F367" t="n">
+        <v>8650</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 12:59:37</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N367" t="n">
+        <v>102107278836</v>
+      </c>
+      <c r="O367" t="inlineStr"/>
+      <c r="P367" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr"/>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr"/>
+      <c r="V367" t="inlineStr"/>
+      <c r="W367" t="inlineStr"/>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>AYESHA NAIK</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z367" t="n">
+        <v>9346210583</v>
+      </c>
+      <c r="AA367" t="inlineStr"/>
+      <c r="AB367" t="inlineStr"/>
+      <c r="AC367" t="inlineStr"/>
+      <c r="AD367" t="inlineStr"/>
+      <c r="AE367" t="inlineStr"/>
+      <c r="AF367" t="inlineStr"/>
+      <c r="AG367" t="inlineStr"/>
+      <c r="AH367" t="inlineStr"/>
+      <c r="AI367" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ367" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK367" t="inlineStr"/>
+      <c r="AL367" t="inlineStr"/>
+      <c r="AM367" t="inlineStr"/>
+      <c r="AN367" t="inlineStr"/>
+      <c r="AO367" t="inlineStr"/>
+      <c r="AP367" t="inlineStr"/>
+      <c r="AQ367" t="inlineStr"/>
+      <c r="AR367" t="inlineStr"/>
+      <c r="AS367" t="inlineStr"/>
+      <c r="AT367" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU367" t="inlineStr"/>
+      <c r="AV367" t="inlineStr"/>
+      <c r="AW367" t="inlineStr"/>
+      <c r="AX367" t="inlineStr"/>
+      <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr"/>
+      <c r="BA367" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB367" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="BC367" t="inlineStr"/>
+      <c r="BD367" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE367" t="n">
+        <v>19024</v>
+      </c>
+      <c r="BF367" t="inlineStr">
+        <is>
+          <t>268411</t>
+        </is>
+      </c>
+      <c r="BG367" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="BH367" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI367" t="n">
+        <v>16375</v>
+      </c>
+      <c r="BJ367" t="inlineStr"/>
+      <c r="BK367" t="inlineStr"/>
+      <c r="BL367" t="inlineStr"/>
+      <c r="BM367" t="inlineStr"/>
+      <c r="BN367" t="inlineStr"/>
+      <c r="BO367" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP367" t="inlineStr"/>
+      <c r="BQ367" t="inlineStr"/>
+      <c r="BR367" t="inlineStr"/>
+      <c r="BS367" t="inlineStr"/>
+      <c r="BT367" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU367" t="inlineStr"/>
+      <c r="BV367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C368" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D368" t="n">
+        <v>11000352288955</v>
+      </c>
+      <c r="E368" t="n">
+        <v>1772507455</v>
+      </c>
+      <c r="F368" t="n">
+        <v>7750</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>03-Mar-2026 08:42:29</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N368" t="n">
+        <v>308920808336</v>
+      </c>
+      <c r="O368" t="inlineStr"/>
+      <c r="P368" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr"/>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr"/>
+      <c r="V368" t="inlineStr"/>
+      <c r="W368" t="inlineStr"/>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>SUVVARI JAIDEEP</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z368" t="n">
+        <v>7386363690</v>
+      </c>
+      <c r="AA368" t="inlineStr"/>
+      <c r="AB368" t="inlineStr"/>
+      <c r="AC368" t="inlineStr"/>
+      <c r="AD368" t="inlineStr"/>
+      <c r="AE368" t="inlineStr"/>
+      <c r="AF368" t="inlineStr"/>
+      <c r="AG368" t="inlineStr"/>
+      <c r="AH368" t="inlineStr"/>
+      <c r="AI368" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ368" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK368" t="inlineStr"/>
+      <c r="AL368" t="inlineStr"/>
+      <c r="AM368" t="inlineStr"/>
+      <c r="AN368" t="inlineStr"/>
+      <c r="AO368" t="inlineStr"/>
+      <c r="AP368" t="inlineStr"/>
+      <c r="AQ368" t="inlineStr"/>
+      <c r="AR368" t="inlineStr"/>
+      <c r="AS368" t="inlineStr"/>
+      <c r="AT368" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU368" t="inlineStr"/>
+      <c r="AV368" t="inlineStr"/>
+      <c r="AW368" t="inlineStr"/>
+      <c r="AX368" t="inlineStr"/>
+      <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr"/>
+      <c r="BA368" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB368" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="BC368" t="inlineStr"/>
+      <c r="BD368" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE368" t="n">
+        <v>20024</v>
+      </c>
+      <c r="BF368" t="inlineStr">
+        <is>
+          <t>266903</t>
+        </is>
+      </c>
+      <c r="BG368" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="BH368" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI368" t="n">
+        <v>17316</v>
+      </c>
+      <c r="BJ368" t="inlineStr"/>
+      <c r="BK368" t="inlineStr"/>
+      <c r="BL368" t="inlineStr"/>
+      <c r="BM368" t="inlineStr"/>
+      <c r="BN368" t="inlineStr"/>
+      <c r="BO368" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP368" t="inlineStr"/>
+      <c r="BQ368" t="inlineStr"/>
+      <c r="BR368" t="inlineStr"/>
+      <c r="BS368" t="inlineStr"/>
+      <c r="BT368" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU368" t="inlineStr"/>
+      <c r="BV368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C369" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D369" t="n">
+        <v>11000352311753</v>
+      </c>
+      <c r="E369" t="n">
+        <v>1772516640</v>
+      </c>
+      <c r="F369" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>03-Mar-2026 11:16:35</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>BANK OF BARODA FSS</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N369" t="n">
+        <v>1.012026062083992e+17</v>
+      </c>
+      <c r="O369" t="inlineStr"/>
+      <c r="P369" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr"/>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr"/>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>UNION BANK OF INDIA</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr"/>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>MOHANA SRI CHILAKA</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z369" t="n">
+        <v>6301934637</v>
+      </c>
+      <c r="AA369" t="inlineStr"/>
+      <c r="AB369" t="inlineStr"/>
+      <c r="AC369" t="inlineStr">
+        <is>
+          <t>XXXXXXXXXXXX2354</t>
+        </is>
+      </c>
+      <c r="AD369" t="inlineStr"/>
+      <c r="AE369" t="inlineStr"/>
+      <c r="AF369" t="inlineStr"/>
+      <c r="AG369" t="inlineStr"/>
+      <c r="AH369" t="inlineStr"/>
+      <c r="AI369" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ369" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK369" t="inlineStr"/>
+      <c r="AL369" t="inlineStr"/>
+      <c r="AM369" t="inlineStr"/>
+      <c r="AN369" t="inlineStr"/>
+      <c r="AO369" t="inlineStr"/>
+      <c r="AP369" t="inlineStr"/>
+      <c r="AQ369" t="inlineStr"/>
+      <c r="AR369" t="inlineStr"/>
+      <c r="AS369" t="inlineStr"/>
+      <c r="AT369" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
+      </c>
+      <c r="AU369" t="inlineStr"/>
+      <c r="AV369" t="inlineStr"/>
+      <c r="AW369" t="inlineStr"/>
+      <c r="AX369" t="inlineStr"/>
+      <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr"/>
+      <c r="BA369" t="inlineStr">
+        <is>
+          <t>RUPAY</t>
+        </is>
+      </c>
+      <c r="BB369" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC369" t="inlineStr"/>
+      <c r="BD369" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE369" t="n">
+        <v>19899</v>
+      </c>
+      <c r="BF369" t="inlineStr">
+        <is>
+          <t>266651</t>
+        </is>
+      </c>
+      <c r="BG369" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH369" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI369" t="n">
+        <v>17185</v>
+      </c>
+      <c r="BJ369" t="inlineStr"/>
+      <c r="BK369" t="inlineStr"/>
+      <c r="BL369" t="inlineStr"/>
+      <c r="BM369" t="inlineStr"/>
+      <c r="BN369" t="inlineStr"/>
+      <c r="BO369" t="inlineStr"/>
+      <c r="BP369" t="inlineStr"/>
+      <c r="BQ369" t="inlineStr"/>
+      <c r="BR369" t="inlineStr"/>
+      <c r="BS369" t="inlineStr"/>
+      <c r="BT369" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU369" t="inlineStr"/>
+      <c r="BV369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/source_data/atom_report.xlsx
+++ b/source_data/atom_report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW425"/>
+  <dimension ref="A1:BW427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66500,7 +66500,11 @@
         <v>605864009197</v>
       </c>
       <c r="O349" t="inlineStr"/>
-      <c r="P349" t="inlineStr"/>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q349" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -66524,9 +66528,21 @@
       <c r="U349" t="inlineStr"/>
       <c r="V349" t="inlineStr"/>
       <c r="W349" t="inlineStr"/>
-      <c r="X349" t="inlineStr"/>
-      <c r="Y349" t="inlineStr"/>
-      <c r="Z349" t="inlineStr"/>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>V****** K*****</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>83****9788</t>
+        </is>
+      </c>
       <c r="AA349" t="inlineStr"/>
       <c r="AB349" t="inlineStr"/>
       <c r="AC349" t="inlineStr"/>
@@ -66697,7 +66713,11 @@
         <v>109277483982</v>
       </c>
       <c r="O350" t="inlineStr"/>
-      <c r="P350" t="inlineStr"/>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q350" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -66717,9 +66737,21 @@
       <c r="U350" t="inlineStr"/>
       <c r="V350" t="inlineStr"/>
       <c r="W350" t="inlineStr"/>
-      <c r="X350" t="inlineStr"/>
-      <c r="Y350" t="inlineStr"/>
-      <c r="Z350" t="inlineStr"/>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>D**** T*********</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>62****4352</t>
+        </is>
+      </c>
       <c r="AA350" t="inlineStr"/>
       <c r="AB350" t="inlineStr"/>
       <c r="AC350" t="inlineStr"/>
@@ -66874,7 +66906,11 @@
         <v>40471991429</v>
       </c>
       <c r="O351" t="inlineStr"/>
-      <c r="P351" t="inlineStr"/>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q351" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -66898,9 +66934,21 @@
       <c r="U351" t="inlineStr"/>
       <c r="V351" t="inlineStr"/>
       <c r="W351" t="inlineStr"/>
-      <c r="X351" t="inlineStr"/>
-      <c r="Y351" t="inlineStr"/>
-      <c r="Z351" t="inlineStr"/>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>Y******** R**** G****</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>99****5552</t>
+        </is>
+      </c>
       <c r="AA351" t="inlineStr"/>
       <c r="AB351" t="inlineStr"/>
       <c r="AC351" t="inlineStr"/>
@@ -67071,7 +67119,11 @@
         <v>146763616167</v>
       </c>
       <c r="O352" t="inlineStr"/>
-      <c r="P352" t="inlineStr"/>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q352" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -67091,9 +67143,21 @@
       <c r="U352" t="inlineStr"/>
       <c r="V352" t="inlineStr"/>
       <c r="W352" t="inlineStr"/>
-      <c r="X352" t="inlineStr"/>
-      <c r="Y352" t="inlineStr"/>
-      <c r="Z352" t="inlineStr"/>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>M******* R**** G****</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>99****5552</t>
+        </is>
+      </c>
       <c r="AA352" t="inlineStr"/>
       <c r="AB352" t="inlineStr"/>
       <c r="AC352" t="inlineStr"/>
@@ -67260,7 +67324,11 @@
         <v>866758700772</v>
       </c>
       <c r="O353" t="inlineStr"/>
-      <c r="P353" t="inlineStr"/>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q353" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -67284,9 +67352,21 @@
       <c r="U353" t="inlineStr"/>
       <c r="V353" t="inlineStr"/>
       <c r="W353" t="inlineStr"/>
-      <c r="X353" t="inlineStr"/>
-      <c r="Y353" t="inlineStr"/>
-      <c r="Z353" t="inlineStr"/>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>D**** B******* S** S**</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>95****7535</t>
+        </is>
+      </c>
       <c r="AA353" t="inlineStr"/>
       <c r="AB353" t="inlineStr"/>
       <c r="AC353" t="inlineStr"/>
@@ -67457,7 +67537,11 @@
         <v>920094640606</v>
       </c>
       <c r="O354" t="inlineStr"/>
-      <c r="P354" t="inlineStr"/>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q354" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -67481,9 +67565,21 @@
       <c r="U354" t="inlineStr"/>
       <c r="V354" t="inlineStr"/>
       <c r="W354" t="inlineStr"/>
-      <c r="X354" t="inlineStr"/>
-      <c r="Y354" t="inlineStr"/>
-      <c r="Z354" t="inlineStr"/>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>D**** M**********</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>95****7535</t>
+        </is>
+      </c>
       <c r="AA354" t="inlineStr"/>
       <c r="AB354" t="inlineStr"/>
       <c r="AC354" t="inlineStr"/>
@@ -67654,7 +67750,11 @@
         <v>891768471043</v>
       </c>
       <c r="O355" t="inlineStr"/>
-      <c r="P355" t="inlineStr"/>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q355" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -67674,9 +67774,21 @@
       <c r="U355" t="inlineStr"/>
       <c r="V355" t="inlineStr"/>
       <c r="W355" t="inlineStr"/>
-      <c r="X355" t="inlineStr"/>
-      <c r="Y355" t="inlineStr"/>
-      <c r="Z355" t="inlineStr"/>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>D**** M**********</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>95****7535</t>
+        </is>
+      </c>
       <c r="AA355" t="inlineStr"/>
       <c r="AB355" t="inlineStr"/>
       <c r="AC355" t="inlineStr"/>
@@ -67835,7 +67947,11 @@
         <v>469507160708</v>
       </c>
       <c r="O356" t="inlineStr"/>
-      <c r="P356" t="inlineStr"/>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q356" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -67859,9 +67975,21 @@
       <c r="U356" t="inlineStr"/>
       <c r="V356" t="inlineStr"/>
       <c r="W356" t="inlineStr"/>
-      <c r="X356" t="inlineStr"/>
-      <c r="Y356" t="inlineStr"/>
-      <c r="Z356" t="inlineStr"/>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>D**** M**********</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>95****7535</t>
+        </is>
+      </c>
       <c r="AA356" t="inlineStr"/>
       <c r="AB356" t="inlineStr"/>
       <c r="AC356" t="inlineStr"/>
@@ -68032,7 +68160,11 @@
         <v>109278991926</v>
       </c>
       <c r="O357" t="inlineStr"/>
-      <c r="P357" t="inlineStr"/>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q357" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -68056,9 +68188,21 @@
       <c r="U357" t="inlineStr"/>
       <c r="V357" t="inlineStr"/>
       <c r="W357" t="inlineStr"/>
-      <c r="X357" t="inlineStr"/>
-      <c r="Y357" t="inlineStr"/>
-      <c r="Z357" t="inlineStr"/>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>S** S***** P*******</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>73****2112</t>
+        </is>
+      </c>
       <c r="AA357" t="inlineStr"/>
       <c r="AB357" t="inlineStr"/>
       <c r="AC357" t="inlineStr"/>
@@ -68225,7 +68369,11 @@
         <v>109279356760</v>
       </c>
       <c r="O358" t="inlineStr"/>
-      <c r="P358" t="inlineStr"/>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q358" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -68249,9 +68397,21 @@
       <c r="U358" t="inlineStr"/>
       <c r="V358" t="inlineStr"/>
       <c r="W358" t="inlineStr"/>
-      <c r="X358" t="inlineStr"/>
-      <c r="Y358" t="inlineStr"/>
-      <c r="Z358" t="inlineStr"/>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>B****** B*** S**** B*****</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>63****5193</t>
+        </is>
+      </c>
       <c r="AA358" t="inlineStr"/>
       <c r="AB358" t="inlineStr"/>
       <c r="AC358" t="inlineStr"/>
@@ -68420,7 +68580,11 @@
       <c r="O359" t="n">
         <v>455738</v>
       </c>
-      <c r="P359" t="inlineStr"/>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q359" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -68448,9 +68612,21 @@
         </is>
       </c>
       <c r="W359" t="inlineStr"/>
-      <c r="X359" t="inlineStr"/>
-      <c r="Y359" t="inlineStr"/>
-      <c r="Z359" t="inlineStr"/>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>S***** S****</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>83****6856</t>
+        </is>
+      </c>
       <c r="AA359" t="inlineStr"/>
       <c r="AB359" t="inlineStr"/>
       <c r="AC359" t="inlineStr">
@@ -68623,7 +68799,11 @@
       <c r="O360" t="n">
         <v>606171974859</v>
       </c>
-      <c r="P360" t="inlineStr"/>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q360" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -68647,9 +68827,21 @@
       <c r="U360" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
       <c r="W360" t="inlineStr"/>
-      <c r="X360" t="inlineStr"/>
-      <c r="Y360" t="inlineStr"/>
-      <c r="Z360" t="inlineStr"/>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>M**** V****** S**</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>92****1340</t>
+        </is>
+      </c>
       <c r="AA360" t="inlineStr"/>
       <c r="AB360" t="inlineStr"/>
       <c r="AC360" t="inlineStr"/>
@@ -68820,7 +69012,11 @@
         <v>778077483731</v>
       </c>
       <c r="O361" t="inlineStr"/>
-      <c r="P361" t="inlineStr"/>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q361" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -68844,9 +69040,21 @@
       <c r="U361" t="inlineStr"/>
       <c r="V361" t="inlineStr"/>
       <c r="W361" t="inlineStr"/>
-      <c r="X361" t="inlineStr"/>
-      <c r="Y361" t="inlineStr"/>
-      <c r="Z361" t="inlineStr"/>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>T***** D********</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>73****9208</t>
+        </is>
+      </c>
       <c r="AA361" t="inlineStr"/>
       <c r="AB361" t="inlineStr"/>
       <c r="AC361" t="inlineStr"/>
@@ -69017,7 +69225,11 @@
         <v>805616523520</v>
       </c>
       <c r="O362" t="inlineStr"/>
-      <c r="P362" t="inlineStr"/>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q362" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -69041,9 +69253,21 @@
       <c r="U362" t="inlineStr"/>
       <c r="V362" t="inlineStr"/>
       <c r="W362" t="inlineStr"/>
-      <c r="X362" t="inlineStr"/>
-      <c r="Y362" t="inlineStr"/>
-      <c r="Z362" t="inlineStr"/>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>T***** H*** C******</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>73****9208</t>
+        </is>
+      </c>
       <c r="AA362" t="inlineStr"/>
       <c r="AB362" t="inlineStr"/>
       <c r="AC362" t="inlineStr"/>
@@ -69214,7 +69438,11 @@
         <v>1.01202606115622e+17</v>
       </c>
       <c r="O363" t="inlineStr"/>
-      <c r="P363" t="inlineStr"/>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q363" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -69238,9 +69466,21 @@
         </is>
       </c>
       <c r="W363" t="inlineStr"/>
-      <c r="X363" t="inlineStr"/>
-      <c r="Y363" t="inlineStr"/>
-      <c r="Z363" t="inlineStr"/>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>K******* E**** E****</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>98****0099</t>
+        </is>
+      </c>
       <c r="AA363" t="inlineStr"/>
       <c r="AB363" t="inlineStr"/>
       <c r="AC363" t="inlineStr">
@@ -69395,7 +69635,11 @@
       <c r="O364" t="n">
         <v>606128095174</v>
       </c>
-      <c r="P364" t="inlineStr"/>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q364" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -69419,9 +69663,21 @@
       <c r="U364" t="inlineStr"/>
       <c r="V364" t="inlineStr"/>
       <c r="W364" t="inlineStr"/>
-      <c r="X364" t="inlineStr"/>
-      <c r="Y364" t="inlineStr"/>
-      <c r="Z364" t="inlineStr"/>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>K******* E**** E****</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>98****0099</t>
+        </is>
+      </c>
       <c r="AA364" t="inlineStr"/>
       <c r="AB364" t="inlineStr"/>
       <c r="AC364" t="inlineStr"/>
@@ -69592,7 +69848,11 @@
         <v>201120935621</v>
       </c>
       <c r="O365" t="inlineStr"/>
-      <c r="P365" t="inlineStr"/>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q365" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -69616,9 +69876,21 @@
       <c r="U365" t="inlineStr"/>
       <c r="V365" t="inlineStr"/>
       <c r="W365" t="inlineStr"/>
-      <c r="X365" t="inlineStr"/>
-      <c r="Y365" t="inlineStr"/>
-      <c r="Z365" t="inlineStr"/>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>R****** J******</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>77****0192</t>
+        </is>
+      </c>
       <c r="AA365" t="inlineStr"/>
       <c r="AB365" t="inlineStr"/>
       <c r="AC365" t="inlineStr"/>
@@ -69789,7 +70061,11 @@
         <v>398196116938</v>
       </c>
       <c r="O366" t="inlineStr"/>
-      <c r="P366" t="inlineStr"/>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q366" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -69813,9 +70089,21 @@
       <c r="U366" t="inlineStr"/>
       <c r="V366" t="inlineStr"/>
       <c r="W366" t="inlineStr"/>
-      <c r="X366" t="inlineStr"/>
-      <c r="Y366" t="inlineStr"/>
-      <c r="Z366" t="inlineStr"/>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>R****** Y**** V****** R*****</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z366" t="inlineStr">
+        <is>
+          <t>77****0192</t>
+        </is>
+      </c>
       <c r="AA366" t="inlineStr"/>
       <c r="AB366" t="inlineStr"/>
       <c r="AC366" t="inlineStr"/>
@@ -69986,7 +70274,11 @@
         <v>102107278836</v>
       </c>
       <c r="O367" t="inlineStr"/>
-      <c r="P367" t="inlineStr"/>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q367" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -70006,9 +70298,21 @@
       <c r="U367" t="inlineStr"/>
       <c r="V367" t="inlineStr"/>
       <c r="W367" t="inlineStr"/>
-      <c r="X367" t="inlineStr"/>
-      <c r="Y367" t="inlineStr"/>
-      <c r="Z367" t="inlineStr"/>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>A***** N***</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>93****0583</t>
+        </is>
+      </c>
       <c r="AA367" t="inlineStr"/>
       <c r="AB367" t="inlineStr"/>
       <c r="AC367" t="inlineStr"/>
@@ -70175,7 +70479,11 @@
         <v>308920808336</v>
       </c>
       <c r="O368" t="inlineStr"/>
-      <c r="P368" t="inlineStr"/>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q368" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -70195,9 +70503,21 @@
       <c r="U368" t="inlineStr"/>
       <c r="V368" t="inlineStr"/>
       <c r="W368" t="inlineStr"/>
-      <c r="X368" t="inlineStr"/>
-      <c r="Y368" t="inlineStr"/>
-      <c r="Z368" t="inlineStr"/>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>S****** J******</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>73****3690</t>
+        </is>
+      </c>
       <c r="AA368" t="inlineStr"/>
       <c r="AB368" t="inlineStr"/>
       <c r="AC368" t="inlineStr"/>
@@ -70356,7 +70676,11 @@
         <v>1.012026062083992e+17</v>
       </c>
       <c r="O369" t="inlineStr"/>
-      <c r="P369" t="inlineStr"/>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q369" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -70380,9 +70704,21 @@
         </is>
       </c>
       <c r="W369" t="inlineStr"/>
-      <c r="X369" t="inlineStr"/>
-      <c r="Y369" t="inlineStr"/>
-      <c r="Z369" t="inlineStr"/>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>M***** S** C******</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>63****4637</t>
+        </is>
+      </c>
       <c r="AA369" t="inlineStr"/>
       <c r="AB369" t="inlineStr"/>
       <c r="AC369" t="inlineStr">
@@ -70541,7 +70877,11 @@
         <v>471174884415</v>
       </c>
       <c r="O370" t="inlineStr"/>
-      <c r="P370" t="inlineStr"/>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q370" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -70565,9 +70905,21 @@
       <c r="U370" t="inlineStr"/>
       <c r="V370" t="inlineStr"/>
       <c r="W370" t="inlineStr"/>
-      <c r="X370" t="inlineStr"/>
-      <c r="Y370" t="inlineStr"/>
-      <c r="Z370" t="inlineStr"/>
+      <c r="X370" t="inlineStr">
+        <is>
+          <t>C******* A************* M*********</t>
+        </is>
+      </c>
+      <c r="Y370" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z370" t="inlineStr">
+        <is>
+          <t>99****6244</t>
+        </is>
+      </c>
       <c r="AA370" t="inlineStr"/>
       <c r="AB370" t="inlineStr"/>
       <c r="AC370" t="inlineStr"/>
@@ -70738,7 +71090,11 @@
         <v>841705895977</v>
       </c>
       <c r="O371" t="inlineStr"/>
-      <c r="P371" t="inlineStr"/>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q371" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -70762,9 +71118,21 @@
       <c r="U371" t="inlineStr"/>
       <c r="V371" t="inlineStr"/>
       <c r="W371" t="inlineStr"/>
-      <c r="X371" t="inlineStr"/>
-      <c r="Y371" t="inlineStr"/>
-      <c r="Z371" t="inlineStr"/>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>C******* A************* M*********</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t>99****6244</t>
+        </is>
+      </c>
       <c r="AA371" t="inlineStr"/>
       <c r="AB371" t="inlineStr"/>
       <c r="AC371" t="inlineStr"/>
@@ -70935,7 +71303,11 @@
         <v>967490825745</v>
       </c>
       <c r="O372" t="inlineStr"/>
-      <c r="P372" t="inlineStr"/>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q372" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -70955,9 +71327,21 @@
       <c r="U372" t="inlineStr"/>
       <c r="V372" t="inlineStr"/>
       <c r="W372" t="inlineStr"/>
-      <c r="X372" t="inlineStr"/>
-      <c r="Y372" t="inlineStr"/>
-      <c r="Z372" t="inlineStr"/>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>H******** R*****</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>63****8581</t>
+        </is>
+      </c>
       <c r="AA372" t="inlineStr"/>
       <c r="AB372" t="inlineStr"/>
       <c r="AC372" t="inlineStr"/>
@@ -71116,7 +71500,11 @@
         <v>104032665366</v>
       </c>
       <c r="O373" t="inlineStr"/>
-      <c r="P373" t="inlineStr"/>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q373" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -71140,9 +71528,21 @@
       <c r="U373" t="inlineStr"/>
       <c r="V373" t="inlineStr"/>
       <c r="W373" t="inlineStr"/>
-      <c r="X373" t="inlineStr"/>
-      <c r="Y373" t="inlineStr"/>
-      <c r="Z373" t="inlineStr"/>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>H******** R*****</t>
+        </is>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>63****8581</t>
+        </is>
+      </c>
       <c r="AA373" t="inlineStr"/>
       <c r="AB373" t="inlineStr"/>
       <c r="AC373" t="inlineStr"/>
@@ -71313,7 +71713,11 @@
         <v>599097516858</v>
       </c>
       <c r="O374" t="inlineStr"/>
-      <c r="P374" t="inlineStr"/>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q374" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -71337,9 +71741,21 @@
       <c r="U374" t="inlineStr"/>
       <c r="V374" t="inlineStr"/>
       <c r="W374" t="inlineStr"/>
-      <c r="X374" t="inlineStr"/>
-      <c r="Y374" t="inlineStr"/>
-      <c r="Z374" t="inlineStr"/>
+      <c r="X374" t="inlineStr">
+        <is>
+          <t>S**** Y****</t>
+        </is>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z374" t="inlineStr">
+        <is>
+          <t>81****6234</t>
+        </is>
+      </c>
       <c r="AA374" t="inlineStr"/>
       <c r="AB374" t="inlineStr"/>
       <c r="AC374" t="inlineStr"/>
@@ -71510,7 +71926,11 @@
         <v>192575940153</v>
       </c>
       <c r="O375" t="inlineStr"/>
-      <c r="P375" t="inlineStr"/>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q375" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -71530,9 +71950,21 @@
       <c r="U375" t="inlineStr"/>
       <c r="V375" t="inlineStr"/>
       <c r="W375" t="inlineStr"/>
-      <c r="X375" t="inlineStr"/>
-      <c r="Y375" t="inlineStr"/>
-      <c r="Z375" t="inlineStr"/>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>B**** A****** S***</t>
+        </is>
+      </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t>90****9626</t>
+        </is>
+      </c>
       <c r="AA375" t="inlineStr"/>
       <c r="AB375" t="inlineStr"/>
       <c r="AC375" t="inlineStr"/>
@@ -71699,7 +72131,11 @@
         <v>1.012026063148447e+17</v>
       </c>
       <c r="O376" t="inlineStr"/>
-      <c r="P376" t="inlineStr"/>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q376" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -71723,9 +72159,21 @@
         </is>
       </c>
       <c r="W376" t="inlineStr"/>
-      <c r="X376" t="inlineStr"/>
-      <c r="Y376" t="inlineStr"/>
-      <c r="Z376" t="inlineStr"/>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>V********* L*******</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>94****2946</t>
+        </is>
+      </c>
       <c r="AA376" t="inlineStr"/>
       <c r="AB376" t="inlineStr"/>
       <c r="AC376" t="inlineStr">
@@ -71880,7 +72328,11 @@
         <v>1.012026063851171e+17</v>
       </c>
       <c r="O377" t="inlineStr"/>
-      <c r="P377" t="inlineStr"/>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q377" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -71904,8 +72356,16 @@
         </is>
       </c>
       <c r="W377" t="inlineStr"/>
-      <c r="X377" t="inlineStr"/>
-      <c r="Y377" t="inlineStr"/>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>V********* L*******</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="Z377" t="inlineStr"/>
       <c r="AA377" t="inlineStr"/>
       <c r="AB377" t="inlineStr"/>
@@ -72061,7 +72521,11 @@
         <v>723742672506</v>
       </c>
       <c r="O378" t="inlineStr"/>
-      <c r="P378" t="inlineStr"/>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q378" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -72085,9 +72549,21 @@
       <c r="U378" t="inlineStr"/>
       <c r="V378" t="inlineStr"/>
       <c r="W378" t="inlineStr"/>
-      <c r="X378" t="inlineStr"/>
-      <c r="Y378" t="inlineStr"/>
-      <c r="Z378" t="inlineStr"/>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>K****** G**********</t>
+        </is>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t>99****1635</t>
+        </is>
+      </c>
       <c r="AA378" t="inlineStr"/>
       <c r="AB378" t="inlineStr"/>
       <c r="AC378" t="inlineStr"/>
@@ -72258,7 +72734,11 @@
         <v>169051468182</v>
       </c>
       <c r="O379" t="inlineStr"/>
-      <c r="P379" t="inlineStr"/>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q379" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -72282,9 +72762,21 @@
       <c r="U379" t="inlineStr"/>
       <c r="V379" t="inlineStr"/>
       <c r="W379" t="inlineStr"/>
-      <c r="X379" t="inlineStr"/>
-      <c r="Y379" t="inlineStr"/>
-      <c r="Z379" t="inlineStr"/>
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>K****** H*****</t>
+        </is>
+      </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t>99****1635</t>
+        </is>
+      </c>
       <c r="AA379" t="inlineStr"/>
       <c r="AB379" t="inlineStr"/>
       <c r="AC379" t="inlineStr"/>
@@ -72455,7 +72947,11 @@
         <v>594651190291</v>
       </c>
       <c r="O380" t="inlineStr"/>
-      <c r="P380" t="inlineStr"/>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q380" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -72479,9 +72975,21 @@
       <c r="U380" t="inlineStr"/>
       <c r="V380" t="inlineStr"/>
       <c r="W380" t="inlineStr"/>
-      <c r="X380" t="inlineStr"/>
-      <c r="Y380" t="inlineStr"/>
-      <c r="Z380" t="inlineStr"/>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>K**** M*********</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>97****1309</t>
+        </is>
+      </c>
       <c r="AA380" t="inlineStr"/>
       <c r="AB380" t="inlineStr"/>
       <c r="AC380" t="inlineStr"/>
@@ -72652,7 +73160,11 @@
         <v>1.012026064983154e+17</v>
       </c>
       <c r="O381" t="inlineStr"/>
-      <c r="P381" t="inlineStr"/>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q381" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -72676,9 +73188,21 @@
         </is>
       </c>
       <c r="W381" t="inlineStr"/>
-      <c r="X381" t="inlineStr"/>
-      <c r="Y381" t="inlineStr"/>
-      <c r="Z381" t="inlineStr"/>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>R****** V***********</t>
+        </is>
+      </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t>98****9449</t>
+        </is>
+      </c>
       <c r="AA381" t="inlineStr"/>
       <c r="AB381" t="inlineStr"/>
       <c r="AC381" t="inlineStr">
@@ -72835,7 +73359,11 @@
       <c r="O382" t="n">
         <v>617759165517</v>
       </c>
-      <c r="P382" t="inlineStr"/>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q382" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -72859,9 +73387,21 @@
       <c r="U382" t="inlineStr"/>
       <c r="V382" t="inlineStr"/>
       <c r="W382" t="inlineStr"/>
-      <c r="X382" t="inlineStr"/>
-      <c r="Y382" t="inlineStr"/>
-      <c r="Z382" t="inlineStr"/>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>R****** V***********</t>
+        </is>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>98****9449</t>
+        </is>
+      </c>
       <c r="AA382" t="inlineStr"/>
       <c r="AB382" t="inlineStr"/>
       <c r="AC382" t="inlineStr"/>
@@ -73032,7 +73572,11 @@
         <v>606512772867</v>
       </c>
       <c r="O383" t="inlineStr"/>
-      <c r="P383" t="inlineStr"/>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q383" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -73056,9 +73600,21 @@
       <c r="U383" t="inlineStr"/>
       <c r="V383" t="inlineStr"/>
       <c r="W383" t="inlineStr"/>
-      <c r="X383" t="inlineStr"/>
-      <c r="Y383" t="inlineStr"/>
-      <c r="Z383" t="inlineStr"/>
+      <c r="X383" t="inlineStr">
+        <is>
+          <t>M******* Z*** K***</t>
+        </is>
+      </c>
+      <c r="Y383" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>82****8795</t>
+        </is>
+      </c>
       <c r="AA383" t="inlineStr"/>
       <c r="AB383" t="inlineStr"/>
       <c r="AC383" t="inlineStr"/>
@@ -73229,7 +73785,11 @@
         <v>685322950436</v>
       </c>
       <c r="O384" t="inlineStr"/>
-      <c r="P384" t="inlineStr"/>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q384" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -73253,9 +73813,21 @@
       <c r="U384" t="inlineStr"/>
       <c r="V384" t="inlineStr"/>
       <c r="W384" t="inlineStr"/>
-      <c r="X384" t="inlineStr"/>
-      <c r="Y384" t="inlineStr"/>
-      <c r="Z384" t="inlineStr"/>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>Y**** Y******* N****</t>
+        </is>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t>94****1196</t>
+        </is>
+      </c>
       <c r="AA384" t="inlineStr"/>
       <c r="AB384" t="inlineStr"/>
       <c r="AC384" t="inlineStr"/>
@@ -73426,7 +73998,11 @@
         <v>606553970981</v>
       </c>
       <c r="O385" t="inlineStr"/>
-      <c r="P385" t="inlineStr"/>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q385" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -73446,9 +74022,21 @@
       <c r="U385" t="inlineStr"/>
       <c r="V385" t="inlineStr"/>
       <c r="W385" t="inlineStr"/>
-      <c r="X385" t="inlineStr"/>
-      <c r="Y385" t="inlineStr"/>
-      <c r="Z385" t="inlineStr"/>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>M***** S******* L****** S** M** R**</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>80****0739</t>
+        </is>
+      </c>
       <c r="AA385" t="inlineStr"/>
       <c r="AB385" t="inlineStr"/>
       <c r="AC385" t="inlineStr"/>
@@ -73615,7 +74203,11 @@
         <v>398424860025</v>
       </c>
       <c r="O386" t="inlineStr"/>
-      <c r="P386" t="inlineStr"/>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q386" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -73635,9 +74227,21 @@
       <c r="U386" t="inlineStr"/>
       <c r="V386" t="inlineStr"/>
       <c r="W386" t="inlineStr"/>
-      <c r="X386" t="inlineStr"/>
-      <c r="Y386" t="inlineStr"/>
-      <c r="Z386" t="inlineStr"/>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>S**** V****** S** V***** V******</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>85****3683</t>
+        </is>
+      </c>
       <c r="AA386" t="inlineStr"/>
       <c r="AB386" t="inlineStr"/>
       <c r="AC386" t="inlineStr"/>
@@ -73806,7 +74410,11 @@
       <c r="O387" t="n">
         <v>149006197244</v>
       </c>
-      <c r="P387" t="inlineStr"/>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q387" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -73830,9 +74438,21 @@
       <c r="U387" t="inlineStr"/>
       <c r="V387" t="inlineStr"/>
       <c r="W387" t="inlineStr"/>
-      <c r="X387" t="inlineStr"/>
-      <c r="Y387" t="inlineStr"/>
-      <c r="Z387" t="inlineStr"/>
+      <c r="X387" t="inlineStr">
+        <is>
+          <t>P******** B******* S**</t>
+        </is>
+      </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t>63****9629</t>
+        </is>
+      </c>
       <c r="AA387" t="inlineStr"/>
       <c r="AB387" t="inlineStr"/>
       <c r="AC387" t="inlineStr"/>
@@ -74003,7 +74623,11 @@
         <v>868411654766</v>
       </c>
       <c r="O388" t="inlineStr"/>
-      <c r="P388" t="inlineStr"/>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q388" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -74027,9 +74651,21 @@
       <c r="U388" t="inlineStr"/>
       <c r="V388" t="inlineStr"/>
       <c r="W388" t="inlineStr"/>
-      <c r="X388" t="inlineStr"/>
-      <c r="Y388" t="inlineStr"/>
-      <c r="Z388" t="inlineStr"/>
+      <c r="X388" t="inlineStr">
+        <is>
+          <t>V******* L********</t>
+        </is>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>88****9151</t>
+        </is>
+      </c>
       <c r="AA388" t="inlineStr"/>
       <c r="AB388" t="inlineStr"/>
       <c r="AC388" t="inlineStr"/>
@@ -74200,7 +74836,11 @@
         <v>600442299844</v>
       </c>
       <c r="O389" t="inlineStr"/>
-      <c r="P389" t="inlineStr"/>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q389" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -74224,9 +74864,21 @@
       <c r="U389" t="inlineStr"/>
       <c r="V389" t="inlineStr"/>
       <c r="W389" t="inlineStr"/>
-      <c r="X389" t="inlineStr"/>
-      <c r="Y389" t="inlineStr"/>
-      <c r="Z389" t="inlineStr"/>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>S**** A******</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>98****7290</t>
+        </is>
+      </c>
       <c r="AA389" t="inlineStr"/>
       <c r="AB389" t="inlineStr"/>
       <c r="AC389" t="inlineStr"/>
@@ -74397,7 +75049,11 @@
         <v>813785429091</v>
       </c>
       <c r="O390" t="inlineStr"/>
-      <c r="P390" t="inlineStr"/>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q390" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -74421,9 +75077,21 @@
       <c r="U390" t="inlineStr"/>
       <c r="V390" t="inlineStr"/>
       <c r="W390" t="inlineStr"/>
-      <c r="X390" t="inlineStr"/>
-      <c r="Y390" t="inlineStr"/>
-      <c r="Z390" t="inlineStr"/>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>R***** H********* V*****</t>
+        </is>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z390" t="inlineStr">
+        <is>
+          <t>93****3084</t>
+        </is>
+      </c>
       <c r="AA390" t="inlineStr"/>
       <c r="AB390" t="inlineStr"/>
       <c r="AC390" t="inlineStr"/>
@@ -74594,7 +75262,11 @@
         <v>606674598901</v>
       </c>
       <c r="O391" t="inlineStr"/>
-      <c r="P391" t="inlineStr"/>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q391" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -74614,9 +75286,21 @@
       <c r="U391" t="inlineStr"/>
       <c r="V391" t="inlineStr"/>
       <c r="W391" t="inlineStr"/>
-      <c r="X391" t="inlineStr"/>
-      <c r="Y391" t="inlineStr"/>
-      <c r="Z391" t="inlineStr"/>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>E******* M*******</t>
+        </is>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z391" t="inlineStr">
+        <is>
+          <t>96****1662</t>
+        </is>
+      </c>
       <c r="AA391" t="inlineStr"/>
       <c r="AB391" t="inlineStr"/>
       <c r="AC391" t="inlineStr"/>
@@ -74777,7 +75461,11 @@
       <c r="O392" t="n">
         <v>134637860821</v>
       </c>
-      <c r="P392" t="inlineStr"/>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q392" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -74801,9 +75489,21 @@
       <c r="U392" t="inlineStr"/>
       <c r="V392" t="inlineStr"/>
       <c r="W392" t="inlineStr"/>
-      <c r="X392" t="inlineStr"/>
-      <c r="Y392" t="inlineStr"/>
-      <c r="Z392" t="inlineStr"/>
+      <c r="X392" t="inlineStr">
+        <is>
+          <t>E******* M*******</t>
+        </is>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>96****1662</t>
+        </is>
+      </c>
       <c r="AA392" t="inlineStr"/>
       <c r="AB392" t="inlineStr"/>
       <c r="AC392" t="inlineStr"/>
@@ -74974,7 +75674,11 @@
         <v>814343009761</v>
       </c>
       <c r="O393" t="inlineStr"/>
-      <c r="P393" t="inlineStr"/>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q393" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -74998,9 +75702,21 @@
       <c r="U393" t="inlineStr"/>
       <c r="V393" t="inlineStr"/>
       <c r="W393" t="inlineStr"/>
-      <c r="X393" t="inlineStr"/>
-      <c r="Y393" t="inlineStr"/>
-      <c r="Z393" t="inlineStr"/>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>S**** B******</t>
+        </is>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z393" t="inlineStr">
+        <is>
+          <t>79****8688</t>
+        </is>
+      </c>
       <c r="AA393" t="inlineStr"/>
       <c r="AB393" t="inlineStr"/>
       <c r="AC393" t="inlineStr"/>
@@ -75171,7 +75887,11 @@
         <v>320147941217</v>
       </c>
       <c r="O394" t="inlineStr"/>
-      <c r="P394" t="inlineStr"/>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q394" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -75195,9 +75915,21 @@
       <c r="U394" t="inlineStr"/>
       <c r="V394" t="inlineStr"/>
       <c r="W394" t="inlineStr"/>
-      <c r="X394" t="inlineStr"/>
-      <c r="Y394" t="inlineStr"/>
-      <c r="Z394" t="inlineStr"/>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>S**** B********* S**</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>79****8688</t>
+        </is>
+      </c>
       <c r="AA394" t="inlineStr"/>
       <c r="AB394" t="inlineStr"/>
       <c r="AC394" t="inlineStr"/>
@@ -75368,7 +76100,11 @@
         <v>405349185208</v>
       </c>
       <c r="O395" t="inlineStr"/>
-      <c r="P395" t="inlineStr"/>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q395" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -75392,9 +76128,21 @@
       <c r="U395" t="inlineStr"/>
       <c r="V395" t="inlineStr"/>
       <c r="W395" t="inlineStr"/>
-      <c r="X395" t="inlineStr"/>
-      <c r="Y395" t="inlineStr"/>
-      <c r="Z395" t="inlineStr"/>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>V****** V******* M****</t>
+        </is>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>76****5088</t>
+        </is>
+      </c>
       <c r="AA395" t="inlineStr"/>
       <c r="AB395" t="inlineStr"/>
       <c r="AC395" t="inlineStr"/>
@@ -75565,7 +76313,11 @@
         <v>800388341317</v>
       </c>
       <c r="O396" t="inlineStr"/>
-      <c r="P396" t="inlineStr"/>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q396" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -75589,9 +76341,21 @@
       <c r="U396" t="inlineStr"/>
       <c r="V396" t="inlineStr"/>
       <c r="W396" t="inlineStr"/>
-      <c r="X396" t="inlineStr"/>
-      <c r="Y396" t="inlineStr"/>
-      <c r="Z396" t="inlineStr"/>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>P******* C****** R******</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>90****9830</t>
+        </is>
+      </c>
       <c r="AA396" t="inlineStr"/>
       <c r="AB396" t="inlineStr"/>
       <c r="AC396" t="inlineStr"/>
@@ -75762,7 +76526,11 @@
         <v>17268084705</v>
       </c>
       <c r="O397" t="inlineStr"/>
-      <c r="P397" t="inlineStr"/>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q397" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -75782,9 +76550,21 @@
       <c r="U397" t="inlineStr"/>
       <c r="V397" t="inlineStr"/>
       <c r="W397" t="inlineStr"/>
-      <c r="X397" t="inlineStr"/>
-      <c r="Y397" t="inlineStr"/>
-      <c r="Z397" t="inlineStr"/>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>T**** T*** K****</t>
+        </is>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>97****8884</t>
+        </is>
+      </c>
       <c r="AA397" t="inlineStr"/>
       <c r="AB397" t="inlineStr"/>
       <c r="AC397" t="inlineStr"/>
@@ -75951,7 +76731,11 @@
         <v>606782833518</v>
       </c>
       <c r="O398" t="inlineStr"/>
-      <c r="P398" t="inlineStr"/>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q398" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -75975,9 +76759,21 @@
       <c r="U398" t="inlineStr"/>
       <c r="V398" t="inlineStr"/>
       <c r="W398" t="inlineStr"/>
-      <c r="X398" t="inlineStr"/>
-      <c r="Y398" t="inlineStr"/>
-      <c r="Z398" t="inlineStr"/>
+      <c r="X398" t="inlineStr">
+        <is>
+          <t>T******* D** C******</t>
+        </is>
+      </c>
+      <c r="Y398" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z398" t="inlineStr">
+        <is>
+          <t>90****6332</t>
+        </is>
+      </c>
       <c r="AA398" t="inlineStr"/>
       <c r="AB398" t="inlineStr"/>
       <c r="AC398" t="inlineStr"/>
@@ -76148,7 +76944,11 @@
         <v>880447423383</v>
       </c>
       <c r="O399" t="inlineStr"/>
-      <c r="P399" t="inlineStr"/>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q399" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -76172,9 +76972,21 @@
       <c r="U399" t="inlineStr"/>
       <c r="V399" t="inlineStr"/>
       <c r="W399" t="inlineStr"/>
-      <c r="X399" t="inlineStr"/>
-      <c r="Y399" t="inlineStr"/>
-      <c r="Z399" t="inlineStr"/>
+      <c r="X399" t="inlineStr">
+        <is>
+          <t>A****** A****** M*********</t>
+        </is>
+      </c>
+      <c r="Y399" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t>99****6244</t>
+        </is>
+      </c>
       <c r="AA399" t="inlineStr"/>
       <c r="AB399" t="inlineStr"/>
       <c r="AC399" t="inlineStr"/>
@@ -76345,7 +77157,11 @@
         <v>215590265908</v>
       </c>
       <c r="O400" t="inlineStr"/>
-      <c r="P400" t="inlineStr"/>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q400" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -76369,9 +77185,21 @@
       <c r="U400" t="inlineStr"/>
       <c r="V400" t="inlineStr"/>
       <c r="W400" t="inlineStr"/>
-      <c r="X400" t="inlineStr"/>
-      <c r="Y400" t="inlineStr"/>
-      <c r="Z400" t="inlineStr"/>
+      <c r="X400" t="inlineStr">
+        <is>
+          <t>A****** A****** M*********</t>
+        </is>
+      </c>
+      <c r="Y400" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z400" t="inlineStr">
+        <is>
+          <t>99****6244</t>
+        </is>
+      </c>
       <c r="AA400" t="inlineStr"/>
       <c r="AB400" t="inlineStr"/>
       <c r="AC400" t="inlineStr"/>
@@ -76542,7 +77370,11 @@
         <v>979389190536</v>
       </c>
       <c r="O401" t="inlineStr"/>
-      <c r="P401" t="inlineStr"/>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q401" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -76566,9 +77398,21 @@
       <c r="U401" t="inlineStr"/>
       <c r="V401" t="inlineStr"/>
       <c r="W401" t="inlineStr"/>
-      <c r="X401" t="inlineStr"/>
-      <c r="Y401" t="inlineStr"/>
-      <c r="Z401" t="inlineStr"/>
+      <c r="X401" t="inlineStr">
+        <is>
+          <t>G******* J***** A***** A******</t>
+        </is>
+      </c>
+      <c r="Y401" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z401" t="inlineStr">
+        <is>
+          <t>82****6967</t>
+        </is>
+      </c>
       <c r="AA401" t="inlineStr"/>
       <c r="AB401" t="inlineStr"/>
       <c r="AC401" t="inlineStr"/>
@@ -76739,7 +77583,11 @@
         <v>618827188164</v>
       </c>
       <c r="O402" t="inlineStr"/>
-      <c r="P402" t="inlineStr"/>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q402" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -76763,9 +77611,21 @@
       <c r="U402" t="inlineStr"/>
       <c r="V402" t="inlineStr"/>
       <c r="W402" t="inlineStr"/>
-      <c r="X402" t="inlineStr"/>
-      <c r="Y402" t="inlineStr"/>
-      <c r="Z402" t="inlineStr"/>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>P******* J*******</t>
+        </is>
+      </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>95****0840</t>
+        </is>
+      </c>
       <c r="AA402" t="inlineStr"/>
       <c r="AB402" t="inlineStr"/>
       <c r="AC402" t="inlineStr"/>
@@ -76936,7 +77796,11 @@
         <v>596296145743</v>
       </c>
       <c r="O403" t="inlineStr"/>
-      <c r="P403" t="inlineStr"/>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q403" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -76956,9 +77820,21 @@
       <c r="U403" t="inlineStr"/>
       <c r="V403" t="inlineStr"/>
       <c r="W403" t="inlineStr"/>
-      <c r="X403" t="inlineStr"/>
-      <c r="Y403" t="inlineStr"/>
-      <c r="Z403" t="inlineStr"/>
+      <c r="X403" t="inlineStr">
+        <is>
+          <t>M****** P*****</t>
+        </is>
+      </c>
+      <c r="Y403" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z403" t="inlineStr">
+        <is>
+          <t>99****3424</t>
+        </is>
+      </c>
       <c r="AA403" t="inlineStr"/>
       <c r="AB403" t="inlineStr"/>
       <c r="AC403" t="inlineStr"/>
@@ -77125,7 +78001,11 @@
         <v>178077962511</v>
       </c>
       <c r="O404" t="inlineStr"/>
-      <c r="P404" t="inlineStr"/>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q404" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -77149,9 +78029,21 @@
       <c r="U404" t="inlineStr"/>
       <c r="V404" t="inlineStr"/>
       <c r="W404" t="inlineStr"/>
-      <c r="X404" t="inlineStr"/>
-      <c r="Y404" t="inlineStr"/>
-      <c r="Z404" t="inlineStr"/>
+      <c r="X404" t="inlineStr">
+        <is>
+          <t>B********** J** A******** S**** S*****</t>
+        </is>
+      </c>
+      <c r="Y404" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t>98****7129</t>
+        </is>
+      </c>
       <c r="AA404" t="inlineStr"/>
       <c r="AB404" t="inlineStr"/>
       <c r="AC404" t="inlineStr"/>
@@ -77322,7 +78214,11 @@
         <v>918003035791</v>
       </c>
       <c r="O405" t="inlineStr"/>
-      <c r="P405" t="inlineStr"/>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q405" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -77346,9 +78242,21 @@
       <c r="U405" t="inlineStr"/>
       <c r="V405" t="inlineStr"/>
       <c r="W405" t="inlineStr"/>
-      <c r="X405" t="inlineStr"/>
-      <c r="Y405" t="inlineStr"/>
-      <c r="Z405" t="inlineStr"/>
+      <c r="X405" t="inlineStr">
+        <is>
+          <t>B********** H*********</t>
+        </is>
+      </c>
+      <c r="Y405" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z405" t="inlineStr">
+        <is>
+          <t>98****7129</t>
+        </is>
+      </c>
       <c r="AA405" t="inlineStr"/>
       <c r="AB405" t="inlineStr"/>
       <c r="AC405" t="inlineStr"/>
@@ -77519,7 +78427,11 @@
         <v>175290481857</v>
       </c>
       <c r="O406" t="inlineStr"/>
-      <c r="P406" t="inlineStr"/>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q406" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -77539,9 +78451,21 @@
       <c r="U406" t="inlineStr"/>
       <c r="V406" t="inlineStr"/>
       <c r="W406" t="inlineStr"/>
-      <c r="X406" t="inlineStr"/>
-      <c r="Y406" t="inlineStr"/>
-      <c r="Z406" t="inlineStr"/>
+      <c r="X406" t="inlineStr">
+        <is>
+          <t>G******* G**********</t>
+        </is>
+      </c>
+      <c r="Y406" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z406" t="inlineStr">
+        <is>
+          <t>93****3464</t>
+        </is>
+      </c>
       <c r="AA406" t="inlineStr"/>
       <c r="AB406" t="inlineStr"/>
       <c r="AC406" t="inlineStr"/>
@@ -77708,7 +78632,11 @@
         <v>491365461344</v>
       </c>
       <c r="O407" t="inlineStr"/>
-      <c r="P407" t="inlineStr"/>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q407" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -77732,9 +78660,21 @@
       <c r="U407" t="inlineStr"/>
       <c r="V407" t="inlineStr"/>
       <c r="W407" t="inlineStr"/>
-      <c r="X407" t="inlineStr"/>
-      <c r="Y407" t="inlineStr"/>
-      <c r="Z407" t="inlineStr"/>
+      <c r="X407" t="inlineStr">
+        <is>
+          <t>G******* R***** N******</t>
+        </is>
+      </c>
+      <c r="Y407" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t>93****3464</t>
+        </is>
+      </c>
       <c r="AA407" t="inlineStr"/>
       <c r="AB407" t="inlineStr"/>
       <c r="AC407" t="inlineStr"/>
@@ -77907,7 +78847,11 @@
       <c r="O408" t="n">
         <v>69448885379</v>
       </c>
-      <c r="P408" t="inlineStr"/>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q408" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -77931,9 +78875,21 @@
       <c r="U408" t="inlineStr"/>
       <c r="V408" t="inlineStr"/>
       <c r="W408" t="inlineStr"/>
-      <c r="X408" t="inlineStr"/>
-      <c r="Y408" t="inlineStr"/>
-      <c r="Z408" t="inlineStr"/>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>J**** C*****</t>
+        </is>
+      </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>81****3759</t>
+        </is>
+      </c>
       <c r="AA408" t="inlineStr"/>
       <c r="AB408" t="inlineStr"/>
       <c r="AC408" t="inlineStr"/>
@@ -78104,7 +79060,11 @@
         <v>775940371339</v>
       </c>
       <c r="O409" t="inlineStr"/>
-      <c r="P409" t="inlineStr"/>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="Q409" t="inlineStr">
         <is>
           <t>SIBL0000899</t>
@@ -78128,9 +79088,21 @@
       <c r="U409" t="inlineStr"/>
       <c r="V409" t="inlineStr"/>
       <c r="W409" t="inlineStr"/>
-      <c r="X409" t="inlineStr"/>
-      <c r="Y409" t="inlineStr"/>
-      <c r="Z409" t="inlineStr"/>
+      <c r="X409" t="inlineStr">
+        <is>
+          <t>S********** S*****</t>
+        </is>
+      </c>
+      <c r="Y409" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>95****8421</t>
+        </is>
+      </c>
       <c r="AA409" t="inlineStr"/>
       <c r="AB409" t="inlineStr"/>
       <c r="AC409" t="inlineStr"/>
@@ -81565,6 +82537,416 @@
         </is>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C426" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D426" t="n">
+        <v>11000357434273</v>
+      </c>
+      <c r="E426" t="n">
+        <v>1775462904</v>
+      </c>
+      <c r="F426" t="n">
+        <v>13500</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H426" s="1" t="n">
+        <v>46118.5684837963</v>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N426" t="n">
+        <v>629926165014</v>
+      </c>
+      <c r="O426" t="inlineStr"/>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr"/>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr"/>
+      <c r="V426" t="inlineStr"/>
+      <c r="W426" t="inlineStr"/>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>M********** A**** L****</t>
+        </is>
+      </c>
+      <c r="Y426" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z426" t="inlineStr">
+        <is>
+          <t>99****4686</t>
+        </is>
+      </c>
+      <c r="AA426" t="inlineStr"/>
+      <c r="AB426" t="inlineStr"/>
+      <c r="AC426" t="inlineStr"/>
+      <c r="AD426" t="inlineStr"/>
+      <c r="AE426" t="inlineStr"/>
+      <c r="AF426" t="inlineStr"/>
+      <c r="AG426" t="inlineStr"/>
+      <c r="AH426" t="inlineStr"/>
+      <c r="AI426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK426" t="inlineStr"/>
+      <c r="AL426" t="inlineStr"/>
+      <c r="AM426" t="inlineStr"/>
+      <c r="AN426" t="inlineStr"/>
+      <c r="AO426" t="inlineStr"/>
+      <c r="AP426" t="inlineStr"/>
+      <c r="AQ426" t="inlineStr"/>
+      <c r="AR426" t="inlineStr"/>
+      <c r="AS426" t="inlineStr"/>
+      <c r="AT426" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU426" t="inlineStr"/>
+      <c r="AV426" t="inlineStr"/>
+      <c r="AW426" t="inlineStr"/>
+      <c r="AX426" t="inlineStr"/>
+      <c r="AY426" t="inlineStr"/>
+      <c r="AZ426" t="inlineStr"/>
+      <c r="BA426" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB426" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC426" t="inlineStr"/>
+      <c r="BD426" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE426" t="n">
+        <v>20008</v>
+      </c>
+      <c r="BF426" t="inlineStr">
+        <is>
+          <t>264999,266649</t>
+        </is>
+      </c>
+      <c r="BG426" t="inlineStr">
+        <is>
+          <t>2047,2055</t>
+        </is>
+      </c>
+      <c r="BH426" t="inlineStr">
+        <is>
+          <t>thirteen thousand five hundred</t>
+        </is>
+      </c>
+      <c r="BI426" t="n">
+        <v>17299</v>
+      </c>
+      <c r="BJ426" t="inlineStr"/>
+      <c r="BK426" t="inlineStr"/>
+      <c r="BL426" t="inlineStr"/>
+      <c r="BM426" t="inlineStr"/>
+      <c r="BN426" t="inlineStr"/>
+      <c r="BO426" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP426" t="inlineStr"/>
+      <c r="BQ426" t="inlineStr"/>
+      <c r="BR426" t="inlineStr"/>
+      <c r="BS426" t="inlineStr"/>
+      <c r="BT426" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU426" t="inlineStr"/>
+      <c r="BV426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BW426" t="inlineStr">
+        <is>
+          <t>Transaction_file20260406-062256.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>753702</v>
+      </c>
+      <c r="C427" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D427" t="n">
+        <v>11000357637359</v>
+      </c>
+      <c r="E427" t="n">
+        <v>1775543193</v>
+      </c>
+      <c r="F427" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H427" s="1" t="n">
+        <v>46119.49782407407</v>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N427" t="n">
+        <v>115726878456</v>
+      </c>
+      <c r="O427" t="inlineStr"/>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>08-Apr-2026 17:44:13</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr"/>
+      <c r="V427" t="inlineStr"/>
+      <c r="W427" t="inlineStr"/>
+      <c r="X427" t="inlineStr">
+        <is>
+          <t>C****** V********</t>
+        </is>
+      </c>
+      <c r="Y427" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z427" t="inlineStr">
+        <is>
+          <t>88****8971</t>
+        </is>
+      </c>
+      <c r="AA427" t="inlineStr"/>
+      <c r="AB427" t="inlineStr"/>
+      <c r="AC427" t="inlineStr"/>
+      <c r="AD427" t="inlineStr"/>
+      <c r="AE427" t="inlineStr"/>
+      <c r="AF427" t="inlineStr"/>
+      <c r="AG427" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH427" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK427" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AL427" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AM427" t="inlineStr">
+        <is>
+          <t>08-Apr-2026 17:44:13</t>
+        </is>
+      </c>
+      <c r="AN427" t="inlineStr"/>
+      <c r="AO427" t="inlineStr"/>
+      <c r="AP427" t="inlineStr"/>
+      <c r="AQ427" t="inlineStr"/>
+      <c r="AR427" t="inlineStr"/>
+      <c r="AS427" t="inlineStr"/>
+      <c r="AT427" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU427" t="inlineStr"/>
+      <c r="AV427" t="inlineStr"/>
+      <c r="AW427" t="inlineStr"/>
+      <c r="AX427" t="inlineStr"/>
+      <c r="AY427" t="inlineStr"/>
+      <c r="AZ427" t="inlineStr"/>
+      <c r="BA427" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB427" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC427" t="inlineStr"/>
+      <c r="BD427" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE427" t="n">
+        <v>19901</v>
+      </c>
+      <c r="BF427" t="inlineStr">
+        <is>
+          <t>266636</t>
+        </is>
+      </c>
+      <c r="BG427" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH427" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI427" t="n">
+        <v>17187</v>
+      </c>
+      <c r="BJ427" t="inlineStr"/>
+      <c r="BK427" t="inlineStr"/>
+      <c r="BL427" t="inlineStr"/>
+      <c r="BM427" t="inlineStr"/>
+      <c r="BN427" t="inlineStr"/>
+      <c r="BO427" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP427" t="inlineStr"/>
+      <c r="BQ427" t="inlineStr"/>
+      <c r="BR427" t="inlineStr"/>
+      <c r="BS427" t="inlineStr"/>
+      <c r="BT427" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU427" t="inlineStr"/>
+      <c r="BV427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BW427" t="inlineStr">
+        <is>
+          <t>Transaction_file20260406-062256.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
